--- a/Financial Analysis/V.xlsx
+++ b/Financial Analysis/V.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E2611C-768A-4380-913C-CB0173000090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9183FDB-9D92-4A25-B068-9C7857A94EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0E0749A9-7B4C-463E-A44A-39D457257264}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{0E0749A9-7B4C-463E-A44A-39D457257264}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -736,14 +736,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="11">
-        <v>347.6</v>
+        <v>357.98</v>
       </c>
       <c r="E3" s="2">
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="2">
         <v>45867</v>
@@ -767,7 +767,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>641356.76</v>
+        <v>660508.89800000004</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -809,7 +809,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>646897.76</v>
+        <v>666049.89800000004</v>
       </c>
     </row>
   </sheetData>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="AN29" s="11">
         <f>Main!D3</f>
-        <v>347.6</v>
+        <v>357.98</v>
       </c>
     </row>
     <row r="30" spans="1:147" x14ac:dyDescent="0.3">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AN30" s="10">
         <f>AN28/AN29-1</f>
-        <v>-0.34683629154151641</v>
+        <v>-0.36577544818099084</v>
       </c>
     </row>
     <row r="31" spans="1:147" x14ac:dyDescent="0.3">

--- a/Financial Analysis/V.xlsx
+++ b/Financial Analysis/V.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9183FDB-9D92-4A25-B068-9C7857A94EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DB0A94-5CF1-47C1-AED5-A640B0ADFEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{0E0749A9-7B4C-463E-A44A-39D457257264}"/>
   </bookViews>
@@ -214,7 +214,7 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Overvalued</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -315,14 +315,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -339,7 +339,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12245340" y="0"/>
+          <a:off x="12954000" y="0"/>
           <a:ext cx="0" cy="6309360"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -736,17 +736,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="11">
-        <v>357.98</v>
+        <v>344.45</v>
       </c>
       <c r="E3" s="2">
-        <v>45804</v>
+        <v>45868</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45868</v>
       </c>
       <c r="G3" s="2">
-        <v>45867</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.3">
@@ -754,8 +754,8 @@
         <v>1</v>
       </c>
       <c r="D4" s="3">
-        <f>1711+4.8+120.3+9</f>
-        <v>1845.1</v>
+        <f>1709+5+120+9</f>
+        <v>1843</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>59</v>
@@ -767,7 +767,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>660508.89800000004</v>
+        <v>634821.35</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -775,11 +775,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="3">
-        <f>11734+2017+1470</f>
-        <v>15221</v>
+        <f>17092+2088+1203</f>
+        <v>20383</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="3:7" x14ac:dyDescent="0.3">
@@ -787,11 +787,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="3">
-        <f>3948+16814</f>
-        <v>20762</v>
+        <f>5548+19590</f>
+        <v>25138</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="3:7" x14ac:dyDescent="0.3">
@@ -800,7 +800,7 @@
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>-5541</v>
+        <v>-4755</v>
       </c>
     </row>
     <row r="9" spans="3:7" x14ac:dyDescent="0.3">
@@ -809,7 +809,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>666049.89800000004</v>
+        <v>639576.35</v>
       </c>
     </row>
   </sheetData>
@@ -1081,12 +1081,11 @@
         <v>9594</v>
       </c>
       <c r="Q3" s="7">
-        <f>M3*1.1</f>
-        <v>9790</v>
+        <v>10172</v>
       </c>
       <c r="R3" s="7">
-        <f>N3*1.07</f>
-        <v>10290.19</v>
+        <f>N3*1.12</f>
+        <v>10771.04</v>
       </c>
       <c r="T3" s="7">
         <v>22977</v>
@@ -1111,47 +1110,47 @@
       </c>
       <c r="Z3" s="7">
         <f>SUM(O3:R3)</f>
-        <v>39184.19</v>
+        <v>40047.040000000001</v>
       </c>
       <c r="AA3" s="7">
-        <f>Z3*1.07</f>
-        <v>41927.083300000006</v>
+        <f>Z3*1.09</f>
+        <v>43651.273600000008</v>
       </c>
       <c r="AB3" s="7">
-        <f>AA3*1.05</f>
-        <v>44023.43746500001</v>
+        <f>AA3*1.07</f>
+        <v>46706.862752000008</v>
       </c>
       <c r="AC3" s="7">
-        <f>AB3*1.03</f>
-        <v>45344.140588950009</v>
+        <f>AB3*1.05</f>
+        <v>49042.205889600009</v>
       </c>
       <c r="AD3" s="7">
-        <f t="shared" ref="AD3:AJ3" si="0">AC3*1.02</f>
-        <v>46251.023400729013</v>
+        <f>AC3*1.04</f>
+        <v>51003.894125184008</v>
       </c>
       <c r="AE3" s="7">
-        <f t="shared" si="0"/>
-        <v>47176.043868743596</v>
+        <f>AD3*1.03</f>
+        <v>52534.010948939533</v>
       </c>
       <c r="AF3" s="7">
-        <f t="shared" si="0"/>
-        <v>48119.564746118471</v>
+        <f t="shared" ref="AD3:AJ3" si="0">AE3*1.02</f>
+        <v>53584.691167918325</v>
       </c>
       <c r="AG3" s="7">
         <f t="shared" si="0"/>
-        <v>49081.956041040838</v>
+        <v>54656.384991276689</v>
       </c>
       <c r="AH3" s="7">
         <f t="shared" si="0"/>
-        <v>50063.595161861653</v>
+        <v>55749.512691102223</v>
       </c>
       <c r="AI3" s="7">
         <f t="shared" si="0"/>
-        <v>51064.867065098886</v>
+        <v>56864.502944924272</v>
       </c>
       <c r="AJ3" s="7">
         <f t="shared" si="0"/>
-        <v>52086.164406400865</v>
+        <v>58001.793003822757</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.3">
@@ -1201,12 +1200,11 @@
         <v>1657</v>
       </c>
       <c r="Q4" s="3">
-        <f t="shared" ref="Q4:R4" si="1">Q3-Q5</f>
-        <v>1762.2000000000007</v>
+        <v>1749</v>
       </c>
       <c r="R4" s="3">
-        <f t="shared" si="1"/>
-        <v>1852.2342000000008</v>
+        <f t="shared" ref="Q4:R4" si="1">R3-R5</f>
+        <v>1938.7872000000007</v>
       </c>
       <c r="T4" s="3">
         <v>3444</v>
@@ -1231,47 +1229,47 @@
       </c>
       <c r="Z4" s="3">
         <f>SUM(O4:R4)</f>
-        <v>7084.4342000000015</v>
+        <v>7157.7872000000007</v>
       </c>
       <c r="AA4" s="3">
         <f t="shared" ref="AA4:AJ4" si="2">AA3-AA5</f>
-        <v>7127.6041610000029</v>
+        <v>7420.7165120000063</v>
       </c>
       <c r="AB4" s="3">
         <f t="shared" si="2"/>
-        <v>7483.9843690500056</v>
+        <v>7940.1666678399997</v>
       </c>
       <c r="AC4" s="3">
         <f t="shared" si="2"/>
-        <v>7708.5039001215046</v>
+        <v>8337.1750012320044</v>
       </c>
       <c r="AD4" s="3">
         <f t="shared" si="2"/>
-        <v>7862.6739781239376</v>
+        <v>8670.6620012812855</v>
       </c>
       <c r="AE4" s="3">
         <f t="shared" si="2"/>
-        <v>8019.9274576864118</v>
+        <v>8930.7818613197232</v>
       </c>
       <c r="AF4" s="3">
         <f t="shared" si="2"/>
-        <v>8180.3260068401432</v>
+        <v>9109.3974985461173</v>
       </c>
       <c r="AG4" s="3">
         <f t="shared" si="2"/>
-        <v>8343.932526976947</v>
+        <v>9291.5854485170421</v>
       </c>
       <c r="AH4" s="3">
         <f t="shared" si="2"/>
-        <v>8510.8111775164798</v>
+        <v>9477.4171574873835</v>
       </c>
       <c r="AI4" s="3">
         <f t="shared" si="2"/>
-        <v>8681.0274010668145</v>
+        <v>9666.9655006371249</v>
       </c>
       <c r="AJ4" s="3">
         <f t="shared" si="2"/>
-        <v>8854.6479490881466</v>
+        <v>9860.3048106498682</v>
       </c>
     </row>
     <row r="5" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1328,7 +1326,7 @@
         <v>8008</v>
       </c>
       <c r="O5" s="7">
-        <f t="shared" ref="O5:P5" si="4">O3-O4</f>
+        <f t="shared" ref="O5:Q5" si="4">O3-O4</f>
         <v>7697</v>
       </c>
       <c r="P5" s="7">
@@ -1336,12 +1334,12 @@
         <v>7937</v>
       </c>
       <c r="Q5" s="7">
-        <f t="shared" ref="Q5:R5" si="5">Q3*0.82</f>
-        <v>8027.7999999999993</v>
+        <f t="shared" si="4"/>
+        <v>8423</v>
       </c>
       <c r="R5" s="7">
-        <f t="shared" si="5"/>
-        <v>8437.9557999999997</v>
+        <f t="shared" ref="Q5:R5" si="5">R3*0.82</f>
+        <v>8832.2528000000002</v>
       </c>
       <c r="T5" s="7">
         <f t="shared" ref="T5:Z5" si="6">T3-T4</f>
@@ -1369,47 +1367,47 @@
       </c>
       <c r="Z5" s="7">
         <f t="shared" si="6"/>
-        <v>32099.755799999999</v>
+        <v>32889.252800000002</v>
       </c>
       <c r="AA5" s="7">
         <f t="shared" ref="AA5:AJ5" si="7">AA3*0.83</f>
-        <v>34799.479139000003</v>
+        <v>36230.557088000001</v>
       </c>
       <c r="AB5" s="7">
         <f t="shared" si="7"/>
-        <v>36539.453095950004</v>
+        <v>38766.696084160008</v>
       </c>
       <c r="AC5" s="7">
         <f t="shared" si="7"/>
-        <v>37635.636688828505</v>
+        <v>40705.030888368005</v>
       </c>
       <c r="AD5" s="7">
         <f t="shared" si="7"/>
-        <v>38388.349422605075</v>
+        <v>42333.232123902722</v>
       </c>
       <c r="AE5" s="7">
         <f t="shared" si="7"/>
-        <v>39156.116411057184</v>
+        <v>43603.229087619809</v>
       </c>
       <c r="AF5" s="7">
         <f t="shared" si="7"/>
-        <v>39939.238739278328</v>
+        <v>44475.293669372208</v>
       </c>
       <c r="AG5" s="7">
         <f t="shared" si="7"/>
-        <v>40738.023514063891</v>
+        <v>45364.799542759647</v>
       </c>
       <c r="AH5" s="7">
         <f t="shared" si="7"/>
-        <v>41552.783984345173</v>
+        <v>46272.09553361484</v>
       </c>
       <c r="AI5" s="7">
         <f t="shared" si="7"/>
-        <v>42383.839664032072</v>
+        <v>47197.537444287147</v>
       </c>
       <c r="AJ5" s="7">
         <f t="shared" si="7"/>
-        <v>43231.516457312719</v>
+        <v>48141.488193172889</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.3">
@@ -1459,12 +1457,11 @@
         <v>381</v>
       </c>
       <c r="Q6" s="3">
-        <f t="shared" ref="Q6" si="8">Q3*0.04</f>
-        <v>391.6</v>
+        <v>421</v>
       </c>
       <c r="R6" s="3">
         <f>R3*0.06</f>
-        <v>617.41139999999996</v>
+        <v>646.26240000000007</v>
       </c>
       <c r="T6" s="3">
         <v>1105</v>
@@ -1476,60 +1473,60 @@
         <v>1136</v>
       </c>
       <c r="W6" s="3">
-        <f t="shared" ref="W6:W11" si="9">SUM(C6:F6)</f>
+        <f t="shared" ref="W6:W11" si="8">SUM(C6:F6)</f>
         <v>1336</v>
       </c>
       <c r="X6" s="3">
-        <f t="shared" ref="X6:X11" si="10">SUM(G6:J6)</f>
+        <f t="shared" ref="X6:X11" si="9">SUM(G6:J6)</f>
         <v>1341</v>
       </c>
       <c r="Y6" s="3">
-        <f t="shared" ref="Y6:Y11" si="11">SUM(K6:N6)</f>
+        <f t="shared" ref="Y6:Y11" si="10">SUM(K6:N6)</f>
         <v>1560</v>
       </c>
       <c r="Z6" s="3">
-        <f t="shared" ref="Z6:Z11" si="12">SUM(O6:R6)</f>
-        <v>1696.0113999999999</v>
+        <f t="shared" ref="Z6:Z11" si="11">SUM(O6:R6)</f>
+        <v>1754.2624000000001</v>
       </c>
       <c r="AA6" s="3">
-        <f t="shared" ref="AA6:AJ6" si="13">AA3*0.04</f>
-        <v>1677.0833320000002</v>
+        <f t="shared" ref="AA6:AJ6" si="12">AA3*0.04</f>
+        <v>1746.0509440000003</v>
       </c>
       <c r="AB6" s="3">
-        <f t="shared" si="13"/>
-        <v>1760.9374986000005</v>
+        <f t="shared" si="12"/>
+        <v>1868.2745100800003</v>
       </c>
       <c r="AC6" s="3">
-        <f t="shared" si="13"/>
-        <v>1813.7656235580005</v>
+        <f t="shared" si="12"/>
+        <v>1961.6882355840005</v>
       </c>
       <c r="AD6" s="3">
-        <f t="shared" si="13"/>
-        <v>1850.0409360291605</v>
+        <f t="shared" si="12"/>
+        <v>2040.1557650073603</v>
       </c>
       <c r="AE6" s="3">
-        <f t="shared" si="13"/>
-        <v>1887.0417547497439</v>
+        <f t="shared" si="12"/>
+        <v>2101.3604379575813</v>
       </c>
       <c r="AF6" s="3">
-        <f t="shared" si="13"/>
-        <v>1924.7825898447388</v>
+        <f t="shared" si="12"/>
+        <v>2143.3876467167329</v>
       </c>
       <c r="AG6" s="3">
-        <f t="shared" si="13"/>
-        <v>1963.2782416416335</v>
+        <f t="shared" si="12"/>
+        <v>2186.2553996510678</v>
       </c>
       <c r="AH6" s="3">
-        <f t="shared" si="13"/>
-        <v>2002.5438064744662</v>
+        <f t="shared" si="12"/>
+        <v>2229.9805076440889</v>
       </c>
       <c r="AI6" s="3">
-        <f t="shared" si="13"/>
-        <v>2042.5946826039556</v>
+        <f t="shared" si="12"/>
+        <v>2274.5801177969711</v>
       </c>
       <c r="AJ6" s="3">
-        <f t="shared" si="13"/>
-        <v>2083.4465762560349</v>
+        <f t="shared" si="12"/>
+        <v>2320.0717201529105</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.3">
@@ -1579,11 +1576,10 @@
         <v>224</v>
       </c>
       <c r="Q7" s="3">
-        <f t="shared" ref="Q7:R7" si="14">M7*1.1</f>
-        <v>220.00000000000003</v>
+        <v>224</v>
       </c>
       <c r="R7" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="Q7:R7" si="13">N7*1.1</f>
         <v>228.8</v>
       </c>
       <c r="T7" s="3">
@@ -1596,60 +1592,60 @@
         <v>730</v>
       </c>
       <c r="W7" s="3">
+        <f t="shared" si="8"/>
+        <v>743</v>
+      </c>
+      <c r="X7" s="3">
         <f t="shared" si="9"/>
-        <v>743</v>
-      </c>
-      <c r="X7" s="3">
+        <v>736</v>
+      </c>
+      <c r="Y7" s="3">
         <f t="shared" si="10"/>
-        <v>736</v>
-      </c>
-      <c r="Y7" s="3">
+        <v>778</v>
+      </c>
+      <c r="Z7" s="3">
         <f t="shared" si="11"/>
-        <v>778</v>
-      </c>
-      <c r="Z7" s="3">
-        <f t="shared" si="12"/>
-        <v>879.8</v>
+        <v>883.8</v>
       </c>
       <c r="AA7" s="3">
-        <f>Z7*1.06</f>
-        <v>932.58799999999997</v>
+        <f>Z7*1.09</f>
+        <v>963.34199999999998</v>
       </c>
       <c r="AB7" s="3">
-        <f>AA7*1.04</f>
-        <v>969.89152000000001</v>
+        <f>AA7*1.05</f>
+        <v>1011.5091</v>
       </c>
       <c r="AC7" s="3">
         <f>AB7*1.03</f>
-        <v>998.98826560000009</v>
+        <v>1041.8543730000001</v>
       </c>
       <c r="AD7" s="3">
         <f>AC7*1.02</f>
-        <v>1018.9680309120001</v>
+        <v>1062.6914604600001</v>
       </c>
       <c r="AE7" s="3">
-        <f t="shared" ref="AE7:AJ7" si="15">AD7*1.01</f>
-        <v>1029.1577112211201</v>
+        <f t="shared" ref="AE7:AJ7" si="14">AD7*1.01</f>
+        <v>1073.3183750646001</v>
       </c>
       <c r="AF7" s="3">
-        <f t="shared" si="15"/>
-        <v>1039.4492883333312</v>
+        <f t="shared" si="14"/>
+        <v>1084.0515588152462</v>
       </c>
       <c r="AG7" s="3">
-        <f t="shared" si="15"/>
-        <v>1049.8437812166644</v>
+        <f t="shared" si="14"/>
+        <v>1094.8920744033987</v>
       </c>
       <c r="AH7" s="3">
-        <f t="shared" si="15"/>
-        <v>1060.3422190288311</v>
+        <f t="shared" si="14"/>
+        <v>1105.8409951474327</v>
       </c>
       <c r="AI7" s="3">
-        <f t="shared" si="15"/>
-        <v>1070.9456412191194</v>
+        <f t="shared" si="14"/>
+        <v>1116.899405098907</v>
       </c>
       <c r="AJ7" s="3">
-        <f t="shared" si="15"/>
-        <v>1081.6550976313106</v>
+        <f t="shared" si="14"/>
+        <v>1128.0683991498961</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.3">
@@ -1699,12 +1695,11 @@
         <v>173</v>
       </c>
       <c r="Q8" s="3">
-        <f t="shared" ref="Q8:R8" si="16">Q3*0.02</f>
-        <v>195.8</v>
+        <v>187</v>
       </c>
       <c r="R8" s="3">
-        <f t="shared" si="16"/>
-        <v>205.80380000000002</v>
+        <f t="shared" ref="Q8:R8" si="15">R3*0.02</f>
+        <v>215.42080000000001</v>
       </c>
       <c r="T8" s="3">
         <v>454</v>
@@ -1716,60 +1711,60 @@
         <v>403</v>
       </c>
       <c r="W8" s="3">
+        <f t="shared" si="8"/>
+        <v>505</v>
+      </c>
+      <c r="X8" s="3">
         <f t="shared" si="9"/>
-        <v>505</v>
-      </c>
-      <c r="X8" s="3">
+        <v>545</v>
+      </c>
+      <c r="Y8" s="3">
         <f t="shared" si="10"/>
-        <v>545</v>
-      </c>
-      <c r="Y8" s="3">
+        <v>635</v>
+      </c>
+      <c r="Z8" s="3">
         <f t="shared" si="11"/>
-        <v>635</v>
-      </c>
-      <c r="Z8" s="3">
-        <f t="shared" si="12"/>
-        <v>717.60380000000009</v>
+        <v>718.42079999999999</v>
       </c>
       <c r="AA8" s="3">
-        <f t="shared" ref="AA8:AJ8" si="17">AA3*0.02</f>
-        <v>838.54166600000008</v>
+        <f t="shared" ref="AA8:AJ8" si="16">AA3*0.02</f>
+        <v>873.02547200000015</v>
       </c>
       <c r="AB8" s="3">
-        <f t="shared" si="17"/>
-        <v>880.46874930000024</v>
+        <f t="shared" si="16"/>
+        <v>934.13725504000013</v>
       </c>
       <c r="AC8" s="3">
-        <f t="shared" si="17"/>
-        <v>906.88281177900024</v>
+        <f t="shared" si="16"/>
+        <v>980.84411779200025</v>
       </c>
       <c r="AD8" s="3">
-        <f t="shared" si="17"/>
-        <v>925.02046801458027</v>
+        <f t="shared" si="16"/>
+        <v>1020.0778825036801</v>
       </c>
       <c r="AE8" s="3">
-        <f t="shared" si="17"/>
-        <v>943.52087737487193</v>
+        <f t="shared" si="16"/>
+        <v>1050.6802189787907</v>
       </c>
       <c r="AF8" s="3">
-        <f t="shared" si="17"/>
-        <v>962.39129492236941</v>
+        <f t="shared" si="16"/>
+        <v>1071.6938233583664</v>
       </c>
       <c r="AG8" s="3">
-        <f t="shared" si="17"/>
-        <v>981.63912082081674</v>
+        <f t="shared" si="16"/>
+        <v>1093.1276998255339</v>
       </c>
       <c r="AH8" s="3">
-        <f t="shared" si="17"/>
-        <v>1001.2719032372331</v>
+        <f t="shared" si="16"/>
+        <v>1114.9902538220445</v>
       </c>
       <c r="AI8" s="3">
-        <f t="shared" si="17"/>
-        <v>1021.2973413019778</v>
+        <f t="shared" si="16"/>
+        <v>1137.2900588984855</v>
       </c>
       <c r="AJ8" s="3">
-        <f t="shared" si="17"/>
-        <v>1041.7232881280174</v>
+        <f t="shared" si="16"/>
+        <v>1160.0358600764553</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
@@ -1819,12 +1814,11 @@
         <v>305</v>
       </c>
       <c r="Q9" s="3">
-        <f>M9*1.16</f>
-        <v>306.23999999999995</v>
+        <v>317</v>
       </c>
       <c r="R9" s="3">
-        <f>N9*1.15</f>
-        <v>315.09999999999997</v>
+        <f>N9*1.18</f>
+        <v>323.32</v>
       </c>
       <c r="T9" s="3">
         <v>656</v>
@@ -1836,20 +1830,20 @@
         <v>804</v>
       </c>
       <c r="W9" s="3">
+        <f t="shared" si="8"/>
+        <v>861</v>
+      </c>
+      <c r="X9" s="3">
         <f t="shared" si="9"/>
-        <v>861</v>
-      </c>
-      <c r="X9" s="3">
+        <v>943</v>
+      </c>
+      <c r="Y9" s="3">
         <f t="shared" si="10"/>
-        <v>943</v>
-      </c>
-      <c r="Y9" s="3">
+        <v>1034</v>
+      </c>
+      <c r="Z9" s="3">
         <f t="shared" si="11"/>
-        <v>1034</v>
-      </c>
-      <c r="Z9" s="3">
-        <f t="shared" si="12"/>
-        <v>1208.3399999999999</v>
+        <v>1227.32</v>
       </c>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
@@ -1909,12 +1903,11 @@
         <v>419</v>
       </c>
       <c r="Q10" s="3">
-        <f>M10*1.15</f>
-        <v>439.29999999999995</v>
+        <v>482</v>
       </c>
       <c r="R10" s="3">
-        <f>N10*1.15</f>
-        <v>487.59999999999997</v>
+        <f>N10*1.2</f>
+        <v>508.79999999999995</v>
       </c>
       <c r="T10" s="3">
         <v>1196</v>
@@ -1926,60 +1919,60 @@
         <v>985</v>
       </c>
       <c r="W10" s="3">
+        <f t="shared" si="8"/>
+        <v>1194</v>
+      </c>
+      <c r="X10" s="3">
         <f t="shared" si="9"/>
-        <v>1194</v>
-      </c>
-      <c r="X10" s="3">
+        <v>1330</v>
+      </c>
+      <c r="Y10" s="3">
         <f t="shared" si="10"/>
-        <v>1330</v>
-      </c>
-      <c r="Y10" s="3">
+        <v>1598</v>
+      </c>
+      <c r="Z10" s="3">
         <f t="shared" si="11"/>
-        <v>1598</v>
-      </c>
-      <c r="Z10" s="3">
-        <f t="shared" si="12"/>
-        <v>1826.8999999999999</v>
+        <v>1890.8</v>
       </c>
       <c r="AA10" s="3">
-        <f>Z10*1.05</f>
-        <v>1918.2449999999999</v>
+        <f>Z10*1.09</f>
+        <v>2060.9720000000002</v>
       </c>
       <c r="AB10" s="3">
-        <f>AA10*1.03</f>
-        <v>1975.7923499999999</v>
+        <f>AA10*1.05</f>
+        <v>2164.0206000000003</v>
       </c>
       <c r="AC10" s="3">
-        <f>AB10*1.02</f>
-        <v>2015.3081970000001</v>
+        <f>AB10*1.03</f>
+        <v>2228.9412180000004</v>
       </c>
       <c r="AD10" s="3">
-        <f t="shared" ref="AD10" si="18">AC10*1.02</f>
-        <v>2055.6143609400001</v>
+        <f t="shared" ref="AD10" si="17">AC10*1.02</f>
+        <v>2273.5200423600004</v>
       </c>
       <c r="AE10" s="3">
         <f>AD10*1.01</f>
-        <v>2076.1705045494</v>
+        <v>2296.2552427836004</v>
       </c>
       <c r="AF10" s="3">
-        <f t="shared" ref="AF10:AJ10" si="19">AE10*1.01</f>
-        <v>2096.9322095948942</v>
+        <f t="shared" ref="AF10:AJ10" si="18">AE10*1.01</f>
+        <v>2319.2177952114362</v>
       </c>
       <c r="AG10" s="3">
-        <f t="shared" si="19"/>
-        <v>2117.9015316908431</v>
+        <f t="shared" si="18"/>
+        <v>2342.4099731635506</v>
       </c>
       <c r="AH10" s="3">
-        <f t="shared" si="19"/>
-        <v>2139.0805470077516</v>
+        <f t="shared" si="18"/>
+        <v>2365.8340728951862</v>
       </c>
       <c r="AI10" s="3">
-        <f t="shared" si="19"/>
-        <v>2160.471352477829</v>
+        <f t="shared" si="18"/>
+        <v>2389.492413624138</v>
       </c>
       <c r="AJ10" s="3">
-        <f t="shared" si="19"/>
-        <v>2182.0760660026071</v>
+        <f t="shared" si="18"/>
+        <v>2413.3873377603795</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
@@ -2029,11 +2022,11 @@
         <v>1000</v>
       </c>
       <c r="Q11" s="3">
-        <v>1000</v>
+        <v>615</v>
       </c>
       <c r="R11" s="3">
         <f>R3*0.04</f>
-        <v>411.60760000000005</v>
+        <v>430.84160000000003</v>
       </c>
       <c r="T11" s="3">
         <v>400</v>
@@ -2045,60 +2038,60 @@
         <v>3</v>
       </c>
       <c r="W11" s="3">
+        <f t="shared" si="8"/>
+        <v>868</v>
+      </c>
+      <c r="X11" s="3">
         <f t="shared" si="9"/>
-        <v>868</v>
-      </c>
-      <c r="X11" s="3">
+        <v>927</v>
+      </c>
+      <c r="Y11" s="3">
         <f t="shared" si="10"/>
-        <v>927</v>
-      </c>
-      <c r="Y11" s="3">
+        <v>462</v>
+      </c>
+      <c r="Z11" s="3">
         <f t="shared" si="11"/>
-        <v>462</v>
-      </c>
-      <c r="Z11" s="3">
-        <f t="shared" si="12"/>
-        <v>2455.6076000000003</v>
+        <v>2089.8416000000002</v>
       </c>
       <c r="AA11" s="3">
-        <f>AA3*0.01</f>
-        <v>419.27083300000004</v>
+        <f>AA3*0.02</f>
+        <v>873.02547200000015</v>
       </c>
       <c r="AB11" s="3">
-        <f t="shared" ref="AB11:AJ11" si="20">AB3*0.01</f>
-        <v>440.23437465000012</v>
+        <f t="shared" ref="AB11:AJ11" si="19">AB3*0.01</f>
+        <v>467.06862752000006</v>
       </c>
       <c r="AC11" s="3">
-        <f t="shared" si="20"/>
-        <v>453.44140588950012</v>
+        <f t="shared" si="19"/>
+        <v>490.42205889600012</v>
       </c>
       <c r="AD11" s="3">
-        <f t="shared" si="20"/>
-        <v>462.51023400729014</v>
+        <f t="shared" si="19"/>
+        <v>510.03894125184007</v>
       </c>
       <c r="AE11" s="3">
-        <f t="shared" si="20"/>
-        <v>471.76043868743596</v>
+        <f t="shared" si="19"/>
+        <v>525.34010948939533</v>
       </c>
       <c r="AF11" s="3">
-        <f t="shared" si="20"/>
-        <v>481.19564746118471</v>
+        <f t="shared" si="19"/>
+        <v>535.84691167918322</v>
       </c>
       <c r="AG11" s="3">
-        <f t="shared" si="20"/>
-        <v>490.81956041040837</v>
+        <f t="shared" si="19"/>
+        <v>546.56384991276695</v>
       </c>
       <c r="AH11" s="3">
-        <f t="shared" si="20"/>
-        <v>500.63595161861656</v>
+        <f t="shared" si="19"/>
+        <v>557.49512691102223</v>
       </c>
       <c r="AI11" s="3">
-        <f t="shared" si="20"/>
-        <v>510.64867065098889</v>
+        <f t="shared" si="19"/>
+        <v>568.64502944924277</v>
       </c>
       <c r="AJ11" s="3">
-        <f t="shared" si="20"/>
-        <v>520.86164406400871</v>
+        <f t="shared" si="19"/>
+        <v>580.01793003822763</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
@@ -2106,136 +2099,136 @@
         <v>18</v>
       </c>
       <c r="C12" s="3">
-        <f t="shared" ref="C12:L12" si="21">SUM(C6:C11)</f>
+        <f t="shared" ref="C12:L12" si="20">SUM(C6:C11)</f>
         <v>1158</v>
       </c>
       <c r="D12" s="3">
+        <f t="shared" si="20"/>
+        <v>1161</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="20"/>
+        <v>1844</v>
+      </c>
+      <c r="F12" s="3">
+        <f t="shared" si="20"/>
+        <v>1344</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" si="20"/>
+        <v>1509</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" si="20"/>
+        <v>1134</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="20"/>
+        <v>1618</v>
+      </c>
+      <c r="J12" s="3">
+        <f t="shared" si="20"/>
+        <v>1561</v>
+      </c>
+      <c r="K12" s="3">
+        <f t="shared" si="20"/>
+        <v>1201</v>
+      </c>
+      <c r="L12" s="3">
+        <f t="shared" si="20"/>
+        <v>1818</v>
+      </c>
+      <c r="M12" s="3">
+        <f t="shared" ref="M12:N12" si="21">SUM(M6:M11)</f>
+        <v>1389</v>
+      </c>
+      <c r="N12" s="3">
         <f t="shared" si="21"/>
-        <v>1161</v>
-      </c>
-      <c r="E12" s="3">
-        <f t="shared" si="21"/>
-        <v>1844</v>
-      </c>
-      <c r="F12" s="3">
-        <f t="shared" si="21"/>
-        <v>1344</v>
-      </c>
-      <c r="G12" s="3">
-        <f t="shared" si="21"/>
-        <v>1509</v>
-      </c>
-      <c r="H12" s="3">
-        <f t="shared" si="21"/>
-        <v>1134</v>
-      </c>
-      <c r="I12" s="3">
-        <f t="shared" si="21"/>
-        <v>1618</v>
-      </c>
-      <c r="J12" s="3">
-        <f t="shared" si="21"/>
-        <v>1561</v>
-      </c>
-      <c r="K12" s="3">
-        <f t="shared" si="21"/>
-        <v>1201</v>
-      </c>
-      <c r="L12" s="3">
-        <f t="shared" si="21"/>
-        <v>1818</v>
-      </c>
-      <c r="M12" s="3">
-        <f t="shared" ref="M12:N12" si="22">SUM(M6:M11)</f>
-        <v>1389</v>
-      </c>
-      <c r="N12" s="3">
+        <v>1659</v>
+      </c>
+      <c r="O12" s="3">
+        <f t="shared" ref="O12:R12" si="22">SUM(O6:O11)</f>
+        <v>1463</v>
+      </c>
+      <c r="P12" s="3">
         <f t="shared" si="22"/>
-        <v>1659</v>
-      </c>
-      <c r="O12" s="3">
-        <f t="shared" ref="O12:R12" si="23">SUM(O6:O11)</f>
-        <v>1463</v>
-      </c>
-      <c r="P12" s="3">
+        <v>2502</v>
+      </c>
+      <c r="Q12" s="3">
+        <f t="shared" si="22"/>
+        <v>2246</v>
+      </c>
+      <c r="R12" s="3">
+        <f t="shared" si="22"/>
+        <v>2353.4448000000002</v>
+      </c>
+      <c r="T12" s="3">
+        <f t="shared" ref="T12:Y12" si="23">SUM(T6:T11)</f>
+        <v>4532</v>
+      </c>
+      <c r="U12" s="3">
         <f t="shared" si="23"/>
-        <v>2502</v>
-      </c>
-      <c r="Q12" s="3">
+        <v>3980</v>
+      </c>
+      <c r="V12" s="3">
         <f t="shared" si="23"/>
-        <v>2552.94</v>
-      </c>
-      <c r="R12" s="3">
+        <v>4061</v>
+      </c>
+      <c r="W12" s="3">
         <f t="shared" si="23"/>
-        <v>2266.3227999999999</v>
-      </c>
-      <c r="T12" s="3">
-        <f t="shared" ref="T12:Y12" si="24">SUM(T6:T11)</f>
-        <v>4532</v>
-      </c>
-      <c r="U12" s="3">
+        <v>5507</v>
+      </c>
+      <c r="X12" s="3">
+        <f t="shared" si="23"/>
+        <v>5822</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="23"/>
+        <v>6067</v>
+      </c>
+      <c r="Z12" s="3">
+        <f t="shared" ref="Z12:AJ12" si="24">SUM(Z6:Z11)</f>
+        <v>8564.4447999999993</v>
+      </c>
+      <c r="AA12" s="3">
         <f t="shared" si="24"/>
-        <v>3980</v>
-      </c>
-      <c r="V12" s="3">
+        <v>6516.4158880000005</v>
+      </c>
+      <c r="AB12" s="3">
         <f t="shared" si="24"/>
-        <v>4061</v>
-      </c>
-      <c r="W12" s="3">
+        <v>6445.0100926400009</v>
+      </c>
+      <c r="AC12" s="3">
         <f t="shared" si="24"/>
-        <v>5507</v>
-      </c>
-      <c r="X12" s="3">
+        <v>6703.7500032720018</v>
+      </c>
+      <c r="AD12" s="3">
         <f t="shared" si="24"/>
-        <v>5822</v>
-      </c>
-      <c r="Y12" s="3">
+        <v>6906.4840915828809</v>
+      </c>
+      <c r="AE12" s="3">
         <f t="shared" si="24"/>
-        <v>6067</v>
-      </c>
-      <c r="Z12" s="3">
-        <f t="shared" ref="Z12:AJ12" si="25">SUM(Z6:Z11)</f>
-        <v>8784.2628000000004</v>
-      </c>
-      <c r="AA12" s="3">
-        <f t="shared" si="25"/>
-        <v>5785.7288310000004</v>
-      </c>
-      <c r="AB12" s="3">
-        <f t="shared" si="25"/>
-        <v>6027.3244925500003</v>
-      </c>
-      <c r="AC12" s="3">
-        <f t="shared" si="25"/>
-        <v>6188.3863038265008</v>
-      </c>
-      <c r="AD12" s="3">
-        <f t="shared" si="25"/>
-        <v>6312.1540299030312</v>
-      </c>
-      <c r="AE12" s="3">
-        <f t="shared" si="25"/>
-        <v>6407.6512865825725</v>
+        <v>7046.9543842739668</v>
       </c>
       <c r="AF12" s="3">
-        <f t="shared" si="25"/>
-        <v>6504.751030156518</v>
+        <f t="shared" si="24"/>
+        <v>7154.1977357809646</v>
       </c>
       <c r="AG12" s="3">
-        <f t="shared" si="25"/>
-        <v>6603.4822357803669</v>
+        <f t="shared" si="24"/>
+        <v>7263.2489969563176</v>
       </c>
       <c r="AH12" s="3">
-        <f t="shared" si="25"/>
-        <v>6703.8744273668981</v>
+        <f t="shared" si="24"/>
+        <v>7374.1409564197747</v>
       </c>
       <c r="AI12" s="3">
-        <f t="shared" si="25"/>
-        <v>6805.9576882538704</v>
+        <f t="shared" si="24"/>
+        <v>7486.9070248677444</v>
       </c>
       <c r="AJ12" s="3">
-        <f t="shared" si="25"/>
-        <v>6909.762672081979</v>
+        <f t="shared" si="24"/>
+        <v>7601.58124717787</v>
       </c>
     </row>
     <row r="13" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2244,136 +2237,136 @@
         <v>19</v>
       </c>
       <c r="C13" s="7">
-        <f t="shared" ref="C13:L13" si="26">C5-C12</f>
+        <f t="shared" ref="C13:L13" si="25">C5-C12</f>
         <v>4776</v>
       </c>
       <c r="D13" s="7">
+        <f t="shared" si="25"/>
+        <v>4802</v>
+      </c>
+      <c r="E13" s="7">
+        <f t="shared" si="25"/>
+        <v>4148</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="25"/>
+        <v>5087</v>
+      </c>
+      <c r="G13" s="7">
+        <f t="shared" si="25"/>
+        <v>5090</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="25"/>
+        <v>5336</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="25"/>
+        <v>5024</v>
+      </c>
+      <c r="J13" s="7">
+        <f t="shared" si="25"/>
+        <v>5550</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="25"/>
+        <v>5954</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="25"/>
+        <v>5354</v>
+      </c>
+      <c r="M13" s="7">
+        <f t="shared" ref="M13:N13" si="26">M5-M12</f>
+        <v>5938</v>
+      </c>
+      <c r="N13" s="7">
         <f t="shared" si="26"/>
-        <v>4802</v>
-      </c>
-      <c r="E13" s="7">
-        <f t="shared" si="26"/>
-        <v>4148</v>
-      </c>
-      <c r="F13" s="7">
-        <f t="shared" si="26"/>
-        <v>5087</v>
-      </c>
-      <c r="G13" s="7">
-        <f t="shared" si="26"/>
-        <v>5090</v>
-      </c>
-      <c r="H13" s="7">
-        <f t="shared" si="26"/>
-        <v>5336</v>
-      </c>
-      <c r="I13" s="7">
-        <f t="shared" si="26"/>
-        <v>5024</v>
-      </c>
-      <c r="J13" s="7">
-        <f t="shared" si="26"/>
-        <v>5550</v>
-      </c>
-      <c r="K13" s="7">
-        <f t="shared" si="26"/>
-        <v>5954</v>
-      </c>
-      <c r="L13" s="7">
-        <f t="shared" si="26"/>
-        <v>5354</v>
-      </c>
-      <c r="M13" s="7">
-        <f t="shared" ref="M13:N13" si="27">M5-M12</f>
-        <v>5938</v>
-      </c>
-      <c r="N13" s="7">
+        <v>6349</v>
+      </c>
+      <c r="O13" s="7">
+        <f t="shared" ref="O13:R13" si="27">O5-O12</f>
+        <v>6234</v>
+      </c>
+      <c r="P13" s="7">
         <f t="shared" si="27"/>
-        <v>6349</v>
-      </c>
-      <c r="O13" s="7">
-        <f t="shared" ref="O13:R13" si="28">O5-O12</f>
-        <v>6234</v>
-      </c>
-      <c r="P13" s="7">
+        <v>5435</v>
+      </c>
+      <c r="Q13" s="7">
+        <f t="shared" si="27"/>
+        <v>6177</v>
+      </c>
+      <c r="R13" s="7">
+        <f t="shared" si="27"/>
+        <v>6478.808</v>
+      </c>
+      <c r="T13" s="7">
+        <f t="shared" ref="T13:Y13" si="28">T5-T12</f>
+        <v>15001</v>
+      </c>
+      <c r="U13" s="7">
         <f t="shared" si="28"/>
-        <v>5435</v>
-      </c>
-      <c r="Q13" s="7">
+        <v>14081</v>
+      </c>
+      <c r="V13" s="7">
         <f t="shared" si="28"/>
-        <v>5474.8599999999988</v>
-      </c>
-      <c r="R13" s="7">
+        <v>15804</v>
+      </c>
+      <c r="W13" s="7">
         <f t="shared" si="28"/>
-        <v>6171.6329999999998</v>
-      </c>
-      <c r="T13" s="7">
-        <f t="shared" ref="T13:Y13" si="29">T5-T12</f>
-        <v>15001</v>
-      </c>
-      <c r="U13" s="7">
+        <v>18813</v>
+      </c>
+      <c r="X13" s="7">
+        <f t="shared" si="28"/>
+        <v>21000</v>
+      </c>
+      <c r="Y13" s="7">
+        <f t="shared" si="28"/>
+        <v>23595</v>
+      </c>
+      <c r="Z13" s="7">
+        <f t="shared" ref="Z13:AJ13" si="29">Z5-Z12</f>
+        <v>24324.808000000005</v>
+      </c>
+      <c r="AA13" s="7">
         <f t="shared" si="29"/>
-        <v>14081</v>
-      </c>
-      <c r="V13" s="7">
+        <v>29714.141200000002</v>
+      </c>
+      <c r="AB13" s="7">
         <f t="shared" si="29"/>
-        <v>15804</v>
-      </c>
-      <c r="W13" s="7">
+        <v>32321.685991520008</v>
+      </c>
+      <c r="AC13" s="7">
         <f t="shared" si="29"/>
-        <v>18813</v>
-      </c>
-      <c r="X13" s="7">
+        <v>34001.280885095999</v>
+      </c>
+      <c r="AD13" s="7">
         <f t="shared" si="29"/>
-        <v>21000</v>
-      </c>
-      <c r="Y13" s="7">
+        <v>35426.74803231984</v>
+      </c>
+      <c r="AE13" s="7">
         <f t="shared" si="29"/>
-        <v>23595</v>
-      </c>
-      <c r="Z13" s="7">
-        <f t="shared" ref="Z13:AJ13" si="30">Z5-Z12</f>
-        <v>23315.492999999999</v>
-      </c>
-      <c r="AA13" s="7">
-        <f t="shared" si="30"/>
-        <v>29013.750308000002</v>
-      </c>
-      <c r="AB13" s="7">
-        <f t="shared" si="30"/>
-        <v>30512.128603400004</v>
-      </c>
-      <c r="AC13" s="7">
-        <f t="shared" si="30"/>
-        <v>31447.250385002004</v>
-      </c>
-      <c r="AD13" s="7">
-        <f t="shared" si="30"/>
-        <v>32076.195392702044</v>
-      </c>
-      <c r="AE13" s="7">
-        <f t="shared" si="30"/>
-        <v>32748.465124474613</v>
+        <v>36556.274703345844</v>
       </c>
       <c r="AF13" s="7">
-        <f t="shared" si="30"/>
-        <v>33434.487709121808</v>
+        <f t="shared" si="29"/>
+        <v>37321.095933591241</v>
       </c>
       <c r="AG13" s="7">
-        <f t="shared" si="30"/>
-        <v>34134.541278283526</v>
+        <f t="shared" si="29"/>
+        <v>38101.550545803329</v>
       </c>
       <c r="AH13" s="7">
-        <f t="shared" si="30"/>
-        <v>34848.909556978273</v>
+        <f t="shared" si="29"/>
+        <v>38897.954577195065</v>
       </c>
       <c r="AI13" s="7">
-        <f t="shared" si="30"/>
-        <v>35577.881975778204</v>
+        <f t="shared" si="29"/>
+        <v>39710.630419419402</v>
       </c>
       <c r="AJ13" s="7">
-        <f t="shared" si="30"/>
-        <v>36321.753785230743</v>
+        <f t="shared" si="29"/>
+        <v>40539.906945995019</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
@@ -2423,7 +2416,7 @@
         <v>158</v>
       </c>
       <c r="Q14" s="3">
-        <v>185</v>
+        <v>39</v>
       </c>
       <c r="R14" s="3">
         <v>185</v>
@@ -2451,47 +2444,47 @@
       </c>
       <c r="Z14" s="3">
         <f>SUM(O14:R14)</f>
-        <v>710</v>
+        <v>564</v>
       </c>
       <c r="AA14" s="3">
-        <f t="shared" ref="AA14:AJ14" si="31">Z14*1.03</f>
-        <v>731.30000000000007</v>
+        <f t="shared" ref="AA14:AJ14" si="30">Z14*1.03</f>
+        <v>580.91999999999996</v>
       </c>
       <c r="AB14" s="3">
-        <f t="shared" si="31"/>
-        <v>753.23900000000015</v>
+        <f t="shared" si="30"/>
+        <v>598.34759999999994</v>
       </c>
       <c r="AC14" s="3">
-        <f t="shared" si="31"/>
-        <v>775.83617000000015</v>
+        <f t="shared" si="30"/>
+        <v>616.29802799999993</v>
       </c>
       <c r="AD14" s="3">
-        <f t="shared" si="31"/>
-        <v>799.11125510000022</v>
+        <f t="shared" si="30"/>
+        <v>634.78696883999999</v>
       </c>
       <c r="AE14" s="3">
-        <f t="shared" si="31"/>
-        <v>823.08459275300027</v>
+        <f t="shared" si="30"/>
+        <v>653.83057790520002</v>
       </c>
       <c r="AF14" s="3">
-        <f t="shared" si="31"/>
-        <v>847.77713053559035</v>
+        <f t="shared" si="30"/>
+        <v>673.44549524235606</v>
       </c>
       <c r="AG14" s="3">
-        <f t="shared" si="31"/>
-        <v>873.21044445165808</v>
+        <f t="shared" si="30"/>
+        <v>693.64886009962675</v>
       </c>
       <c r="AH14" s="3">
-        <f t="shared" si="31"/>
-        <v>899.40675778520779</v>
+        <f t="shared" si="30"/>
+        <v>714.45832590261557</v>
       </c>
       <c r="AI14" s="3">
-        <f t="shared" si="31"/>
-        <v>926.38896051876407</v>
+        <f t="shared" si="30"/>
+        <v>735.89207567969402</v>
       </c>
       <c r="AJ14" s="3">
-        <f t="shared" si="31"/>
-        <v>954.18062933432702</v>
+        <f t="shared" si="30"/>
+        <v>757.96883795008489</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
@@ -2541,7 +2534,7 @@
         <v>-161</v>
       </c>
       <c r="Q15" s="3">
-        <v>-200</v>
+        <v>-195</v>
       </c>
       <c r="R15" s="3">
         <v>-200</v>
@@ -2569,47 +2562,47 @@
       </c>
       <c r="Z15" s="3">
         <f>SUM(O15:R15)</f>
-        <v>-709</v>
+        <v>-704</v>
       </c>
       <c r="AA15" s="3">
-        <f t="shared" ref="AA15:AJ15" si="32">Z15*1.01</f>
-        <v>-716.09</v>
+        <f t="shared" ref="AA15:AJ15" si="31">Z15*1.01</f>
+        <v>-711.04</v>
       </c>
       <c r="AB15" s="3">
-        <f t="shared" si="32"/>
-        <v>-723.2509</v>
+        <f t="shared" si="31"/>
+        <v>-718.15039999999999</v>
       </c>
       <c r="AC15" s="3">
-        <f t="shared" si="32"/>
-        <v>-730.48340900000005</v>
+        <f t="shared" si="31"/>
+        <v>-725.33190400000001</v>
       </c>
       <c r="AD15" s="3">
-        <f t="shared" si="32"/>
-        <v>-737.78824309000004</v>
+        <f t="shared" si="31"/>
+        <v>-732.58522303999996</v>
       </c>
       <c r="AE15" s="3">
-        <f t="shared" si="32"/>
-        <v>-745.1661255209001</v>
+        <f t="shared" si="31"/>
+        <v>-739.91107527039992</v>
       </c>
       <c r="AF15" s="3">
-        <f t="shared" si="32"/>
-        <v>-752.61778677610914</v>
+        <f t="shared" si="31"/>
+        <v>-747.31018602310394</v>
       </c>
       <c r="AG15" s="3">
-        <f t="shared" si="32"/>
-        <v>-760.14396464387028</v>
+        <f t="shared" si="31"/>
+        <v>-754.78328788333499</v>
       </c>
       <c r="AH15" s="3">
-        <f t="shared" si="32"/>
-        <v>-767.74540429030901</v>
+        <f t="shared" si="31"/>
+        <v>-762.33112076216833</v>
       </c>
       <c r="AI15" s="3">
-        <f t="shared" si="32"/>
-        <v>-775.42285833321216</v>
+        <f t="shared" si="31"/>
+        <v>-769.95443196978999</v>
       </c>
       <c r="AJ15" s="3">
-        <f t="shared" si="32"/>
-        <v>-783.17708691654434</v>
+        <f t="shared" si="31"/>
+        <v>-777.6539762894879</v>
       </c>
     </row>
     <row r="16" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2618,136 +2611,136 @@
         <v>22</v>
       </c>
       <c r="C16" s="7">
-        <f t="shared" ref="C16:L16" si="33">C13-C14-C15</f>
+        <f t="shared" ref="C16:L16" si="32">C13-C14-C15</f>
         <v>4897</v>
       </c>
       <c r="D16" s="7">
+        <f t="shared" si="32"/>
+        <v>4542</v>
+      </c>
+      <c r="E16" s="7">
+        <f t="shared" si="32"/>
+        <v>3829</v>
+      </c>
+      <c r="F16" s="7">
+        <f t="shared" si="32"/>
+        <v>4868</v>
+      </c>
+      <c r="G16" s="7">
+        <f t="shared" si="32"/>
+        <v>4977</v>
+      </c>
+      <c r="H16" s="7">
+        <f t="shared" si="32"/>
+        <v>5278</v>
+      </c>
+      <c r="I16" s="7">
+        <f t="shared" si="32"/>
+        <v>5146</v>
+      </c>
+      <c r="J16" s="7">
+        <f t="shared" si="32"/>
+        <v>5636</v>
+      </c>
+      <c r="K16" s="7">
+        <f t="shared" si="32"/>
+        <v>6042</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="32"/>
+        <v>5513</v>
+      </c>
+      <c r="M16" s="7">
+        <f t="shared" ref="M16:N16" si="33">M13-M14-M15</f>
+        <v>5989</v>
+      </c>
+      <c r="N16" s="7">
         <f t="shared" si="33"/>
-        <v>4542</v>
-      </c>
-      <c r="E16" s="7">
-        <f t="shared" si="33"/>
-        <v>3829</v>
-      </c>
-      <c r="F16" s="7">
-        <f t="shared" si="33"/>
-        <v>4868</v>
-      </c>
-      <c r="G16" s="7">
-        <f t="shared" si="33"/>
-        <v>4977</v>
-      </c>
-      <c r="H16" s="7">
-        <f t="shared" si="33"/>
-        <v>5278</v>
-      </c>
-      <c r="I16" s="7">
-        <f t="shared" si="33"/>
-        <v>5146</v>
-      </c>
-      <c r="J16" s="7">
-        <f t="shared" si="33"/>
-        <v>5636</v>
-      </c>
-      <c r="K16" s="7">
-        <f t="shared" si="33"/>
-        <v>6042</v>
-      </c>
-      <c r="L16" s="7">
-        <f t="shared" si="33"/>
-        <v>5513</v>
-      </c>
-      <c r="M16" s="7">
-        <f t="shared" ref="M16:N16" si="34">M13-M14-M15</f>
-        <v>5989</v>
-      </c>
-      <c r="N16" s="7">
+        <v>6372</v>
+      </c>
+      <c r="O16" s="7">
+        <f t="shared" ref="O16:R16" si="34">O13-O14-O15</f>
+        <v>6200</v>
+      </c>
+      <c r="P16" s="7">
         <f t="shared" si="34"/>
-        <v>6372</v>
-      </c>
-      <c r="O16" s="7">
-        <f t="shared" ref="O16:R16" si="35">O13-O14-O15</f>
-        <v>6200</v>
-      </c>
-      <c r="P16" s="7">
+        <v>5438</v>
+      </c>
+      <c r="Q16" s="7">
+        <f t="shared" si="34"/>
+        <v>6333</v>
+      </c>
+      <c r="R16" s="7">
+        <f t="shared" si="34"/>
+        <v>6493.808</v>
+      </c>
+      <c r="T16" s="7">
+        <f t="shared" ref="T16:Z16" si="35">T13-T14-T15</f>
+        <v>14884</v>
+      </c>
+      <c r="U16" s="7">
         <f t="shared" si="35"/>
-        <v>5438</v>
-      </c>
-      <c r="Q16" s="7">
+        <v>13790</v>
+      </c>
+      <c r="V16" s="7">
         <f t="shared" si="35"/>
-        <v>5489.8599999999988</v>
-      </c>
-      <c r="R16" s="7">
+        <v>16063</v>
+      </c>
+      <c r="W16" s="7">
         <f t="shared" si="35"/>
-        <v>6186.6329999999998</v>
-      </c>
-      <c r="T16" s="7">
-        <f t="shared" ref="T16:Z16" si="36">T13-T14-T15</f>
-        <v>14884</v>
-      </c>
-      <c r="U16" s="7">
+        <v>18136</v>
+      </c>
+      <c r="X16" s="7">
+        <f t="shared" si="35"/>
+        <v>21037</v>
+      </c>
+      <c r="Y16" s="7">
+        <f t="shared" si="35"/>
+        <v>23916</v>
+      </c>
+      <c r="Z16" s="7">
+        <f t="shared" si="35"/>
+        <v>24464.808000000005</v>
+      </c>
+      <c r="AA16" s="7">
+        <f t="shared" ref="AA16:AJ16" si="36">AA13-AA14-AA15</f>
+        <v>29844.261200000004</v>
+      </c>
+      <c r="AB16" s="7">
         <f t="shared" si="36"/>
-        <v>13790</v>
-      </c>
-      <c r="V16" s="7">
+        <v>32441.488791520005</v>
+      </c>
+      <c r="AC16" s="7">
         <f t="shared" si="36"/>
-        <v>16063</v>
-      </c>
-      <c r="W16" s="7">
+        <v>34110.314761096</v>
+      </c>
+      <c r="AD16" s="7">
         <f t="shared" si="36"/>
-        <v>18136</v>
-      </c>
-      <c r="X16" s="7">
+        <v>35524.546286519835</v>
+      </c>
+      <c r="AE16" s="7">
         <f t="shared" si="36"/>
-        <v>21037</v>
-      </c>
-      <c r="Y16" s="7">
+        <v>36642.355200711041</v>
+      </c>
+      <c r="AF16" s="7">
         <f t="shared" si="36"/>
-        <v>23916</v>
-      </c>
-      <c r="Z16" s="7">
+        <v>37394.96062437199</v>
+      </c>
+      <c r="AG16" s="7">
         <f t="shared" si="36"/>
-        <v>23314.492999999999</v>
-      </c>
-      <c r="AA16" s="7">
-        <f t="shared" ref="AA16:AJ16" si="37">AA13-AA14-AA15</f>
-        <v>28998.540308000003</v>
-      </c>
-      <c r="AB16" s="7">
-        <f t="shared" si="37"/>
-        <v>30482.140503400002</v>
-      </c>
-      <c r="AC16" s="7">
-        <f t="shared" si="37"/>
-        <v>31401.897624002006</v>
-      </c>
-      <c r="AD16" s="7">
-        <f t="shared" si="37"/>
-        <v>32014.872380692042</v>
-      </c>
-      <c r="AE16" s="7">
-        <f t="shared" si="37"/>
-        <v>32670.546657242514</v>
-      </c>
-      <c r="AF16" s="7">
-        <f t="shared" si="37"/>
-        <v>33339.328365362329</v>
-      </c>
-      <c r="AG16" s="7">
-        <f t="shared" si="37"/>
-        <v>34021.474798475741</v>
+        <v>38162.684973587042</v>
       </c>
       <c r="AH16" s="7">
-        <f t="shared" si="37"/>
-        <v>34717.248203483374</v>
+        <f t="shared" si="36"/>
+        <v>38945.827372054613</v>
       </c>
       <c r="AI16" s="7">
-        <f t="shared" si="37"/>
-        <v>35426.915873592654</v>
+        <f t="shared" si="36"/>
+        <v>39744.692775709496</v>
       </c>
       <c r="AJ16" s="7">
-        <f t="shared" si="37"/>
-        <v>36150.750242812959</v>
+        <f t="shared" si="36"/>
+        <v>40559.592084334421</v>
       </c>
     </row>
     <row r="17" spans="1:147" x14ac:dyDescent="0.3">
@@ -2797,12 +2790,11 @@
         <v>861</v>
       </c>
       <c r="Q17" s="3">
-        <f t="shared" ref="Q17:R17" si="38">Q16*0.17</f>
-        <v>933.2761999999999</v>
+        <v>1061</v>
       </c>
       <c r="R17" s="3">
-        <f t="shared" si="38"/>
-        <v>1051.7276100000001</v>
+        <f t="shared" ref="Q17:R17" si="37">R16*0.17</f>
+        <v>1103.9473600000001</v>
       </c>
       <c r="T17" s="3">
         <v>2804</v>
@@ -2827,47 +2819,47 @@
       </c>
       <c r="Z17" s="3">
         <f>SUM(O17:R17)</f>
-        <v>3927.0038100000002</v>
+        <v>4106.9473600000001</v>
       </c>
       <c r="AA17" s="3">
-        <f t="shared" ref="AA17:AJ17" si="39">AA16*0.18</f>
-        <v>5219.7372554400008</v>
+        <f t="shared" ref="AA17:AJ17" si="38">AA16*0.18</f>
+        <v>5371.9670160000005</v>
       </c>
       <c r="AB17" s="3">
-        <f t="shared" si="39"/>
-        <v>5486.7852906119997</v>
+        <f t="shared" si="38"/>
+        <v>5839.4679824736004</v>
       </c>
       <c r="AC17" s="3">
-        <f t="shared" si="39"/>
-        <v>5652.3415723203607</v>
+        <f t="shared" si="38"/>
+        <v>6139.85665699728</v>
       </c>
       <c r="AD17" s="3">
-        <f t="shared" si="39"/>
-        <v>5762.6770285245675</v>
+        <f t="shared" si="38"/>
+        <v>6394.41833157357</v>
       </c>
       <c r="AE17" s="3">
-        <f t="shared" si="39"/>
-        <v>5880.6983983036525</v>
+        <f t="shared" si="38"/>
+        <v>6595.6239361279868</v>
       </c>
       <c r="AF17" s="3">
-        <f t="shared" si="39"/>
-        <v>6001.0791057652186</v>
+        <f t="shared" si="38"/>
+        <v>6731.0929123869582</v>
       </c>
       <c r="AG17" s="3">
-        <f t="shared" si="39"/>
-        <v>6123.8654637256332</v>
+        <f t="shared" si="38"/>
+        <v>6869.2832952456674</v>
       </c>
       <c r="AH17" s="3">
-        <f t="shared" si="39"/>
-        <v>6249.1046766270074</v>
+        <f t="shared" si="38"/>
+        <v>7010.2489269698299</v>
       </c>
       <c r="AI17" s="3">
-        <f t="shared" si="39"/>
-        <v>6376.8448572466777</v>
+        <f t="shared" si="38"/>
+        <v>7154.0446996277087</v>
       </c>
       <c r="AJ17" s="3">
-        <f t="shared" si="39"/>
-        <v>6507.135043706332</v>
+        <f t="shared" si="38"/>
+        <v>7300.7265751801951</v>
       </c>
     </row>
     <row r="18" spans="1:147" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2876,580 +2868,580 @@
         <v>24</v>
       </c>
       <c r="C18" s="7">
-        <f t="shared" ref="C18:L18" si="40">C16-C17</f>
+        <f t="shared" ref="C18:L18" si="39">C16-C17</f>
         <v>4059</v>
       </c>
       <c r="D18" s="7">
+        <f t="shared" si="39"/>
+        <v>3647</v>
+      </c>
+      <c r="E18" s="7">
+        <f t="shared" si="39"/>
+        <v>3411</v>
+      </c>
+      <c r="F18" s="7">
+        <f t="shared" si="39"/>
+        <v>3940</v>
+      </c>
+      <c r="G18" s="7">
+        <f t="shared" si="39"/>
+        <v>4179</v>
+      </c>
+      <c r="H18" s="7">
+        <f t="shared" si="39"/>
+        <v>4257</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" si="39"/>
+        <v>4156</v>
+      </c>
+      <c r="J18" s="7">
+        <f t="shared" si="39"/>
+        <v>4681</v>
+      </c>
+      <c r="K18" s="7">
+        <f t="shared" si="39"/>
+        <v>4890</v>
+      </c>
+      <c r="L18" s="7">
+        <f t="shared" si="39"/>
+        <v>4663</v>
+      </c>
+      <c r="M18" s="7">
+        <f t="shared" ref="M18:O18" si="40">M16-M17</f>
+        <v>4872</v>
+      </c>
+      <c r="N18" s="7">
         <f t="shared" si="40"/>
-        <v>3647</v>
-      </c>
-      <c r="E18" s="7">
+        <v>5318</v>
+      </c>
+      <c r="O18" s="7">
         <f t="shared" si="40"/>
-        <v>3411</v>
-      </c>
-      <c r="F18" s="7">
-        <f t="shared" si="40"/>
-        <v>3940</v>
-      </c>
-      <c r="G18" s="7">
-        <f t="shared" si="40"/>
-        <v>4179</v>
-      </c>
-      <c r="H18" s="7">
-        <f t="shared" si="40"/>
-        <v>4257</v>
-      </c>
-      <c r="I18" s="7">
-        <f t="shared" si="40"/>
-        <v>4156</v>
-      </c>
-      <c r="J18" s="7">
-        <f t="shared" si="40"/>
-        <v>4681</v>
-      </c>
-      <c r="K18" s="7">
-        <f t="shared" si="40"/>
-        <v>4890</v>
-      </c>
-      <c r="L18" s="7">
-        <f t="shared" si="40"/>
-        <v>4663</v>
-      </c>
-      <c r="M18" s="7">
-        <f t="shared" ref="M18:O18" si="41">M16-M17</f>
-        <v>4872</v>
-      </c>
-      <c r="N18" s="7">
+        <v>5119</v>
+      </c>
+      <c r="P18" s="7">
+        <f t="shared" ref="P18:R18" si="41">P16-P17</f>
+        <v>4577</v>
+      </c>
+      <c r="Q18" s="7">
         <f t="shared" si="41"/>
-        <v>5318</v>
-      </c>
-      <c r="O18" s="7">
+        <v>5272</v>
+      </c>
+      <c r="R18" s="7">
         <f t="shared" si="41"/>
-        <v>5119</v>
-      </c>
-      <c r="P18" s="7">
-        <f t="shared" ref="P18:R18" si="42">P16-P17</f>
-        <v>4577</v>
-      </c>
-      <c r="Q18" s="7">
+        <v>5389.8606399999999</v>
+      </c>
+      <c r="T18" s="7">
+        <f t="shared" ref="T18:Z18" si="42">T16-T17</f>
+        <v>12080</v>
+      </c>
+      <c r="U18" s="7">
         <f t="shared" si="42"/>
-        <v>4556.5837999999985</v>
-      </c>
-      <c r="R18" s="7">
+        <v>10866</v>
+      </c>
+      <c r="V18" s="7">
         <f t="shared" si="42"/>
-        <v>5134.9053899999999</v>
-      </c>
-      <c r="T18" s="7">
-        <f t="shared" ref="T18:Z18" si="43">T16-T17</f>
-        <v>12080</v>
-      </c>
-      <c r="U18" s="7">
+        <v>12311</v>
+      </c>
+      <c r="W18" s="7">
+        <f t="shared" si="42"/>
+        <v>15057</v>
+      </c>
+      <c r="X18" s="7">
+        <f t="shared" si="42"/>
+        <v>17273</v>
+      </c>
+      <c r="Y18" s="7">
+        <f t="shared" si="42"/>
+        <v>19743</v>
+      </c>
+      <c r="Z18" s="7">
+        <f t="shared" si="42"/>
+        <v>20357.860640000006</v>
+      </c>
+      <c r="AA18" s="7">
+        <f t="shared" ref="AA18:AJ18" si="43">AA16-AA17</f>
+        <v>24472.294184000006</v>
+      </c>
+      <c r="AB18" s="7">
         <f t="shared" si="43"/>
-        <v>10866</v>
-      </c>
-      <c r="V18" s="7">
+        <v>26602.020809046404</v>
+      </c>
+      <c r="AC18" s="7">
         <f t="shared" si="43"/>
-        <v>12311</v>
-      </c>
-      <c r="W18" s="7">
+        <v>27970.458104098721</v>
+      </c>
+      <c r="AD18" s="7">
         <f t="shared" si="43"/>
-        <v>15057</v>
-      </c>
-      <c r="X18" s="7">
+        <v>29130.127954946263</v>
+      </c>
+      <c r="AE18" s="7">
         <f t="shared" si="43"/>
-        <v>17273</v>
-      </c>
-      <c r="Y18" s="7">
+        <v>30046.731264583053</v>
+      </c>
+      <c r="AF18" s="7">
         <f t="shared" si="43"/>
-        <v>19743</v>
-      </c>
-      <c r="Z18" s="7">
+        <v>30663.867711985033</v>
+      </c>
+      <c r="AG18" s="7">
         <f t="shared" si="43"/>
-        <v>19387.48919</v>
-      </c>
-      <c r="AA18" s="7">
-        <f t="shared" ref="AA18:AJ18" si="44">AA16-AA17</f>
-        <v>23778.803052560004</v>
-      </c>
-      <c r="AB18" s="7">
-        <f t="shared" si="44"/>
-        <v>24995.355212788003</v>
-      </c>
-      <c r="AC18" s="7">
-        <f t="shared" si="44"/>
-        <v>25749.556051681644</v>
-      </c>
-      <c r="AD18" s="7">
-        <f t="shared" si="44"/>
-        <v>26252.195352167473</v>
-      </c>
-      <c r="AE18" s="7">
-        <f t="shared" si="44"/>
-        <v>26789.848258938862</v>
-      </c>
-      <c r="AF18" s="7">
-        <f t="shared" si="44"/>
-        <v>27338.249259597113</v>
-      </c>
-      <c r="AG18" s="7">
-        <f t="shared" si="44"/>
-        <v>27897.609334750108</v>
+        <v>31293.401678341375</v>
       </c>
       <c r="AH18" s="7">
-        <f t="shared" si="44"/>
-        <v>28468.143526856365</v>
+        <f t="shared" si="43"/>
+        <v>31935.578445084782</v>
       </c>
       <c r="AI18" s="7">
-        <f t="shared" si="44"/>
-        <v>29050.071016345977</v>
+        <f t="shared" si="43"/>
+        <v>32590.648076081787</v>
       </c>
       <c r="AJ18" s="7">
-        <f t="shared" si="44"/>
-        <v>29643.615199106629</v>
+        <f t="shared" si="43"/>
+        <v>33258.865509154224</v>
       </c>
       <c r="AK18" s="6">
         <f>AJ18+($AN$23*AJ18)</f>
-        <v>29347.179047115562</v>
+        <v>32926.276854062678</v>
       </c>
       <c r="AL18" s="6">
-        <f t="shared" ref="AL18:CW18" si="45">AK18+($AN$23*AK18)</f>
-        <v>29053.707256644408</v>
+        <f t="shared" ref="AL18:CW18" si="44">AK18+($AN$23*AK18)</f>
+        <v>32597.014085522052</v>
       </c>
       <c r="AM18" s="6">
+        <f t="shared" si="44"/>
+        <v>32271.043944666832</v>
+      </c>
+      <c r="AN18" s="6">
+        <f t="shared" si="44"/>
+        <v>31948.333505220162</v>
+      </c>
+      <c r="AO18" s="6">
+        <f t="shared" si="44"/>
+        <v>31628.85017016796</v>
+      </c>
+      <c r="AP18" s="6">
+        <f t="shared" si="44"/>
+        <v>31312.561668466282</v>
+      </c>
+      <c r="AQ18" s="6">
+        <f t="shared" si="44"/>
+        <v>30999.43605178162</v>
+      </c>
+      <c r="AR18" s="6">
+        <f t="shared" si="44"/>
+        <v>30689.441691263804</v>
+      </c>
+      <c r="AS18" s="6">
+        <f t="shared" si="44"/>
+        <v>30382.547274351167</v>
+      </c>
+      <c r="AT18" s="6">
+        <f t="shared" si="44"/>
+        <v>30078.721801607655</v>
+      </c>
+      <c r="AU18" s="6">
+        <f t="shared" si="44"/>
+        <v>29777.934583591577</v>
+      </c>
+      <c r="AV18" s="6">
+        <f t="shared" si="44"/>
+        <v>29480.155237755662</v>
+      </c>
+      <c r="AW18" s="6">
+        <f t="shared" si="44"/>
+        <v>29185.353685378104</v>
+      </c>
+      <c r="AX18" s="6">
+        <f t="shared" si="44"/>
+        <v>28893.500148524323</v>
+      </c>
+      <c r="AY18" s="6">
+        <f t="shared" si="44"/>
+        <v>28604.56514703908</v>
+      </c>
+      <c r="AZ18" s="6">
+        <f t="shared" si="44"/>
+        <v>28318.519495568689</v>
+      </c>
+      <c r="BA18" s="6">
+        <f t="shared" si="44"/>
+        <v>28035.334300613002</v>
+      </c>
+      <c r="BB18" s="6">
+        <f t="shared" si="44"/>
+        <v>27754.980957606873</v>
+      </c>
+      <c r="BC18" s="6">
+        <f t="shared" si="44"/>
+        <v>27477.431148030802</v>
+      </c>
+      <c r="BD18" s="6">
+        <f t="shared" si="44"/>
+        <v>27202.656836550494</v>
+      </c>
+      <c r="BE18" s="6">
+        <f t="shared" si="44"/>
+        <v>26930.630268184988</v>
+      </c>
+      <c r="BF18" s="6">
+        <f t="shared" si="44"/>
+        <v>26661.323965503139</v>
+      </c>
+      <c r="BG18" s="6">
+        <f t="shared" si="44"/>
+        <v>26394.710725848108</v>
+      </c>
+      <c r="BH18" s="6">
+        <f t="shared" si="44"/>
+        <v>26130.763618589626</v>
+      </c>
+      <c r="BI18" s="6">
+        <f t="shared" si="44"/>
+        <v>25869.455982403731</v>
+      </c>
+      <c r="BJ18" s="6">
+        <f t="shared" si="44"/>
+        <v>25610.761422579693</v>
+      </c>
+      <c r="BK18" s="6">
+        <f t="shared" si="44"/>
+        <v>25354.653808353898</v>
+      </c>
+      <c r="BL18" s="6">
+        <f t="shared" si="44"/>
+        <v>25101.10727027036</v>
+      </c>
+      <c r="BM18" s="6">
+        <f t="shared" si="44"/>
+        <v>24850.096197567658</v>
+      </c>
+      <c r="BN18" s="6">
+        <f t="shared" si="44"/>
+        <v>24601.59523559198</v>
+      </c>
+      <c r="BO18" s="6">
+        <f t="shared" si="44"/>
+        <v>24355.57928323606</v>
+      </c>
+      <c r="BP18" s="6">
+        <f t="shared" si="44"/>
+        <v>24112.023490403699</v>
+      </c>
+      <c r="BQ18" s="6">
+        <f t="shared" si="44"/>
+        <v>23870.903255499663</v>
+      </c>
+      <c r="BR18" s="6">
+        <f t="shared" si="44"/>
+        <v>23632.194222944665</v>
+      </c>
+      <c r="BS18" s="6">
+        <f t="shared" si="44"/>
+        <v>23395.872280715219</v>
+      </c>
+      <c r="BT18" s="6">
+        <f t="shared" si="44"/>
+        <v>23161.913557908068</v>
+      </c>
+      <c r="BU18" s="6">
+        <f t="shared" si="44"/>
+        <v>22930.294422328989</v>
+      </c>
+      <c r="BV18" s="6">
+        <f t="shared" si="44"/>
+        <v>22700.991478105698</v>
+      </c>
+      <c r="BW18" s="6">
+        <f t="shared" si="44"/>
+        <v>22473.98156332464</v>
+      </c>
+      <c r="BX18" s="6">
+        <f t="shared" si="44"/>
+        <v>22249.241747691394</v>
+      </c>
+      <c r="BY18" s="6">
+        <f t="shared" si="44"/>
+        <v>22026.749330214479</v>
+      </c>
+      <c r="BZ18" s="6">
+        <f t="shared" si="44"/>
+        <v>21806.481836912335</v>
+      </c>
+      <c r="CA18" s="6">
+        <f t="shared" si="44"/>
+        <v>21588.417018543212</v>
+      </c>
+      <c r="CB18" s="6">
+        <f t="shared" si="44"/>
+        <v>21372.53284835778</v>
+      </c>
+      <c r="CC18" s="6">
+        <f t="shared" si="44"/>
+        <v>21158.807519874201</v>
+      </c>
+      <c r="CD18" s="6">
+        <f t="shared" si="44"/>
+        <v>20947.219444675458</v>
+      </c>
+      <c r="CE18" s="6">
+        <f t="shared" si="44"/>
+        <v>20737.747250228706</v>
+      </c>
+      <c r="CF18" s="6">
+        <f t="shared" si="44"/>
+        <v>20530.369777726417</v>
+      </c>
+      <c r="CG18" s="6">
+        <f t="shared" si="44"/>
+        <v>20325.066079949152</v>
+      </c>
+      <c r="CH18" s="6">
+        <f t="shared" si="44"/>
+        <v>20121.815419149661</v>
+      </c>
+      <c r="CI18" s="6">
+        <f t="shared" si="44"/>
+        <v>19920.597264958164</v>
+      </c>
+      <c r="CJ18" s="6">
+        <f t="shared" si="44"/>
+        <v>19721.391292308581</v>
+      </c>
+      <c r="CK18" s="6">
+        <f t="shared" si="44"/>
+        <v>19524.177379385495</v>
+      </c>
+      <c r="CL18" s="6">
+        <f t="shared" si="44"/>
+        <v>19328.93560559164</v>
+      </c>
+      <c r="CM18" s="6">
+        <f t="shared" si="44"/>
+        <v>19135.646249535723</v>
+      </c>
+      <c r="CN18" s="6">
+        <f t="shared" si="44"/>
+        <v>18944.289787040365</v>
+      </c>
+      <c r="CO18" s="6">
+        <f t="shared" si="44"/>
+        <v>18754.846889169959</v>
+      </c>
+      <c r="CP18" s="6">
+        <f t="shared" si="44"/>
+        <v>18567.298420278261</v>
+      </c>
+      <c r="CQ18" s="6">
+        <f t="shared" si="44"/>
+        <v>18381.625436075479</v>
+      </c>
+      <c r="CR18" s="6">
+        <f t="shared" si="44"/>
+        <v>18197.809181714725</v>
+      </c>
+      <c r="CS18" s="6">
+        <f t="shared" si="44"/>
+        <v>18015.83108989758</v>
+      </c>
+      <c r="CT18" s="6">
+        <f t="shared" si="44"/>
+        <v>17835.672778998603</v>
+      </c>
+      <c r="CU18" s="6">
+        <f t="shared" si="44"/>
+        <v>17657.316051208618</v>
+      </c>
+      <c r="CV18" s="6">
+        <f t="shared" si="44"/>
+        <v>17480.742890696532</v>
+      </c>
+      <c r="CW18" s="6">
+        <f t="shared" si="44"/>
+        <v>17305.935461789566</v>
+      </c>
+      <c r="CX18" s="6">
+        <f t="shared" ref="CX18:EQ18" si="45">CW18+($AN$23*CW18)</f>
+        <v>17132.876107171669</v>
+      </c>
+      <c r="CY18" s="6">
         <f t="shared" si="45"/>
-        <v>28763.170184077964</v>
-      </c>
-      <c r="AN18" s="6">
+        <v>16961.547346099953</v>
+      </c>
+      <c r="CZ18" s="6">
         <f t="shared" si="45"/>
-        <v>28475.538482237185</v>
-      </c>
-      <c r="AO18" s="6">
+        <v>16791.931872638954</v>
+      </c>
+      <c r="DA18" s="6">
         <f t="shared" si="45"/>
-        <v>28190.783097414813</v>
-      </c>
-      <c r="AP18" s="6">
+        <v>16624.012553912566</v>
+      </c>
+      <c r="DB18" s="6">
         <f t="shared" si="45"/>
-        <v>27908.875266440664</v>
-      </c>
-      <c r="AQ18" s="6">
+        <v>16457.772428373439</v>
+      </c>
+      <c r="DC18" s="6">
         <f t="shared" si="45"/>
-        <v>27629.786513776256</v>
-      </c>
-      <c r="AR18" s="6">
+        <v>16293.194704089705</v>
+      </c>
+      <c r="DD18" s="6">
         <f t="shared" si="45"/>
-        <v>27353.488648638493</v>
-      </c>
-      <c r="AS18" s="6">
+        <v>16130.262757048808</v>
+      </c>
+      <c r="DE18" s="6">
         <f t="shared" si="45"/>
-        <v>27079.953762152109</v>
-      </c>
-      <c r="AT18" s="6">
+        <v>15968.960129478319</v>
+      </c>
+      <c r="DF18" s="6">
         <f t="shared" si="45"/>
-        <v>26809.154224530586</v>
-      </c>
-      <c r="AU18" s="6">
+        <v>15809.270528183535</v>
+      </c>
+      <c r="DG18" s="6">
         <f t="shared" si="45"/>
-        <v>26541.062682285279</v>
-      </c>
-      <c r="AV18" s="6">
+        <v>15651.1778229017</v>
+      </c>
+      <c r="DH18" s="6">
         <f t="shared" si="45"/>
-        <v>26275.652055462426</v>
-      </c>
-      <c r="AW18" s="6">
+        <v>15494.666044672684</v>
+      </c>
+      <c r="DI18" s="6">
         <f t="shared" si="45"/>
-        <v>26012.895534907802</v>
-      </c>
-      <c r="AX18" s="6">
+        <v>15339.719384225957</v>
+      </c>
+      <c r="DJ18" s="6">
         <f t="shared" si="45"/>
-        <v>25752.766579558724</v>
-      </c>
-      <c r="AY18" s="6">
+        <v>15186.322190383697</v>
+      </c>
+      <c r="DK18" s="6">
         <f t="shared" si="45"/>
-        <v>25495.238913763136</v>
-      </c>
-      <c r="AZ18" s="6">
+        <v>15034.458968479859</v>
+      </c>
+      <c r="DL18" s="6">
         <f t="shared" si="45"/>
-        <v>25240.286524625506</v>
-      </c>
-      <c r="BA18" s="6">
+        <v>14884.11437879506</v>
+      </c>
+      <c r="DM18" s="6">
         <f t="shared" si="45"/>
-        <v>24987.883659379251</v>
-      </c>
-      <c r="BB18" s="6">
+        <v>14735.273235007109</v>
+      </c>
+      <c r="DN18" s="6">
         <f t="shared" si="45"/>
-        <v>24738.00482278546</v>
-      </c>
-      <c r="BC18" s="6">
+        <v>14587.920502657038</v>
+      </c>
+      <c r="DO18" s="6">
         <f t="shared" si="45"/>
-        <v>24490.624774557607</v>
-      </c>
-      <c r="BD18" s="6">
+        <v>14442.041297630467</v>
+      </c>
+      <c r="DP18" s="6">
         <f t="shared" si="45"/>
-        <v>24245.71852681203</v>
-      </c>
-      <c r="BE18" s="6">
+        <v>14297.620884654163</v>
+      </c>
+      <c r="DQ18" s="6">
         <f t="shared" si="45"/>
-        <v>24003.261341543908</v>
-      </c>
-      <c r="BF18" s="6">
+        <v>14154.644675807622</v>
+      </c>
+      <c r="DR18" s="6">
         <f t="shared" si="45"/>
-        <v>23763.22872812847</v>
-      </c>
-      <c r="BG18" s="6">
+        <v>14013.098229049545</v>
+      </c>
+      <c r="DS18" s="6">
         <f t="shared" si="45"/>
-        <v>23525.596440847185</v>
-      </c>
-      <c r="BH18" s="6">
+        <v>13872.96724675905</v>
+      </c>
+      <c r="DT18" s="6">
         <f t="shared" si="45"/>
-        <v>23290.340476438712</v>
-      </c>
-      <c r="BI18" s="6">
+        <v>13734.237574291459</v>
+      </c>
+      <c r="DU18" s="6">
         <f t="shared" si="45"/>
-        <v>23057.437071674325</v>
-      </c>
-      <c r="BJ18" s="6">
+        <v>13596.895198548544</v>
+      </c>
+      <c r="DV18" s="6">
         <f t="shared" si="45"/>
-        <v>22826.862700957583</v>
-      </c>
-      <c r="BK18" s="6">
+        <v>13460.926246563058</v>
+      </c>
+      <c r="DW18" s="6">
         <f t="shared" si="45"/>
-        <v>22598.594073948007</v>
-      </c>
-      <c r="BL18" s="6">
+        <v>13326.316984097428</v>
+      </c>
+      <c r="DX18" s="6">
         <f t="shared" si="45"/>
-        <v>22372.608133208527</v>
-      </c>
-      <c r="BM18" s="6">
+        <v>13193.053814256453</v>
+      </c>
+      <c r="DY18" s="6">
         <f t="shared" si="45"/>
-        <v>22148.882051876441</v>
-      </c>
-      <c r="BN18" s="6">
+        <v>13061.123276113889</v>
+      </c>
+      <c r="DZ18" s="6">
         <f t="shared" si="45"/>
-        <v>21927.393231357677</v>
-      </c>
-      <c r="BO18" s="6">
+        <v>12930.51204335275</v>
+      </c>
+      <c r="EA18" s="6">
         <f t="shared" si="45"/>
-        <v>21708.119299044101</v>
-      </c>
-      <c r="BP18" s="6">
+        <v>12801.206922919222</v>
+      </c>
+      <c r="EB18" s="6">
         <f t="shared" si="45"/>
-        <v>21491.03810605366</v>
-      </c>
-      <c r="BQ18" s="6">
+        <v>12673.194853690029</v>
+      </c>
+      <c r="EC18" s="6">
         <f t="shared" si="45"/>
-        <v>21276.127724993123</v>
-      </c>
-      <c r="BR18" s="6">
+        <v>12546.462905153128</v>
+      </c>
+      <c r="ED18" s="6">
         <f t="shared" si="45"/>
-        <v>21063.366447743192</v>
-      </c>
-      <c r="BS18" s="6">
+        <v>12420.998276101596</v>
+      </c>
+      <c r="EE18" s="6">
         <f t="shared" si="45"/>
-        <v>20852.732783265761</v>
-      </c>
-      <c r="BT18" s="6">
+        <v>12296.78829334058</v>
+      </c>
+      <c r="EF18" s="6">
         <f t="shared" si="45"/>
-        <v>20644.205455433104</v>
-      </c>
-      <c r="BU18" s="6">
+        <v>12173.820410407174</v>
+      </c>
+      <c r="EG18" s="6">
         <f t="shared" si="45"/>
-        <v>20437.763400878772</v>
-      </c>
-      <c r="BV18" s="6">
+        <v>12052.082206303103</v>
+      </c>
+      <c r="EH18" s="6">
         <f t="shared" si="45"/>
-        <v>20233.385766869986</v>
-      </c>
-      <c r="BW18" s="6">
+        <v>11931.561384240073</v>
+      </c>
+      <c r="EI18" s="6">
         <f t="shared" si="45"/>
-        <v>20031.051909201287</v>
-      </c>
-      <c r="BX18" s="6">
+        <v>11812.245770397672</v>
+      </c>
+      <c r="EJ18" s="6">
         <f t="shared" si="45"/>
-        <v>19830.741390109273</v>
-      </c>
-      <c r="BY18" s="6">
+        <v>11694.123312693695</v>
+      </c>
+      <c r="EK18" s="6">
         <f t="shared" si="45"/>
-        <v>19632.43397620818</v>
-      </c>
-      <c r="BZ18" s="6">
+        <v>11577.182079566757</v>
+      </c>
+      <c r="EL18" s="6">
         <f t="shared" si="45"/>
-        <v>19436.109636446097</v>
-      </c>
-      <c r="CA18" s="6">
+        <v>11461.41025877109</v>
+      </c>
+      <c r="EM18" s="6">
         <f t="shared" si="45"/>
-        <v>19241.748540081637</v>
-      </c>
-      <c r="CB18" s="6">
+        <v>11346.796156183378</v>
+      </c>
+      <c r="EN18" s="6">
         <f t="shared" si="45"/>
-        <v>19049.331054680821</v>
-      </c>
-      <c r="CC18" s="6">
+        <v>11233.328194621545</v>
+      </c>
+      <c r="EO18" s="6">
         <f t="shared" si="45"/>
-        <v>18858.837744134013</v>
-      </c>
-      <c r="CD18" s="6">
+        <v>11120.994912675329</v>
+      </c>
+      <c r="EP18" s="6">
         <f t="shared" si="45"/>
-        <v>18670.249366692671</v>
-      </c>
-      <c r="CE18" s="6">
+        <v>11009.784963548576</v>
+      </c>
+      <c r="EQ18" s="6">
         <f t="shared" si="45"/>
-        <v>18483.546873025745</v>
-      </c>
-      <c r="CF18" s="6">
-        <f t="shared" si="45"/>
-        <v>18298.711404295489</v>
-      </c>
-      <c r="CG18" s="6">
-        <f t="shared" si="45"/>
-        <v>18115.724290252536</v>
-      </c>
-      <c r="CH18" s="6">
-        <f t="shared" si="45"/>
-        <v>17934.56704735001</v>
-      </c>
-      <c r="CI18" s="6">
-        <f t="shared" si="45"/>
-        <v>17755.22137687651</v>
-      </c>
-      <c r="CJ18" s="6">
-        <f t="shared" si="45"/>
-        <v>17577.669163107745</v>
-      </c>
-      <c r="CK18" s="6">
-        <f t="shared" si="45"/>
-        <v>17401.892471476669</v>
-      </c>
-      <c r="CL18" s="6">
-        <f t="shared" si="45"/>
-        <v>17227.873546761901</v>
-      </c>
-      <c r="CM18" s="6">
-        <f t="shared" si="45"/>
-        <v>17055.594811294282</v>
-      </c>
-      <c r="CN18" s="6">
-        <f t="shared" si="45"/>
-        <v>16885.03886318134</v>
-      </c>
-      <c r="CO18" s="6">
-        <f t="shared" si="45"/>
-        <v>16716.188474549526</v>
-      </c>
-      <c r="CP18" s="6">
-        <f t="shared" si="45"/>
-        <v>16549.026589804031</v>
-      </c>
-      <c r="CQ18" s="6">
-        <f t="shared" si="45"/>
-        <v>16383.53632390599</v>
-      </c>
-      <c r="CR18" s="6">
-        <f t="shared" si="45"/>
-        <v>16219.700960666931</v>
-      </c>
-      <c r="CS18" s="6">
-        <f t="shared" si="45"/>
-        <v>16057.503951060262</v>
-      </c>
-      <c r="CT18" s="6">
-        <f t="shared" si="45"/>
-        <v>15896.928911549659</v>
-      </c>
-      <c r="CU18" s="6">
-        <f t="shared" si="45"/>
-        <v>15737.959622434162</v>
-      </c>
-      <c r="CV18" s="6">
-        <f t="shared" si="45"/>
-        <v>15580.58002620982</v>
-      </c>
-      <c r="CW18" s="6">
-        <f t="shared" si="45"/>
-        <v>15424.774225947722</v>
-      </c>
-      <c r="CX18" s="6">
-        <f t="shared" ref="CX18:EQ18" si="46">CW18+($AN$23*CW18)</f>
-        <v>15270.526483688245</v>
-      </c>
-      <c r="CY18" s="6">
-        <f t="shared" si="46"/>
-        <v>15117.821218851363</v>
-      </c>
-      <c r="CZ18" s="6">
-        <f t="shared" si="46"/>
-        <v>14966.643006662849</v>
-      </c>
-      <c r="DA18" s="6">
-        <f t="shared" si="46"/>
-        <v>14816.97657659622</v>
-      </c>
-      <c r="DB18" s="6">
-        <f t="shared" si="46"/>
-        <v>14668.806810830258</v>
-      </c>
-      <c r="DC18" s="6">
-        <f t="shared" si="46"/>
-        <v>14522.118742721956</v>
-      </c>
-      <c r="DD18" s="6">
-        <f t="shared" si="46"/>
-        <v>14376.897555294736</v>
-      </c>
-      <c r="DE18" s="6">
-        <f t="shared" si="46"/>
-        <v>14233.128579741788</v>
-      </c>
-      <c r="DF18" s="6">
-        <f t="shared" si="46"/>
-        <v>14090.79729394437</v>
-      </c>
-      <c r="DG18" s="6">
-        <f t="shared" si="46"/>
-        <v>13949.889321004926</v>
-      </c>
-      <c r="DH18" s="6">
-        <f t="shared" si="46"/>
-        <v>13810.390427794877</v>
-      </c>
-      <c r="DI18" s="6">
-        <f t="shared" si="46"/>
-        <v>13672.286523516928</v>
-      </c>
-      <c r="DJ18" s="6">
-        <f t="shared" si="46"/>
-        <v>13535.563658281759</v>
-      </c>
-      <c r="DK18" s="6">
-        <f t="shared" si="46"/>
-        <v>13400.208021698942</v>
-      </c>
-      <c r="DL18" s="6">
-        <f t="shared" si="46"/>
-        <v>13266.205941481952</v>
-      </c>
-      <c r="DM18" s="6">
-        <f t="shared" si="46"/>
-        <v>13133.543882067133</v>
-      </c>
-      <c r="DN18" s="6">
-        <f t="shared" si="46"/>
-        <v>13002.208443246462</v>
-      </c>
-      <c r="DO18" s="6">
-        <f t="shared" si="46"/>
-        <v>12872.186358813997</v>
-      </c>
-      <c r="DP18" s="6">
-        <f t="shared" si="46"/>
-        <v>12743.464495225857</v>
-      </c>
-      <c r="DQ18" s="6">
-        <f t="shared" si="46"/>
-        <v>12616.029850273599</v>
-      </c>
-      <c r="DR18" s="6">
-        <f t="shared" si="46"/>
-        <v>12489.869551770862</v>
-      </c>
-      <c r="DS18" s="6">
-        <f t="shared" si="46"/>
-        <v>12364.970856253154</v>
-      </c>
-      <c r="DT18" s="6">
-        <f t="shared" si="46"/>
-        <v>12241.321147690622</v>
-      </c>
-      <c r="DU18" s="6">
-        <f t="shared" si="46"/>
-        <v>12118.907936213716</v>
-      </c>
-      <c r="DV18" s="6">
-        <f t="shared" si="46"/>
-        <v>11997.718856851579</v>
-      </c>
-      <c r="DW18" s="6">
-        <f t="shared" si="46"/>
-        <v>11877.741668283064</v>
-      </c>
-      <c r="DX18" s="6">
-        <f t="shared" si="46"/>
-        <v>11758.964251600233</v>
-      </c>
-      <c r="DY18" s="6">
-        <f t="shared" si="46"/>
-        <v>11641.374609084231</v>
-      </c>
-      <c r="DZ18" s="6">
-        <f t="shared" si="46"/>
-        <v>11524.960862993388</v>
-      </c>
-      <c r="EA18" s="6">
-        <f t="shared" si="46"/>
-        <v>11409.711254363454</v>
-      </c>
-      <c r="EB18" s="6">
-        <f t="shared" si="46"/>
-        <v>11295.614141819819</v>
-      </c>
-      <c r="EC18" s="6">
-        <f t="shared" si="46"/>
-        <v>11182.65800040162</v>
-      </c>
-      <c r="ED18" s="6">
-        <f t="shared" si="46"/>
-        <v>11070.831420397604</v>
-      </c>
-      <c r="EE18" s="6">
-        <f t="shared" si="46"/>
-        <v>10960.123106193629</v>
-      </c>
-      <c r="EF18" s="6">
-        <f t="shared" si="46"/>
-        <v>10850.521875131692</v>
-      </c>
-      <c r="EG18" s="6">
-        <f t="shared" si="46"/>
-        <v>10742.016656380374</v>
-      </c>
-      <c r="EH18" s="6">
-        <f t="shared" si="46"/>
-        <v>10634.596489816571</v>
-      </c>
-      <c r="EI18" s="6">
-        <f t="shared" si="46"/>
-        <v>10528.250524918405</v>
-      </c>
-      <c r="EJ18" s="6">
-        <f t="shared" si="46"/>
-        <v>10422.968019669221</v>
-      </c>
-      <c r="EK18" s="6">
-        <f t="shared" si="46"/>
-        <v>10318.738339472529</v>
-      </c>
-      <c r="EL18" s="6">
-        <f t="shared" si="46"/>
-        <v>10215.550956077805</v>
-      </c>
-      <c r="EM18" s="6">
-        <f t="shared" si="46"/>
-        <v>10113.395446517026</v>
-      </c>
-      <c r="EN18" s="6">
-        <f t="shared" si="46"/>
-        <v>10012.261492051855</v>
-      </c>
-      <c r="EO18" s="6">
-        <f t="shared" si="46"/>
-        <v>9912.1388771313377</v>
-      </c>
-      <c r="EP18" s="6">
-        <f t="shared" si="46"/>
-        <v>9813.0174883600248</v>
-      </c>
-      <c r="EQ18" s="6">
-        <f t="shared" si="46"/>
-        <v>9714.8873134764253</v>
+        <v>10899.687113913091</v>
       </c>
     </row>
     <row r="19" spans="1:147" x14ac:dyDescent="0.3">
@@ -3457,43 +3449,43 @@
         <v>1</v>
       </c>
       <c r="C19" s="3">
-        <f t="shared" ref="C19:L19" si="47">1574.2+245.5+9.3</f>
+        <f t="shared" ref="C19:L19" si="46">1574.2+245.5+9.3</f>
         <v>1829</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="G19" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="I19" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="K19" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="L19" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="M19" s="3">
@@ -3512,80 +3504,80 @@
         <v>1845.1</v>
       </c>
       <c r="Q19" s="3">
-        <f>1711+4.8+120.3+9</f>
-        <v>1845.1</v>
+        <f>1709+5+120+9</f>
+        <v>1843</v>
       </c>
       <c r="R19" s="3">
-        <f>1711+4.8+120.3+9</f>
-        <v>1845.1</v>
+        <f>1709+5+120+9</f>
+        <v>1843</v>
       </c>
       <c r="T19" s="3">
-        <f t="shared" ref="T19:X19" si="48">1574.2+245.5+9.3</f>
+        <f t="shared" ref="T19:X19" si="47">1574.2+245.5+9.3</f>
         <v>1829</v>
       </c>
       <c r="U19" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>1829</v>
       </c>
       <c r="V19" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>1829</v>
       </c>
       <c r="W19" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>1829</v>
       </c>
       <c r="X19" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>1829</v>
       </c>
       <c r="Y19" s="3">
-        <f t="shared" ref="Y19" si="49">1728.1+4.8+120.3+9.6</f>
+        <f t="shared" ref="Y19" si="48">1728.1+4.8+120.3+9.6</f>
         <v>1862.7999999999997</v>
       </c>
       <c r="Z19" s="3">
-        <f t="shared" ref="Z19:AJ19" si="50">1711+4.8+120.3+9</f>
-        <v>1845.1</v>
+        <f>1709+5+120+9</f>
+        <v>1843</v>
       </c>
       <c r="AA19" s="3">
-        <f t="shared" si="50"/>
-        <v>1845.1</v>
+        <f>1709+5+120+9</f>
+        <v>1843</v>
       </c>
       <c r="AB19" s="3">
-        <f t="shared" si="50"/>
-        <v>1845.1</v>
+        <f>1709+5+120+9</f>
+        <v>1843</v>
       </c>
       <c r="AC19" s="3">
-        <f t="shared" si="50"/>
-        <v>1845.1</v>
+        <f>1709+5+120+9</f>
+        <v>1843</v>
       </c>
       <c r="AD19" s="3">
-        <f t="shared" si="50"/>
-        <v>1845.1</v>
+        <f>1709+5+120+9</f>
+        <v>1843</v>
       </c>
       <c r="AE19" s="3">
-        <f t="shared" si="50"/>
-        <v>1845.1</v>
+        <f>1709+5+120+9</f>
+        <v>1843</v>
       </c>
       <c r="AF19" s="3">
-        <f t="shared" si="50"/>
-        <v>1845.1</v>
+        <f>1709+5+120+9</f>
+        <v>1843</v>
       </c>
       <c r="AG19" s="3">
-        <f t="shared" si="50"/>
-        <v>1845.1</v>
+        <f>1709+5+120+9</f>
+        <v>1843</v>
       </c>
       <c r="AH19" s="3">
-        <f t="shared" si="50"/>
-        <v>1845.1</v>
+        <f>1709+5+120+9</f>
+        <v>1843</v>
       </c>
       <c r="AI19" s="3">
-        <f t="shared" si="50"/>
-        <v>1845.1</v>
+        <f>1709+5+120+9</f>
+        <v>1843</v>
       </c>
       <c r="AJ19" s="3">
-        <f t="shared" si="50"/>
-        <v>1845.1</v>
+        <f>1709+5+120+9</f>
+        <v>1843</v>
       </c>
     </row>
     <row r="20" spans="1:147" x14ac:dyDescent="0.3">
@@ -3593,136 +3585,136 @@
         <v>25</v>
       </c>
       <c r="C20" s="5">
-        <f t="shared" ref="C20:L20" si="51">C18/C19</f>
+        <f t="shared" ref="C20:L20" si="49">C18/C19</f>
         <v>2.2192454893384364</v>
       </c>
       <c r="D20" s="5">
+        <f t="shared" si="49"/>
+        <v>1.9939857845817386</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" si="49"/>
+        <v>1.8649535265172226</v>
+      </c>
+      <c r="F20" s="5">
+        <f t="shared" si="49"/>
+        <v>2.1541826134499726</v>
+      </c>
+      <c r="G20" s="5">
+        <f t="shared" si="49"/>
+        <v>2.2848551120831053</v>
+      </c>
+      <c r="H20" s="5">
+        <f t="shared" si="49"/>
+        <v>2.3275013668671405</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="49"/>
+        <v>2.2722799343903772</v>
+      </c>
+      <c r="J20" s="5">
+        <f t="shared" si="49"/>
+        <v>2.5593220338983049</v>
+      </c>
+      <c r="K20" s="5">
+        <f t="shared" si="49"/>
+        <v>2.6735921268452705</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" si="49"/>
+        <v>2.5494805904866049</v>
+      </c>
+      <c r="M20" s="5">
+        <f t="shared" ref="M20:O20" si="50">M18/M19</f>
+        <v>2.6739846322722283</v>
+      </c>
+      <c r="N20" s="5">
+        <f t="shared" si="50"/>
+        <v>2.854842173072794</v>
+      </c>
+      <c r="O20" s="5">
+        <f t="shared" si="50"/>
+        <v>2.7555579480002153</v>
+      </c>
+      <c r="P20" s="5">
+        <f t="shared" ref="P20:R20" si="51">P18/P19</f>
+        <v>2.4806243564034469</v>
+      </c>
+      <c r="Q20" s="5">
         <f t="shared" si="51"/>
-        <v>1.9939857845817386</v>
-      </c>
-      <c r="E20" s="5">
+        <v>2.8605534454693435</v>
+      </c>
+      <c r="R20" s="5">
         <f t="shared" si="51"/>
-        <v>1.8649535265172226</v>
-      </c>
-      <c r="F20" s="5">
-        <f t="shared" si="51"/>
-        <v>2.1541826134499726</v>
-      </c>
-      <c r="G20" s="5">
-        <f t="shared" si="51"/>
-        <v>2.2848551120831053</v>
-      </c>
-      <c r="H20" s="5">
-        <f t="shared" si="51"/>
-        <v>2.3275013668671405</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="51"/>
-        <v>2.2722799343903772</v>
-      </c>
-      <c r="J20" s="5">
-        <f t="shared" si="51"/>
-        <v>2.5593220338983049</v>
-      </c>
-      <c r="K20" s="5">
-        <f t="shared" si="51"/>
-        <v>2.6735921268452705</v>
-      </c>
-      <c r="L20" s="5">
-        <f t="shared" si="51"/>
-        <v>2.5494805904866049</v>
-      </c>
-      <c r="M20" s="5">
-        <f t="shared" ref="M20:O20" si="52">M18/M19</f>
-        <v>2.6739846322722283</v>
-      </c>
-      <c r="N20" s="5">
+        <v>2.9245038741182854</v>
+      </c>
+      <c r="T20" s="5">
+        <f t="shared" ref="T20:Z20" si="52">T18/T19</f>
+        <v>6.6047020229633677</v>
+      </c>
+      <c r="U20" s="5">
         <f t="shared" si="52"/>
-        <v>2.854842173072794</v>
-      </c>
-      <c r="O20" s="5">
+        <v>5.9409513395297981</v>
+      </c>
+      <c r="V20" s="5">
         <f t="shared" si="52"/>
-        <v>2.7555579480002153</v>
-      </c>
-      <c r="P20" s="5">
-        <f t="shared" ref="P20:R20" si="53">P18/P19</f>
-        <v>2.4806243564034469</v>
-      </c>
-      <c r="Q20" s="5">
+        <v>6.7310005467468565</v>
+      </c>
+      <c r="W20" s="5">
+        <f t="shared" si="52"/>
+        <v>8.2323674138873706</v>
+      </c>
+      <c r="X20" s="5">
+        <f t="shared" si="52"/>
+        <v>9.4439584472389289</v>
+      </c>
+      <c r="Y20" s="5">
+        <f t="shared" si="52"/>
+        <v>10.598561305561521</v>
+      </c>
+      <c r="Z20" s="5">
+        <f t="shared" si="52"/>
+        <v>11.046044839934892</v>
+      </c>
+      <c r="AA20" s="5">
+        <f t="shared" ref="AA20:AJ20" si="53">AA18/AA19</f>
+        <v>13.278510137818778</v>
+      </c>
+      <c r="AB20" s="5">
         <f t="shared" si="53"/>
-        <v>2.4695592650804827</v>
-      </c>
-      <c r="R20" s="5">
+        <v>14.434086168771787</v>
+      </c>
+      <c r="AC20" s="5">
         <f t="shared" si="53"/>
-        <v>2.7829957129694867</v>
-      </c>
-      <c r="T20" s="5">
-        <f t="shared" ref="T20:Z20" si="54">T18/T19</f>
-        <v>6.6047020229633677</v>
-      </c>
-      <c r="U20" s="5">
-        <f t="shared" si="54"/>
-        <v>5.9409513395297981</v>
-      </c>
-      <c r="V20" s="5">
-        <f t="shared" si="54"/>
-        <v>6.7310005467468565</v>
-      </c>
-      <c r="W20" s="5">
-        <f t="shared" si="54"/>
-        <v>8.2323674138873706</v>
-      </c>
-      <c r="X20" s="5">
-        <f t="shared" si="54"/>
-        <v>9.4439584472389289</v>
-      </c>
-      <c r="Y20" s="5">
-        <f t="shared" si="54"/>
-        <v>10.598561305561521</v>
-      </c>
-      <c r="Z20" s="5">
-        <f t="shared" si="54"/>
-        <v>10.507554707061949</v>
-      </c>
-      <c r="AA20" s="5">
-        <f t="shared" ref="AA20:AJ20" si="55">AA18/AA19</f>
-        <v>12.887541625147691</v>
-      </c>
-      <c r="AB20" s="5">
-        <f t="shared" si="55"/>
-        <v>13.546883753069213</v>
-      </c>
-      <c r="AC20" s="5">
-        <f t="shared" si="55"/>
-        <v>13.955642540611157</v>
+        <v>15.176591483504462</v>
       </c>
       <c r="AD20" s="5">
-        <f t="shared" si="55"/>
-        <v>14.228061000578546</v>
+        <f t="shared" si="53"/>
+        <v>15.80582091966699</v>
       </c>
       <c r="AE20" s="5">
-        <f t="shared" si="55"/>
-        <v>14.519455996389823</v>
+        <f t="shared" si="53"/>
+        <v>16.303164006827483</v>
       </c>
       <c r="AF20" s="5">
-        <f t="shared" si="55"/>
-        <v>14.816676201613525</v>
+        <f t="shared" si="53"/>
+        <v>16.638018291907233</v>
       </c>
       <c r="AG20" s="5">
-        <f t="shared" si="55"/>
-        <v>15.119835962685009</v>
+        <f t="shared" si="53"/>
+        <v>16.979599391395212</v>
       </c>
       <c r="AH20" s="5">
-        <f t="shared" si="55"/>
-        <v>15.429051827465377</v>
+        <f t="shared" si="53"/>
+        <v>17.32804039342636</v>
       </c>
       <c r="AI20" s="5">
-        <f t="shared" si="55"/>
-        <v>15.744442586497197</v>
+        <f t="shared" si="53"/>
+        <v>17.683476981053602</v>
       </c>
       <c r="AJ20" s="5">
-        <f t="shared" si="55"/>
-        <v>16.066129315000072</v>
+        <f t="shared" si="53"/>
+        <v>18.046047481906797</v>
       </c>
     </row>
     <row r="22" spans="1:147" x14ac:dyDescent="0.3">
@@ -3734,48 +3726,48 @@
         <v>0.12423856070264905</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22:N22" si="56">H3/D3-1</f>
+        <f t="shared" ref="H22:N22" si="54">H3/D3-1</f>
         <v>0.11072471831965514</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0.11656357388316141</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0.1055605496340053</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>8.7953629032258007E-2</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>9.8935504070131408E-2</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>9.5654314908285132E-2</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0.11708676965965847</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" ref="O22" si="57">O3/K3-1</f>
+        <f t="shared" ref="O22" si="55">O3/K3-1</f>
         <v>0.10145934676858936</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" ref="P22" si="58">P3/L3-1</f>
+        <f t="shared" ref="P22" si="56">P3/L3-1</f>
         <v>9.3333333333333268E-2</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22" si="59">Q3/M3-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="Q22" si="57">Q3/M3-1</f>
+        <v>0.14292134831460679</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" ref="R22" si="60">R3/N3-1</f>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" ref="R22" si="58">R3/N3-1</f>
+        <v>0.12000000000000011</v>
       </c>
       <c r="T22" s="9"/>
       <c r="U22" s="9">
@@ -3783,63 +3775,63 @@
         <v>-4.92231361796579E-2</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22:AJ22" si="61">V3/U3-1</f>
+        <f t="shared" ref="V22:AJ22" si="59">V3/U3-1</f>
         <v>0.10340565778632249</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.21593030491599263</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.11405663596042315</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.10023581294214923</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" si="61"/>
-        <v>9.0691699604743103E-2</v>
+        <f t="shared" si="59"/>
+        <v>0.11470912431108382</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
+        <v>9.000000000000008E-2</v>
+      </c>
+      <c r="AB22" s="9">
+        <f t="shared" si="59"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="AB22" s="9">
-        <f t="shared" si="61"/>
+      <c r="AC22" s="9">
+        <f t="shared" si="59"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AC22" s="9">
-        <f t="shared" si="61"/>
+      <c r="AD22" s="9">
+        <f t="shared" si="59"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AE22" s="9">
+        <f t="shared" si="59"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AD22" s="9">
-        <f t="shared" si="61"/>
+      <c r="AF22" s="9">
+        <f t="shared" si="59"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE22" s="9">
-        <f t="shared" si="61"/>
+      <c r="AG22" s="9">
+        <f t="shared" si="59"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF22" s="9">
-        <f t="shared" si="61"/>
+      <c r="AH22" s="9">
+        <f t="shared" si="59"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG22" s="9">
-        <f t="shared" si="61"/>
+      <c r="AI22" s="9">
+        <f t="shared" si="59"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH22" s="9">
-        <f t="shared" si="61"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AI22" s="9">
-        <f t="shared" si="61"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -3848,19 +3840,19 @@
         <v>40</v>
       </c>
       <c r="C23" s="9">
-        <f t="shared" ref="C23:F23" si="62">C5/C3</f>
+        <f t="shared" ref="C23:F23" si="60">C5/C3</f>
         <v>0.84062898427539312</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.82946167756294342</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.82364261168384878</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.82586361885193271</v>
       </c>
       <c r="G23" s="9">
@@ -3868,115 +3860,115 @@
         <v>0.8315272177419355</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" ref="H23:N23" si="63">H5/H3</f>
+        <f t="shared" ref="H23:N23" si="61">H5/H3</f>
         <v>0.81026925485284906</v>
       </c>
       <c r="I23" s="9">
+        <f t="shared" si="61"/>
+        <v>0.81767819771020556</v>
+      </c>
+      <c r="J23" s="9">
+        <f t="shared" si="61"/>
+        <v>0.82599605064467418</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" si="61"/>
+        <v>0.82870048644892291</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="61"/>
+        <v>0.81732193732193736</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="61"/>
+        <v>0.82325842696629215</v>
+      </c>
+      <c r="N23" s="9">
+        <f t="shared" si="61"/>
+        <v>0.83269210772590208</v>
+      </c>
+      <c r="O23" s="9">
+        <f t="shared" ref="O23:R23" si="62">O5/O3</f>
+        <v>0.80935856992639332</v>
+      </c>
+      <c r="P23" s="9">
+        <f t="shared" si="62"/>
+        <v>0.82728788826349797</v>
+      </c>
+      <c r="Q23" s="9">
+        <f t="shared" si="62"/>
+        <v>0.82805741250491549</v>
+      </c>
+      <c r="R23" s="9">
+        <f t="shared" si="62"/>
+        <v>0.82</v>
+      </c>
+      <c r="T23" s="9">
+        <f t="shared" ref="T23:AJ23" si="63">T5/T3</f>
+        <v>0.85011098054576317</v>
+      </c>
+      <c r="U23" s="9">
         <f t="shared" si="63"/>
-        <v>0.81767819771020556</v>
-      </c>
-      <c r="J23" s="9">
+        <v>0.82674173761787051</v>
+      </c>
+      <c r="V23" s="9">
         <f t="shared" si="63"/>
-        <v>0.82599605064467418</v>
-      </c>
-      <c r="K23" s="9">
+        <v>0.82410288321924907</v>
+      </c>
+      <c r="W23" s="9">
         <f t="shared" si="63"/>
-        <v>0.82870048644892291</v>
-      </c>
-      <c r="L23" s="9">
+        <v>0.82975093824633228</v>
+      </c>
+      <c r="X23" s="9">
         <f t="shared" si="63"/>
-        <v>0.81732193732193736</v>
-      </c>
-      <c r="M23" s="9">
+        <v>0.82142529017241905</v>
+      </c>
+      <c r="Y23" s="9">
         <f t="shared" si="63"/>
-        <v>0.82325842696629215</v>
-      </c>
-      <c r="N23" s="9">
+        <v>0.82564159661526471</v>
+      </c>
+      <c r="Z23" s="9">
         <f t="shared" si="63"/>
-        <v>0.83269210772590208</v>
-      </c>
-      <c r="O23" s="9">
-        <f t="shared" ref="O23:R23" si="64">O5/O3</f>
-        <v>0.80935856992639332</v>
-      </c>
-      <c r="P23" s="9">
-        <f t="shared" si="64"/>
-        <v>0.82728788826349797</v>
-      </c>
-      <c r="Q23" s="9">
-        <f t="shared" si="64"/>
-        <v>0.82</v>
-      </c>
-      <c r="R23" s="9">
-        <f t="shared" si="64"/>
-        <v>0.82</v>
-      </c>
-      <c r="T23" s="9">
-        <f t="shared" ref="T23:AJ23" si="65">T5/T3</f>
-        <v>0.85011098054576317</v>
-      </c>
-      <c r="U23" s="9">
-        <f t="shared" si="65"/>
-        <v>0.82674173761787051</v>
-      </c>
-      <c r="V23" s="9">
-        <f t="shared" si="65"/>
-        <v>0.82410288321924907</v>
-      </c>
-      <c r="W23" s="9">
-        <f t="shared" si="65"/>
-        <v>0.82975093824633228</v>
-      </c>
-      <c r="X23" s="9">
-        <f t="shared" si="65"/>
-        <v>0.82142529017241905</v>
-      </c>
-      <c r="Y23" s="9">
-        <f t="shared" si="65"/>
-        <v>0.82564159661526471</v>
-      </c>
-      <c r="Z23" s="9">
-        <f t="shared" si="65"/>
-        <v>0.81920171885650817</v>
+        <v>0.82126551175817242</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
+        <v>0.82999999999999985</v>
+      </c>
+      <c r="AB23" s="9">
+        <f t="shared" si="63"/>
+        <v>0.83000000000000007</v>
+      </c>
+      <c r="AC23" s="9">
+        <f t="shared" si="63"/>
         <v>0.83</v>
       </c>
-      <c r="AB23" s="9">
-        <f t="shared" si="65"/>
+      <c r="AD23" s="9">
+        <f t="shared" si="63"/>
         <v>0.83</v>
       </c>
-      <c r="AC23" s="9">
-        <f t="shared" si="65"/>
+      <c r="AE23" s="9">
+        <f t="shared" si="63"/>
         <v>0.83</v>
       </c>
-      <c r="AD23" s="9">
-        <f t="shared" si="65"/>
+      <c r="AF23" s="9">
+        <f t="shared" si="63"/>
+        <v>0.83</v>
+      </c>
+      <c r="AG23" s="9">
+        <f t="shared" si="63"/>
+        <v>0.83</v>
+      </c>
+      <c r="AH23" s="9">
+        <f t="shared" si="63"/>
         <v>0.82999999999999985</v>
       </c>
-      <c r="AE23" s="9">
-        <f t="shared" si="65"/>
-        <v>0.83</v>
-      </c>
-      <c r="AF23" s="9">
-        <f t="shared" si="65"/>
-        <v>0.83</v>
-      </c>
-      <c r="AG23" s="9">
-        <f t="shared" si="65"/>
-        <v>0.83</v>
-      </c>
-      <c r="AH23" s="9">
-        <f t="shared" si="65"/>
+      <c r="AI23" s="9">
+        <f t="shared" si="63"/>
         <v>0.83000000000000007</v>
       </c>
-      <c r="AI23" s="9">
-        <f t="shared" si="65"/>
-        <v>0.83</v>
-      </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>0.83</v>
       </c>
       <c r="AM23" t="s">
@@ -3991,19 +3983,19 @@
         <v>41</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:F24" si="66">C6/C3</f>
+        <f t="shared" ref="C24:F24" si="64">C6/C3</f>
         <v>3.9665675024791049E-2</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>4.3677841146195578E-2</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>4.3024054982817868E-2</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>5.5091819699499167E-2</v>
       </c>
       <c r="G24" s="9">
@@ -4011,115 +4003,115 @@
         <v>4.1834677419354836E-2</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24:N24" si="67">H6/H3</f>
+        <f t="shared" ref="H24:N24" si="65">H6/H3</f>
         <v>3.8697557921102063E-2</v>
       </c>
       <c r="I24" s="9">
+        <f t="shared" si="65"/>
+        <v>3.6562846239074236E-2</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="65"/>
+        <v>4.6811476361946797E-2</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" si="65"/>
+        <v>3.3935603428306697E-2</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="65"/>
+        <v>3.8518518518518521E-2</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" si="65"/>
+        <v>4.2471910112359554E-2</v>
+      </c>
+      <c r="N24" s="9">
+        <f t="shared" si="65"/>
+        <v>5.7294374545076431E-2</v>
+      </c>
+      <c r="O24" s="9">
+        <f t="shared" ref="O24:R24" si="66">O6/O3</f>
+        <v>3.2176656151419555E-2</v>
+      </c>
+      <c r="P24" s="9">
+        <f t="shared" si="66"/>
+        <v>3.9712320200125079E-2</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" si="66"/>
+        <v>4.1388124262681875E-2</v>
+      </c>
+      <c r="R24" s="9">
+        <f t="shared" si="66"/>
+        <v>6.0000000000000005E-2</v>
+      </c>
+      <c r="T24" s="9">
+        <f t="shared" ref="T24:AJ24" si="67">T6/T3</f>
+        <v>4.8091569830700266E-2</v>
+      </c>
+      <c r="U24" s="9">
         <f t="shared" si="67"/>
-        <v>3.6562846239074236E-2</v>
-      </c>
-      <c r="J24" s="9">
+        <v>4.4447496109127529E-2</v>
+      </c>
+      <c r="V24" s="9">
         <f t="shared" si="67"/>
-        <v>4.6811476361946797E-2</v>
-      </c>
-      <c r="K24" s="9">
+        <v>4.7127152043144577E-2</v>
+      </c>
+      <c r="W24" s="9">
         <f t="shared" si="67"/>
-        <v>3.3935603428306697E-2</v>
-      </c>
-      <c r="L24" s="9">
+        <v>4.5581712726032071E-2</v>
+      </c>
+      <c r="X24" s="9">
         <f t="shared" si="67"/>
-        <v>3.8518518518518521E-2</v>
-      </c>
-      <c r="M24" s="9">
+        <v>4.1068202002878758E-2</v>
+      </c>
+      <c r="Y24" s="9">
         <f t="shared" si="67"/>
-        <v>4.2471910112359554E-2</v>
-      </c>
-      <c r="N24" s="9">
+        <v>4.3422590881255912E-2</v>
+      </c>
+      <c r="Z24" s="9">
         <f t="shared" si="67"/>
-        <v>5.7294374545076431E-2</v>
-      </c>
-      <c r="O24" s="9">
-        <f t="shared" ref="O24:R24" si="68">O6/O3</f>
-        <v>3.2176656151419555E-2</v>
-      </c>
-      <c r="P24" s="9">
-        <f t="shared" si="68"/>
-        <v>3.9712320200125079E-2</v>
-      </c>
-      <c r="Q24" s="9">
-        <f t="shared" si="68"/>
+        <v>4.3805045266766283E-2</v>
+      </c>
+      <c r="AA24" s="9">
+        <f t="shared" si="67"/>
         <v>0.04</v>
       </c>
-      <c r="R24" s="9">
-        <f t="shared" si="68"/>
-        <v>5.9999999999999991E-2</v>
-      </c>
-      <c r="T24" s="9">
-        <f t="shared" ref="T24:AJ24" si="69">T6/T3</f>
-        <v>4.8091569830700266E-2</v>
-      </c>
-      <c r="U24" s="9">
-        <f t="shared" si="69"/>
-        <v>4.4447496109127529E-2</v>
-      </c>
-      <c r="V24" s="9">
-        <f t="shared" si="69"/>
-        <v>4.7127152043144577E-2</v>
-      </c>
-      <c r="W24" s="9">
-        <f t="shared" si="69"/>
-        <v>4.5581712726032071E-2</v>
-      </c>
-      <c r="X24" s="9">
-        <f t="shared" si="69"/>
-        <v>4.1068202002878758E-2</v>
-      </c>
-      <c r="Y24" s="9">
-        <f t="shared" si="69"/>
-        <v>4.3422590881255912E-2</v>
-      </c>
-      <c r="Z24" s="9">
-        <f t="shared" si="69"/>
-        <v>4.3283053700995215E-2</v>
-      </c>
-      <c r="AA24" s="9">
-        <f t="shared" si="69"/>
+      <c r="AB24" s="9">
+        <f t="shared" si="67"/>
         <v>0.04</v>
       </c>
-      <c r="AB24" s="9">
-        <f t="shared" si="69"/>
+      <c r="AC24" s="9">
+        <f t="shared" si="67"/>
         <v>0.04</v>
       </c>
-      <c r="AC24" s="9">
-        <f t="shared" si="69"/>
+      <c r="AD24" s="9">
+        <f t="shared" si="67"/>
         <v>0.04</v>
       </c>
-      <c r="AD24" s="9">
-        <f t="shared" si="69"/>
+      <c r="AE24" s="9">
+        <f t="shared" si="67"/>
         <v>0.04</v>
       </c>
-      <c r="AE24" s="9">
-        <f t="shared" si="69"/>
+      <c r="AF24" s="9">
+        <f t="shared" si="67"/>
         <v>0.04</v>
       </c>
-      <c r="AF24" s="9">
-        <f t="shared" si="69"/>
+      <c r="AG24" s="9">
+        <f t="shared" si="67"/>
+        <v>4.0000000000000008E-2</v>
+      </c>
+      <c r="AH24" s="9">
+        <f t="shared" si="67"/>
         <v>0.04</v>
       </c>
-      <c r="AG24" s="9">
-        <f t="shared" si="69"/>
+      <c r="AI24" s="9">
+        <f t="shared" si="67"/>
         <v>0.04</v>
       </c>
-      <c r="AH24" s="9">
-        <f t="shared" si="69"/>
-        <v>0.04</v>
-      </c>
-      <c r="AI24" s="9">
-        <f t="shared" si="69"/>
-        <v>0.04</v>
-      </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>4.0000000000000008E-2</v>
       </c>
       <c r="AM24" t="s">
@@ -4142,47 +4134,47 @@
         <v>-6.315789473684208E-2</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" ref="H25:N25" si="70">H7/D7-1</f>
+        <f t="shared" ref="H25:N25" si="68">H7/D7-1</f>
         <v>-5.7894736842105221E-2</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>2.2471910112359605E-2</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>6.4864864864864868E-2</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>1.6853932584269593E-2</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>5.5865921787709549E-2</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>9.8901098901098994E-2</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>5.5837563451776706E-2</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" ref="O25" si="71">O7/K7-1</f>
+        <f t="shared" ref="O25" si="69">O7/K7-1</f>
         <v>0.14364640883977908</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" ref="P25" si="72">P7/L7-1</f>
+        <f t="shared" ref="P25" si="70">P7/L7-1</f>
         <v>0.18518518518518512</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" ref="Q25" si="73">Q7/M7-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="Q25" si="71">Q7/M7-1</f>
+        <v>0.12000000000000011</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" ref="R25" si="74">R7/N7-1</f>
+        <f t="shared" ref="R25" si="72">R7/N7-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="S25" s="9"/>
@@ -4192,63 +4184,63 @@
         <v>8.3217753120665705E-3</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" ref="V25:AJ25" si="75">V7/U7-1</f>
+        <f t="shared" ref="V25:AJ25" si="73">V7/U7-1</f>
         <v>4.126547455295837E-3</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>1.7808219178082174E-2</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>-9.421265141319024E-3</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>5.7065217391304435E-2</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.13084832904884314</v>
+        <f t="shared" si="73"/>
+        <v>0.13598971722365039</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="75"/>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" si="73"/>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="75"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="73"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM25" t="s">
@@ -4256,7 +4248,7 @@
       </c>
       <c r="AN25" s="3">
         <f>NPV(AN24,Z18:EQ18)</f>
-        <v>424451.95980651764</v>
+        <v>470736.38303071231</v>
       </c>
     </row>
     <row r="26" spans="1:147" x14ac:dyDescent="0.3">
@@ -4264,19 +4256,19 @@
         <v>42</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:F26" si="76">C8/C3</f>
+        <f t="shared" ref="C26:F26" si="74">C8/C3</f>
         <v>1.4166312508853945E-2</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>1.7387675615523717E-2</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>1.6082474226804123E-2</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>2.0932323102606908E-2</v>
       </c>
       <c r="G26" s="9">
@@ -4284,115 +4276,115 @@
         <v>1.3734879032258064E-2</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" ref="H26:N26" si="77">H8/H3</f>
+        <f t="shared" ref="H26:N26" si="75">H8/H3</f>
         <v>1.6280525986224169E-2</v>
       </c>
       <c r="I26" s="9">
+        <f t="shared" si="75"/>
+        <v>1.6373261110427181E-2</v>
+      </c>
+      <c r="J26" s="9">
+        <f t="shared" si="75"/>
+        <v>2.0095249157858056E-2</v>
+      </c>
+      <c r="K26" s="9">
+        <f t="shared" si="75"/>
+        <v>1.5172573546444291E-2</v>
+      </c>
+      <c r="L26" s="9">
+        <f t="shared" si="75"/>
+        <v>1.8233618233618232E-2</v>
+      </c>
+      <c r="M26" s="9">
+        <f t="shared" si="75"/>
+        <v>1.707865168539326E-2</v>
+      </c>
+      <c r="N26" s="9">
+        <f t="shared" si="75"/>
+        <v>1.9964645939482165E-2</v>
+      </c>
+      <c r="O26" s="9">
+        <f t="shared" ref="O26:R26" si="76">O8/O3</f>
+        <v>1.5036803364879074E-2</v>
+      </c>
+      <c r="P26" s="9">
+        <f t="shared" si="76"/>
+        <v>1.8032103397957057E-2</v>
+      </c>
+      <c r="Q26" s="9">
+        <f t="shared" si="76"/>
+        <v>1.838379866299646E-2</v>
+      </c>
+      <c r="R26" s="9">
+        <f t="shared" si="76"/>
+        <v>0.02</v>
+      </c>
+      <c r="T26" s="9">
+        <f t="shared" ref="T26:AJ26" si="77">T8/T3</f>
+        <v>1.9758889324106715E-2</v>
+      </c>
+      <c r="U26" s="9">
         <f t="shared" si="77"/>
-        <v>1.6373261110427181E-2</v>
-      </c>
-      <c r="J26" s="9">
+        <v>1.8676187860477891E-2</v>
+      </c>
+      <c r="V26" s="9">
         <f t="shared" si="77"/>
-        <v>2.0095249157858056E-2</v>
-      </c>
-      <c r="K26" s="9">
+        <v>1.6718523127981746E-2</v>
+      </c>
+      <c r="W26" s="9">
         <f t="shared" si="77"/>
-        <v>1.5172573546444291E-2</v>
-      </c>
-      <c r="L26" s="9">
+        <v>1.7229614466052541E-2</v>
+      </c>
+      <c r="X26" s="9">
         <f t="shared" si="77"/>
-        <v>1.8233618233618232E-2</v>
-      </c>
-      <c r="M26" s="9">
+        <v>1.6690656294980552E-2</v>
+      </c>
+      <c r="Y26" s="9">
         <f t="shared" si="77"/>
-        <v>1.707865168539326E-2</v>
-      </c>
-      <c r="N26" s="9">
+        <v>1.7675221288203528E-2</v>
+      </c>
+      <c r="Z26" s="9">
         <f t="shared" si="77"/>
-        <v>1.9964645939482165E-2</v>
-      </c>
-      <c r="O26" s="9">
-        <f t="shared" ref="O26:R26" si="78">O8/O3</f>
-        <v>1.5036803364879074E-2</v>
-      </c>
-      <c r="P26" s="9">
-        <f t="shared" si="78"/>
-        <v>1.8032103397957057E-2</v>
-      </c>
-      <c r="Q26" s="9">
-        <f t="shared" si="78"/>
+        <v>1.7939423238271791E-2</v>
+      </c>
+      <c r="AA26" s="9">
+        <f t="shared" si="77"/>
         <v>0.02</v>
       </c>
-      <c r="R26" s="9">
-        <f t="shared" si="78"/>
+      <c r="AB26" s="9">
+        <f t="shared" si="77"/>
         <v>0.02</v>
       </c>
-      <c r="T26" s="9">
-        <f t="shared" ref="T26:AJ26" si="79">T8/T3</f>
-        <v>1.9758889324106715E-2</v>
-      </c>
-      <c r="U26" s="9">
-        <f t="shared" si="79"/>
-        <v>1.8676187860477891E-2</v>
-      </c>
-      <c r="V26" s="9">
-        <f t="shared" si="79"/>
-        <v>1.6718523127981746E-2</v>
-      </c>
-      <c r="W26" s="9">
-        <f t="shared" si="79"/>
-        <v>1.7229614466052541E-2</v>
-      </c>
-      <c r="X26" s="9">
-        <f t="shared" si="79"/>
-        <v>1.6690656294980552E-2</v>
-      </c>
-      <c r="Y26" s="9">
-        <f t="shared" si="79"/>
-        <v>1.7675221288203528E-2</v>
-      </c>
-      <c r="Z26" s="9">
-        <f t="shared" si="79"/>
-        <v>1.8313605563876657E-2</v>
-      </c>
-      <c r="AA26" s="9">
-        <f t="shared" si="79"/>
+      <c r="AC26" s="9">
+        <f t="shared" si="77"/>
         <v>0.02</v>
       </c>
-      <c r="AB26" s="9">
-        <f t="shared" si="79"/>
+      <c r="AD26" s="9">
+        <f t="shared" si="77"/>
         <v>0.02</v>
       </c>
-      <c r="AC26" s="9">
-        <f t="shared" si="79"/>
+      <c r="AE26" s="9">
+        <f t="shared" si="77"/>
         <v>0.02</v>
       </c>
-      <c r="AD26" s="9">
-        <f t="shared" si="79"/>
+      <c r="AF26" s="9">
+        <f t="shared" si="77"/>
         <v>0.02</v>
       </c>
-      <c r="AE26" s="9">
-        <f t="shared" si="79"/>
+      <c r="AG26" s="9">
+        <f t="shared" si="77"/>
+        <v>2.0000000000000004E-2</v>
+      </c>
+      <c r="AH26" s="9">
+        <f t="shared" si="77"/>
         <v>0.02</v>
       </c>
-      <c r="AF26" s="9">
-        <f t="shared" si="79"/>
+      <c r="AI26" s="9">
+        <f t="shared" si="77"/>
         <v>0.02</v>
       </c>
-      <c r="AG26" s="9">
-        <f t="shared" si="79"/>
-        <v>0.02</v>
-      </c>
-      <c r="AH26" s="9">
-        <f t="shared" si="79"/>
-        <v>0.02</v>
-      </c>
-      <c r="AI26" s="9">
-        <f t="shared" si="79"/>
-        <v>0.02</v>
-      </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000004E-2</v>
       </c>
       <c r="AM26" t="s">
@@ -4400,7 +4392,7 @@
       </c>
       <c r="AN26" s="3">
         <f>Main!D8</f>
-        <v>-5541</v>
+        <v>-4755</v>
       </c>
     </row>
     <row r="27" spans="1:147" x14ac:dyDescent="0.3">
@@ -4416,48 +4408,48 @@
         <v>0.14646464646464641</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:N27" si="80">H9/D9-1</f>
+        <f t="shared" ref="H27:N27" si="78">H9/D9-1</f>
         <v>0.13043478260869557</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>2.1739130434782705E-2</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>9.2920353982300918E-2</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>8.8105726872246715E-2</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>6.4102564102564097E-2</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>0.123404255319149</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>0.10931174089068829</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" ref="O27:O28" si="81">O9/K9-1</f>
+        <f t="shared" ref="O27:O28" si="79">O9/K9-1</f>
         <v>0.14170040485829949</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" ref="P27:P28" si="82">P9/L9-1</f>
+        <f t="shared" ref="P27:P28" si="80">P9/L9-1</f>
         <v>0.22489959839357421</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" ref="Q27:Q28" si="83">Q9/M9-1</f>
-        <v>0.15999999999999992</v>
+        <f t="shared" ref="Q27:Q28" si="81">Q9/M9-1</f>
+        <v>0.20075757575757569</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" ref="R27:R28" si="84">R9/N9-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="R27:R28" si="82">R9/N9-1</f>
+        <v>0.17999999999999994</v>
       </c>
       <c r="T27" s="9"/>
       <c r="U27" s="9">
@@ -4465,24 +4457,24 @@
         <v>0.16920731707317072</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" ref="V27:Z27" si="85">V9/U9-1</f>
+        <f t="shared" ref="V27:Z27" si="83">V9/U9-1</f>
         <v>4.8239895697522739E-2</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>7.0895522388059629E-2</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>9.5238095238095344E-2</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>9.6500530222693559E-2</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" si="85"/>
-        <v>0.16860735009671179</v>
+        <f t="shared" si="83"/>
+        <v>0.18696324951644105</v>
       </c>
       <c r="AA27" s="9"/>
       <c r="AB27" s="9"/>
@@ -4499,7 +4491,7 @@
       </c>
       <c r="AN27" s="3">
         <f>AN25+AN26</f>
-        <v>418910.95980651764</v>
+        <v>465981.38303071231</v>
       </c>
     </row>
     <row r="28" spans="1:147" x14ac:dyDescent="0.3">
@@ -4515,48 +4507,48 @@
         <v>0.33057851239669422</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" ref="H28:N28" si="86">H10/D10-1</f>
+        <f t="shared" ref="H28:N28" si="84">H10/D10-1</f>
         <v>-0.13230769230769235</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>8.6505190311418678E-2</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>0.21893491124260356</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>5.5900621118012417E-2</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>0.60283687943262421</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>0.21656050955414008</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>2.9126213592232997E-2</v>
       </c>
       <c r="O28" s="9">
+        <f t="shared" si="79"/>
+        <v>0.41470588235294126</v>
+      </c>
+      <c r="P28" s="9">
+        <f t="shared" si="80"/>
+        <v>-7.3008849557522071E-2</v>
+      </c>
+      <c r="Q28" s="9">
         <f t="shared" si="81"/>
-        <v>0.41470588235294126</v>
-      </c>
-      <c r="P28" s="9">
+        <v>0.26178010471204183</v>
+      </c>
+      <c r="R28" s="9">
         <f t="shared" si="82"/>
-        <v>-7.3008849557522071E-2</v>
-      </c>
-      <c r="Q28" s="9">
-        <f t="shared" si="83"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="R28" s="9">
-        <f t="shared" si="84"/>
-        <v>0.14999999999999991</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="T28" s="9"/>
       <c r="U28" s="9">
@@ -4564,63 +4556,63 @@
         <v>-8.361204013377932E-2</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" ref="V28:AJ28" si="87">V10/U10-1</f>
+        <f t="shared" ref="V28:AJ28" si="85">V10/U10-1</f>
         <v>-0.10127737226277367</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>0.21218274111675117</v>
       </c>
       <c r="X28" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>0.11390284757118918</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>0.2015037593984963</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" si="87"/>
-        <v>0.14324155193992483</v>
+        <f t="shared" si="85"/>
+        <v>0.18322903629536924</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
+        <v>9.000000000000008E-2</v>
+      </c>
+      <c r="AB28" s="9">
+        <f t="shared" si="85"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AB28" s="9">
-        <f t="shared" si="87"/>
+      <c r="AC28" s="9">
+        <f t="shared" si="85"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AC28" s="9">
-        <f t="shared" si="87"/>
+      <c r="AD28" s="9">
+        <f t="shared" si="85"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AD28" s="9">
-        <f t="shared" si="87"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AE28" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM28" t="s">
@@ -4628,7 +4620,7 @@
       </c>
       <c r="AN28" s="11">
         <f>AN27/AJ19</f>
-        <v>227.0397050601689</v>
+        <v>252.83851493798824</v>
       </c>
     </row>
     <row r="29" spans="1:147" x14ac:dyDescent="0.3">
@@ -4636,19 +4628,19 @@
         <v>45</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:F29" si="88">C11/C3</f>
+        <f t="shared" ref="C29:F29" si="86">C11/C3</f>
         <v>2.0966142513103841E-2</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>9.855670103092784E-2</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>3.8525748041607808E-4</v>
       </c>
       <c r="G29" s="9">
@@ -4656,115 +4648,115 @@
         <v>4.296875E-2</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" ref="H29:N29" si="89">H11/H3</f>
+        <f t="shared" ref="H29:N29" si="87">H11/H3</f>
         <v>0</v>
       </c>
       <c r="I29" s="9">
+        <f t="shared" si="87"/>
+        <v>5.6260002462144527E-2</v>
+      </c>
+      <c r="J29" s="9">
+        <f t="shared" si="87"/>
+        <v>1.4984318736206296E-2</v>
+      </c>
+      <c r="K29" s="9">
+        <f t="shared" si="87"/>
+        <v>1.0423905489923557E-3</v>
+      </c>
+      <c r="L29" s="9">
+        <f t="shared" si="87"/>
+        <v>4.9002849002849E-2</v>
+      </c>
+      <c r="M29" s="9">
+        <f t="shared" si="87"/>
+        <v>1.4606741573033708E-3</v>
+      </c>
+      <c r="N29" s="9">
+        <f t="shared" si="87"/>
+        <v>1.0398253093480295E-3</v>
+      </c>
+      <c r="O29" s="9">
+        <f t="shared" ref="O29:R29" si="88">O11/O3</f>
+        <v>4.6267087276550996E-3</v>
+      </c>
+      <c r="P29" s="9">
+        <f t="shared" si="88"/>
+        <v>0.10423181154888472</v>
+      </c>
+      <c r="Q29" s="9">
+        <f t="shared" si="88"/>
+        <v>6.0460086511993708E-2</v>
+      </c>
+      <c r="R29" s="9">
+        <f t="shared" si="88"/>
+        <v>0.04</v>
+      </c>
+      <c r="T29" s="9">
+        <f t="shared" ref="T29:AJ29" si="89">T11/T3</f>
+        <v>1.7408713060886975E-2</v>
+      </c>
+      <c r="U29" s="9">
         <f t="shared" si="89"/>
-        <v>5.6260002462144527E-2</v>
-      </c>
-      <c r="J29" s="9">
+        <v>5.0352467270896274E-4</v>
+      </c>
+      <c r="V29" s="9">
         <f t="shared" si="89"/>
-        <v>1.4984318736206296E-2</v>
-      </c>
-      <c r="K29" s="9">
+        <v>1.2445550715619165E-4</v>
+      </c>
+      <c r="W29" s="9">
         <f t="shared" si="89"/>
-        <v>1.0423905489923557E-3</v>
-      </c>
-      <c r="L29" s="9">
+        <v>2.9614466052541796E-2</v>
+      </c>
+      <c r="X29" s="9">
         <f t="shared" si="89"/>
-        <v>4.9002849002849E-2</v>
-      </c>
-      <c r="M29" s="9">
+        <v>2.838942823017793E-2</v>
+      </c>
+      <c r="Y29" s="9">
         <f t="shared" si="89"/>
-        <v>1.4606741573033708E-3</v>
-      </c>
-      <c r="N29" s="9">
+        <v>1.2859767299448868E-2</v>
+      </c>
+      <c r="Z29" s="9">
         <f t="shared" si="89"/>
-        <v>1.0398253093480295E-3</v>
-      </c>
-      <c r="O29" s="9">
-        <f t="shared" ref="O29:R29" si="90">O11/O3</f>
-        <v>4.6267087276550996E-3</v>
-      </c>
-      <c r="P29" s="9">
-        <f t="shared" si="90"/>
-        <v>0.10423181154888472</v>
-      </c>
-      <c r="Q29" s="9">
-        <f t="shared" si="90"/>
-        <v>0.10214504596527069</v>
-      </c>
-      <c r="R29" s="9">
-        <f t="shared" si="90"/>
-        <v>0.04</v>
-      </c>
-      <c r="T29" s="9">
-        <f t="shared" ref="T29:AJ29" si="91">T11/T3</f>
-        <v>1.7408713060886975E-2</v>
-      </c>
-      <c r="U29" s="9">
-        <f t="shared" si="91"/>
-        <v>5.0352467270896274E-4</v>
-      </c>
-      <c r="V29" s="9">
-        <f t="shared" si="91"/>
-        <v>1.2445550715619165E-4</v>
-      </c>
-      <c r="W29" s="9">
-        <f t="shared" si="91"/>
-        <v>2.9614466052541796E-2</v>
-      </c>
-      <c r="X29" s="9">
-        <f t="shared" si="91"/>
-        <v>2.838942823017793E-2</v>
-      </c>
-      <c r="Y29" s="9">
-        <f t="shared" si="91"/>
-        <v>1.2859767299448868E-2</v>
-      </c>
-      <c r="Z29" s="9">
-        <f t="shared" si="91"/>
-        <v>6.2668326179512707E-2</v>
+        <v>5.2184670827107323E-2</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="89"/>
+        <v>0.02</v>
+      </c>
+      <c r="AB29" s="9">
+        <f t="shared" si="89"/>
         <v>0.01</v>
       </c>
-      <c r="AB29" s="9">
-        <f t="shared" si="91"/>
+      <c r="AC29" s="9">
+        <f t="shared" si="89"/>
         <v>0.01</v>
       </c>
-      <c r="AC29" s="9">
-        <f t="shared" si="91"/>
+      <c r="AD29" s="9">
+        <f t="shared" si="89"/>
         <v>0.01</v>
       </c>
-      <c r="AD29" s="9">
-        <f t="shared" si="91"/>
+      <c r="AE29" s="9">
+        <f t="shared" si="89"/>
         <v>0.01</v>
       </c>
-      <c r="AE29" s="9">
-        <f t="shared" si="91"/>
+      <c r="AF29" s="9">
+        <f t="shared" si="89"/>
         <v>0.01</v>
       </c>
-      <c r="AF29" s="9">
-        <f t="shared" si="91"/>
+      <c r="AG29" s="9">
+        <f t="shared" si="89"/>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="AH29" s="9">
+        <f t="shared" si="89"/>
         <v>0.01</v>
       </c>
-      <c r="AG29" s="9">
-        <f t="shared" si="91"/>
+      <c r="AI29" s="9">
+        <f t="shared" si="89"/>
         <v>0.01</v>
       </c>
-      <c r="AH29" s="9">
-        <f t="shared" si="91"/>
-        <v>0.01</v>
-      </c>
-      <c r="AI29" s="9">
-        <f t="shared" si="91"/>
-        <v>0.01</v>
-      </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="89"/>
         <v>1.0000000000000002E-2</v>
       </c>
       <c r="AM29" t="s">
@@ -4772,7 +4764,7 @@
       </c>
       <c r="AN29" s="11">
         <f>Main!D3</f>
-        <v>357.98</v>
+        <v>344.45</v>
       </c>
     </row>
     <row r="30" spans="1:147" x14ac:dyDescent="0.3">
@@ -4780,19 +4772,19 @@
         <v>46</v>
       </c>
       <c r="C30" s="9">
-        <f t="shared" ref="C30:F30" si="92">C13/C3</f>
+        <f t="shared" ref="C30:F30" si="90">C13/C3</f>
         <v>0.67658308542286438</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>0.66796494644595905</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>0.57017182130584187</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>0.6532682676255297</v>
       </c>
       <c r="G30" s="9">
@@ -4800,123 +4792,123 @@
         <v>0.64138104838709675</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" ref="H30:N30" si="93">H13/H3</f>
+        <f t="shared" ref="H30:N30" si="91">H13/H3</f>
         <v>0.66825297432686281</v>
       </c>
       <c r="I30" s="9">
+        <f t="shared" si="91"/>
+        <v>0.6184907054044072</v>
+      </c>
+      <c r="J30" s="9">
+        <f t="shared" si="91"/>
+        <v>0.64467417818561967</v>
+      </c>
+      <c r="K30" s="9">
+        <f t="shared" si="91"/>
+        <v>0.68959925874449846</v>
+      </c>
+      <c r="L30" s="9">
+        <f t="shared" si="91"/>
+        <v>0.61014245014245017</v>
+      </c>
+      <c r="M30" s="9">
+        <f t="shared" si="91"/>
+        <v>0.66719101123595503</v>
+      </c>
+      <c r="N30" s="9">
+        <f t="shared" si="91"/>
+        <v>0.660185088905064</v>
+      </c>
+      <c r="O30" s="9">
+        <f t="shared" ref="O30:R30" si="92">O13/O3</f>
+        <v>0.65552050473186119</v>
+      </c>
+      <c r="P30" s="9">
+        <f t="shared" si="92"/>
+        <v>0.56649989576818849</v>
+      </c>
+      <c r="Q30" s="9">
+        <f t="shared" si="92"/>
+        <v>0.60725521038143926</v>
+      </c>
+      <c r="R30" s="9">
+        <f t="shared" si="92"/>
+        <v>0.60150254757200783</v>
+      </c>
+      <c r="T30" s="9">
+        <f t="shared" ref="T30:AJ30" si="93">T13/T3</f>
+        <v>0.65287026156591377</v>
+      </c>
+      <c r="U30" s="9">
         <f t="shared" si="93"/>
-        <v>0.6184907054044072</v>
-      </c>
-      <c r="J30" s="9">
+        <v>0.64455735603771858</v>
+      </c>
+      <c r="V30" s="9">
         <f t="shared" si="93"/>
-        <v>0.64467417818561967</v>
-      </c>
-      <c r="K30" s="9">
+        <v>0.65563161169881767</v>
+      </c>
+      <c r="W30" s="9">
         <f t="shared" si="93"/>
-        <v>0.68959925874449846</v>
-      </c>
-      <c r="L30" s="9">
+        <v>0.64186284544524053</v>
+      </c>
+      <c r="X30" s="9">
         <f t="shared" si="93"/>
-        <v>0.61014245014245017</v>
-      </c>
-      <c r="M30" s="9">
+        <v>0.64312620586163594</v>
+      </c>
+      <c r="Y30" s="9">
         <f t="shared" si="93"/>
-        <v>0.66719101123595503</v>
-      </c>
-      <c r="N30" s="9">
+        <v>0.65676668707899566</v>
+      </c>
+      <c r="Z30" s="9">
         <f t="shared" si="93"/>
-        <v>0.660185088905064</v>
-      </c>
-      <c r="O30" s="9">
-        <f t="shared" ref="O30:R30" si="94">O13/O3</f>
-        <v>0.65552050473186119</v>
-      </c>
-      <c r="P30" s="9">
-        <f t="shared" si="94"/>
-        <v>0.56649989576818849</v>
-      </c>
-      <c r="Q30" s="9">
-        <f t="shared" si="94"/>
-        <v>0.55922982635342178</v>
-      </c>
-      <c r="R30" s="9">
-        <f t="shared" si="94"/>
-        <v>0.59975889658014081</v>
-      </c>
-      <c r="T30" s="9">
-        <f t="shared" ref="T30:AJ30" si="95">T13/T3</f>
-        <v>0.65287026156591377</v>
-      </c>
-      <c r="U30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.64455735603771858</v>
-      </c>
-      <c r="V30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.65563161169881767</v>
-      </c>
-      <c r="W30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.64186284544524053</v>
-      </c>
-      <c r="X30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.64312620586163594</v>
-      </c>
-      <c r="Y30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.65676668707899566</v>
-      </c>
-      <c r="Z30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.59502296717119829</v>
+        <v>0.60740589067256912</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.69200497684035178</v>
+        <f t="shared" si="93"/>
+        <v>0.68071647742255104</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.69308828116064514</v>
+        <f t="shared" si="93"/>
+        <v>0.69201149653614824</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.69352401383179896</v>
+        <f t="shared" si="93"/>
+        <v>0.69330651564974533</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.69352401383179896</v>
+        <f t="shared" si="93"/>
+        <v>0.694589082656481</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.69417573918638931</v>
+        <f t="shared" si="93"/>
+        <v>0.69585919755635528</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.69482107507671864</v>
+        <f t="shared" si="93"/>
+        <v>0.69648802895286155</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.69546008414459404</v>
+        <f t="shared" si="93"/>
+        <v>0.6971106953356766</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.69609282841768627</v>
+        <f t="shared" si="93"/>
+        <v>0.69772725714611106</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.69671936931555212</v>
+        <f t="shared" si="93"/>
+        <v>0.69833777423291399</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="95"/>
-        <v>0.6973397676555958</v>
+        <f t="shared" si="93"/>
+        <v>0.69894230585808148</v>
       </c>
       <c r="AM30" s="6" t="s">
         <v>55</v>
       </c>
       <c r="AN30" s="10">
         <f>AN28/AN29-1</f>
-        <v>-0.36577544818099084</v>
+        <v>-0.26596453784877849</v>
       </c>
     </row>
     <row r="31" spans="1:147" x14ac:dyDescent="0.3">
@@ -4924,19 +4916,19 @@
         <v>23</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:F31" si="96">C17/C16</f>
+        <f t="shared" ref="C31:F31" si="94">C17/C16</f>
         <v>0.171125178680825</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>0.19704975781594011</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>0.10916688430399582</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>0.19063270336894</v>
       </c>
       <c r="G31" s="9">
@@ -4944,115 +4936,115 @@
         <v>0.16033755274261605</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" ref="H31:N31" si="97">H17/H16</f>
+        <f t="shared" ref="H31:N31" si="95">H17/H16</f>
         <v>0.19344448654793484</v>
       </c>
       <c r="I31" s="9">
+        <f t="shared" si="95"/>
+        <v>0.19238243295763699</v>
+      </c>
+      <c r="J31" s="9">
+        <f t="shared" si="95"/>
+        <v>0.16944641589779985</v>
+      </c>
+      <c r="K31" s="9">
+        <f t="shared" si="95"/>
+        <v>0.1906653426017875</v>
+      </c>
+      <c r="L31" s="9">
+        <f t="shared" si="95"/>
+        <v>0.15418102666424813</v>
+      </c>
+      <c r="M31" s="9">
+        <f t="shared" si="95"/>
+        <v>0.18650859909834697</v>
+      </c>
+      <c r="N31" s="9">
+        <f t="shared" si="95"/>
+        <v>0.16541117388575016</v>
+      </c>
+      <c r="O31" s="9">
+        <f t="shared" ref="O31:R31" si="96">O17/O16</f>
+        <v>0.17435483870967741</v>
+      </c>
+      <c r="P31" s="9">
+        <f t="shared" si="96"/>
+        <v>0.15833026848105922</v>
+      </c>
+      <c r="Q31" s="9">
+        <f t="shared" si="96"/>
+        <v>0.16753513342807516</v>
+      </c>
+      <c r="R31" s="9">
+        <f t="shared" si="96"/>
+        <v>0.17</v>
+      </c>
+      <c r="T31" s="9">
+        <f t="shared" ref="T31:AJ31" si="97">T17/T16</f>
+        <v>0.18839021768341843</v>
+      </c>
+      <c r="U31" s="9">
         <f t="shared" si="97"/>
-        <v>0.19238243295763699</v>
-      </c>
-      <c r="J31" s="9">
+        <v>0.212037708484409</v>
+      </c>
+      <c r="V31" s="9">
         <f t="shared" si="97"/>
-        <v>0.16944641589779985</v>
-      </c>
-      <c r="K31" s="9">
+        <v>0.23358027765672665</v>
+      </c>
+      <c r="W31" s="9">
         <f t="shared" si="97"/>
-        <v>0.1906653426017875</v>
-      </c>
-      <c r="L31" s="9">
+        <v>0.16977282752536391</v>
+      </c>
+      <c r="X31" s="9">
         <f t="shared" si="97"/>
-        <v>0.15418102666424813</v>
-      </c>
-      <c r="M31" s="9">
+        <v>0.17892285021628559</v>
+      </c>
+      <c r="Y31" s="9">
         <f t="shared" si="97"/>
-        <v>0.18650859909834697</v>
-      </c>
-      <c r="N31" s="9">
+        <v>0.17448569994982438</v>
+      </c>
+      <c r="Z31" s="9">
         <f t="shared" si="97"/>
-        <v>0.16541117388575016</v>
-      </c>
-      <c r="O31" s="9">
-        <f t="shared" ref="O31:R31" si="98">O17/O16</f>
-        <v>0.17435483870967741</v>
-      </c>
-      <c r="P31" s="9">
-        <f t="shared" si="98"/>
-        <v>0.15833026848105922</v>
-      </c>
-      <c r="Q31" s="9">
-        <f t="shared" si="98"/>
-        <v>0.17</v>
-      </c>
-      <c r="R31" s="9">
-        <f t="shared" si="98"/>
-        <v>0.17000000000000004</v>
-      </c>
-      <c r="T31" s="9">
-        <f t="shared" ref="T31:AJ31" si="99">T17/T16</f>
-        <v>0.18839021768341843</v>
-      </c>
-      <c r="U31" s="9">
-        <f t="shared" si="99"/>
-        <v>0.212037708484409</v>
-      </c>
-      <c r="V31" s="9">
-        <f t="shared" si="99"/>
-        <v>0.23358027765672665</v>
-      </c>
-      <c r="W31" s="9">
-        <f t="shared" si="99"/>
-        <v>0.16977282752536391</v>
-      </c>
-      <c r="X31" s="9">
-        <f t="shared" si="99"/>
-        <v>0.17892285021628559</v>
-      </c>
-      <c r="Y31" s="9">
-        <f t="shared" si="99"/>
-        <v>0.17448569994982438</v>
-      </c>
-      <c r="Z31" s="9">
-        <f t="shared" si="99"/>
-        <v>0.16843616586472632</v>
+        <v>0.16787163667910246</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" si="99"/>
-        <v>0.18000000000000002</v>
+        <f t="shared" si="97"/>
+        <v>0.18</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AM31" t="s">
@@ -5071,132 +5063,132 @@
         <v>0.57501062473438169</v>
       </c>
       <c r="D32" s="9">
-        <f t="shared" ref="D32:N32" si="100">D18/D3</f>
+        <f t="shared" ref="D32:N32" si="98">D18/D3</f>
         <v>0.50730282375851998</v>
       </c>
       <c r="E32" s="9">
+        <f t="shared" si="98"/>
+        <v>0.46886597938144331</v>
+      </c>
+      <c r="F32" s="9">
+        <f t="shared" si="98"/>
+        <v>0.50597149094644922</v>
+      </c>
+      <c r="G32" s="9">
+        <f t="shared" si="98"/>
+        <v>0.52658770161290325</v>
+      </c>
+      <c r="H32" s="9">
+        <f t="shared" si="98"/>
+        <v>0.53312460864120226</v>
+      </c>
+      <c r="I32" s="9">
+        <f t="shared" si="98"/>
+        <v>0.5116336328942509</v>
+      </c>
+      <c r="J32" s="9">
+        <f t="shared" si="98"/>
+        <v>0.54373330235799744</v>
+      </c>
+      <c r="K32" s="9">
+        <f t="shared" si="98"/>
+        <v>0.56636553161918002</v>
+      </c>
+      <c r="L32" s="9">
+        <f t="shared" si="98"/>
+        <v>0.53139601139601145</v>
+      </c>
+      <c r="M32" s="9">
+        <f t="shared" si="98"/>
+        <v>0.54741573033707869</v>
+      </c>
+      <c r="N32" s="9">
+        <f t="shared" si="98"/>
+        <v>0.5529790995112821</v>
+      </c>
+      <c r="O32" s="9">
+        <f t="shared" ref="O32:R32" si="99">O18/O3</f>
+        <v>0.5382754994742377</v>
+      </c>
+      <c r="P32" s="9">
+        <f t="shared" si="99"/>
+        <v>0.47706900145924536</v>
+      </c>
+      <c r="Q32" s="9">
+        <f t="shared" si="99"/>
+        <v>0.51828548957923715</v>
+      </c>
+      <c r="R32" s="9">
+        <f t="shared" si="99"/>
+        <v>0.50040299172596137</v>
+      </c>
+      <c r="T32" s="9">
+        <f t="shared" ref="T32:AJ32" si="100">T18/T3</f>
+        <v>0.52574313443878662</v>
+      </c>
+      <c r="U32" s="9">
         <f t="shared" si="100"/>
-        <v>0.46886597938144331</v>
-      </c>
-      <c r="F32" s="9">
+        <v>0.49739082669596263</v>
+      </c>
+      <c r="V32" s="9">
         <f t="shared" si="100"/>
-        <v>0.50597149094644922</v>
-      </c>
-      <c r="G32" s="9">
+        <v>0.51072391619995849</v>
+      </c>
+      <c r="W32" s="9">
         <f t="shared" si="100"/>
-        <v>0.52658770161290325</v>
-      </c>
-      <c r="H32" s="9">
+        <v>0.51371545547594677</v>
+      </c>
+      <c r="X32" s="9">
         <f t="shared" si="100"/>
-        <v>0.53312460864120226</v>
-      </c>
-      <c r="I32" s="9">
+        <v>0.52898661684990655</v>
+      </c>
+      <c r="Y32" s="9">
         <f t="shared" si="100"/>
-        <v>0.5116336328942509</v>
-      </c>
-      <c r="J32" s="9">
+        <v>0.54954628959527918</v>
+      </c>
+      <c r="Z32" s="9">
         <f t="shared" si="100"/>
-        <v>0.54373330235799744</v>
-      </c>
-      <c r="K32" s="9">
+        <v>0.50834869793123305</v>
+      </c>
+      <c r="AA32" s="9">
         <f t="shared" si="100"/>
-        <v>0.56636553161918002</v>
-      </c>
-      <c r="L32" s="9">
+        <v>0.56063184795597809</v>
+      </c>
+      <c r="AB32" s="9">
         <f t="shared" si="100"/>
-        <v>0.53139601139601145</v>
-      </c>
-      <c r="M32" s="9">
+        <v>0.56955272184080263</v>
+      </c>
+      <c r="AC32" s="9">
         <f t="shared" si="100"/>
-        <v>0.54741573033707869</v>
-      </c>
-      <c r="N32" s="9">
+        <v>0.57033442107118171</v>
+      </c>
+      <c r="AD32" s="9">
         <f t="shared" si="100"/>
-        <v>0.5529790995112821</v>
-      </c>
-      <c r="O32" s="9">
-        <f t="shared" ref="O32:R32" si="101">O18/O3</f>
-        <v>0.5382754994742377</v>
-      </c>
-      <c r="P32" s="9">
-        <f t="shared" si="101"/>
-        <v>0.47706900145924536</v>
-      </c>
-      <c r="Q32" s="9">
-        <f t="shared" si="101"/>
-        <v>0.46543246169560759</v>
-      </c>
-      <c r="R32" s="9">
-        <f t="shared" si="101"/>
-        <v>0.49900977435790783</v>
-      </c>
-      <c r="T32" s="9">
-        <f t="shared" ref="T32:AJ32" si="102">T18/T3</f>
-        <v>0.52574313443878662</v>
-      </c>
-      <c r="U32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.49739082669596263</v>
-      </c>
-      <c r="V32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.51072391619995849</v>
-      </c>
-      <c r="W32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.51371545547594677</v>
-      </c>
-      <c r="X32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.52898661684990655</v>
-      </c>
-      <c r="Y32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.54954628959527918</v>
-      </c>
-      <c r="Z32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.49477835805716536</v>
-      </c>
-      <c r="AA32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.56714660741878986</v>
-      </c>
-      <c r="AB32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.56777381894951029</v>
-      </c>
-      <c r="AC32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.56786953545121543</v>
-      </c>
-      <c r="AD32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.56760247497039562</v>
+        <v>0.57113537024152017</v>
       </c>
       <c r="AE32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.56786975044951638</v>
+        <f t="shared" si="100"/>
+        <v>0.57194816694630446</v>
       </c>
       <c r="AF32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.56813168206809961</v>
+        <f t="shared" si="100"/>
+        <v>0.57225052610443683</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.56838829551583026</v>
+        <f t="shared" si="100"/>
+        <v>0.57254795909637801</v>
       </c>
       <c r="AH32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.56863961596875767</v>
+        <f t="shared" si="100"/>
+        <v>0.57284049498394607</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.56888566809176555</v>
+        <f t="shared" si="100"/>
+        <v>0.57312816235547226</v>
       </c>
       <c r="AJ32" s="9">
-        <f t="shared" si="102"/>
-        <v>0.5691264760409912</v>
+        <f t="shared" si="100"/>
+        <v>0.57341098932859225</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/V.xlsx
+++ b/Financial Analysis/V.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DB0A94-5CF1-47C1-AED5-A640B0ADFEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A69309-21A2-47D3-87CF-11AB30DFA74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{0E0749A9-7B4C-463E-A44A-39D457257264}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0E0749A9-7B4C-463E-A44A-39D457257264}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -315,14 +315,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -339,7 +339,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12954000" y="0"/>
+          <a:off x="13685520" y="0"/>
           <a:ext cx="0" cy="6309360"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -365,13 +365,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
@@ -736,17 +736,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="11">
-        <v>344.45</v>
+        <v>345.94</v>
       </c>
       <c r="E3" s="2">
-        <v>45868</v>
+        <v>45959</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45868</v>
+        <v>45959</v>
       </c>
       <c r="G3" s="2">
-        <v>45958</v>
+        <v>46044</v>
       </c>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.3">
@@ -754,11 +754,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="3">
-        <f>1709+5+120+9</f>
-        <v>1843</v>
+        <f>1696+5+120+9</f>
+        <v>1830</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="3:7" x14ac:dyDescent="0.3">
@@ -767,7 +767,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>634821.35</v>
+        <v>633070.19999999995</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -809,7 +809,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>639576.35</v>
+        <v>637825.19999999995</v>
       </c>
     </row>
   </sheetData>
@@ -820,18 +820,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F83A1B6C-1CC8-4332-BFEF-F20E1EFE721D}">
-  <dimension ref="A1:EQ32"/>
+  <dimension ref="A1:EU32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.5546875" customWidth="1"/>
     <col min="3" max="14" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="10.5546875" customWidth="1"/>
-    <col min="20" max="36" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="17.6640625" customWidth="1"/>
+    <col min="15" max="22" width="10.5546875" customWidth="1"/>
+    <col min="24" max="40" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
       <c r="C1" s="8">
         <v>44561</v>
       </c>
@@ -880,59 +880,63 @@
       <c r="R1" s="8">
         <v>45930</v>
       </c>
-      <c r="T1" s="8">
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="X1" s="8">
         <v>43738</v>
       </c>
-      <c r="U1" s="8">
+      <c r="Y1" s="8">
         <v>44104</v>
       </c>
-      <c r="V1" s="8">
+      <c r="Z1" s="8">
         <v>44469</v>
       </c>
-      <c r="W1" s="8">
+      <c r="AA1" s="8">
         <v>44834</v>
       </c>
-      <c r="X1" s="8">
+      <c r="AB1" s="8">
         <v>45199</v>
       </c>
-      <c r="Y1" s="8">
+      <c r="AC1" s="8">
         <v>45565</v>
       </c>
-      <c r="Z1" s="8">
+      <c r="AD1" s="8">
         <v>45930</v>
       </c>
-      <c r="AA1" s="8">
+      <c r="AE1" s="8">
         <v>46295</v>
       </c>
-      <c r="AB1" s="8">
+      <c r="AF1" s="8">
         <v>46660</v>
       </c>
-      <c r="AC1" s="8">
+      <c r="AG1" s="8">
         <v>47026</v>
       </c>
-      <c r="AD1" s="8">
+      <c r="AH1" s="8">
         <v>47391</v>
       </c>
-      <c r="AE1" s="8">
+      <c r="AI1" s="8">
         <v>47756</v>
       </c>
-      <c r="AF1" s="8">
+      <c r="AJ1" s="8">
         <v>48121</v>
       </c>
-      <c r="AG1" s="8">
+      <c r="AK1" s="8">
         <v>48487</v>
       </c>
-      <c r="AH1" s="8">
+      <c r="AL1" s="8">
         <v>48852</v>
       </c>
-      <c r="AI1" s="8">
+      <c r="AM1" s="8">
         <v>49217</v>
       </c>
-      <c r="AJ1" s="8">
+      <c r="AN1" s="8">
         <v>49582</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.3">
       <c r="C2" s="4" t="s">
         <v>26</v>
       </c>
@@ -981,59 +985,63 @@
       <c r="R2" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="T2">
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="X2">
         <v>2019</v>
       </c>
-      <c r="U2">
+      <c r="Y2">
         <v>2020</v>
       </c>
-      <c r="V2">
+      <c r="Z2">
         <v>2021</v>
       </c>
-      <c r="W2">
+      <c r="AA2">
         <v>2022</v>
       </c>
-      <c r="X2">
+      <c r="AB2">
         <v>2023</v>
       </c>
-      <c r="Y2">
+      <c r="AC2">
         <v>2024</v>
       </c>
-      <c r="Z2">
+      <c r="AD2">
         <v>2025</v>
       </c>
-      <c r="AA2">
+      <c r="AE2">
         <v>2026</v>
       </c>
-      <c r="AB2">
+      <c r="AF2">
         <v>2027</v>
       </c>
-      <c r="AC2">
+      <c r="AG2">
         <v>2028</v>
       </c>
-      <c r="AD2">
+      <c r="AH2">
         <v>2029</v>
       </c>
-      <c r="AE2">
+      <c r="AI2">
         <v>2030</v>
       </c>
-      <c r="AF2">
+      <c r="AJ2">
         <v>2031</v>
       </c>
-      <c r="AG2">
+      <c r="AK2">
         <v>2032</v>
       </c>
-      <c r="AH2">
+      <c r="AL2">
         <v>2033</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <v>2034</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3"/>
       <c r="B3" s="6" t="s">
         <v>10</v>
@@ -1084,76 +1092,79 @@
         <v>10172</v>
       </c>
       <c r="R3" s="7">
-        <f>N3*1.12</f>
-        <v>10771.04</v>
-      </c>
-      <c r="T3" s="7">
+        <v>10724</v>
+      </c>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="X3" s="7">
         <v>22977</v>
       </c>
-      <c r="U3" s="7">
+      <c r="Y3" s="7">
         <v>21846</v>
       </c>
-      <c r="V3" s="7">
+      <c r="Z3" s="7">
         <v>24105</v>
       </c>
-      <c r="W3" s="7">
+      <c r="AA3" s="7">
         <f>SUM(C3:F3)</f>
         <v>29310</v>
       </c>
-      <c r="X3" s="7">
+      <c r="AB3" s="7">
         <f>SUM(G3:J3)</f>
         <v>32653</v>
       </c>
-      <c r="Y3" s="7">
+      <c r="AC3" s="7">
         <f>SUM(K3:N3)</f>
         <v>35926</v>
       </c>
-      <c r="Z3" s="7">
+      <c r="AD3" s="7">
         <f>SUM(O3:R3)</f>
-        <v>40047.040000000001</v>
-      </c>
-      <c r="AA3" s="7">
-        <f>Z3*1.09</f>
-        <v>43651.273600000008</v>
-      </c>
-      <c r="AB3" s="7">
-        <f>AA3*1.07</f>
-        <v>46706.862752000008</v>
-      </c>
-      <c r="AC3" s="7">
-        <f>AB3*1.05</f>
-        <v>49042.205889600009</v>
-      </c>
-      <c r="AD3" s="7">
-        <f>AC3*1.04</f>
-        <v>51003.894125184008</v>
+        <v>40000</v>
       </c>
       <c r="AE3" s="7">
-        <f>AD3*1.03</f>
-        <v>52534.010948939533</v>
+        <f>AD3*1.09</f>
+        <v>43600</v>
       </c>
       <c r="AF3" s="7">
-        <f t="shared" ref="AD3:AJ3" si="0">AE3*1.02</f>
-        <v>53584.691167918325</v>
+        <f>AE3*1.07</f>
+        <v>46652</v>
       </c>
       <c r="AG3" s="7">
+        <f>AF3*1.05</f>
+        <v>48984.6</v>
+      </c>
+      <c r="AH3" s="7">
+        <f>AG3*1.04</f>
+        <v>50943.983999999997</v>
+      </c>
+      <c r="AI3" s="7">
+        <f>AH3*1.03</f>
+        <v>52472.303520000001</v>
+      </c>
+      <c r="AJ3" s="7">
+        <f t="shared" ref="AJ3:AN3" si="0">AI3*1.02</f>
+        <v>53521.749590400002</v>
+      </c>
+      <c r="AK3" s="7">
         <f t="shared" si="0"/>
-        <v>54656.384991276689</v>
-      </c>
-      <c r="AH3" s="7">
+        <v>54592.184582208007</v>
+      </c>
+      <c r="AL3" s="7">
         <f t="shared" si="0"/>
-        <v>55749.512691102223</v>
-      </c>
-      <c r="AI3" s="7">
+        <v>55684.028273852171</v>
+      </c>
+      <c r="AM3" s="7">
         <f t="shared" si="0"/>
-        <v>56864.502944924272</v>
-      </c>
-      <c r="AJ3" s="7">
+        <v>56797.708839329214</v>
+      </c>
+      <c r="AN3" s="7">
         <f t="shared" si="0"/>
-        <v>58001.793003822757</v>
+        <v>57933.663016115803</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -1203,214 +1214,221 @@
         <v>1749</v>
       </c>
       <c r="R4" s="3">
-        <f t="shared" ref="Q4:R4" si="1">R3-R5</f>
-        <v>1938.7872000000007</v>
-      </c>
-      <c r="T4" s="3">
+        <v>1742</v>
+      </c>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="X4" s="3">
         <v>3444</v>
       </c>
-      <c r="U4" s="3">
+      <c r="Y4" s="3">
         <v>3785</v>
       </c>
-      <c r="V4" s="3">
+      <c r="Z4" s="3">
         <v>4240</v>
       </c>
-      <c r="W4" s="3">
+      <c r="AA4" s="3">
         <f>SUM(C4:F4)</f>
         <v>4990</v>
       </c>
-      <c r="X4" s="3">
+      <c r="AB4" s="3">
         <f>SUM(G4:J4)</f>
         <v>5831</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="AC4" s="3">
         <f>SUM(K4:N4)</f>
         <v>6264</v>
       </c>
-      <c r="Z4" s="3">
+      <c r="AD4" s="3">
         <f>SUM(O4:R4)</f>
-        <v>7157.7872000000007</v>
-      </c>
-      <c r="AA4" s="3">
-        <f t="shared" ref="AA4:AJ4" si="2">AA3-AA5</f>
-        <v>7420.7165120000063</v>
-      </c>
-      <c r="AB4" s="3">
-        <f t="shared" si="2"/>
-        <v>7940.1666678399997</v>
-      </c>
-      <c r="AC4" s="3">
-        <f t="shared" si="2"/>
-        <v>8337.1750012320044</v>
-      </c>
-      <c r="AD4" s="3">
-        <f t="shared" si="2"/>
-        <v>8670.6620012812855</v>
+        <v>6961</v>
       </c>
       <c r="AE4" s="3">
-        <f t="shared" si="2"/>
-        <v>8930.7818613197232</v>
+        <f t="shared" ref="AE4:AN4" si="1">AE3-AE5</f>
+        <v>6976</v>
       </c>
       <c r="AF4" s="3">
-        <f t="shared" si="2"/>
-        <v>9109.3974985461173</v>
+        <f t="shared" si="1"/>
+        <v>7464.32</v>
       </c>
       <c r="AG4" s="3">
-        <f t="shared" si="2"/>
-        <v>9291.5854485170421</v>
+        <f t="shared" si="1"/>
+        <v>7837.5360000000001</v>
       </c>
       <c r="AH4" s="3">
-        <f t="shared" si="2"/>
-        <v>9477.4171574873835</v>
+        <f t="shared" si="1"/>
+        <v>8151.0374400000001</v>
       </c>
       <c r="AI4" s="3">
-        <f t="shared" si="2"/>
-        <v>9666.9655006371249</v>
+        <f t="shared" si="1"/>
+        <v>8395.5685632000022</v>
       </c>
       <c r="AJ4" s="3">
-        <f t="shared" si="2"/>
-        <v>9860.3048106498682</v>
+        <f t="shared" si="1"/>
+        <v>8563.4799344640051</v>
+      </c>
+      <c r="AK4" s="3">
+        <f t="shared" si="1"/>
+        <v>8734.7495331532846</v>
+      </c>
+      <c r="AL4" s="3">
+        <f t="shared" si="1"/>
+        <v>8909.4445238163462</v>
+      </c>
+      <c r="AM4" s="3">
+        <f t="shared" si="1"/>
+        <v>9087.6334142926789</v>
+      </c>
+      <c r="AN4" s="3">
+        <f t="shared" si="1"/>
+        <v>9269.3860825785305</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5"/>
       <c r="B5" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="7">
-        <f t="shared" ref="C5:N5" si="3">C3-C4</f>
+        <f t="shared" ref="C5:N5" si="2">C3-C4</f>
         <v>5934</v>
       </c>
       <c r="D5" s="7">
+        <f t="shared" si="2"/>
+        <v>5963</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" si="2"/>
+        <v>5992</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" si="2"/>
+        <v>6431</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="2"/>
+        <v>6599</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" si="2"/>
+        <v>6470</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="2"/>
+        <v>6642</v>
+      </c>
+      <c r="J5" s="7">
+        <f t="shared" si="2"/>
+        <v>7111</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="2"/>
+        <v>7155</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="2"/>
+        <v>7172</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="2"/>
+        <v>7327</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="2"/>
+        <v>8008</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" ref="O5:R5" si="3">O3-O4</f>
+        <v>7697</v>
+      </c>
+      <c r="P5" s="7">
         <f t="shared" si="3"/>
-        <v>5963</v>
-      </c>
-      <c r="E5" s="7">
+        <v>7937</v>
+      </c>
+      <c r="Q5" s="7">
         <f t="shared" si="3"/>
-        <v>5992</v>
-      </c>
-      <c r="F5" s="7">
+        <v>8423</v>
+      </c>
+      <c r="R5" s="7">
         <f t="shared" si="3"/>
-        <v>6431</v>
-      </c>
-      <c r="G5" s="7">
-        <f t="shared" si="3"/>
-        <v>6599</v>
-      </c>
-      <c r="H5" s="7">
-        <f t="shared" si="3"/>
-        <v>6470</v>
-      </c>
-      <c r="I5" s="7">
-        <f t="shared" si="3"/>
-        <v>6642</v>
-      </c>
-      <c r="J5" s="7">
-        <f t="shared" si="3"/>
-        <v>7111</v>
-      </c>
-      <c r="K5" s="7">
-        <f t="shared" si="3"/>
-        <v>7155</v>
-      </c>
-      <c r="L5" s="7">
-        <f t="shared" si="3"/>
-        <v>7172</v>
-      </c>
-      <c r="M5" s="7">
-        <f t="shared" si="3"/>
-        <v>7327</v>
-      </c>
-      <c r="N5" s="7">
-        <f t="shared" si="3"/>
-        <v>8008</v>
-      </c>
-      <c r="O5" s="7">
-        <f t="shared" ref="O5:Q5" si="4">O3-O4</f>
-        <v>7697</v>
-      </c>
-      <c r="P5" s="7">
+        <v>8982</v>
+      </c>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="X5" s="7">
+        <f t="shared" ref="X5:AD5" si="4">X3-X4</f>
+        <v>19533</v>
+      </c>
+      <c r="Y5" s="7">
         <f t="shared" si="4"/>
-        <v>7937</v>
-      </c>
-      <c r="Q5" s="7">
+        <v>18061</v>
+      </c>
+      <c r="Z5" s="7">
         <f t="shared" si="4"/>
-        <v>8423</v>
-      </c>
-      <c r="R5" s="7">
-        <f t="shared" ref="Q5:R5" si="5">R3*0.82</f>
-        <v>8832.2528000000002</v>
-      </c>
-      <c r="T5" s="7">
-        <f t="shared" ref="T5:Z5" si="6">T3-T4</f>
-        <v>19533</v>
-      </c>
-      <c r="U5" s="7">
-        <f t="shared" si="6"/>
-        <v>18061</v>
-      </c>
-      <c r="V5" s="7">
-        <f t="shared" si="6"/>
         <v>19865</v>
       </c>
-      <c r="W5" s="7">
-        <f t="shared" si="6"/>
+      <c r="AA5" s="7">
+        <f t="shared" si="4"/>
         <v>24320</v>
       </c>
-      <c r="X5" s="7">
-        <f t="shared" si="6"/>
+      <c r="AB5" s="7">
+        <f t="shared" si="4"/>
         <v>26822</v>
       </c>
-      <c r="Y5" s="7">
-        <f t="shared" si="6"/>
+      <c r="AC5" s="7">
+        <f t="shared" si="4"/>
         <v>29662</v>
       </c>
-      <c r="Z5" s="7">
-        <f t="shared" si="6"/>
-        <v>32889.252800000002</v>
-      </c>
-      <c r="AA5" s="7">
-        <f t="shared" ref="AA5:AJ5" si="7">AA3*0.83</f>
-        <v>36230.557088000001</v>
-      </c>
-      <c r="AB5" s="7">
-        <f t="shared" si="7"/>
-        <v>38766.696084160008</v>
-      </c>
-      <c r="AC5" s="7">
-        <f t="shared" si="7"/>
-        <v>40705.030888368005</v>
-      </c>
       <c r="AD5" s="7">
-        <f t="shared" si="7"/>
-        <v>42333.232123902722</v>
+        <f t="shared" si="4"/>
+        <v>33039</v>
       </c>
       <c r="AE5" s="7">
-        <f t="shared" si="7"/>
-        <v>43603.229087619809</v>
+        <f>AE3*0.84</f>
+        <v>36624</v>
       </c>
       <c r="AF5" s="7">
-        <f t="shared" si="7"/>
-        <v>44475.293669372208</v>
+        <f t="shared" ref="AF5:AN5" si="5">AF3*0.84</f>
+        <v>39187.68</v>
       </c>
       <c r="AG5" s="7">
-        <f t="shared" si="7"/>
-        <v>45364.799542759647</v>
+        <f t="shared" si="5"/>
+        <v>41147.063999999998</v>
       </c>
       <c r="AH5" s="7">
-        <f t="shared" si="7"/>
-        <v>46272.09553361484</v>
+        <f t="shared" si="5"/>
+        <v>42792.946559999997</v>
       </c>
       <c r="AI5" s="7">
-        <f t="shared" si="7"/>
-        <v>47197.537444287147</v>
+        <f t="shared" si="5"/>
+        <v>44076.734956799999</v>
       </c>
       <c r="AJ5" s="7">
-        <f t="shared" si="7"/>
-        <v>48141.488193172889</v>
+        <f t="shared" si="5"/>
+        <v>44958.269655935997</v>
+      </c>
+      <c r="AK5" s="7">
+        <f t="shared" si="5"/>
+        <v>45857.435049054722</v>
+      </c>
+      <c r="AL5" s="7">
+        <f t="shared" si="5"/>
+        <v>46774.583750035825</v>
+      </c>
+      <c r="AM5" s="7">
+        <f t="shared" si="5"/>
+        <v>47710.075425036535</v>
+      </c>
+      <c r="AN5" s="7">
+        <f t="shared" si="5"/>
+        <v>48664.276933537272</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>12</v>
       </c>
@@ -1460,76 +1478,79 @@
         <v>421</v>
       </c>
       <c r="R6" s="3">
-        <f>R3*0.06</f>
-        <v>646.26240000000007</v>
-      </c>
-      <c r="T6" s="3">
+        <v>576</v>
+      </c>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="X6" s="3">
         <v>1105</v>
       </c>
-      <c r="U6" s="3">
+      <c r="Y6" s="3">
         <v>971</v>
       </c>
-      <c r="V6" s="3">
+      <c r="Z6" s="3">
         <v>1136</v>
       </c>
-      <c r="W6" s="3">
-        <f t="shared" ref="W6:W11" si="8">SUM(C6:F6)</f>
+      <c r="AA6" s="3">
+        <f t="shared" ref="AA6:AA11" si="6">SUM(C6:F6)</f>
         <v>1336</v>
       </c>
-      <c r="X6" s="3">
-        <f t="shared" ref="X6:X11" si="9">SUM(G6:J6)</f>
+      <c r="AB6" s="3">
+        <f t="shared" ref="AB6:AB11" si="7">SUM(G6:J6)</f>
         <v>1341</v>
       </c>
-      <c r="Y6" s="3">
-        <f t="shared" ref="Y6:Y11" si="10">SUM(K6:N6)</f>
+      <c r="AC6" s="3">
+        <f t="shared" ref="AC6:AC11" si="8">SUM(K6:N6)</f>
         <v>1560</v>
       </c>
-      <c r="Z6" s="3">
-        <f t="shared" ref="Z6:Z11" si="11">SUM(O6:R6)</f>
-        <v>1754.2624000000001</v>
-      </c>
-      <c r="AA6" s="3">
-        <f t="shared" ref="AA6:AJ6" si="12">AA3*0.04</f>
-        <v>1746.0509440000003</v>
-      </c>
-      <c r="AB6" s="3">
-        <f t="shared" si="12"/>
-        <v>1868.2745100800003</v>
-      </c>
-      <c r="AC6" s="3">
-        <f t="shared" si="12"/>
-        <v>1961.6882355840005</v>
-      </c>
       <c r="AD6" s="3">
-        <f t="shared" si="12"/>
-        <v>2040.1557650073603</v>
+        <f t="shared" ref="AD6:AD11" si="9">SUM(O6:R6)</f>
+        <v>1684</v>
       </c>
       <c r="AE6" s="3">
-        <f t="shared" si="12"/>
-        <v>2101.3604379575813</v>
+        <f t="shared" ref="AE6:AN6" si="10">AE3*0.04</f>
+        <v>1744</v>
       </c>
       <c r="AF6" s="3">
-        <f t="shared" si="12"/>
-        <v>2143.3876467167329</v>
+        <f t="shared" si="10"/>
+        <v>1866.08</v>
       </c>
       <c r="AG6" s="3">
-        <f t="shared" si="12"/>
-        <v>2186.2553996510678</v>
+        <f t="shared" si="10"/>
+        <v>1959.384</v>
       </c>
       <c r="AH6" s="3">
-        <f t="shared" si="12"/>
-        <v>2229.9805076440889</v>
+        <f t="shared" si="10"/>
+        <v>2037.75936</v>
       </c>
       <c r="AI6" s="3">
-        <f t="shared" si="12"/>
-        <v>2274.5801177969711</v>
+        <f t="shared" si="10"/>
+        <v>2098.8921408000001</v>
       </c>
       <c r="AJ6" s="3">
-        <f t="shared" si="12"/>
-        <v>2320.0717201529105</v>
+        <f t="shared" si="10"/>
+        <v>2140.8699836160004</v>
+      </c>
+      <c r="AK6" s="3">
+        <f t="shared" si="10"/>
+        <v>2183.6873832883202</v>
+      </c>
+      <c r="AL6" s="3">
+        <f t="shared" si="10"/>
+        <v>2227.361130954087</v>
+      </c>
+      <c r="AM6" s="3">
+        <f t="shared" si="10"/>
+        <v>2271.9083535731688</v>
+      </c>
+      <c r="AN6" s="3">
+        <f t="shared" si="10"/>
+        <v>2317.3465206446322</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>13</v>
       </c>
@@ -1579,76 +1600,79 @@
         <v>224</v>
       </c>
       <c r="R7" s="3">
-        <f t="shared" ref="Q7:R7" si="13">N7*1.1</f>
-        <v>228.8</v>
-      </c>
-      <c r="T7" s="3">
+        <v>239</v>
+      </c>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="X7" s="3">
         <v>721</v>
       </c>
-      <c r="U7" s="3">
+      <c r="Y7" s="3">
         <v>727</v>
       </c>
-      <c r="V7" s="3">
+      <c r="Z7" s="3">
         <v>730</v>
       </c>
-      <c r="W7" s="3">
+      <c r="AA7" s="3">
+        <f t="shared" si="6"/>
+        <v>743</v>
+      </c>
+      <c r="AB7" s="3">
+        <f t="shared" si="7"/>
+        <v>736</v>
+      </c>
+      <c r="AC7" s="3">
         <f t="shared" si="8"/>
-        <v>743</v>
-      </c>
-      <c r="X7" s="3">
+        <v>778</v>
+      </c>
+      <c r="AD7" s="3">
         <f t="shared" si="9"/>
-        <v>736</v>
-      </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="10"/>
-        <v>778</v>
-      </c>
-      <c r="Z7" s="3">
+        <v>894</v>
+      </c>
+      <c r="AE7" s="3">
+        <f>AD7*1.09</f>
+        <v>974.46</v>
+      </c>
+      <c r="AF7" s="3">
+        <f>AE7*1.05</f>
+        <v>1023.1830000000001</v>
+      </c>
+      <c r="AG7" s="3">
+        <f>AF7*1.03</f>
+        <v>1053.8784900000001</v>
+      </c>
+      <c r="AH7" s="3">
+        <f>AG7*1.02</f>
+        <v>1074.9560598</v>
+      </c>
+      <c r="AI7" s="3">
+        <f t="shared" ref="AI7:AN7" si="11">AH7*1.01</f>
+        <v>1085.7056203980001</v>
+      </c>
+      <c r="AJ7" s="3">
         <f t="shared" si="11"/>
-        <v>883.8</v>
-      </c>
-      <c r="AA7" s="3">
-        <f>Z7*1.09</f>
-        <v>963.34199999999998</v>
-      </c>
-      <c r="AB7" s="3">
-        <f>AA7*1.05</f>
-        <v>1011.5091</v>
-      </c>
-      <c r="AC7" s="3">
-        <f>AB7*1.03</f>
-        <v>1041.8543730000001</v>
-      </c>
-      <c r="AD7" s="3">
-        <f>AC7*1.02</f>
-        <v>1062.6914604600001</v>
-      </c>
-      <c r="AE7" s="3">
-        <f t="shared" ref="AE7:AJ7" si="14">AD7*1.01</f>
-        <v>1073.3183750646001</v>
-      </c>
-      <c r="AF7" s="3">
-        <f t="shared" si="14"/>
-        <v>1084.0515588152462</v>
-      </c>
-      <c r="AG7" s="3">
-        <f t="shared" si="14"/>
-        <v>1094.8920744033987</v>
-      </c>
-      <c r="AH7" s="3">
-        <f t="shared" si="14"/>
-        <v>1105.8409951474327</v>
-      </c>
-      <c r="AI7" s="3">
-        <f t="shared" si="14"/>
-        <v>1116.899405098907</v>
-      </c>
-      <c r="AJ7" s="3">
-        <f t="shared" si="14"/>
-        <v>1128.0683991498961</v>
+        <v>1096.56267660198</v>
+      </c>
+      <c r="AK7" s="3">
+        <f t="shared" si="11"/>
+        <v>1107.5283033679998</v>
+      </c>
+      <c r="AL7" s="3">
+        <f t="shared" si="11"/>
+        <v>1118.6035864016799</v>
+      </c>
+      <c r="AM7" s="3">
+        <f t="shared" si="11"/>
+        <v>1129.7896222656966</v>
+      </c>
+      <c r="AN7" s="3">
+        <f t="shared" si="11"/>
+        <v>1141.0875184883537</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>14</v>
       </c>
@@ -1698,76 +1722,79 @@
         <v>187</v>
       </c>
       <c r="R8" s="3">
-        <f t="shared" ref="Q8:R8" si="15">R3*0.02</f>
-        <v>215.42080000000001</v>
-      </c>
-      <c r="T8" s="3">
+        <v>256</v>
+      </c>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="X8" s="3">
         <v>454</v>
       </c>
-      <c r="U8" s="3">
+      <c r="Y8" s="3">
         <v>408</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Z8" s="3">
         <v>403</v>
       </c>
-      <c r="W8" s="3">
+      <c r="AA8" s="3">
+        <f t="shared" si="6"/>
+        <v>505</v>
+      </c>
+      <c r="AB8" s="3">
+        <f t="shared" si="7"/>
+        <v>545</v>
+      </c>
+      <c r="AC8" s="3">
         <f t="shared" si="8"/>
-        <v>505</v>
-      </c>
-      <c r="X8" s="3">
+        <v>635</v>
+      </c>
+      <c r="AD8" s="3">
         <f t="shared" si="9"/>
-        <v>545</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="10"/>
-        <v>635</v>
-      </c>
-      <c r="Z8" s="3">
-        <f t="shared" si="11"/>
-        <v>718.42079999999999</v>
-      </c>
-      <c r="AA8" s="3">
-        <f t="shared" ref="AA8:AJ8" si="16">AA3*0.02</f>
-        <v>873.02547200000015</v>
-      </c>
-      <c r="AB8" s="3">
-        <f t="shared" si="16"/>
-        <v>934.13725504000013</v>
-      </c>
-      <c r="AC8" s="3">
-        <f t="shared" si="16"/>
-        <v>980.84411779200025</v>
-      </c>
-      <c r="AD8" s="3">
-        <f t="shared" si="16"/>
-        <v>1020.0778825036801</v>
+        <v>759</v>
       </c>
       <c r="AE8" s="3">
-        <f t="shared" si="16"/>
-        <v>1050.6802189787907</v>
+        <f t="shared" ref="AE8:AN8" si="12">AE3*0.02</f>
+        <v>872</v>
       </c>
       <c r="AF8" s="3">
-        <f t="shared" si="16"/>
-        <v>1071.6938233583664</v>
+        <f t="shared" si="12"/>
+        <v>933.04</v>
       </c>
       <c r="AG8" s="3">
-        <f t="shared" si="16"/>
-        <v>1093.1276998255339</v>
+        <f t="shared" si="12"/>
+        <v>979.69200000000001</v>
       </c>
       <c r="AH8" s="3">
-        <f t="shared" si="16"/>
-        <v>1114.9902538220445</v>
+        <f t="shared" si="12"/>
+        <v>1018.87968</v>
       </c>
       <c r="AI8" s="3">
-        <f t="shared" si="16"/>
-        <v>1137.2900588984855</v>
+        <f t="shared" si="12"/>
+        <v>1049.4460704000001</v>
       </c>
       <c r="AJ8" s="3">
-        <f t="shared" si="16"/>
-        <v>1160.0358600764553</v>
+        <f t="shared" si="12"/>
+        <v>1070.4349918080002</v>
+      </c>
+      <c r="AK8" s="3">
+        <f t="shared" si="12"/>
+        <v>1091.8436916441601</v>
+      </c>
+      <c r="AL8" s="3">
+        <f t="shared" si="12"/>
+        <v>1113.6805654770435</v>
+      </c>
+      <c r="AM8" s="3">
+        <f t="shared" si="12"/>
+        <v>1135.9541767865844</v>
+      </c>
+      <c r="AN8" s="3">
+        <f t="shared" si="12"/>
+        <v>1158.6732603223161</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>15</v>
       </c>
@@ -1817,46 +1844,49 @@
         <v>317</v>
       </c>
       <c r="R9" s="3">
-        <f>N9*1.18</f>
-        <v>323.32</v>
-      </c>
-      <c r="T9" s="3">
+        <v>316</v>
+      </c>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="X9" s="3">
         <v>656</v>
       </c>
-      <c r="U9" s="3">
+      <c r="Y9" s="3">
         <v>767</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Z9" s="3">
         <v>804</v>
       </c>
-      <c r="W9" s="3">
+      <c r="AA9" s="3">
+        <f t="shared" si="6"/>
+        <v>861</v>
+      </c>
+      <c r="AB9" s="3">
+        <f t="shared" si="7"/>
+        <v>943</v>
+      </c>
+      <c r="AC9" s="3">
         <f t="shared" si="8"/>
-        <v>861</v>
-      </c>
-      <c r="X9" s="3">
+        <v>1034</v>
+      </c>
+      <c r="AD9" s="3">
         <f t="shared" si="9"/>
-        <v>943</v>
-      </c>
-      <c r="Y9" s="3">
-        <f t="shared" si="10"/>
-        <v>1034</v>
-      </c>
-      <c r="Z9" s="3">
-        <f t="shared" si="11"/>
-        <v>1227.32</v>
-      </c>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
+        <v>1220</v>
+      </c>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
+      <c r="AK9" s="3"/>
+      <c r="AL9" s="3"/>
+      <c r="AM9" s="3"/>
+      <c r="AN9" s="3"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -1906,76 +1936,79 @@
         <v>482</v>
       </c>
       <c r="R10" s="3">
-        <f>N10*1.2</f>
-        <v>508.79999999999995</v>
-      </c>
-      <c r="T10" s="3">
+        <v>544</v>
+      </c>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="X10" s="3">
         <v>1196</v>
       </c>
-      <c r="U10" s="3">
+      <c r="Y10" s="3">
         <v>1096</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Z10" s="3">
         <v>985</v>
       </c>
-      <c r="W10" s="3">
+      <c r="AA10" s="3">
+        <f t="shared" si="6"/>
+        <v>1194</v>
+      </c>
+      <c r="AB10" s="3">
+        <f t="shared" si="7"/>
+        <v>1330</v>
+      </c>
+      <c r="AC10" s="3">
         <f t="shared" si="8"/>
-        <v>1194</v>
-      </c>
-      <c r="X10" s="3">
+        <v>1598</v>
+      </c>
+      <c r="AD10" s="3">
         <f t="shared" si="9"/>
-        <v>1330</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="10"/>
-        <v>1598</v>
-      </c>
-      <c r="Z10" s="3">
-        <f t="shared" si="11"/>
-        <v>1890.8</v>
-      </c>
-      <c r="AA10" s="3">
-        <f>Z10*1.09</f>
-        <v>2060.9720000000002</v>
-      </c>
-      <c r="AB10" s="3">
-        <f>AA10*1.05</f>
-        <v>2164.0206000000003</v>
-      </c>
-      <c r="AC10" s="3">
-        <f>AB10*1.03</f>
-        <v>2228.9412180000004</v>
-      </c>
-      <c r="AD10" s="3">
-        <f t="shared" ref="AD10" si="17">AC10*1.02</f>
-        <v>2273.5200423600004</v>
+        <v>1926</v>
       </c>
       <c r="AE10" s="3">
-        <f>AD10*1.01</f>
-        <v>2296.2552427836004</v>
+        <f>AD10*1.09</f>
+        <v>2099.34</v>
       </c>
       <c r="AF10" s="3">
-        <f t="shared" ref="AF10:AJ10" si="18">AE10*1.01</f>
-        <v>2319.2177952114362</v>
+        <f>AE10*1.05</f>
+        <v>2204.3070000000002</v>
       </c>
       <c r="AG10" s="3">
-        <f t="shared" si="18"/>
-        <v>2342.4099731635506</v>
+        <f>AF10*1.03</f>
+        <v>2270.4362100000003</v>
       </c>
       <c r="AH10" s="3">
-        <f t="shared" si="18"/>
-        <v>2365.8340728951862</v>
+        <f t="shared" ref="AH10" si="13">AG10*1.02</f>
+        <v>2315.8449342000004</v>
       </c>
       <c r="AI10" s="3">
-        <f t="shared" si="18"/>
-        <v>2389.492413624138</v>
+        <f>AH10*1.01</f>
+        <v>2339.0033835420004</v>
       </c>
       <c r="AJ10" s="3">
-        <f t="shared" si="18"/>
-        <v>2413.3873377603795</v>
+        <f t="shared" ref="AJ10:AN10" si="14">AI10*1.01</f>
+        <v>2362.3934173774205</v>
+      </c>
+      <c r="AK10" s="3">
+        <f t="shared" si="14"/>
+        <v>2386.0173515511947</v>
+      </c>
+      <c r="AL10" s="3">
+        <f t="shared" si="14"/>
+        <v>2409.8775250667068</v>
+      </c>
+      <c r="AM10" s="3">
+        <f t="shared" si="14"/>
+        <v>2433.9763003173739</v>
+      </c>
+      <c r="AN10" s="3">
+        <f t="shared" si="14"/>
+        <v>2458.3160633205475</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -2025,351 +2058,362 @@
         <v>615</v>
       </c>
       <c r="R11" s="3">
-        <f>R3*0.04</f>
-        <v>430.84160000000003</v>
-      </c>
-      <c r="T11" s="3">
+        <v>903</v>
+      </c>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="X11" s="3">
         <v>400</v>
       </c>
-      <c r="U11" s="3">
+      <c r="Y11" s="3">
         <v>11</v>
       </c>
-      <c r="V11" s="3">
+      <c r="Z11" s="3">
         <v>3</v>
       </c>
-      <c r="W11" s="3">
+      <c r="AA11" s="3">
+        <f t="shared" si="6"/>
+        <v>868</v>
+      </c>
+      <c r="AB11" s="3">
+        <f t="shared" si="7"/>
+        <v>927</v>
+      </c>
+      <c r="AC11" s="3">
         <f t="shared" si="8"/>
-        <v>868</v>
-      </c>
-      <c r="X11" s="3">
+        <v>462</v>
+      </c>
+      <c r="AD11" s="3">
         <f t="shared" si="9"/>
-        <v>927</v>
-      </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="10"/>
-        <v>462</v>
-      </c>
-      <c r="Z11" s="3">
-        <f t="shared" si="11"/>
-        <v>2089.8416000000002</v>
-      </c>
-      <c r="AA11" s="3">
-        <f>AA3*0.02</f>
-        <v>873.02547200000015</v>
-      </c>
-      <c r="AB11" s="3">
-        <f t="shared" ref="AB11:AJ11" si="19">AB3*0.01</f>
-        <v>467.06862752000006</v>
-      </c>
-      <c r="AC11" s="3">
-        <f t="shared" si="19"/>
-        <v>490.42205889600012</v>
-      </c>
-      <c r="AD11" s="3">
-        <f t="shared" si="19"/>
-        <v>510.03894125184007</v>
+        <v>2562</v>
       </c>
       <c r="AE11" s="3">
-        <f t="shared" si="19"/>
-        <v>525.34010948939533</v>
+        <f>AE3*0.02</f>
+        <v>872</v>
       </c>
       <c r="AF11" s="3">
-        <f t="shared" si="19"/>
-        <v>535.84691167918322</v>
+        <f t="shared" ref="AF11:AN11" si="15">AF3*0.01</f>
+        <v>466.52</v>
       </c>
       <c r="AG11" s="3">
-        <f t="shared" si="19"/>
-        <v>546.56384991276695</v>
+        <f t="shared" si="15"/>
+        <v>489.846</v>
       </c>
       <c r="AH11" s="3">
-        <f t="shared" si="19"/>
-        <v>557.49512691102223</v>
+        <f t="shared" si="15"/>
+        <v>509.43984</v>
       </c>
       <c r="AI11" s="3">
-        <f t="shared" si="19"/>
-        <v>568.64502944924277</v>
+        <f t="shared" si="15"/>
+        <v>524.72303520000003</v>
       </c>
       <c r="AJ11" s="3">
-        <f t="shared" si="19"/>
-        <v>580.01793003822763</v>
+        <f t="shared" si="15"/>
+        <v>535.21749590400009</v>
+      </c>
+      <c r="AK11" s="3">
+        <f t="shared" si="15"/>
+        <v>545.92184582208006</v>
+      </c>
+      <c r="AL11" s="3">
+        <f t="shared" si="15"/>
+        <v>556.84028273852175</v>
+      </c>
+      <c r="AM11" s="3">
+        <f t="shared" si="15"/>
+        <v>567.97708839329221</v>
+      </c>
+      <c r="AN11" s="3">
+        <f t="shared" si="15"/>
+        <v>579.33663016115804</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="3">
-        <f t="shared" ref="C12:L12" si="20">SUM(C6:C11)</f>
+        <f t="shared" ref="C12:L12" si="16">SUM(C6:C11)</f>
         <v>1158</v>
       </c>
       <c r="D12" s="3">
+        <f t="shared" si="16"/>
+        <v>1161</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="16"/>
+        <v>1844</v>
+      </c>
+      <c r="F12" s="3">
+        <f t="shared" si="16"/>
+        <v>1344</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" si="16"/>
+        <v>1509</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" si="16"/>
+        <v>1134</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="16"/>
+        <v>1618</v>
+      </c>
+      <c r="J12" s="3">
+        <f t="shared" si="16"/>
+        <v>1561</v>
+      </c>
+      <c r="K12" s="3">
+        <f t="shared" si="16"/>
+        <v>1201</v>
+      </c>
+      <c r="L12" s="3">
+        <f t="shared" si="16"/>
+        <v>1818</v>
+      </c>
+      <c r="M12" s="3">
+        <f t="shared" ref="M12:N12" si="17">SUM(M6:M11)</f>
+        <v>1389</v>
+      </c>
+      <c r="N12" s="3">
+        <f t="shared" si="17"/>
+        <v>1659</v>
+      </c>
+      <c r="O12" s="3">
+        <f t="shared" ref="O12:R12" si="18">SUM(O6:O11)</f>
+        <v>1463</v>
+      </c>
+      <c r="P12" s="3">
+        <f t="shared" si="18"/>
+        <v>2502</v>
+      </c>
+      <c r="Q12" s="3">
+        <f t="shared" si="18"/>
+        <v>2246</v>
+      </c>
+      <c r="R12" s="3">
+        <f t="shared" si="18"/>
+        <v>2834</v>
+      </c>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="X12" s="3">
+        <f t="shared" ref="X12:AC12" si="19">SUM(X6:X11)</f>
+        <v>4532</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="19"/>
+        <v>3980</v>
+      </c>
+      <c r="Z12" s="3">
+        <f t="shared" si="19"/>
+        <v>4061</v>
+      </c>
+      <c r="AA12" s="3">
+        <f t="shared" si="19"/>
+        <v>5507</v>
+      </c>
+      <c r="AB12" s="3">
+        <f t="shared" si="19"/>
+        <v>5822</v>
+      </c>
+      <c r="AC12" s="3">
+        <f t="shared" si="19"/>
+        <v>6067</v>
+      </c>
+      <c r="AD12" s="3">
+        <f t="shared" ref="AD12:AN12" si="20">SUM(AD6:AD11)</f>
+        <v>9045</v>
+      </c>
+      <c r="AE12" s="3">
         <f t="shared" si="20"/>
-        <v>1161</v>
-      </c>
-      <c r="E12" s="3">
+        <v>6561.8</v>
+      </c>
+      <c r="AF12" s="3">
         <f t="shared" si="20"/>
-        <v>1844</v>
-      </c>
-      <c r="F12" s="3">
+        <v>6493.130000000001</v>
+      </c>
+      <c r="AG12" s="3">
         <f t="shared" si="20"/>
-        <v>1344</v>
-      </c>
-      <c r="G12" s="3">
+        <v>6753.2366999999995</v>
+      </c>
+      <c r="AH12" s="3">
         <f t="shared" si="20"/>
-        <v>1509</v>
-      </c>
-      <c r="H12" s="3">
+        <v>6956.8798740000002</v>
+      </c>
+      <c r="AI12" s="3">
         <f t="shared" si="20"/>
-        <v>1134</v>
-      </c>
-      <c r="I12" s="3">
+        <v>7097.7702503400005</v>
+      </c>
+      <c r="AJ12" s="3">
         <f t="shared" si="20"/>
-        <v>1618</v>
-      </c>
-      <c r="J12" s="3">
+        <v>7205.4785653074014</v>
+      </c>
+      <c r="AK12" s="3">
         <f t="shared" si="20"/>
-        <v>1561</v>
-      </c>
-      <c r="K12" s="3">
+        <v>7314.9985756737551</v>
+      </c>
+      <c r="AL12" s="3">
         <f t="shared" si="20"/>
-        <v>1201</v>
-      </c>
-      <c r="L12" s="3">
+        <v>7426.3630906380386</v>
+      </c>
+      <c r="AM12" s="3">
         <f t="shared" si="20"/>
-        <v>1818</v>
-      </c>
-      <c r="M12" s="3">
-        <f t="shared" ref="M12:N12" si="21">SUM(M6:M11)</f>
-        <v>1389</v>
-      </c>
-      <c r="N12" s="3">
-        <f t="shared" si="21"/>
-        <v>1659</v>
-      </c>
-      <c r="O12" s="3">
-        <f t="shared" ref="O12:R12" si="22">SUM(O6:O11)</f>
-        <v>1463</v>
-      </c>
-      <c r="P12" s="3">
-        <f t="shared" si="22"/>
-        <v>2502</v>
-      </c>
-      <c r="Q12" s="3">
-        <f t="shared" si="22"/>
-        <v>2246</v>
-      </c>
-      <c r="R12" s="3">
-        <f t="shared" si="22"/>
-        <v>2353.4448000000002</v>
-      </c>
-      <c r="T12" s="3">
-        <f t="shared" ref="T12:Y12" si="23">SUM(T6:T11)</f>
-        <v>4532</v>
-      </c>
-      <c r="U12" s="3">
-        <f t="shared" si="23"/>
-        <v>3980</v>
-      </c>
-      <c r="V12" s="3">
-        <f t="shared" si="23"/>
-        <v>4061</v>
-      </c>
-      <c r="W12" s="3">
-        <f t="shared" si="23"/>
-        <v>5507</v>
-      </c>
-      <c r="X12" s="3">
-        <f t="shared" si="23"/>
-        <v>5822</v>
-      </c>
-      <c r="Y12" s="3">
-        <f t="shared" si="23"/>
-        <v>6067</v>
-      </c>
-      <c r="Z12" s="3">
-        <f t="shared" ref="Z12:AJ12" si="24">SUM(Z6:Z11)</f>
-        <v>8564.4447999999993</v>
-      </c>
-      <c r="AA12" s="3">
-        <f t="shared" si="24"/>
-        <v>6516.4158880000005</v>
-      </c>
-      <c r="AB12" s="3">
-        <f t="shared" si="24"/>
-        <v>6445.0100926400009</v>
-      </c>
-      <c r="AC12" s="3">
-        <f t="shared" si="24"/>
-        <v>6703.7500032720018</v>
-      </c>
-      <c r="AD12" s="3">
-        <f t="shared" si="24"/>
-        <v>6906.4840915828809</v>
-      </c>
-      <c r="AE12" s="3">
-        <f t="shared" si="24"/>
-        <v>7046.9543842739668</v>
-      </c>
-      <c r="AF12" s="3">
-        <f t="shared" si="24"/>
-        <v>7154.1977357809646</v>
-      </c>
-      <c r="AG12" s="3">
-        <f t="shared" si="24"/>
-        <v>7263.2489969563176</v>
-      </c>
-      <c r="AH12" s="3">
-        <f t="shared" si="24"/>
-        <v>7374.1409564197747</v>
-      </c>
-      <c r="AI12" s="3">
-        <f t="shared" si="24"/>
-        <v>7486.9070248677444</v>
-      </c>
-      <c r="AJ12" s="3">
-        <f t="shared" si="24"/>
-        <v>7601.58124717787</v>
+        <v>7539.6055413361155</v>
+      </c>
+      <c r="AN12" s="3">
+        <f t="shared" si="20"/>
+        <v>7654.7599929370072</v>
       </c>
     </row>
-    <row r="13" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13"/>
       <c r="B13" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="7">
-        <f t="shared" ref="C13:L13" si="25">C5-C12</f>
+        <f t="shared" ref="C13:L13" si="21">C5-C12</f>
         <v>4776</v>
       </c>
       <c r="D13" s="7">
+        <f t="shared" si="21"/>
+        <v>4802</v>
+      </c>
+      <c r="E13" s="7">
+        <f t="shared" si="21"/>
+        <v>4148</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="21"/>
+        <v>5087</v>
+      </c>
+      <c r="G13" s="7">
+        <f t="shared" si="21"/>
+        <v>5090</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="21"/>
+        <v>5336</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="21"/>
+        <v>5024</v>
+      </c>
+      <c r="J13" s="7">
+        <f t="shared" si="21"/>
+        <v>5550</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="21"/>
+        <v>5954</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="21"/>
+        <v>5354</v>
+      </c>
+      <c r="M13" s="7">
+        <f t="shared" ref="M13:N13" si="22">M5-M12</f>
+        <v>5938</v>
+      </c>
+      <c r="N13" s="7">
+        <f t="shared" si="22"/>
+        <v>6349</v>
+      </c>
+      <c r="O13" s="7">
+        <f t="shared" ref="O13:R13" si="23">O5-O12</f>
+        <v>6234</v>
+      </c>
+      <c r="P13" s="7">
+        <f t="shared" si="23"/>
+        <v>5435</v>
+      </c>
+      <c r="Q13" s="7">
+        <f t="shared" si="23"/>
+        <v>6177</v>
+      </c>
+      <c r="R13" s="7">
+        <f t="shared" si="23"/>
+        <v>6148</v>
+      </c>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="X13" s="7">
+        <f t="shared" ref="X13:AC13" si="24">X5-X12</f>
+        <v>15001</v>
+      </c>
+      <c r="Y13" s="7">
+        <f t="shared" si="24"/>
+        <v>14081</v>
+      </c>
+      <c r="Z13" s="7">
+        <f t="shared" si="24"/>
+        <v>15804</v>
+      </c>
+      <c r="AA13" s="7">
+        <f t="shared" si="24"/>
+        <v>18813</v>
+      </c>
+      <c r="AB13" s="7">
+        <f t="shared" si="24"/>
+        <v>21000</v>
+      </c>
+      <c r="AC13" s="7">
+        <f t="shared" si="24"/>
+        <v>23595</v>
+      </c>
+      <c r="AD13" s="7">
+        <f t="shared" ref="AD13:AN13" si="25">AD5-AD12</f>
+        <v>23994</v>
+      </c>
+      <c r="AE13" s="7">
         <f t="shared" si="25"/>
-        <v>4802</v>
-      </c>
-      <c r="E13" s="7">
+        <v>30062.2</v>
+      </c>
+      <c r="AF13" s="7">
         <f t="shared" si="25"/>
-        <v>4148</v>
-      </c>
-      <c r="F13" s="7">
+        <v>32694.55</v>
+      </c>
+      <c r="AG13" s="7">
         <f t="shared" si="25"/>
-        <v>5087</v>
-      </c>
-      <c r="G13" s="7">
+        <v>34393.827299999997</v>
+      </c>
+      <c r="AH13" s="7">
         <f t="shared" si="25"/>
-        <v>5090</v>
-      </c>
-      <c r="H13" s="7">
+        <v>35836.066685999998</v>
+      </c>
+      <c r="AI13" s="7">
         <f t="shared" si="25"/>
-        <v>5336</v>
-      </c>
-      <c r="I13" s="7">
+        <v>36978.964706459999</v>
+      </c>
+      <c r="AJ13" s="7">
         <f t="shared" si="25"/>
-        <v>5024</v>
-      </c>
-      <c r="J13" s="7">
+        <v>37752.791090628598</v>
+      </c>
+      <c r="AK13" s="7">
         <f t="shared" si="25"/>
-        <v>5550</v>
-      </c>
-      <c r="K13" s="7">
+        <v>38542.436473380963</v>
+      </c>
+      <c r="AL13" s="7">
         <f t="shared" si="25"/>
-        <v>5954</v>
-      </c>
-      <c r="L13" s="7">
+        <v>39348.22065939779</v>
+      </c>
+      <c r="AM13" s="7">
         <f t="shared" si="25"/>
-        <v>5354</v>
-      </c>
-      <c r="M13" s="7">
-        <f t="shared" ref="M13:N13" si="26">M5-M12</f>
-        <v>5938</v>
-      </c>
-      <c r="N13" s="7">
-        <f t="shared" si="26"/>
-        <v>6349</v>
-      </c>
-      <c r="O13" s="7">
-        <f t="shared" ref="O13:R13" si="27">O5-O12</f>
-        <v>6234</v>
-      </c>
-      <c r="P13" s="7">
-        <f t="shared" si="27"/>
-        <v>5435</v>
-      </c>
-      <c r="Q13" s="7">
-        <f t="shared" si="27"/>
-        <v>6177</v>
-      </c>
-      <c r="R13" s="7">
-        <f t="shared" si="27"/>
-        <v>6478.808</v>
-      </c>
-      <c r="T13" s="7">
-        <f t="shared" ref="T13:Y13" si="28">T5-T12</f>
-        <v>15001</v>
-      </c>
-      <c r="U13" s="7">
-        <f t="shared" si="28"/>
-        <v>14081</v>
-      </c>
-      <c r="V13" s="7">
-        <f t="shared" si="28"/>
-        <v>15804</v>
-      </c>
-      <c r="W13" s="7">
-        <f t="shared" si="28"/>
-        <v>18813</v>
-      </c>
-      <c r="X13" s="7">
-        <f t="shared" si="28"/>
-        <v>21000</v>
-      </c>
-      <c r="Y13" s="7">
-        <f t="shared" si="28"/>
-        <v>23595</v>
-      </c>
-      <c r="Z13" s="7">
-        <f t="shared" ref="Z13:AJ13" si="29">Z5-Z12</f>
-        <v>24324.808000000005</v>
-      </c>
-      <c r="AA13" s="7">
-        <f t="shared" si="29"/>
-        <v>29714.141200000002</v>
-      </c>
-      <c r="AB13" s="7">
-        <f t="shared" si="29"/>
-        <v>32321.685991520008</v>
-      </c>
-      <c r="AC13" s="7">
-        <f t="shared" si="29"/>
-        <v>34001.280885095999</v>
-      </c>
-      <c r="AD13" s="7">
-        <f t="shared" si="29"/>
-        <v>35426.74803231984</v>
-      </c>
-      <c r="AE13" s="7">
-        <f t="shared" si="29"/>
-        <v>36556.274703345844</v>
-      </c>
-      <c r="AF13" s="7">
-        <f t="shared" si="29"/>
-        <v>37321.095933591241</v>
-      </c>
-      <c r="AG13" s="7">
-        <f t="shared" si="29"/>
-        <v>38101.550545803329</v>
-      </c>
-      <c r="AH13" s="7">
-        <f t="shared" si="29"/>
-        <v>38897.954577195065</v>
-      </c>
-      <c r="AI13" s="7">
-        <f t="shared" si="29"/>
-        <v>39710.630419419402</v>
-      </c>
-      <c r="AJ13" s="7">
-        <f t="shared" si="29"/>
-        <v>40539.906945995019</v>
+        <v>40170.469883700418</v>
+      </c>
+      <c r="AN13" s="7">
+        <f t="shared" si="25"/>
+        <v>41009.516940600268</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>20</v>
       </c>
@@ -2419,75 +2463,79 @@
         <v>39</v>
       </c>
       <c r="R14" s="3">
-        <v>185</v>
-      </c>
-      <c r="T14" s="3">
+        <v>210</v>
+      </c>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="X14" s="3">
         <v>533</v>
       </c>
-      <c r="U14" s="3">
+      <c r="Y14" s="3">
         <v>516</v>
       </c>
-      <c r="V14" s="3">
+      <c r="Z14" s="3">
         <v>513</v>
       </c>
-      <c r="W14" s="3">
+      <c r="AA14" s="3">
         <f>SUM(C14:F14)</f>
         <v>538</v>
       </c>
-      <c r="X14" s="3">
+      <c r="AB14" s="3">
         <f>SUM(G14:J14)</f>
         <v>644</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AC14" s="3">
         <f>SUM(K14:N14)</f>
         <v>641</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AD14" s="3">
         <f>SUM(O14:R14)</f>
-        <v>564</v>
-      </c>
-      <c r="AA14" s="3">
-        <f t="shared" ref="AA14:AJ14" si="30">Z14*1.03</f>
-        <v>580.91999999999996</v>
-      </c>
-      <c r="AB14" s="3">
-        <f t="shared" si="30"/>
-        <v>598.34759999999994</v>
-      </c>
-      <c r="AC14" s="3">
-        <f t="shared" si="30"/>
-        <v>616.29802799999993</v>
-      </c>
-      <c r="AD14" s="3">
-        <f t="shared" si="30"/>
-        <v>634.78696883999999</v>
+        <v>589</v>
       </c>
       <c r="AE14" s="3">
-        <f t="shared" si="30"/>
-        <v>653.83057790520002</v>
+        <f t="shared" ref="AE14:AN14" si="26">AD14*1.03</f>
+        <v>606.66999999999996</v>
       </c>
       <c r="AF14" s="3">
-        <f t="shared" si="30"/>
-        <v>673.44549524235606</v>
+        <f t="shared" si="26"/>
+        <v>624.87009999999998</v>
       </c>
       <c r="AG14" s="3">
-        <f t="shared" si="30"/>
-        <v>693.64886009962675</v>
+        <f t="shared" si="26"/>
+        <v>643.61620300000004</v>
       </c>
       <c r="AH14" s="3">
-        <f t="shared" si="30"/>
-        <v>714.45832590261557</v>
+        <f t="shared" si="26"/>
+        <v>662.92468909000002</v>
       </c>
       <c r="AI14" s="3">
-        <f t="shared" si="30"/>
-        <v>735.89207567969402</v>
+        <f t="shared" si="26"/>
+        <v>682.81242976270005</v>
       </c>
       <c r="AJ14" s="3">
-        <f t="shared" si="30"/>
-        <v>757.96883795008489</v>
+        <f t="shared" si="26"/>
+        <v>703.29680265558102</v>
+      </c>
+      <c r="AK14" s="3">
+        <f t="shared" si="26"/>
+        <v>724.3957067352485</v>
+      </c>
+      <c r="AL14" s="3">
+        <f t="shared" si="26"/>
+        <v>746.127577937306</v>
+      </c>
+      <c r="AM14" s="3">
+        <f t="shared" si="26"/>
+        <v>768.5114052754252</v>
+      </c>
+      <c r="AN14" s="3">
+        <f t="shared" si="26"/>
+        <v>791.56674743368796</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>21</v>
       </c>
@@ -2537,213 +2585,221 @@
         <v>-195</v>
       </c>
       <c r="R15" s="3">
-        <v>-200</v>
-      </c>
-      <c r="T15" s="3">
+        <v>-285</v>
+      </c>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="X15" s="3">
         <v>-416</v>
       </c>
-      <c r="U15" s="3">
+      <c r="Y15" s="3">
         <v>-225</v>
       </c>
-      <c r="V15" s="3">
+      <c r="Z15" s="3">
         <v>-772</v>
       </c>
-      <c r="W15" s="3">
+      <c r="AA15" s="3">
         <f>SUM(C15:F15)</f>
         <v>139</v>
       </c>
-      <c r="X15" s="3">
+      <c r="AB15" s="3">
         <f>SUM(G15:J15)</f>
         <v>-681</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AC15" s="3">
         <f>SUM(K15:N15)</f>
         <v>-962</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AD15" s="3">
         <f>SUM(O15:R15)</f>
-        <v>-704</v>
-      </c>
-      <c r="AA15" s="3">
-        <f t="shared" ref="AA15:AJ15" si="31">Z15*1.01</f>
-        <v>-711.04</v>
-      </c>
-      <c r="AB15" s="3">
-        <f t="shared" si="31"/>
-        <v>-718.15039999999999</v>
-      </c>
-      <c r="AC15" s="3">
-        <f t="shared" si="31"/>
-        <v>-725.33190400000001</v>
-      </c>
-      <c r="AD15" s="3">
-        <f t="shared" si="31"/>
-        <v>-732.58522303999996</v>
+        <v>-789</v>
       </c>
       <c r="AE15" s="3">
-        <f t="shared" si="31"/>
-        <v>-739.91107527039992</v>
+        <f t="shared" ref="AE15:AN15" si="27">AD15*1.01</f>
+        <v>-796.89</v>
       </c>
       <c r="AF15" s="3">
-        <f t="shared" si="31"/>
-        <v>-747.31018602310394</v>
+        <f t="shared" si="27"/>
+        <v>-804.85889999999995</v>
       </c>
       <c r="AG15" s="3">
-        <f t="shared" si="31"/>
-        <v>-754.78328788333499</v>
+        <f t="shared" si="27"/>
+        <v>-812.90748899999994</v>
       </c>
       <c r="AH15" s="3">
-        <f t="shared" si="31"/>
-        <v>-762.33112076216833</v>
+        <f t="shared" si="27"/>
+        <v>-821.03656388999991</v>
       </c>
       <c r="AI15" s="3">
-        <f t="shared" si="31"/>
-        <v>-769.95443196978999</v>
+        <f t="shared" si="27"/>
+        <v>-829.24692952889995</v>
       </c>
       <c r="AJ15" s="3">
-        <f t="shared" si="31"/>
-        <v>-777.6539762894879</v>
+        <f t="shared" si="27"/>
+        <v>-837.53939882418899</v>
+      </c>
+      <c r="AK15" s="3">
+        <f t="shared" si="27"/>
+        <v>-845.91479281243085</v>
+      </c>
+      <c r="AL15" s="3">
+        <f t="shared" si="27"/>
+        <v>-854.37394074055521</v>
+      </c>
+      <c r="AM15" s="3">
+        <f t="shared" si="27"/>
+        <v>-862.91768014796082</v>
+      </c>
+      <c r="AN15" s="3">
+        <f t="shared" si="27"/>
+        <v>-871.54685694944044</v>
       </c>
     </row>
-    <row r="16" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16"/>
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C16" s="7">
-        <f t="shared" ref="C16:L16" si="32">C13-C14-C15</f>
+        <f t="shared" ref="C16:L16" si="28">C13-C14-C15</f>
         <v>4897</v>
       </c>
       <c r="D16" s="7">
+        <f t="shared" si="28"/>
+        <v>4542</v>
+      </c>
+      <c r="E16" s="7">
+        <f t="shared" si="28"/>
+        <v>3829</v>
+      </c>
+      <c r="F16" s="7">
+        <f t="shared" si="28"/>
+        <v>4868</v>
+      </c>
+      <c r="G16" s="7">
+        <f t="shared" si="28"/>
+        <v>4977</v>
+      </c>
+      <c r="H16" s="7">
+        <f t="shared" si="28"/>
+        <v>5278</v>
+      </c>
+      <c r="I16" s="7">
+        <f t="shared" si="28"/>
+        <v>5146</v>
+      </c>
+      <c r="J16" s="7">
+        <f t="shared" si="28"/>
+        <v>5636</v>
+      </c>
+      <c r="K16" s="7">
+        <f t="shared" si="28"/>
+        <v>6042</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="28"/>
+        <v>5513</v>
+      </c>
+      <c r="M16" s="7">
+        <f t="shared" ref="M16:N16" si="29">M13-M14-M15</f>
+        <v>5989</v>
+      </c>
+      <c r="N16" s="7">
+        <f t="shared" si="29"/>
+        <v>6372</v>
+      </c>
+      <c r="O16" s="7">
+        <f t="shared" ref="O16:R16" si="30">O13-O14-O15</f>
+        <v>6200</v>
+      </c>
+      <c r="P16" s="7">
+        <f t="shared" si="30"/>
+        <v>5438</v>
+      </c>
+      <c r="Q16" s="7">
+        <f t="shared" si="30"/>
+        <v>6333</v>
+      </c>
+      <c r="R16" s="7">
+        <f t="shared" si="30"/>
+        <v>6223</v>
+      </c>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="X16" s="7">
+        <f t="shared" ref="X16:AD16" si="31">X13-X14-X15</f>
+        <v>14884</v>
+      </c>
+      <c r="Y16" s="7">
+        <f t="shared" si="31"/>
+        <v>13790</v>
+      </c>
+      <c r="Z16" s="7">
+        <f t="shared" si="31"/>
+        <v>16063</v>
+      </c>
+      <c r="AA16" s="7">
+        <f t="shared" si="31"/>
+        <v>18136</v>
+      </c>
+      <c r="AB16" s="7">
+        <f t="shared" si="31"/>
+        <v>21037</v>
+      </c>
+      <c r="AC16" s="7">
+        <f t="shared" si="31"/>
+        <v>23916</v>
+      </c>
+      <c r="AD16" s="7">
+        <f t="shared" si="31"/>
+        <v>24194</v>
+      </c>
+      <c r="AE16" s="7">
+        <f t="shared" ref="AE16:AN16" si="32">AE13-AE14-AE15</f>
+        <v>30252.420000000002</v>
+      </c>
+      <c r="AF16" s="7">
         <f t="shared" si="32"/>
-        <v>4542</v>
-      </c>
-      <c r="E16" s="7">
+        <v>32874.538800000002</v>
+      </c>
+      <c r="AG16" s="7">
         <f t="shared" si="32"/>
-        <v>3829</v>
-      </c>
-      <c r="F16" s="7">
+        <v>34563.118585999997</v>
+      </c>
+      <c r="AH16" s="7">
         <f t="shared" si="32"/>
-        <v>4868</v>
-      </c>
-      <c r="G16" s="7">
+        <v>35994.178560799992</v>
+      </c>
+      <c r="AI16" s="7">
         <f t="shared" si="32"/>
-        <v>4977</v>
-      </c>
-      <c r="H16" s="7">
+        <v>37125.399206226197</v>
+      </c>
+      <c r="AJ16" s="7">
         <f t="shared" si="32"/>
-        <v>5278</v>
-      </c>
-      <c r="I16" s="7">
+        <v>37887.033686797207</v>
+      </c>
+      <c r="AK16" s="7">
         <f t="shared" si="32"/>
-        <v>5146</v>
-      </c>
-      <c r="J16" s="7">
+        <v>38663.955559458147</v>
+      </c>
+      <c r="AL16" s="7">
         <f t="shared" si="32"/>
-        <v>5636</v>
-      </c>
-      <c r="K16" s="7">
+        <v>39456.467022201039</v>
+      </c>
+      <c r="AM16" s="7">
         <f t="shared" si="32"/>
-        <v>6042</v>
-      </c>
-      <c r="L16" s="7">
+        <v>40264.876158572952</v>
+      </c>
+      <c r="AN16" s="7">
         <f t="shared" si="32"/>
-        <v>5513</v>
-      </c>
-      <c r="M16" s="7">
-        <f t="shared" ref="M16:N16" si="33">M13-M14-M15</f>
-        <v>5989</v>
-      </c>
-      <c r="N16" s="7">
-        <f t="shared" si="33"/>
-        <v>6372</v>
-      </c>
-      <c r="O16" s="7">
-        <f t="shared" ref="O16:R16" si="34">O13-O14-O15</f>
-        <v>6200</v>
-      </c>
-      <c r="P16" s="7">
-        <f t="shared" si="34"/>
-        <v>5438</v>
-      </c>
-      <c r="Q16" s="7">
-        <f t="shared" si="34"/>
-        <v>6333</v>
-      </c>
-      <c r="R16" s="7">
-        <f t="shared" si="34"/>
-        <v>6493.808</v>
-      </c>
-      <c r="T16" s="7">
-        <f t="shared" ref="T16:Z16" si="35">T13-T14-T15</f>
-        <v>14884</v>
-      </c>
-      <c r="U16" s="7">
-        <f t="shared" si="35"/>
-        <v>13790</v>
-      </c>
-      <c r="V16" s="7">
-        <f t="shared" si="35"/>
-        <v>16063</v>
-      </c>
-      <c r="W16" s="7">
-        <f t="shared" si="35"/>
-        <v>18136</v>
-      </c>
-      <c r="X16" s="7">
-        <f t="shared" si="35"/>
-        <v>21037</v>
-      </c>
-      <c r="Y16" s="7">
-        <f t="shared" si="35"/>
-        <v>23916</v>
-      </c>
-      <c r="Z16" s="7">
-        <f t="shared" si="35"/>
-        <v>24464.808000000005</v>
-      </c>
-      <c r="AA16" s="7">
-        <f t="shared" ref="AA16:AJ16" si="36">AA13-AA14-AA15</f>
-        <v>29844.261200000004</v>
-      </c>
-      <c r="AB16" s="7">
-        <f t="shared" si="36"/>
-        <v>32441.488791520005</v>
-      </c>
-      <c r="AC16" s="7">
-        <f t="shared" si="36"/>
-        <v>34110.314761096</v>
-      </c>
-      <c r="AD16" s="7">
-        <f t="shared" si="36"/>
-        <v>35524.546286519835</v>
-      </c>
-      <c r="AE16" s="7">
-        <f t="shared" si="36"/>
-        <v>36642.355200711041</v>
-      </c>
-      <c r="AF16" s="7">
-        <f t="shared" si="36"/>
-        <v>37394.96062437199</v>
-      </c>
-      <c r="AG16" s="7">
-        <f t="shared" si="36"/>
-        <v>38162.684973587042</v>
-      </c>
-      <c r="AH16" s="7">
-        <f t="shared" si="36"/>
-        <v>38945.827372054613</v>
-      </c>
-      <c r="AI16" s="7">
-        <f t="shared" si="36"/>
-        <v>39744.692775709496</v>
-      </c>
-      <c r="AJ16" s="7">
-        <f t="shared" si="36"/>
-        <v>40559.592084334421</v>
+        <v>41089.497050116021</v>
       </c>
     </row>
-    <row r="17" spans="1:147" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:151" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>23</v>
       </c>
@@ -2793,699 +2849,706 @@
         <v>1061</v>
       </c>
       <c r="R17" s="3">
-        <f t="shared" ref="Q17:R17" si="37">R16*0.17</f>
-        <v>1103.9473600000001</v>
-      </c>
-      <c r="T17" s="3">
+        <v>1133</v>
+      </c>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="X17" s="3">
         <v>2804</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <v>2924</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>3752</v>
       </c>
-      <c r="W17" s="3">
+      <c r="AA17" s="3">
         <f>SUM(C17:F17)</f>
         <v>3079</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AB17" s="3">
         <f>SUM(G17:J17)</f>
         <v>3764</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AC17" s="3">
         <f>SUM(K17:N17)</f>
         <v>4173</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AD17" s="3">
         <f>SUM(O17:R17)</f>
-        <v>4106.9473600000001</v>
-      </c>
-      <c r="AA17" s="3">
-        <f t="shared" ref="AA17:AJ17" si="38">AA16*0.18</f>
-        <v>5371.9670160000005</v>
-      </c>
-      <c r="AB17" s="3">
-        <f t="shared" si="38"/>
-        <v>5839.4679824736004</v>
-      </c>
-      <c r="AC17" s="3">
-        <f t="shared" si="38"/>
-        <v>6139.85665699728</v>
-      </c>
-      <c r="AD17" s="3">
-        <f t="shared" si="38"/>
-        <v>6394.41833157357</v>
+        <v>4136</v>
       </c>
       <c r="AE17" s="3">
-        <f t="shared" si="38"/>
-        <v>6595.6239361279868</v>
+        <f t="shared" ref="AE17:AN17" si="33">AE16*0.18</f>
+        <v>5445.4355999999998</v>
       </c>
       <c r="AF17" s="3">
-        <f t="shared" si="38"/>
-        <v>6731.0929123869582</v>
+        <f t="shared" si="33"/>
+        <v>5917.4169840000004</v>
       </c>
       <c r="AG17" s="3">
-        <f t="shared" si="38"/>
-        <v>6869.2832952456674</v>
+        <f t="shared" si="33"/>
+        <v>6221.3613454799988</v>
       </c>
       <c r="AH17" s="3">
-        <f t="shared" si="38"/>
-        <v>7010.2489269698299</v>
+        <f t="shared" si="33"/>
+        <v>6478.9521409439985</v>
       </c>
       <c r="AI17" s="3">
-        <f t="shared" si="38"/>
-        <v>7154.0446996277087</v>
+        <f t="shared" si="33"/>
+        <v>6682.5718571207153</v>
       </c>
       <c r="AJ17" s="3">
-        <f t="shared" si="38"/>
-        <v>7300.7265751801951</v>
+        <f t="shared" si="33"/>
+        <v>6819.6660636234974</v>
+      </c>
+      <c r="AK17" s="3">
+        <f t="shared" si="33"/>
+        <v>6959.5120007024661</v>
+      </c>
+      <c r="AL17" s="3">
+        <f t="shared" si="33"/>
+        <v>7102.164063996187</v>
+      </c>
+      <c r="AM17" s="3">
+        <f t="shared" si="33"/>
+        <v>7247.6777085431313</v>
+      </c>
+      <c r="AN17" s="3">
+        <f t="shared" si="33"/>
+        <v>7396.1094690208838</v>
       </c>
     </row>
-    <row r="18" spans="1:147" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:151" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18"/>
       <c r="B18" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="7">
-        <f t="shared" ref="C18:L18" si="39">C16-C17</f>
+        <f t="shared" ref="C18:L18" si="34">C16-C17</f>
         <v>4059</v>
       </c>
       <c r="D18" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="34"/>
         <v>3647</v>
       </c>
       <c r="E18" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="34"/>
         <v>3411</v>
       </c>
       <c r="F18" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="34"/>
         <v>3940</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="34"/>
         <v>4179</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="34"/>
         <v>4257</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="34"/>
         <v>4156</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="34"/>
         <v>4681</v>
       </c>
       <c r="K18" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="34"/>
         <v>4890</v>
       </c>
       <c r="L18" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="34"/>
         <v>4663</v>
       </c>
       <c r="M18" s="7">
-        <f t="shared" ref="M18:O18" si="40">M16-M17</f>
+        <f t="shared" ref="M18:O18" si="35">M16-M17</f>
         <v>4872</v>
       </c>
       <c r="N18" s="7">
+        <f t="shared" si="35"/>
+        <v>5318</v>
+      </c>
+      <c r="O18" s="7">
+        <f t="shared" si="35"/>
+        <v>5119</v>
+      </c>
+      <c r="P18" s="7">
+        <f t="shared" ref="P18:R18" si="36">P16-P17</f>
+        <v>4577</v>
+      </c>
+      <c r="Q18" s="7">
+        <f t="shared" si="36"/>
+        <v>5272</v>
+      </c>
+      <c r="R18" s="7">
+        <f t="shared" si="36"/>
+        <v>5090</v>
+      </c>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="X18" s="7">
+        <f t="shared" ref="X18:AD18" si="37">X16-X17</f>
+        <v>12080</v>
+      </c>
+      <c r="Y18" s="7">
+        <f t="shared" si="37"/>
+        <v>10866</v>
+      </c>
+      <c r="Z18" s="7">
+        <f t="shared" si="37"/>
+        <v>12311</v>
+      </c>
+      <c r="AA18" s="7">
+        <f t="shared" si="37"/>
+        <v>15057</v>
+      </c>
+      <c r="AB18" s="7">
+        <f t="shared" si="37"/>
+        <v>17273</v>
+      </c>
+      <c r="AC18" s="7">
+        <f t="shared" si="37"/>
+        <v>19743</v>
+      </c>
+      <c r="AD18" s="7">
+        <f t="shared" si="37"/>
+        <v>20058</v>
+      </c>
+      <c r="AE18" s="7">
+        <f t="shared" ref="AE18:AN18" si="38">AE16-AE17</f>
+        <v>24806.984400000001</v>
+      </c>
+      <c r="AF18" s="7">
+        <f t="shared" si="38"/>
+        <v>26957.121816000003</v>
+      </c>
+      <c r="AG18" s="7">
+        <f t="shared" si="38"/>
+        <v>28341.757240519997</v>
+      </c>
+      <c r="AH18" s="7">
+        <f t="shared" si="38"/>
+        <v>29515.226419855993</v>
+      </c>
+      <c r="AI18" s="7">
+        <f t="shared" si="38"/>
+        <v>30442.827349105482</v>
+      </c>
+      <c r="AJ18" s="7">
+        <f t="shared" si="38"/>
+        <v>31067.367623173712</v>
+      </c>
+      <c r="AK18" s="7">
+        <f t="shared" si="38"/>
+        <v>31704.44355875568</v>
+      </c>
+      <c r="AL18" s="7">
+        <f t="shared" si="38"/>
+        <v>32354.302958204851</v>
+      </c>
+      <c r="AM18" s="7">
+        <f t="shared" si="38"/>
+        <v>33017.19845002982</v>
+      </c>
+      <c r="AN18" s="7">
+        <f t="shared" si="38"/>
+        <v>33693.387581095136</v>
+      </c>
+      <c r="AO18" s="6">
+        <f>AN18+($AR$23*AN18)</f>
+        <v>33356.453705284184</v>
+      </c>
+      <c r="AP18" s="6">
+        <f t="shared" ref="AP18:DA18" si="39">AO18+($AR$23*AO18)</f>
+        <v>33022.889168231341</v>
+      </c>
+      <c r="AQ18" s="6">
+        <f t="shared" si="39"/>
+        <v>32692.660276549028</v>
+      </c>
+      <c r="AR18" s="6">
+        <f t="shared" si="39"/>
+        <v>32365.733673783539</v>
+      </c>
+      <c r="AS18" s="6">
+        <f t="shared" si="39"/>
+        <v>32042.076337045703</v>
+      </c>
+      <c r="AT18" s="6">
+        <f t="shared" si="39"/>
+        <v>31721.655573675245</v>
+      </c>
+      <c r="AU18" s="6">
+        <f t="shared" si="39"/>
+        <v>31404.439017938494</v>
+      </c>
+      <c r="AV18" s="6">
+        <f t="shared" si="39"/>
+        <v>31090.394627759109</v>
+      </c>
+      <c r="AW18" s="6">
+        <f t="shared" si="39"/>
+        <v>30779.490681481519</v>
+      </c>
+      <c r="AX18" s="6">
+        <f t="shared" si="39"/>
+        <v>30471.695774666703</v>
+      </c>
+      <c r="AY18" s="6">
+        <f t="shared" si="39"/>
+        <v>30166.978816920036</v>
+      </c>
+      <c r="AZ18" s="6">
+        <f t="shared" si="39"/>
+        <v>29865.309028750835</v>
+      </c>
+      <c r="BA18" s="6">
+        <f t="shared" si="39"/>
+        <v>29566.655938463326</v>
+      </c>
+      <c r="BB18" s="6">
+        <f t="shared" si="39"/>
+        <v>29270.989379078692</v>
+      </c>
+      <c r="BC18" s="6">
+        <f t="shared" si="39"/>
+        <v>28978.279485287905</v>
+      </c>
+      <c r="BD18" s="6">
+        <f t="shared" si="39"/>
+        <v>28688.496690435026</v>
+      </c>
+      <c r="BE18" s="6">
+        <f t="shared" si="39"/>
+        <v>28401.611723530674</v>
+      </c>
+      <c r="BF18" s="6">
+        <f t="shared" si="39"/>
+        <v>28117.595606295366</v>
+      </c>
+      <c r="BG18" s="6">
+        <f t="shared" si="39"/>
+        <v>27836.419650232412</v>
+      </c>
+      <c r="BH18" s="6">
+        <f t="shared" si="39"/>
+        <v>27558.055453730089</v>
+      </c>
+      <c r="BI18" s="6">
+        <f t="shared" si="39"/>
+        <v>27282.474899192788</v>
+      </c>
+      <c r="BJ18" s="6">
+        <f t="shared" si="39"/>
+        <v>27009.650150200861</v>
+      </c>
+      <c r="BK18" s="6">
+        <f t="shared" si="39"/>
+        <v>26739.553648698853</v>
+      </c>
+      <c r="BL18" s="6">
+        <f t="shared" si="39"/>
+        <v>26472.158112211866</v>
+      </c>
+      <c r="BM18" s="6">
+        <f t="shared" si="39"/>
+        <v>26207.436531089748</v>
+      </c>
+      <c r="BN18" s="6">
+        <f t="shared" si="39"/>
+        <v>25945.36216577885</v>
+      </c>
+      <c r="BO18" s="6">
+        <f t="shared" si="39"/>
+        <v>25685.908544121063</v>
+      </c>
+      <c r="BP18" s="6">
+        <f t="shared" si="39"/>
+        <v>25429.049458679852</v>
+      </c>
+      <c r="BQ18" s="6">
+        <f t="shared" si="39"/>
+        <v>25174.758964093053</v>
+      </c>
+      <c r="BR18" s="6">
+        <f t="shared" si="39"/>
+        <v>24923.011374452122</v>
+      </c>
+      <c r="BS18" s="6">
+        <f t="shared" si="39"/>
+        <v>24673.781260707601</v>
+      </c>
+      <c r="BT18" s="6">
+        <f t="shared" si="39"/>
+        <v>24427.043448100525</v>
+      </c>
+      <c r="BU18" s="6">
+        <f t="shared" si="39"/>
+        <v>24182.77301361952</v>
+      </c>
+      <c r="BV18" s="6">
+        <f t="shared" si="39"/>
+        <v>23940.945283483325</v>
+      </c>
+      <c r="BW18" s="6">
+        <f t="shared" si="39"/>
+        <v>23701.535830648492</v>
+      </c>
+      <c r="BX18" s="6">
+        <f t="shared" si="39"/>
+        <v>23464.520472342007</v>
+      </c>
+      <c r="BY18" s="6">
+        <f t="shared" si="39"/>
+        <v>23229.875267618587</v>
+      </c>
+      <c r="BZ18" s="6">
+        <f t="shared" si="39"/>
+        <v>22997.576514942401</v>
+      </c>
+      <c r="CA18" s="6">
+        <f t="shared" si="39"/>
+        <v>22767.600749792975</v>
+      </c>
+      <c r="CB18" s="6">
+        <f t="shared" si="39"/>
+        <v>22539.924742295047</v>
+      </c>
+      <c r="CC18" s="6">
+        <f t="shared" si="39"/>
+        <v>22314.525494872098</v>
+      </c>
+      <c r="CD18" s="6">
+        <f t="shared" si="39"/>
+        <v>22091.380239923375</v>
+      </c>
+      <c r="CE18" s="6">
+        <f t="shared" si="39"/>
+        <v>21870.466437524141</v>
+      </c>
+      <c r="CF18" s="6">
+        <f t="shared" si="39"/>
+        <v>21651.761773148901</v>
+      </c>
+      <c r="CG18" s="6">
+        <f t="shared" si="39"/>
+        <v>21435.244155417411</v>
+      </c>
+      <c r="CH18" s="6">
+        <f t="shared" si="39"/>
+        <v>21220.891713863239</v>
+      </c>
+      <c r="CI18" s="6">
+        <f t="shared" si="39"/>
+        <v>21008.682796724606</v>
+      </c>
+      <c r="CJ18" s="6">
+        <f t="shared" si="39"/>
+        <v>20798.59596875736</v>
+      </c>
+      <c r="CK18" s="6">
+        <f t="shared" si="39"/>
+        <v>20590.610009069787</v>
+      </c>
+      <c r="CL18" s="6">
+        <f t="shared" si="39"/>
+        <v>20384.703908979089</v>
+      </c>
+      <c r="CM18" s="6">
+        <f t="shared" si="39"/>
+        <v>20180.8568698893</v>
+      </c>
+      <c r="CN18" s="6">
+        <f t="shared" si="39"/>
+        <v>19979.048301190407</v>
+      </c>
+      <c r="CO18" s="6">
+        <f t="shared" si="39"/>
+        <v>19779.257818178503</v>
+      </c>
+      <c r="CP18" s="6">
+        <f t="shared" si="39"/>
+        <v>19581.465239996716</v>
+      </c>
+      <c r="CQ18" s="6">
+        <f t="shared" si="39"/>
+        <v>19385.650587596749</v>
+      </c>
+      <c r="CR18" s="6">
+        <f t="shared" si="39"/>
+        <v>19191.794081720782</v>
+      </c>
+      <c r="CS18" s="6">
+        <f t="shared" si="39"/>
+        <v>18999.876140903572</v>
+      </c>
+      <c r="CT18" s="6">
+        <f t="shared" si="39"/>
+        <v>18809.877379494537</v>
+      </c>
+      <c r="CU18" s="6">
+        <f t="shared" si="39"/>
+        <v>18621.77860569959</v>
+      </c>
+      <c r="CV18" s="6">
+        <f t="shared" si="39"/>
+        <v>18435.560819642593</v>
+      </c>
+      <c r="CW18" s="6">
+        <f t="shared" si="39"/>
+        <v>18251.205211446166</v>
+      </c>
+      <c r="CX18" s="6">
+        <f t="shared" si="39"/>
+        <v>18068.693159331706</v>
+      </c>
+      <c r="CY18" s="6">
+        <f t="shared" si="39"/>
+        <v>17888.006227738388</v>
+      </c>
+      <c r="CZ18" s="6">
+        <f t="shared" si="39"/>
+        <v>17709.126165461003</v>
+      </c>
+      <c r="DA18" s="6">
+        <f t="shared" si="39"/>
+        <v>17532.034903806394</v>
+      </c>
+      <c r="DB18" s="6">
+        <f t="shared" ref="DB18:EU18" si="40">DA18+($AR$23*DA18)</f>
+        <v>17356.714554768329</v>
+      </c>
+      <c r="DC18" s="6">
         <f t="shared" si="40"/>
-        <v>5318</v>
-      </c>
-      <c r="O18" s="7">
+        <v>17183.147409220644</v>
+      </c>
+      <c r="DD18" s="6">
         <f t="shared" si="40"/>
-        <v>5119</v>
-      </c>
-      <c r="P18" s="7">
-        <f t="shared" ref="P18:R18" si="41">P16-P17</f>
-        <v>4577</v>
-      </c>
-      <c r="Q18" s="7">
-        <f t="shared" si="41"/>
-        <v>5272</v>
-      </c>
-      <c r="R18" s="7">
-        <f t="shared" si="41"/>
-        <v>5389.8606399999999</v>
-      </c>
-      <c r="T18" s="7">
-        <f t="shared" ref="T18:Z18" si="42">T16-T17</f>
-        <v>12080</v>
-      </c>
-      <c r="U18" s="7">
-        <f t="shared" si="42"/>
-        <v>10866</v>
-      </c>
-      <c r="V18" s="7">
-        <f t="shared" si="42"/>
-        <v>12311</v>
-      </c>
-      <c r="W18" s="7">
-        <f t="shared" si="42"/>
-        <v>15057</v>
-      </c>
-      <c r="X18" s="7">
-        <f t="shared" si="42"/>
-        <v>17273</v>
-      </c>
-      <c r="Y18" s="7">
-        <f t="shared" si="42"/>
-        <v>19743</v>
-      </c>
-      <c r="Z18" s="7">
-        <f t="shared" si="42"/>
-        <v>20357.860640000006</v>
-      </c>
-      <c r="AA18" s="7">
-        <f t="shared" ref="AA18:AJ18" si="43">AA16-AA17</f>
-        <v>24472.294184000006</v>
-      </c>
-      <c r="AB18" s="7">
-        <f t="shared" si="43"/>
-        <v>26602.020809046404</v>
-      </c>
-      <c r="AC18" s="7">
-        <f t="shared" si="43"/>
-        <v>27970.458104098721</v>
-      </c>
-      <c r="AD18" s="7">
-        <f t="shared" si="43"/>
-        <v>29130.127954946263</v>
-      </c>
-      <c r="AE18" s="7">
-        <f t="shared" si="43"/>
-        <v>30046.731264583053</v>
-      </c>
-      <c r="AF18" s="7">
-        <f t="shared" si="43"/>
-        <v>30663.867711985033</v>
-      </c>
-      <c r="AG18" s="7">
-        <f t="shared" si="43"/>
-        <v>31293.401678341375</v>
-      </c>
-      <c r="AH18" s="7">
-        <f t="shared" si="43"/>
-        <v>31935.578445084782</v>
-      </c>
-      <c r="AI18" s="7">
-        <f t="shared" si="43"/>
-        <v>32590.648076081787</v>
-      </c>
-      <c r="AJ18" s="7">
-        <f t="shared" si="43"/>
-        <v>33258.865509154224</v>
-      </c>
-      <c r="AK18" s="6">
-        <f>AJ18+($AN$23*AJ18)</f>
-        <v>32926.276854062678</v>
-      </c>
-      <c r="AL18" s="6">
-        <f t="shared" ref="AL18:CW18" si="44">AK18+($AN$23*AK18)</f>
-        <v>32597.014085522052</v>
-      </c>
-      <c r="AM18" s="6">
-        <f t="shared" si="44"/>
-        <v>32271.043944666832</v>
-      </c>
-      <c r="AN18" s="6">
-        <f t="shared" si="44"/>
-        <v>31948.333505220162</v>
-      </c>
-      <c r="AO18" s="6">
-        <f t="shared" si="44"/>
-        <v>31628.85017016796</v>
-      </c>
-      <c r="AP18" s="6">
-        <f t="shared" si="44"/>
-        <v>31312.561668466282</v>
-      </c>
-      <c r="AQ18" s="6">
-        <f t="shared" si="44"/>
-        <v>30999.43605178162</v>
-      </c>
-      <c r="AR18" s="6">
-        <f t="shared" si="44"/>
-        <v>30689.441691263804</v>
-      </c>
-      <c r="AS18" s="6">
-        <f t="shared" si="44"/>
-        <v>30382.547274351167</v>
-      </c>
-      <c r="AT18" s="6">
-        <f t="shared" si="44"/>
-        <v>30078.721801607655</v>
-      </c>
-      <c r="AU18" s="6">
-        <f t="shared" si="44"/>
-        <v>29777.934583591577</v>
-      </c>
-      <c r="AV18" s="6">
-        <f t="shared" si="44"/>
-        <v>29480.155237755662</v>
-      </c>
-      <c r="AW18" s="6">
-        <f t="shared" si="44"/>
-        <v>29185.353685378104</v>
-      </c>
-      <c r="AX18" s="6">
-        <f t="shared" si="44"/>
-        <v>28893.500148524323</v>
-      </c>
-      <c r="AY18" s="6">
-        <f t="shared" si="44"/>
-        <v>28604.56514703908</v>
-      </c>
-      <c r="AZ18" s="6">
-        <f t="shared" si="44"/>
-        <v>28318.519495568689</v>
-      </c>
-      <c r="BA18" s="6">
-        <f t="shared" si="44"/>
-        <v>28035.334300613002</v>
-      </c>
-      <c r="BB18" s="6">
-        <f t="shared" si="44"/>
-        <v>27754.980957606873</v>
-      </c>
-      <c r="BC18" s="6">
-        <f t="shared" si="44"/>
-        <v>27477.431148030802</v>
-      </c>
-      <c r="BD18" s="6">
-        <f t="shared" si="44"/>
-        <v>27202.656836550494</v>
-      </c>
-      <c r="BE18" s="6">
-        <f t="shared" si="44"/>
-        <v>26930.630268184988</v>
-      </c>
-      <c r="BF18" s="6">
-        <f t="shared" si="44"/>
-        <v>26661.323965503139</v>
-      </c>
-      <c r="BG18" s="6">
-        <f t="shared" si="44"/>
-        <v>26394.710725848108</v>
-      </c>
-      <c r="BH18" s="6">
-        <f t="shared" si="44"/>
-        <v>26130.763618589626</v>
-      </c>
-      <c r="BI18" s="6">
-        <f t="shared" si="44"/>
-        <v>25869.455982403731</v>
-      </c>
-      <c r="BJ18" s="6">
-        <f t="shared" si="44"/>
-        <v>25610.761422579693</v>
-      </c>
-      <c r="BK18" s="6">
-        <f t="shared" si="44"/>
-        <v>25354.653808353898</v>
-      </c>
-      <c r="BL18" s="6">
-        <f t="shared" si="44"/>
-        <v>25101.10727027036</v>
-      </c>
-      <c r="BM18" s="6">
-        <f t="shared" si="44"/>
-        <v>24850.096197567658</v>
-      </c>
-      <c r="BN18" s="6">
-        <f t="shared" si="44"/>
-        <v>24601.59523559198</v>
-      </c>
-      <c r="BO18" s="6">
-        <f t="shared" si="44"/>
-        <v>24355.57928323606</v>
-      </c>
-      <c r="BP18" s="6">
-        <f t="shared" si="44"/>
-        <v>24112.023490403699</v>
-      </c>
-      <c r="BQ18" s="6">
-        <f t="shared" si="44"/>
-        <v>23870.903255499663</v>
-      </c>
-      <c r="BR18" s="6">
-        <f t="shared" si="44"/>
-        <v>23632.194222944665</v>
-      </c>
-      <c r="BS18" s="6">
-        <f t="shared" si="44"/>
-        <v>23395.872280715219</v>
-      </c>
-      <c r="BT18" s="6">
-        <f t="shared" si="44"/>
-        <v>23161.913557908068</v>
-      </c>
-      <c r="BU18" s="6">
-        <f t="shared" si="44"/>
-        <v>22930.294422328989</v>
-      </c>
-      <c r="BV18" s="6">
-        <f t="shared" si="44"/>
-        <v>22700.991478105698</v>
-      </c>
-      <c r="BW18" s="6">
-        <f t="shared" si="44"/>
-        <v>22473.98156332464</v>
-      </c>
-      <c r="BX18" s="6">
-        <f t="shared" si="44"/>
-        <v>22249.241747691394</v>
-      </c>
-      <c r="BY18" s="6">
-        <f t="shared" si="44"/>
-        <v>22026.749330214479</v>
-      </c>
-      <c r="BZ18" s="6">
-        <f t="shared" si="44"/>
-        <v>21806.481836912335</v>
-      </c>
-      <c r="CA18" s="6">
-        <f t="shared" si="44"/>
-        <v>21588.417018543212</v>
-      </c>
-      <c r="CB18" s="6">
-        <f t="shared" si="44"/>
-        <v>21372.53284835778</v>
-      </c>
-      <c r="CC18" s="6">
-        <f t="shared" si="44"/>
-        <v>21158.807519874201</v>
-      </c>
-      <c r="CD18" s="6">
-        <f t="shared" si="44"/>
-        <v>20947.219444675458</v>
-      </c>
-      <c r="CE18" s="6">
-        <f t="shared" si="44"/>
-        <v>20737.747250228706</v>
-      </c>
-      <c r="CF18" s="6">
-        <f t="shared" si="44"/>
-        <v>20530.369777726417</v>
-      </c>
-      <c r="CG18" s="6">
-        <f t="shared" si="44"/>
-        <v>20325.066079949152</v>
-      </c>
-      <c r="CH18" s="6">
-        <f t="shared" si="44"/>
-        <v>20121.815419149661</v>
-      </c>
-      <c r="CI18" s="6">
-        <f t="shared" si="44"/>
-        <v>19920.597264958164</v>
-      </c>
-      <c r="CJ18" s="6">
-        <f t="shared" si="44"/>
-        <v>19721.391292308581</v>
-      </c>
-      <c r="CK18" s="6">
-        <f t="shared" si="44"/>
-        <v>19524.177379385495</v>
-      </c>
-      <c r="CL18" s="6">
-        <f t="shared" si="44"/>
-        <v>19328.93560559164</v>
-      </c>
-      <c r="CM18" s="6">
-        <f t="shared" si="44"/>
-        <v>19135.646249535723</v>
-      </c>
-      <c r="CN18" s="6">
-        <f t="shared" si="44"/>
-        <v>18944.289787040365</v>
-      </c>
-      <c r="CO18" s="6">
-        <f t="shared" si="44"/>
-        <v>18754.846889169959</v>
-      </c>
-      <c r="CP18" s="6">
-        <f t="shared" si="44"/>
-        <v>18567.298420278261</v>
-      </c>
-      <c r="CQ18" s="6">
-        <f t="shared" si="44"/>
-        <v>18381.625436075479</v>
-      </c>
-      <c r="CR18" s="6">
-        <f t="shared" si="44"/>
-        <v>18197.809181714725</v>
-      </c>
-      <c r="CS18" s="6">
-        <f t="shared" si="44"/>
-        <v>18015.83108989758</v>
-      </c>
-      <c r="CT18" s="6">
-        <f t="shared" si="44"/>
-        <v>17835.672778998603</v>
-      </c>
-      <c r="CU18" s="6">
-        <f t="shared" si="44"/>
-        <v>17657.316051208618</v>
-      </c>
-      <c r="CV18" s="6">
-        <f t="shared" si="44"/>
-        <v>17480.742890696532</v>
-      </c>
-      <c r="CW18" s="6">
-        <f t="shared" si="44"/>
-        <v>17305.935461789566</v>
-      </c>
-      <c r="CX18" s="6">
-        <f t="shared" ref="CX18:EQ18" si="45">CW18+($AN$23*CW18)</f>
-        <v>17132.876107171669</v>
-      </c>
-      <c r="CY18" s="6">
-        <f t="shared" si="45"/>
-        <v>16961.547346099953</v>
-      </c>
-      <c r="CZ18" s="6">
-        <f t="shared" si="45"/>
-        <v>16791.931872638954</v>
-      </c>
-      <c r="DA18" s="6">
-        <f t="shared" si="45"/>
-        <v>16624.012553912566</v>
-      </c>
-      <c r="DB18" s="6">
-        <f t="shared" si="45"/>
-        <v>16457.772428373439</v>
-      </c>
-      <c r="DC18" s="6">
-        <f t="shared" si="45"/>
-        <v>16293.194704089705</v>
-      </c>
-      <c r="DD18" s="6">
-        <f t="shared" si="45"/>
-        <v>16130.262757048808</v>
+        <v>17011.315935128438</v>
       </c>
       <c r="DE18" s="6">
-        <f t="shared" si="45"/>
-        <v>15968.960129478319</v>
+        <f t="shared" si="40"/>
+        <v>16841.202775777154</v>
       </c>
       <c r="DF18" s="6">
-        <f t="shared" si="45"/>
-        <v>15809.270528183535</v>
+        <f t="shared" si="40"/>
+        <v>16672.790748019383</v>
       </c>
       <c r="DG18" s="6">
-        <f t="shared" si="45"/>
-        <v>15651.1778229017</v>
+        <f t="shared" si="40"/>
+        <v>16506.062840539187</v>
       </c>
       <c r="DH18" s="6">
-        <f t="shared" si="45"/>
-        <v>15494.666044672684</v>
+        <f t="shared" si="40"/>
+        <v>16341.002212133795</v>
       </c>
       <c r="DI18" s="6">
-        <f t="shared" si="45"/>
-        <v>15339.719384225957</v>
+        <f t="shared" si="40"/>
+        <v>16177.592190012458</v>
       </c>
       <c r="DJ18" s="6">
-        <f t="shared" si="45"/>
-        <v>15186.322190383697</v>
+        <f t="shared" si="40"/>
+        <v>16015.816268112332</v>
       </c>
       <c r="DK18" s="6">
-        <f t="shared" si="45"/>
-        <v>15034.458968479859</v>
+        <f t="shared" si="40"/>
+        <v>15855.658105431208</v>
       </c>
       <c r="DL18" s="6">
-        <f t="shared" si="45"/>
-        <v>14884.11437879506</v>
+        <f t="shared" si="40"/>
+        <v>15697.101524376896</v>
       </c>
       <c r="DM18" s="6">
-        <f t="shared" si="45"/>
-        <v>14735.273235007109</v>
+        <f t="shared" si="40"/>
+        <v>15540.130509133127</v>
       </c>
       <c r="DN18" s="6">
-        <f t="shared" si="45"/>
-        <v>14587.920502657038</v>
+        <f t="shared" si="40"/>
+        <v>15384.729204041796</v>
       </c>
       <c r="DO18" s="6">
-        <f t="shared" si="45"/>
-        <v>14442.041297630467</v>
+        <f t="shared" si="40"/>
+        <v>15230.881912001378</v>
       </c>
       <c r="DP18" s="6">
-        <f t="shared" si="45"/>
-        <v>14297.620884654163</v>
+        <f t="shared" si="40"/>
+        <v>15078.573092881365</v>
       </c>
       <c r="DQ18" s="6">
-        <f t="shared" si="45"/>
-        <v>14154.644675807622</v>
+        <f t="shared" si="40"/>
+        <v>14927.787361952551</v>
       </c>
       <c r="DR18" s="6">
-        <f t="shared" si="45"/>
-        <v>14013.098229049545</v>
+        <f t="shared" si="40"/>
+        <v>14778.509488333026</v>
       </c>
       <c r="DS18" s="6">
-        <f t="shared" si="45"/>
-        <v>13872.96724675905</v>
+        <f t="shared" si="40"/>
+        <v>14630.724393449695</v>
       </c>
       <c r="DT18" s="6">
-        <f t="shared" si="45"/>
-        <v>13734.237574291459</v>
+        <f t="shared" si="40"/>
+        <v>14484.417149515197</v>
       </c>
       <c r="DU18" s="6">
-        <f t="shared" si="45"/>
-        <v>13596.895198548544</v>
+        <f t="shared" si="40"/>
+        <v>14339.572978020045</v>
       </c>
       <c r="DV18" s="6">
-        <f t="shared" si="45"/>
-        <v>13460.926246563058</v>
+        <f t="shared" si="40"/>
+        <v>14196.177248239845</v>
       </c>
       <c r="DW18" s="6">
-        <f t="shared" si="45"/>
-        <v>13326.316984097428</v>
+        <f t="shared" si="40"/>
+        <v>14054.215475757446</v>
       </c>
       <c r="DX18" s="6">
-        <f t="shared" si="45"/>
-        <v>13193.053814256453</v>
+        <f t="shared" si="40"/>
+        <v>13913.673320999871</v>
       </c>
       <c r="DY18" s="6">
-        <f t="shared" si="45"/>
-        <v>13061.123276113889</v>
+        <f t="shared" si="40"/>
+        <v>13774.536587789873</v>
       </c>
       <c r="DZ18" s="6">
-        <f t="shared" si="45"/>
-        <v>12930.51204335275</v>
+        <f t="shared" si="40"/>
+        <v>13636.791221911973</v>
       </c>
       <c r="EA18" s="6">
-        <f t="shared" si="45"/>
-        <v>12801.206922919222</v>
+        <f t="shared" si="40"/>
+        <v>13500.423309692853</v>
       </c>
       <c r="EB18" s="6">
-        <f t="shared" si="45"/>
-        <v>12673.194853690029</v>
+        <f t="shared" si="40"/>
+        <v>13365.419076595925</v>
       </c>
       <c r="EC18" s="6">
-        <f t="shared" si="45"/>
-        <v>12546.462905153128</v>
+        <f t="shared" si="40"/>
+        <v>13231.764885829965</v>
       </c>
       <c r="ED18" s="6">
-        <f t="shared" si="45"/>
-        <v>12420.998276101596</v>
+        <f t="shared" si="40"/>
+        <v>13099.447236971666</v>
       </c>
       <c r="EE18" s="6">
-        <f t="shared" si="45"/>
-        <v>12296.78829334058</v>
+        <f t="shared" si="40"/>
+        <v>12968.452764601949</v>
       </c>
       <c r="EF18" s="6">
-        <f t="shared" si="45"/>
-        <v>12173.820410407174</v>
+        <f t="shared" si="40"/>
+        <v>12838.76823695593</v>
       </c>
       <c r="EG18" s="6">
-        <f t="shared" si="45"/>
-        <v>12052.082206303103</v>
+        <f t="shared" si="40"/>
+        <v>12710.380554586371</v>
       </c>
       <c r="EH18" s="6">
-        <f t="shared" si="45"/>
-        <v>11931.561384240073</v>
+        <f t="shared" si="40"/>
+        <v>12583.276749040508</v>
       </c>
       <c r="EI18" s="6">
-        <f t="shared" si="45"/>
-        <v>11812.245770397672</v>
+        <f t="shared" si="40"/>
+        <v>12457.443981550103</v>
       </c>
       <c r="EJ18" s="6">
-        <f t="shared" si="45"/>
-        <v>11694.123312693695</v>
+        <f t="shared" si="40"/>
+        <v>12332.869541734603</v>
       </c>
       <c r="EK18" s="6">
-        <f t="shared" si="45"/>
-        <v>11577.182079566757</v>
+        <f t="shared" si="40"/>
+        <v>12209.540846317257</v>
       </c>
       <c r="EL18" s="6">
-        <f t="shared" si="45"/>
-        <v>11461.41025877109</v>
+        <f t="shared" si="40"/>
+        <v>12087.445437854085</v>
       </c>
       <c r="EM18" s="6">
-        <f t="shared" si="45"/>
-        <v>11346.796156183378</v>
+        <f t="shared" si="40"/>
+        <v>11966.570983475543</v>
       </c>
       <c r="EN18" s="6">
-        <f t="shared" si="45"/>
-        <v>11233.328194621545</v>
+        <f t="shared" si="40"/>
+        <v>11846.905273640788</v>
       </c>
       <c r="EO18" s="6">
-        <f t="shared" si="45"/>
-        <v>11120.994912675329</v>
+        <f t="shared" si="40"/>
+        <v>11728.436220904381</v>
       </c>
       <c r="EP18" s="6">
-        <f t="shared" si="45"/>
-        <v>11009.784963548576</v>
+        <f t="shared" si="40"/>
+        <v>11611.151858695337</v>
       </c>
       <c r="EQ18" s="6">
-        <f t="shared" si="45"/>
-        <v>10899.687113913091</v>
+        <f t="shared" si="40"/>
+        <v>11495.040340108384</v>
+      </c>
+      <c r="ER18" s="6">
+        <f t="shared" si="40"/>
+        <v>11380.0899367073</v>
+      </c>
+      <c r="ES18" s="6">
+        <f t="shared" si="40"/>
+        <v>11266.289037340226</v>
+      </c>
+      <c r="ET18" s="6">
+        <f t="shared" si="40"/>
+        <v>11153.626146966824</v>
+      </c>
+      <c r="EU18" s="6">
+        <f t="shared" si="40"/>
+        <v>11042.089885497157</v>
       </c>
     </row>
-    <row r="19" spans="1:147" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:151" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>1</v>
       </c>
       <c r="C19" s="3">
-        <f t="shared" ref="C19:L19" si="46">1574.2+245.5+9.3</f>
+        <f t="shared" ref="C19:L19" si="41">1574.2+245.5+9.3</f>
         <v>1829</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>1829</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>1829</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>1829</v>
       </c>
       <c r="G19" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>1829</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>1829</v>
       </c>
       <c r="I19" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>1829</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>1829</v>
       </c>
       <c r="K19" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>1829</v>
       </c>
       <c r="L19" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>1829</v>
       </c>
       <c r="M19" s="3">
@@ -3508,216 +3571,224 @@
         <v>1843</v>
       </c>
       <c r="R19" s="3">
-        <f>1709+5+120+9</f>
-        <v>1843</v>
-      </c>
-      <c r="T19" s="3">
-        <f t="shared" ref="T19:X19" si="47">1574.2+245.5+9.3</f>
+        <f>1696+5+120+9</f>
+        <v>1830</v>
+      </c>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="X19" s="3">
+        <f t="shared" ref="X19:AB19" si="42">1574.2+245.5+9.3</f>
         <v>1829</v>
       </c>
-      <c r="U19" s="3">
-        <f t="shared" si="47"/>
+      <c r="Y19" s="3">
+        <f t="shared" si="42"/>
         <v>1829</v>
       </c>
-      <c r="V19" s="3">
-        <f t="shared" si="47"/>
+      <c r="Z19" s="3">
+        <f t="shared" si="42"/>
         <v>1829</v>
       </c>
-      <c r="W19" s="3">
-        <f t="shared" si="47"/>
+      <c r="AA19" s="3">
+        <f t="shared" si="42"/>
         <v>1829</v>
       </c>
-      <c r="X19" s="3">
-        <f t="shared" si="47"/>
+      <c r="AB19" s="3">
+        <f t="shared" si="42"/>
         <v>1829</v>
       </c>
-      <c r="Y19" s="3">
-        <f t="shared" ref="Y19" si="48">1728.1+4.8+120.3+9.6</f>
+      <c r="AC19" s="3">
+        <f t="shared" ref="AC19" si="43">1728.1+4.8+120.3+9.6</f>
         <v>1862.7999999999997</v>
       </c>
-      <c r="Z19" s="3">
-        <f>1709+5+120+9</f>
-        <v>1843</v>
-      </c>
-      <c r="AA19" s="3">
-        <f>1709+5+120+9</f>
-        <v>1843</v>
-      </c>
-      <c r="AB19" s="3">
-        <f>1709+5+120+9</f>
-        <v>1843</v>
-      </c>
-      <c r="AC19" s="3">
-        <f>1709+5+120+9</f>
-        <v>1843</v>
-      </c>
       <c r="AD19" s="3">
-        <f>1709+5+120+9</f>
-        <v>1843</v>
+        <f t="shared" ref="AD19:AN19" si="44">1696+5+120+9</f>
+        <v>1830</v>
       </c>
       <c r="AE19" s="3">
-        <f>1709+5+120+9</f>
-        <v>1843</v>
+        <f t="shared" si="44"/>
+        <v>1830</v>
       </c>
       <c r="AF19" s="3">
-        <f>1709+5+120+9</f>
-        <v>1843</v>
+        <f t="shared" si="44"/>
+        <v>1830</v>
       </c>
       <c r="AG19" s="3">
-        <f>1709+5+120+9</f>
-        <v>1843</v>
+        <f t="shared" si="44"/>
+        <v>1830</v>
       </c>
       <c r="AH19" s="3">
-        <f>1709+5+120+9</f>
-        <v>1843</v>
+        <f t="shared" si="44"/>
+        <v>1830</v>
       </c>
       <c r="AI19" s="3">
-        <f>1709+5+120+9</f>
-        <v>1843</v>
+        <f t="shared" si="44"/>
+        <v>1830</v>
       </c>
       <c r="AJ19" s="3">
-        <f>1709+5+120+9</f>
-        <v>1843</v>
+        <f t="shared" si="44"/>
+        <v>1830</v>
+      </c>
+      <c r="AK19" s="3">
+        <f t="shared" si="44"/>
+        <v>1830</v>
+      </c>
+      <c r="AL19" s="3">
+        <f t="shared" si="44"/>
+        <v>1830</v>
+      </c>
+      <c r="AM19" s="3">
+        <f t="shared" si="44"/>
+        <v>1830</v>
+      </c>
+      <c r="AN19" s="3">
+        <f t="shared" si="44"/>
+        <v>1830</v>
       </c>
     </row>
-    <row r="20" spans="1:147" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:151" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="5">
-        <f t="shared" ref="C20:L20" si="49">C18/C19</f>
+        <f t="shared" ref="C20:L20" si="45">C18/C19</f>
         <v>2.2192454893384364</v>
       </c>
       <c r="D20" s="5">
+        <f t="shared" si="45"/>
+        <v>1.9939857845817386</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" si="45"/>
+        <v>1.8649535265172226</v>
+      </c>
+      <c r="F20" s="5">
+        <f t="shared" si="45"/>
+        <v>2.1541826134499726</v>
+      </c>
+      <c r="G20" s="5">
+        <f t="shared" si="45"/>
+        <v>2.2848551120831053</v>
+      </c>
+      <c r="H20" s="5">
+        <f t="shared" si="45"/>
+        <v>2.3275013668671405</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="45"/>
+        <v>2.2722799343903772</v>
+      </c>
+      <c r="J20" s="5">
+        <f t="shared" si="45"/>
+        <v>2.5593220338983049</v>
+      </c>
+      <c r="K20" s="5">
+        <f t="shared" si="45"/>
+        <v>2.6735921268452705</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" si="45"/>
+        <v>2.5494805904866049</v>
+      </c>
+      <c r="M20" s="5">
+        <f t="shared" ref="M20:O20" si="46">M18/M19</f>
+        <v>2.6739846322722283</v>
+      </c>
+      <c r="N20" s="5">
+        <f t="shared" si="46"/>
+        <v>2.854842173072794</v>
+      </c>
+      <c r="O20" s="5">
+        <f t="shared" si="46"/>
+        <v>2.7555579480002153</v>
+      </c>
+      <c r="P20" s="5">
+        <f t="shared" ref="P20:R20" si="47">P18/P19</f>
+        <v>2.4806243564034469</v>
+      </c>
+      <c r="Q20" s="5">
+        <f t="shared" si="47"/>
+        <v>2.8605534454693435</v>
+      </c>
+      <c r="R20" s="5">
+        <f t="shared" si="47"/>
+        <v>2.7814207650273226</v>
+      </c>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="X20" s="5">
+        <f t="shared" ref="X20:AD20" si="48">X18/X19</f>
+        <v>6.6047020229633677</v>
+      </c>
+      <c r="Y20" s="5">
+        <f t="shared" si="48"/>
+        <v>5.9409513395297981</v>
+      </c>
+      <c r="Z20" s="5">
+        <f t="shared" si="48"/>
+        <v>6.7310005467468565</v>
+      </c>
+      <c r="AA20" s="5">
+        <f t="shared" si="48"/>
+        <v>8.2323674138873706</v>
+      </c>
+      <c r="AB20" s="5">
+        <f t="shared" si="48"/>
+        <v>9.4439584472389289</v>
+      </c>
+      <c r="AC20" s="5">
+        <f t="shared" si="48"/>
+        <v>10.598561305561521</v>
+      </c>
+      <c r="AD20" s="5">
+        <f t="shared" si="48"/>
+        <v>10.960655737704919</v>
+      </c>
+      <c r="AE20" s="5">
+        <f t="shared" ref="AE20:AN20" si="49">AE18/AE19</f>
+        <v>13.555729180327869</v>
+      </c>
+      <c r="AF20" s="5">
         <f t="shared" si="49"/>
-        <v>1.9939857845817386</v>
-      </c>
-      <c r="E20" s="5">
+        <v>14.730667659016396</v>
+      </c>
+      <c r="AG20" s="5">
         <f t="shared" si="49"/>
-        <v>1.8649535265172226</v>
-      </c>
-      <c r="F20" s="5">
+        <v>15.487299038535518</v>
+      </c>
+      <c r="AH20" s="5">
         <f t="shared" si="49"/>
-        <v>2.1541826134499726</v>
-      </c>
-      <c r="G20" s="5">
+        <v>16.128539027243711</v>
+      </c>
+      <c r="AI20" s="5">
         <f t="shared" si="49"/>
-        <v>2.2848551120831053</v>
-      </c>
-      <c r="H20" s="5">
+        <v>16.635424780931956</v>
+      </c>
+      <c r="AJ20" s="5">
         <f t="shared" si="49"/>
-        <v>2.3275013668671405</v>
-      </c>
-      <c r="I20" s="5">
+        <v>16.976703619220608</v>
+      </c>
+      <c r="AK20" s="5">
         <f t="shared" si="49"/>
-        <v>2.2722799343903772</v>
-      </c>
-      <c r="J20" s="5">
+        <v>17.324832545768132</v>
+      </c>
+      <c r="AL20" s="5">
         <f t="shared" si="49"/>
-        <v>2.5593220338983049</v>
-      </c>
-      <c r="K20" s="5">
+        <v>17.679946971696641</v>
+      </c>
+      <c r="AM20" s="5">
         <f t="shared" si="49"/>
-        <v>2.6735921268452705</v>
-      </c>
-      <c r="L20" s="5">
+        <v>18.042184945371485</v>
+      </c>
+      <c r="AN20" s="5">
         <f t="shared" si="49"/>
-        <v>2.5494805904866049</v>
-      </c>
-      <c r="M20" s="5">
-        <f t="shared" ref="M20:O20" si="50">M18/M19</f>
-        <v>2.6739846322722283</v>
-      </c>
-      <c r="N20" s="5">
-        <f t="shared" si="50"/>
-        <v>2.854842173072794</v>
-      </c>
-      <c r="O20" s="5">
-        <f t="shared" si="50"/>
-        <v>2.7555579480002153</v>
-      </c>
-      <c r="P20" s="5">
-        <f t="shared" ref="P20:R20" si="51">P18/P19</f>
-        <v>2.4806243564034469</v>
-      </c>
-      <c r="Q20" s="5">
-        <f t="shared" si="51"/>
-        <v>2.8605534454693435</v>
-      </c>
-      <c r="R20" s="5">
-        <f t="shared" si="51"/>
-        <v>2.9245038741182854</v>
-      </c>
-      <c r="T20" s="5">
-        <f t="shared" ref="T20:Z20" si="52">T18/T19</f>
-        <v>6.6047020229633677</v>
-      </c>
-      <c r="U20" s="5">
-        <f t="shared" si="52"/>
-        <v>5.9409513395297981</v>
-      </c>
-      <c r="V20" s="5">
-        <f t="shared" si="52"/>
-        <v>6.7310005467468565</v>
-      </c>
-      <c r="W20" s="5">
-        <f t="shared" si="52"/>
-        <v>8.2323674138873706</v>
-      </c>
-      <c r="X20" s="5">
-        <f t="shared" si="52"/>
-        <v>9.4439584472389289</v>
-      </c>
-      <c r="Y20" s="5">
-        <f t="shared" si="52"/>
-        <v>10.598561305561521</v>
-      </c>
-      <c r="Z20" s="5">
-        <f t="shared" si="52"/>
-        <v>11.046044839934892</v>
-      </c>
-      <c r="AA20" s="5">
-        <f t="shared" ref="AA20:AJ20" si="53">AA18/AA19</f>
-        <v>13.278510137818778</v>
-      </c>
-      <c r="AB20" s="5">
-        <f t="shared" si="53"/>
-        <v>14.434086168771787</v>
-      </c>
-      <c r="AC20" s="5">
-        <f t="shared" si="53"/>
-        <v>15.176591483504462</v>
-      </c>
-      <c r="AD20" s="5">
-        <f t="shared" si="53"/>
-        <v>15.80582091966699</v>
-      </c>
-      <c r="AE20" s="5">
-        <f t="shared" si="53"/>
-        <v>16.303164006827483</v>
-      </c>
-      <c r="AF20" s="5">
-        <f t="shared" si="53"/>
-        <v>16.638018291907233</v>
-      </c>
-      <c r="AG20" s="5">
-        <f t="shared" si="53"/>
-        <v>16.979599391395212</v>
-      </c>
-      <c r="AH20" s="5">
-        <f t="shared" si="53"/>
-        <v>17.32804039342636</v>
-      </c>
-      <c r="AI20" s="5">
-        <f t="shared" si="53"/>
-        <v>17.683476981053602</v>
-      </c>
-      <c r="AJ20" s="5">
-        <f t="shared" si="53"/>
-        <v>18.046047481906797</v>
+        <v>18.411687202784226</v>
       </c>
     </row>
-    <row r="22" spans="1:147" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:151" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>39</v>
       </c>
@@ -3726,133 +3797,137 @@
         <v>0.12423856070264905</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22:N22" si="54">H3/D3-1</f>
+        <f t="shared" ref="H22:N22" si="50">H3/D3-1</f>
         <v>0.11072471831965514</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>0.11656357388316141</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>0.1055605496340053</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>8.7953629032258007E-2</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>9.8935504070131408E-2</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>9.5654314908285132E-2</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>0.11708676965965847</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" ref="O22" si="55">O3/K3-1</f>
+        <f t="shared" ref="O22" si="51">O3/K3-1</f>
         <v>0.10145934676858936</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" ref="P22" si="56">P3/L3-1</f>
+        <f t="shared" ref="P22" si="52">P3/L3-1</f>
         <v>9.3333333333333268E-2</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22" si="57">Q3/M3-1</f>
+        <f t="shared" ref="Q22" si="53">Q3/M3-1</f>
         <v>0.14292134831460679</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" ref="R22" si="58">R3/N3-1</f>
-        <v>0.12000000000000011</v>
-      </c>
+        <f t="shared" ref="R22" si="54">R3/N3-1</f>
+        <v>0.11510866174482692</v>
+      </c>
+      <c r="S22" s="9"/>
       <c r="T22" s="9"/>
-      <c r="U22" s="9">
-        <f>U3/T3-1</f>
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9">
+        <f>Y3/X3-1</f>
         <v>-4.92231361796579E-2</v>
       </c>
-      <c r="V22" s="9">
-        <f t="shared" ref="V22:AJ22" si="59">V3/U3-1</f>
+      <c r="Z22" s="9">
+        <f t="shared" ref="Z22:AN22" si="55">Z3/Y3-1</f>
         <v>0.10340565778632249</v>
       </c>
-      <c r="W22" s="9">
-        <f t="shared" si="59"/>
+      <c r="AA22" s="9">
+        <f t="shared" si="55"/>
         <v>0.21593030491599263</v>
       </c>
-      <c r="X22" s="9">
-        <f t="shared" si="59"/>
+      <c r="AB22" s="9">
+        <f t="shared" si="55"/>
         <v>0.11405663596042315</v>
       </c>
-      <c r="Y22" s="9">
-        <f t="shared" si="59"/>
+      <c r="AC22" s="9">
+        <f t="shared" si="55"/>
         <v>0.10023581294214923</v>
       </c>
-      <c r="Z22" s="9">
-        <f t="shared" si="59"/>
-        <v>0.11470912431108382</v>
-      </c>
-      <c r="AA22" s="9">
-        <f t="shared" si="59"/>
+      <c r="AD22" s="9">
+        <f t="shared" si="55"/>
+        <v>0.11339976618604908</v>
+      </c>
+      <c r="AE22" s="9">
+        <f t="shared" si="55"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="AB22" s="9">
-        <f t="shared" si="59"/>
+      <c r="AF22" s="9">
+        <f t="shared" si="55"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="AC22" s="9">
-        <f t="shared" si="59"/>
+      <c r="AG22" s="9">
+        <f t="shared" si="55"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AD22" s="9">
-        <f t="shared" si="59"/>
+      <c r="AH22" s="9">
+        <f t="shared" si="55"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AE22" s="9">
-        <f t="shared" si="59"/>
+      <c r="AI22" s="9">
+        <f t="shared" si="55"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AF22" s="9">
-        <f t="shared" si="59"/>
+      <c r="AJ22" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG22" s="9">
-        <f t="shared" si="59"/>
+      <c r="AK22" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH22" s="9">
-        <f t="shared" si="59"/>
+      <c r="AL22" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI22" s="9">
-        <f t="shared" si="59"/>
+      <c r="AM22" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AJ22" s="9">
-        <f t="shared" si="59"/>
+      <c r="AN22" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:147" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:151" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>40</v>
       </c>
       <c r="C23" s="9">
-        <f t="shared" ref="C23:F23" si="60">C5/C3</f>
+        <f t="shared" ref="C23:F23" si="56">C5/C3</f>
         <v>0.84062898427539312</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="56"/>
         <v>0.82946167756294342</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="56"/>
         <v>0.82364261168384878</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="56"/>
         <v>0.82586361885193271</v>
       </c>
       <c r="G23" s="9">
@@ -3860,142 +3935,146 @@
         <v>0.8315272177419355</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" ref="H23:N23" si="61">H5/H3</f>
+        <f t="shared" ref="H23:N23" si="57">H5/H3</f>
         <v>0.81026925485284906</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="57"/>
         <v>0.81767819771020556</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="57"/>
         <v>0.82599605064467418</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="57"/>
         <v>0.82870048644892291</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="57"/>
         <v>0.81732193732193736</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="57"/>
         <v>0.82325842696629215</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="57"/>
         <v>0.83269210772590208</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" ref="O23:R23" si="62">O5/O3</f>
+        <f t="shared" ref="O23:R23" si="58">O5/O3</f>
         <v>0.80935856992639332</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.82728788826349797</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.82805741250491549</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="62"/>
-        <v>0.82</v>
-      </c>
-      <c r="T23" s="9">
-        <f t="shared" ref="T23:AJ23" si="63">T5/T3</f>
+        <f t="shared" si="58"/>
+        <v>0.83756061171204776</v>
+      </c>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="X23" s="9">
+        <f t="shared" ref="X23:AN23" si="59">X5/X3</f>
         <v>0.85011098054576317</v>
       </c>
-      <c r="U23" s="9">
-        <f t="shared" si="63"/>
+      <c r="Y23" s="9">
+        <f t="shared" si="59"/>
         <v>0.82674173761787051</v>
       </c>
-      <c r="V23" s="9">
-        <f t="shared" si="63"/>
+      <c r="Z23" s="9">
+        <f t="shared" si="59"/>
         <v>0.82410288321924907</v>
       </c>
-      <c r="W23" s="9">
-        <f t="shared" si="63"/>
+      <c r="AA23" s="9">
+        <f t="shared" si="59"/>
         <v>0.82975093824633228</v>
       </c>
-      <c r="X23" s="9">
-        <f t="shared" si="63"/>
+      <c r="AB23" s="9">
+        <f t="shared" si="59"/>
         <v>0.82142529017241905</v>
       </c>
-      <c r="Y23" s="9">
-        <f t="shared" si="63"/>
+      <c r="AC23" s="9">
+        <f t="shared" si="59"/>
         <v>0.82564159661526471</v>
       </c>
-      <c r="Z23" s="9">
-        <f t="shared" si="63"/>
-        <v>0.82126551175817242</v>
-      </c>
-      <c r="AA23" s="9">
-        <f t="shared" si="63"/>
-        <v>0.82999999999999985</v>
-      </c>
-      <c r="AB23" s="9">
-        <f t="shared" si="63"/>
-        <v>0.83000000000000007</v>
-      </c>
-      <c r="AC23" s="9">
-        <f t="shared" si="63"/>
-        <v>0.83</v>
-      </c>
       <c r="AD23" s="9">
-        <f t="shared" si="63"/>
-        <v>0.83</v>
+        <f t="shared" si="59"/>
+        <v>0.82597500000000001</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="63"/>
-        <v>0.83</v>
+        <f t="shared" si="59"/>
+        <v>0.84</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="63"/>
-        <v>0.83</v>
+        <f t="shared" si="59"/>
+        <v>0.84</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="63"/>
-        <v>0.83</v>
+        <f t="shared" si="59"/>
+        <v>0.84</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="63"/>
-        <v>0.82999999999999985</v>
+        <f t="shared" si="59"/>
+        <v>0.84</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="63"/>
-        <v>0.83000000000000007</v>
+        <f t="shared" si="59"/>
+        <v>0.84</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="63"/>
-        <v>0.83</v>
-      </c>
-      <c r="AM23" t="s">
+        <f t="shared" si="59"/>
+        <v>0.83999999999999986</v>
+      </c>
+      <c r="AK23" s="9">
+        <f t="shared" si="59"/>
+        <v>0.84</v>
+      </c>
+      <c r="AL23" s="9">
+        <f t="shared" si="59"/>
+        <v>0.84</v>
+      </c>
+      <c r="AM23" s="9">
+        <f t="shared" si="59"/>
+        <v>0.84</v>
+      </c>
+      <c r="AN23" s="9">
+        <f t="shared" si="59"/>
+        <v>0.84</v>
+      </c>
+      <c r="AQ23" t="s">
         <v>48</v>
       </c>
-      <c r="AN23" s="9">
+      <c r="AR23" s="9">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="24" spans="1:147" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:151" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:F24" si="64">C6/C3</f>
+        <f t="shared" ref="C24:F24" si="60">C6/C3</f>
         <v>3.9665675024791049E-2</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>4.3677841146195578E-2</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>4.3024054982817868E-2</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>5.5091819699499167E-2</v>
       </c>
       <c r="G24" s="9">
@@ -4003,125 +4082,129 @@
         <v>4.1834677419354836E-2</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24:N24" si="65">H6/H3</f>
+        <f t="shared" ref="H24:N24" si="61">H6/H3</f>
         <v>3.8697557921102063E-2</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>3.6562846239074236E-2</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>4.6811476361946797E-2</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>3.3935603428306697E-2</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>3.8518518518518521E-2</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>4.2471910112359554E-2</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>5.7294374545076431E-2</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" ref="O24:R24" si="66">O6/O3</f>
+        <f t="shared" ref="O24:R24" si="62">O6/O3</f>
         <v>3.2176656151419555E-2</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="62"/>
         <v>3.9712320200125079E-2</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="62"/>
         <v>4.1388124262681875E-2</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="66"/>
-        <v>6.0000000000000005E-2</v>
-      </c>
-      <c r="T24" s="9">
-        <f t="shared" ref="T24:AJ24" si="67">T6/T3</f>
+        <f t="shared" si="62"/>
+        <v>5.3711301753077208E-2</v>
+      </c>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="X24" s="9">
+        <f t="shared" ref="X24:AN24" si="63">X6/X3</f>
         <v>4.8091569830700266E-2</v>
       </c>
-      <c r="U24" s="9">
-        <f t="shared" si="67"/>
+      <c r="Y24" s="9">
+        <f t="shared" si="63"/>
         <v>4.4447496109127529E-2</v>
       </c>
-      <c r="V24" s="9">
-        <f t="shared" si="67"/>
+      <c r="Z24" s="9">
+        <f t="shared" si="63"/>
         <v>4.7127152043144577E-2</v>
       </c>
-      <c r="W24" s="9">
-        <f t="shared" si="67"/>
+      <c r="AA24" s="9">
+        <f t="shared" si="63"/>
         <v>4.5581712726032071E-2</v>
       </c>
-      <c r="X24" s="9">
-        <f t="shared" si="67"/>
+      <c r="AB24" s="9">
+        <f t="shared" si="63"/>
         <v>4.1068202002878758E-2</v>
       </c>
-      <c r="Y24" s="9">
-        <f t="shared" si="67"/>
+      <c r="AC24" s="9">
+        <f t="shared" si="63"/>
         <v>4.3422590881255912E-2</v>
       </c>
-      <c r="Z24" s="9">
-        <f t="shared" si="67"/>
-        <v>4.3805045266766283E-2</v>
-      </c>
-      <c r="AA24" s="9">
-        <f t="shared" si="67"/>
+      <c r="AD24" s="9">
+        <f t="shared" si="63"/>
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="AE24" s="9">
+        <f t="shared" si="63"/>
         <v>0.04</v>
       </c>
-      <c r="AB24" s="9">
-        <f t="shared" si="67"/>
+      <c r="AF24" s="9">
+        <f t="shared" si="63"/>
         <v>0.04</v>
       </c>
-      <c r="AC24" s="9">
-        <f t="shared" si="67"/>
+      <c r="AG24" s="9">
+        <f t="shared" si="63"/>
         <v>0.04</v>
       </c>
-      <c r="AD24" s="9">
-        <f t="shared" si="67"/>
+      <c r="AH24" s="9">
+        <f t="shared" si="63"/>
         <v>0.04</v>
       </c>
-      <c r="AE24" s="9">
-        <f t="shared" si="67"/>
+      <c r="AI24" s="9">
+        <f t="shared" si="63"/>
         <v>0.04</v>
       </c>
-      <c r="AF24" s="9">
-        <f t="shared" si="67"/>
+      <c r="AJ24" s="9">
+        <f t="shared" si="63"/>
+        <v>4.0000000000000008E-2</v>
+      </c>
+      <c r="AK24" s="9">
+        <f t="shared" si="63"/>
         <v>0.04</v>
       </c>
-      <c r="AG24" s="9">
-        <f t="shared" si="67"/>
+      <c r="AL24" s="9">
+        <f t="shared" si="63"/>
+        <v>0.04</v>
+      </c>
+      <c r="AM24" s="9">
+        <f t="shared" si="63"/>
         <v>4.0000000000000008E-2</v>
       </c>
-      <c r="AH24" s="9">
-        <f t="shared" si="67"/>
+      <c r="AN24" s="9">
+        <f t="shared" si="63"/>
         <v>0.04</v>
       </c>
-      <c r="AI24" s="9">
-        <f t="shared" si="67"/>
-        <v>0.04</v>
-      </c>
-      <c r="AJ24" s="9">
-        <f t="shared" si="67"/>
-        <v>4.0000000000000008E-2</v>
-      </c>
-      <c r="AM24" t="s">
+      <c r="AQ24" t="s">
         <v>49</v>
       </c>
-      <c r="AN24" s="9">
+      <c r="AR24" s="9">
         <v>0.06</v>
       </c>
     </row>
-    <row r="25" spans="1:147" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:151" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>47</v>
       </c>
@@ -4134,141 +4217,145 @@
         <v>-6.315789473684208E-2</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" ref="H25:N25" si="68">H7/D7-1</f>
+        <f t="shared" ref="H25:N25" si="64">H7/D7-1</f>
         <v>-5.7894736842105221E-2</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>2.2471910112359605E-2</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>6.4864864864864868E-2</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>1.6853932584269593E-2</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>5.5865921787709549E-2</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>9.8901098901098994E-2</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>5.5837563451776706E-2</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" ref="O25" si="69">O7/K7-1</f>
+        <f t="shared" ref="O25" si="65">O7/K7-1</f>
         <v>0.14364640883977908</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" ref="P25" si="70">P7/L7-1</f>
+        <f t="shared" ref="P25" si="66">P7/L7-1</f>
         <v>0.18518518518518512</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" ref="Q25" si="71">Q7/M7-1</f>
+        <f t="shared" ref="Q25" si="67">Q7/M7-1</f>
         <v>0.12000000000000011</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" ref="R25" si="72">R7/N7-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="R25" si="68">R7/N7-1</f>
+        <v>0.14903846153846145</v>
       </c>
       <c r="S25" s="9"/>
       <c r="T25" s="9"/>
-      <c r="U25" s="9">
-        <f>U7/T7-1</f>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9">
+        <f>Y7/X7-1</f>
         <v>8.3217753120665705E-3</v>
       </c>
-      <c r="V25" s="9">
-        <f t="shared" ref="V25:AJ25" si="73">V7/U7-1</f>
+      <c r="Z25" s="9">
+        <f t="shared" ref="Z25:AN25" si="69">Z7/Y7-1</f>
         <v>4.126547455295837E-3</v>
       </c>
-      <c r="W25" s="9">
-        <f t="shared" si="73"/>
+      <c r="AA25" s="9">
+        <f t="shared" si="69"/>
         <v>1.7808219178082174E-2</v>
       </c>
-      <c r="X25" s="9">
-        <f t="shared" si="73"/>
+      <c r="AB25" s="9">
+        <f t="shared" si="69"/>
         <v>-9.421265141319024E-3</v>
       </c>
-      <c r="Y25" s="9">
-        <f t="shared" si="73"/>
+      <c r="AC25" s="9">
+        <f t="shared" si="69"/>
         <v>5.7065217391304435E-2</v>
       </c>
-      <c r="Z25" s="9">
-        <f t="shared" si="73"/>
-        <v>0.13598971722365039</v>
-      </c>
-      <c r="AA25" s="9">
-        <f t="shared" si="73"/>
+      <c r="AD25" s="9">
+        <f t="shared" si="69"/>
+        <v>0.14910025706940866</v>
+      </c>
+      <c r="AE25" s="9">
+        <f t="shared" si="69"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="AB25" s="9">
-        <f t="shared" si="73"/>
+      <c r="AF25" s="9">
+        <f t="shared" si="69"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AC25" s="9">
-        <f t="shared" si="73"/>
+      <c r="AG25" s="9">
+        <f t="shared" si="69"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AD25" s="9">
-        <f t="shared" si="73"/>
+      <c r="AH25" s="9">
+        <f t="shared" si="69"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE25" s="9">
-        <f t="shared" si="73"/>
+      <c r="AI25" s="9">
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AF25" s="9">
-        <f t="shared" si="73"/>
+      <c r="AJ25" s="9">
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AG25" s="9">
-        <f t="shared" si="73"/>
+      <c r="AK25" s="9">
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH25" s="9">
-        <f t="shared" si="73"/>
+      <c r="AL25" s="9">
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AI25" s="9">
-        <f t="shared" si="73"/>
+      <c r="AM25" s="9">
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AJ25" s="9">
-        <f t="shared" si="73"/>
+      <c r="AN25" s="9">
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AM25" t="s">
+      <c r="AQ25" t="s">
         <v>50</v>
       </c>
-      <c r="AN25" s="3">
-        <f>NPV(AN24,Z18:EQ18)</f>
-        <v>470736.38303071231</v>
+      <c r="AR25" s="3">
+        <f>NPV(AR24,AD18:EU18)</f>
+        <v>476387.45635461435</v>
       </c>
     </row>
-    <row r="26" spans="1:147" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:151" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>42</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:F26" si="74">C8/C3</f>
+        <f t="shared" ref="C26:F26" si="70">C8/C3</f>
         <v>1.4166312508853945E-2</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="70"/>
         <v>1.7387675615523717E-2</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="70"/>
         <v>1.6082474226804123E-2</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="70"/>
         <v>2.0932323102606908E-2</v>
       </c>
       <c r="G26" s="9">
@@ -4276,126 +4363,130 @@
         <v>1.3734879032258064E-2</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" ref="H26:N26" si="75">H8/H3</f>
+        <f t="shared" ref="H26:N26" si="71">H8/H3</f>
         <v>1.6280525986224169E-2</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>1.6373261110427181E-2</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>2.0095249157858056E-2</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>1.5172573546444291E-2</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>1.8233618233618232E-2</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>1.707865168539326E-2</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>1.9964645939482165E-2</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" ref="O26:R26" si="76">O8/O3</f>
+        <f t="shared" ref="O26:R26" si="72">O8/O3</f>
         <v>1.5036803364879074E-2</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>1.8032103397957057E-2</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>1.838379866299646E-2</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
+        <v>2.3871689668034317E-2</v>
+      </c>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="X26" s="9">
+        <f t="shared" ref="X26:AN26" si="73">X8/X3</f>
+        <v>1.9758889324106715E-2</v>
+      </c>
+      <c r="Y26" s="9">
+        <f t="shared" si="73"/>
+        <v>1.8676187860477891E-2</v>
+      </c>
+      <c r="Z26" s="9">
+        <f t="shared" si="73"/>
+        <v>1.6718523127981746E-2</v>
+      </c>
+      <c r="AA26" s="9">
+        <f t="shared" si="73"/>
+        <v>1.7229614466052541E-2</v>
+      </c>
+      <c r="AB26" s="9">
+        <f t="shared" si="73"/>
+        <v>1.6690656294980552E-2</v>
+      </c>
+      <c r="AC26" s="9">
+        <f t="shared" si="73"/>
+        <v>1.7675221288203528E-2</v>
+      </c>
+      <c r="AD26" s="9">
+        <f t="shared" si="73"/>
+        <v>1.8974999999999999E-2</v>
+      </c>
+      <c r="AE26" s="9">
+        <f t="shared" si="73"/>
         <v>0.02</v>
       </c>
-      <c r="T26" s="9">
-        <f t="shared" ref="T26:AJ26" si="77">T8/T3</f>
-        <v>1.9758889324106715E-2</v>
-      </c>
-      <c r="U26" s="9">
-        <f t="shared" si="77"/>
-        <v>1.8676187860477891E-2</v>
-      </c>
-      <c r="V26" s="9">
-        <f t="shared" si="77"/>
-        <v>1.6718523127981746E-2</v>
-      </c>
-      <c r="W26" s="9">
-        <f t="shared" si="77"/>
-        <v>1.7229614466052541E-2</v>
-      </c>
-      <c r="X26" s="9">
-        <f t="shared" si="77"/>
-        <v>1.6690656294980552E-2</v>
-      </c>
-      <c r="Y26" s="9">
-        <f t="shared" si="77"/>
-        <v>1.7675221288203528E-2</v>
-      </c>
-      <c r="Z26" s="9">
-        <f t="shared" si="77"/>
-        <v>1.7939423238271791E-2</v>
-      </c>
-      <c r="AA26" s="9">
-        <f t="shared" si="77"/>
+      <c r="AF26" s="9">
+        <f t="shared" si="73"/>
         <v>0.02</v>
       </c>
-      <c r="AB26" s="9">
-        <f t="shared" si="77"/>
+      <c r="AG26" s="9">
+        <f t="shared" si="73"/>
         <v>0.02</v>
       </c>
-      <c r="AC26" s="9">
-        <f t="shared" si="77"/>
+      <c r="AH26" s="9">
+        <f t="shared" si="73"/>
         <v>0.02</v>
       </c>
-      <c r="AD26" s="9">
-        <f t="shared" si="77"/>
+      <c r="AI26" s="9">
+        <f t="shared" si="73"/>
         <v>0.02</v>
       </c>
-      <c r="AE26" s="9">
-        <f t="shared" si="77"/>
+      <c r="AJ26" s="9">
+        <f t="shared" si="73"/>
+        <v>2.0000000000000004E-2</v>
+      </c>
+      <c r="AK26" s="9">
+        <f t="shared" si="73"/>
         <v>0.02</v>
       </c>
-      <c r="AF26" s="9">
-        <f t="shared" si="77"/>
+      <c r="AL26" s="9">
+        <f t="shared" si="73"/>
         <v>0.02</v>
       </c>
-      <c r="AG26" s="9">
-        <f t="shared" si="77"/>
+      <c r="AM26" s="9">
+        <f t="shared" si="73"/>
         <v>2.0000000000000004E-2</v>
       </c>
-      <c r="AH26" s="9">
-        <f t="shared" si="77"/>
+      <c r="AN26" s="9">
+        <f t="shared" si="73"/>
         <v>0.02</v>
       </c>
-      <c r="AI26" s="9">
-        <f t="shared" si="77"/>
-        <v>0.02</v>
-      </c>
-      <c r="AJ26" s="9">
-        <f t="shared" si="77"/>
-        <v>2.0000000000000004E-2</v>
-      </c>
-      <c r="AM26" t="s">
+      <c r="AQ26" t="s">
         <v>51</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AR26" s="3">
         <f>Main!D8</f>
         <v>-4755</v>
       </c>
     </row>
-    <row r="27" spans="1:147" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:151" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>43</v>
       </c>
@@ -4408,93 +4499,97 @@
         <v>0.14646464646464641</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:N27" si="78">H9/D9-1</f>
+        <f t="shared" ref="H27:N27" si="74">H9/D9-1</f>
         <v>0.13043478260869557</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>2.1739130434782705E-2</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>9.2920353982300918E-2</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>8.8105726872246715E-2</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>6.4102564102564097E-2</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>0.123404255319149</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>0.10931174089068829</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" ref="O27:O28" si="79">O9/K9-1</f>
+        <f t="shared" ref="O27:O28" si="75">O9/K9-1</f>
         <v>0.14170040485829949</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" ref="P27:P28" si="80">P9/L9-1</f>
+        <f t="shared" ref="P27:P28" si="76">P9/L9-1</f>
         <v>0.22489959839357421</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" ref="Q27:Q28" si="81">Q9/M9-1</f>
+        <f t="shared" ref="Q27:Q28" si="77">Q9/M9-1</f>
         <v>0.20075757575757569</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" ref="R27:R28" si="82">R9/N9-1</f>
-        <v>0.17999999999999994</v>
-      </c>
+        <f t="shared" ref="R27:R28" si="78">R9/N9-1</f>
+        <v>0.15328467153284664</v>
+      </c>
+      <c r="S27" s="9"/>
       <c r="T27" s="9"/>
-      <c r="U27" s="9">
-        <f>U9/T9-1</f>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9">
+        <f>Y9/X9-1</f>
         <v>0.16920731707317072</v>
       </c>
-      <c r="V27" s="9">
-        <f t="shared" ref="V27:Z27" si="83">V9/U9-1</f>
+      <c r="Z27" s="9">
+        <f t="shared" ref="Z27:AD27" si="79">Z9/Y9-1</f>
         <v>4.8239895697522739E-2</v>
       </c>
-      <c r="W27" s="9">
-        <f t="shared" si="83"/>
+      <c r="AA27" s="9">
+        <f t="shared" si="79"/>
         <v>7.0895522388059629E-2</v>
       </c>
-      <c r="X27" s="9">
-        <f t="shared" si="83"/>
+      <c r="AB27" s="9">
+        <f t="shared" si="79"/>
         <v>9.5238095238095344E-2</v>
       </c>
-      <c r="Y27" s="9">
-        <f t="shared" si="83"/>
+      <c r="AC27" s="9">
+        <f t="shared" si="79"/>
         <v>9.6500530222693559E-2</v>
       </c>
-      <c r="Z27" s="9">
-        <f t="shared" si="83"/>
-        <v>0.18696324951644105</v>
-      </c>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
-      <c r="AD27" s="9"/>
+      <c r="AD27" s="9">
+        <f t="shared" si="79"/>
+        <v>0.17988394584139256</v>
+      </c>
       <c r="AE27" s="9"/>
       <c r="AF27" s="9"/>
       <c r="AG27" s="9"/>
       <c r="AH27" s="9"/>
       <c r="AI27" s="9"/>
       <c r="AJ27" s="9"/>
-      <c r="AM27" t="s">
+      <c r="AK27" s="9"/>
+      <c r="AL27" s="9"/>
+      <c r="AM27" s="9"/>
+      <c r="AN27" s="9"/>
+      <c r="AQ27" t="s">
         <v>52</v>
       </c>
-      <c r="AN27" s="3">
-        <f>AN25+AN26</f>
-        <v>465981.38303071231</v>
+      <c r="AR27" s="3">
+        <f>AR25+AR26</f>
+        <v>471632.45635461435</v>
       </c>
     </row>
-    <row r="28" spans="1:147" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:151" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>44</v>
       </c>
@@ -4507,140 +4602,144 @@
         <v>0.33057851239669422</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" ref="H28:N28" si="84">H10/D10-1</f>
+        <f t="shared" ref="H28:N28" si="80">H10/D10-1</f>
         <v>-0.13230769230769235</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>8.6505190311418678E-2</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>0.21893491124260356</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>5.5900621118012417E-2</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>0.60283687943262421</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>0.21656050955414008</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>2.9126213592232997E-2</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.41470588235294126</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="76"/>
         <v>-7.3008849557522071E-2</v>
       </c>
       <c r="Q28" s="9">
+        <f t="shared" si="77"/>
+        <v>0.26178010471204183</v>
+      </c>
+      <c r="R28" s="9">
+        <f t="shared" si="78"/>
+        <v>0.28301886792452824</v>
+      </c>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9">
+        <f>Y10/X10-1</f>
+        <v>-8.361204013377932E-2</v>
+      </c>
+      <c r="Z28" s="9">
+        <f t="shared" ref="Z28:AN28" si="81">Z10/Y10-1</f>
+        <v>-0.10127737226277367</v>
+      </c>
+      <c r="AA28" s="9">
         <f t="shared" si="81"/>
-        <v>0.26178010471204183</v>
-      </c>
-      <c r="R28" s="9">
-        <f t="shared" si="82"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9">
-        <f>U10/T10-1</f>
-        <v>-8.361204013377932E-2</v>
-      </c>
-      <c r="V28" s="9">
-        <f t="shared" ref="V28:AJ28" si="85">V10/U10-1</f>
-        <v>-0.10127737226277367</v>
-      </c>
-      <c r="W28" s="9">
-        <f t="shared" si="85"/>
         <v>0.21218274111675117</v>
       </c>
-      <c r="X28" s="9">
-        <f t="shared" si="85"/>
+      <c r="AB28" s="9">
+        <f t="shared" si="81"/>
         <v>0.11390284757118918</v>
       </c>
-      <c r="Y28" s="9">
-        <f t="shared" si="85"/>
+      <c r="AC28" s="9">
+        <f t="shared" si="81"/>
         <v>0.2015037593984963</v>
       </c>
-      <c r="Z28" s="9">
-        <f t="shared" si="85"/>
-        <v>0.18322903629536924</v>
-      </c>
-      <c r="AA28" s="9">
-        <f t="shared" si="85"/>
+      <c r="AD28" s="9">
+        <f t="shared" si="81"/>
+        <v>0.20525657071339176</v>
+      </c>
+      <c r="AE28" s="9">
+        <f t="shared" si="81"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="AB28" s="9">
-        <f t="shared" si="85"/>
+      <c r="AF28" s="9">
+        <f t="shared" si="81"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AC28" s="9">
-        <f t="shared" si="85"/>
+      <c r="AG28" s="9">
+        <f t="shared" si="81"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AD28" s="9">
-        <f t="shared" si="85"/>
+      <c r="AH28" s="9">
+        <f t="shared" si="81"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE28" s="9">
-        <f t="shared" si="85"/>
+      <c r="AI28" s="9">
+        <f t="shared" si="81"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AF28" s="9">
-        <f t="shared" si="85"/>
+      <c r="AJ28" s="9">
+        <f t="shared" si="81"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AG28" s="9">
-        <f t="shared" si="85"/>
+      <c r="AK28" s="9">
+        <f t="shared" si="81"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH28" s="9">
-        <f t="shared" si="85"/>
+      <c r="AL28" s="9">
+        <f t="shared" si="81"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AI28" s="9">
-        <f t="shared" si="85"/>
+      <c r="AM28" s="9">
+        <f t="shared" si="81"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AJ28" s="9">
-        <f t="shared" si="85"/>
+      <c r="AN28" s="9">
+        <f t="shared" si="81"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AM28" t="s">
+      <c r="AQ28" t="s">
         <v>53</v>
       </c>
-      <c r="AN28" s="11">
-        <f>AN27/AJ19</f>
-        <v>252.83851493798824</v>
+      <c r="AR28" s="11">
+        <f>AR27/AN19</f>
+        <v>257.72265374569088</v>
       </c>
     </row>
-    <row r="29" spans="1:147" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:151" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:F29" si="86">C11/C3</f>
+        <f t="shared" ref="C29:F29" si="82">C11/C3</f>
         <v>2.0966142513103841E-2</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>9.855670103092784E-2</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>3.8525748041607808E-4</v>
       </c>
       <c r="G29" s="9">
@@ -4648,143 +4747,147 @@
         <v>4.296875E-2</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" ref="H29:N29" si="87">H11/H3</f>
+        <f t="shared" ref="H29:N29" si="83">H11/H3</f>
         <v>0</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>5.6260002462144527E-2</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>1.4984318736206296E-2</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>1.0423905489923557E-3</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>4.9002849002849E-2</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>1.4606741573033708E-3</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>1.0398253093480295E-3</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" ref="O29:R29" si="88">O11/O3</f>
+        <f t="shared" ref="O29:R29" si="84">O11/O3</f>
         <v>4.6267087276550996E-3</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="84"/>
         <v>0.10423181154888472</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="84"/>
         <v>6.0460086511993708E-2</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="88"/>
-        <v>0.04</v>
-      </c>
-      <c r="T29" s="9">
-        <f t="shared" ref="T29:AJ29" si="89">T11/T3</f>
+        <f t="shared" si="84"/>
+        <v>8.4203655352480422E-2</v>
+      </c>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="X29" s="9">
+        <f t="shared" ref="X29:AN29" si="85">X11/X3</f>
         <v>1.7408713060886975E-2</v>
       </c>
-      <c r="U29" s="9">
-        <f t="shared" si="89"/>
+      <c r="Y29" s="9">
+        <f t="shared" si="85"/>
         <v>5.0352467270896274E-4</v>
       </c>
-      <c r="V29" s="9">
-        <f t="shared" si="89"/>
+      <c r="Z29" s="9">
+        <f t="shared" si="85"/>
         <v>1.2445550715619165E-4</v>
       </c>
-      <c r="W29" s="9">
-        <f t="shared" si="89"/>
+      <c r="AA29" s="9">
+        <f t="shared" si="85"/>
         <v>2.9614466052541796E-2</v>
       </c>
-      <c r="X29" s="9">
-        <f t="shared" si="89"/>
+      <c r="AB29" s="9">
+        <f t="shared" si="85"/>
         <v>2.838942823017793E-2</v>
       </c>
-      <c r="Y29" s="9">
-        <f t="shared" si="89"/>
+      <c r="AC29" s="9">
+        <f t="shared" si="85"/>
         <v>1.2859767299448868E-2</v>
       </c>
-      <c r="Z29" s="9">
-        <f t="shared" si="89"/>
-        <v>5.2184670827107323E-2</v>
-      </c>
-      <c r="AA29" s="9">
-        <f t="shared" si="89"/>
+      <c r="AD29" s="9">
+        <f t="shared" si="85"/>
+        <v>6.4049999999999996E-2</v>
+      </c>
+      <c r="AE29" s="9">
+        <f t="shared" si="85"/>
         <v>0.02</v>
       </c>
-      <c r="AB29" s="9">
-        <f t="shared" si="89"/>
+      <c r="AF29" s="9">
+        <f t="shared" si="85"/>
         <v>0.01</v>
       </c>
-      <c r="AC29" s="9">
-        <f t="shared" si="89"/>
+      <c r="AG29" s="9">
+        <f t="shared" si="85"/>
         <v>0.01</v>
       </c>
-      <c r="AD29" s="9">
-        <f t="shared" si="89"/>
+      <c r="AH29" s="9">
+        <f t="shared" si="85"/>
         <v>0.01</v>
       </c>
-      <c r="AE29" s="9">
-        <f t="shared" si="89"/>
+      <c r="AI29" s="9">
+        <f t="shared" si="85"/>
         <v>0.01</v>
       </c>
-      <c r="AF29" s="9">
-        <f t="shared" si="89"/>
+      <c r="AJ29" s="9">
+        <f t="shared" si="85"/>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="AK29" s="9">
+        <f t="shared" si="85"/>
         <v>0.01</v>
       </c>
-      <c r="AG29" s="9">
-        <f t="shared" si="89"/>
+      <c r="AL29" s="9">
+        <f t="shared" si="85"/>
+        <v>0.01</v>
+      </c>
+      <c r="AM29" s="9">
+        <f t="shared" si="85"/>
         <v>1.0000000000000002E-2</v>
       </c>
-      <c r="AH29" s="9">
-        <f t="shared" si="89"/>
+      <c r="AN29" s="9">
+        <f t="shared" si="85"/>
         <v>0.01</v>
       </c>
-      <c r="AI29" s="9">
-        <f t="shared" si="89"/>
-        <v>0.01</v>
-      </c>
-      <c r="AJ29" s="9">
-        <f t="shared" si="89"/>
-        <v>1.0000000000000002E-2</v>
-      </c>
-      <c r="AM29" t="s">
+      <c r="AQ29" t="s">
         <v>54</v>
       </c>
-      <c r="AN29" s="11">
+      <c r="AR29" s="11">
         <f>Main!D3</f>
-        <v>344.45</v>
+        <v>345.94</v>
       </c>
     </row>
-    <row r="30" spans="1:147" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:151" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>46</v>
       </c>
       <c r="C30" s="9">
-        <f t="shared" ref="C30:F30" si="90">C13/C3</f>
+        <f t="shared" ref="C30:F30" si="86">C13/C3</f>
         <v>0.67658308542286438</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="86"/>
         <v>0.66796494644595905</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="86"/>
         <v>0.57017182130584187</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="86"/>
         <v>0.6532682676255297</v>
       </c>
       <c r="G30" s="9">
@@ -4792,143 +4895,147 @@
         <v>0.64138104838709675</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" ref="H30:N30" si="91">H13/H3</f>
+        <f t="shared" ref="H30:N30" si="87">H13/H3</f>
         <v>0.66825297432686281</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="87"/>
         <v>0.6184907054044072</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="87"/>
         <v>0.64467417818561967</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="87"/>
         <v>0.68959925874449846</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="87"/>
         <v>0.61014245014245017</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="87"/>
         <v>0.66719101123595503</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="87"/>
         <v>0.660185088905064</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" ref="O30:R30" si="92">O13/O3</f>
+        <f t="shared" ref="O30:R30" si="88">O13/O3</f>
         <v>0.65552050473186119</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="88"/>
         <v>0.56649989576818849</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="88"/>
         <v>0.60725521038143926</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="92"/>
-        <v>0.60150254757200783</v>
-      </c>
-      <c r="T30" s="9">
-        <f t="shared" ref="T30:AJ30" si="93">T13/T3</f>
+        <f t="shared" si="88"/>
+        <v>0.57329354718388659</v>
+      </c>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="X30" s="9">
+        <f t="shared" ref="X30:AN30" si="89">X13/X3</f>
         <v>0.65287026156591377</v>
       </c>
-      <c r="U30" s="9">
-        <f t="shared" si="93"/>
+      <c r="Y30" s="9">
+        <f t="shared" si="89"/>
         <v>0.64455735603771858</v>
       </c>
-      <c r="V30" s="9">
-        <f t="shared" si="93"/>
+      <c r="Z30" s="9">
+        <f t="shared" si="89"/>
         <v>0.65563161169881767</v>
       </c>
-      <c r="W30" s="9">
-        <f t="shared" si="93"/>
+      <c r="AA30" s="9">
+        <f t="shared" si="89"/>
         <v>0.64186284544524053</v>
       </c>
-      <c r="X30" s="9">
-        <f t="shared" si="93"/>
+      <c r="AB30" s="9">
+        <f t="shared" si="89"/>
         <v>0.64312620586163594</v>
       </c>
-      <c r="Y30" s="9">
-        <f t="shared" si="93"/>
+      <c r="AC30" s="9">
+        <f t="shared" si="89"/>
         <v>0.65676668707899566</v>
       </c>
-      <c r="Z30" s="9">
-        <f t="shared" si="93"/>
-        <v>0.60740589067256912</v>
-      </c>
-      <c r="AA30" s="9">
-        <f t="shared" si="93"/>
-        <v>0.68071647742255104</v>
-      </c>
-      <c r="AB30" s="9">
-        <f t="shared" si="93"/>
-        <v>0.69201149653614824</v>
-      </c>
-      <c r="AC30" s="9">
-        <f t="shared" si="93"/>
-        <v>0.69330651564974533</v>
-      </c>
       <c r="AD30" s="9">
-        <f t="shared" si="93"/>
-        <v>0.694589082656481</v>
+        <f t="shared" si="89"/>
+        <v>0.59984999999999999</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="93"/>
-        <v>0.69585919755635528</v>
+        <f t="shared" si="89"/>
+        <v>0.6895</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="93"/>
-        <v>0.69648802895286155</v>
+        <f t="shared" si="89"/>
+        <v>0.70081775700934579</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="93"/>
-        <v>0.6971106953356766</v>
+        <f t="shared" si="89"/>
+        <v>0.70213551401869156</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="93"/>
-        <v>0.69772725714611106</v>
+        <f t="shared" si="89"/>
+        <v>0.70344060028756294</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="93"/>
-        <v>0.69833777423291399</v>
+        <f t="shared" si="89"/>
+        <v>0.70473301581595971</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="93"/>
-        <v>0.69894230585808148</v>
-      </c>
-      <c r="AM30" s="6" t="s">
+        <f t="shared" si="89"/>
+        <v>0.70537288820992083</v>
+      </c>
+      <c r="AK30" s="9">
+        <f t="shared" si="89"/>
+        <v>0.70600648734511762</v>
+      </c>
+      <c r="AL30" s="9">
+        <f t="shared" si="89"/>
+        <v>0.70663387472408734</v>
+      </c>
+      <c r="AM30" s="9">
+        <f t="shared" si="89"/>
+        <v>0.70725511124639995</v>
+      </c>
+      <c r="AN30" s="9">
+        <f t="shared" si="89"/>
+        <v>0.70787025721457264</v>
+      </c>
+      <c r="AQ30" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AN30" s="10">
-        <f>AN28/AN29-1</f>
-        <v>-0.26596453784877849</v>
+      <c r="AR30" s="10">
+        <f>AR28/AR29-1</f>
+        <v>-0.25500764946033738</v>
       </c>
     </row>
-    <row r="31" spans="1:147" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:151" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>23</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:F31" si="94">C17/C16</f>
+        <f t="shared" ref="C31:F31" si="90">C17/C16</f>
         <v>0.171125178680825</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>0.19704975781594011</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>0.10916688430399582</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>0.19063270336894</v>
       </c>
       <c r="G31" s="9">
@@ -4936,125 +5043,129 @@
         <v>0.16033755274261605</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" ref="H31:N31" si="95">H17/H16</f>
+        <f t="shared" ref="H31:N31" si="91">H17/H16</f>
         <v>0.19344448654793484</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="91"/>
         <v>0.19238243295763699</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="91"/>
         <v>0.16944641589779985</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="91"/>
         <v>0.1906653426017875</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="91"/>
         <v>0.15418102666424813</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="91"/>
         <v>0.18650859909834697</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="91"/>
         <v>0.16541117388575016</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" ref="O31:R31" si="96">O17/O16</f>
+        <f t="shared" ref="O31:R31" si="92">O17/O16</f>
         <v>0.17435483870967741</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="92"/>
         <v>0.15833026848105922</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="92"/>
         <v>0.16753513342807516</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="96"/>
-        <v>0.17</v>
-      </c>
-      <c r="T31" s="9">
-        <f t="shared" ref="T31:AJ31" si="97">T17/T16</f>
+        <f t="shared" si="92"/>
+        <v>0.18206652739836091</v>
+      </c>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="X31" s="9">
+        <f t="shared" ref="X31:AN31" si="93">X17/X16</f>
         <v>0.18839021768341843</v>
       </c>
-      <c r="U31" s="9">
-        <f t="shared" si="97"/>
+      <c r="Y31" s="9">
+        <f t="shared" si="93"/>
         <v>0.212037708484409</v>
       </c>
-      <c r="V31" s="9">
-        <f t="shared" si="97"/>
+      <c r="Z31" s="9">
+        <f t="shared" si="93"/>
         <v>0.23358027765672665</v>
       </c>
-      <c r="W31" s="9">
-        <f t="shared" si="97"/>
+      <c r="AA31" s="9">
+        <f t="shared" si="93"/>
         <v>0.16977282752536391</v>
       </c>
-      <c r="X31" s="9">
-        <f t="shared" si="97"/>
+      <c r="AB31" s="9">
+        <f t="shared" si="93"/>
         <v>0.17892285021628559</v>
       </c>
-      <c r="Y31" s="9">
-        <f t="shared" si="97"/>
+      <c r="AC31" s="9">
+        <f t="shared" si="93"/>
         <v>0.17448569994982438</v>
       </c>
-      <c r="Z31" s="9">
-        <f t="shared" si="97"/>
-        <v>0.16787163667910246</v>
-      </c>
-      <c r="AA31" s="9">
-        <f t="shared" si="97"/>
+      <c r="AD31" s="9">
+        <f t="shared" si="93"/>
+        <v>0.17095147557245599</v>
+      </c>
+      <c r="AE31" s="9">
+        <f t="shared" si="93"/>
         <v>0.18</v>
       </c>
-      <c r="AB31" s="9">
-        <f t="shared" si="97"/>
+      <c r="AF31" s="9">
+        <f t="shared" si="93"/>
         <v>0.18</v>
       </c>
-      <c r="AC31" s="9">
-        <f t="shared" si="97"/>
+      <c r="AG31" s="9">
+        <f t="shared" si="93"/>
         <v>0.18</v>
       </c>
-      <c r="AD31" s="9">
-        <f t="shared" si="97"/>
+      <c r="AH31" s="9">
+        <f t="shared" si="93"/>
         <v>0.18</v>
       </c>
-      <c r="AE31" s="9">
-        <f t="shared" si="97"/>
+      <c r="AI31" s="9">
+        <f t="shared" si="93"/>
         <v>0.18</v>
       </c>
-      <c r="AF31" s="9">
-        <f t="shared" si="97"/>
+      <c r="AJ31" s="9">
+        <f t="shared" si="93"/>
         <v>0.18</v>
       </c>
-      <c r="AG31" s="9">
-        <f t="shared" si="97"/>
+      <c r="AK31" s="9">
+        <f t="shared" si="93"/>
         <v>0.18</v>
       </c>
-      <c r="AH31" s="9">
-        <f t="shared" si="97"/>
+      <c r="AL31" s="9">
+        <f t="shared" si="93"/>
         <v>0.18</v>
       </c>
-      <c r="AI31" s="9">
-        <f t="shared" si="97"/>
+      <c r="AM31" s="9">
+        <f t="shared" si="93"/>
         <v>0.18</v>
       </c>
-      <c r="AJ31" s="9">
-        <f t="shared" si="97"/>
+      <c r="AN31" s="9">
+        <f t="shared" si="93"/>
         <v>0.18</v>
       </c>
-      <c r="AM31" t="s">
+      <c r="AQ31" t="s">
         <v>56</v>
       </c>
-      <c r="AN31" s="4" t="s">
+      <c r="AR31" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:147" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:151" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>57</v>
       </c>
@@ -5063,132 +5174,136 @@
         <v>0.57501062473438169</v>
       </c>
       <c r="D32" s="9">
-        <f t="shared" ref="D32:N32" si="98">D18/D3</f>
+        <f t="shared" ref="D32:N32" si="94">D18/D3</f>
         <v>0.50730282375851998</v>
       </c>
       <c r="E32" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.46886597938144331</v>
       </c>
       <c r="F32" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.50597149094644922</v>
       </c>
       <c r="G32" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.52658770161290325</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.53312460864120226</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.5116336328942509</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.54373330235799744</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.56636553161918002</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.53139601139601145</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.54741573033707869</v>
       </c>
       <c r="N32" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.5529790995112821</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" ref="O32:R32" si="99">O18/O3</f>
+        <f t="shared" ref="O32:R32" si="95">O18/O3</f>
         <v>0.5382754994742377</v>
       </c>
       <c r="P32" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="95"/>
         <v>0.47706900145924536</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="95"/>
         <v>0.51828548957923715</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="99"/>
-        <v>0.50040299172596137</v>
-      </c>
-      <c r="T32" s="9">
-        <f t="shared" ref="T32:AJ32" si="100">T18/T3</f>
+        <f t="shared" si="95"/>
+        <v>0.47463632972771352</v>
+      </c>
+      <c r="S32" s="9"/>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="X32" s="9">
+        <f t="shared" ref="X32:AN32" si="96">X18/X3</f>
         <v>0.52574313443878662</v>
       </c>
-      <c r="U32" s="9">
-        <f t="shared" si="100"/>
+      <c r="Y32" s="9">
+        <f t="shared" si="96"/>
         <v>0.49739082669596263</v>
       </c>
-      <c r="V32" s="9">
-        <f t="shared" si="100"/>
+      <c r="Z32" s="9">
+        <f t="shared" si="96"/>
         <v>0.51072391619995849</v>
       </c>
-      <c r="W32" s="9">
-        <f t="shared" si="100"/>
+      <c r="AA32" s="9">
+        <f t="shared" si="96"/>
         <v>0.51371545547594677</v>
       </c>
-      <c r="X32" s="9">
-        <f t="shared" si="100"/>
+      <c r="AB32" s="9">
+        <f t="shared" si="96"/>
         <v>0.52898661684990655</v>
       </c>
-      <c r="Y32" s="9">
-        <f t="shared" si="100"/>
+      <c r="AC32" s="9">
+        <f t="shared" si="96"/>
         <v>0.54954628959527918</v>
       </c>
-      <c r="Z32" s="9">
-        <f t="shared" si="100"/>
-        <v>0.50834869793123305</v>
-      </c>
-      <c r="AA32" s="9">
-        <f t="shared" si="100"/>
-        <v>0.56063184795597809</v>
-      </c>
-      <c r="AB32" s="9">
-        <f t="shared" si="100"/>
-        <v>0.56955272184080263</v>
-      </c>
-      <c r="AC32" s="9">
-        <f t="shared" si="100"/>
-        <v>0.57033442107118171</v>
-      </c>
       <c r="AD32" s="9">
-        <f t="shared" si="100"/>
-        <v>0.57113537024152017</v>
+        <f t="shared" si="96"/>
+        <v>0.50144999999999995</v>
       </c>
       <c r="AE32" s="9">
-        <f t="shared" si="100"/>
-        <v>0.57194816694630446</v>
+        <f t="shared" si="96"/>
+        <v>0.56896753211009177</v>
       </c>
       <c r="AF32" s="9">
-        <f t="shared" si="100"/>
-        <v>0.57225052610443683</v>
+        <f t="shared" si="96"/>
+        <v>0.57783421538197721</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="100"/>
-        <v>0.57254795909637801</v>
+        <f t="shared" si="96"/>
+        <v>0.5785850500059202</v>
       </c>
       <c r="AH32" s="9">
-        <f t="shared" si="100"/>
-        <v>0.57284049498394607</v>
+        <f t="shared" si="96"/>
+        <v>0.57936627845705968</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="100"/>
-        <v>0.57312816235547226</v>
+        <f t="shared" si="96"/>
+        <v>0.58016944763063605</v>
       </c>
       <c r="AJ32" s="9">
-        <f t="shared" si="100"/>
-        <v>0.57341098932859225</v>
+        <f t="shared" si="96"/>
+        <v>0.58046248227928166</v>
+      </c>
+      <c r="AK32" s="9">
+        <f t="shared" si="96"/>
+        <v>0.58075059280716879</v>
+      </c>
+      <c r="AL32" s="9">
+        <f t="shared" si="96"/>
+        <v>0.58103380737987353</v>
+      </c>
+      <c r="AM32" s="9">
+        <f t="shared" si="96"/>
+        <v>0.5813121536896797</v>
+      </c>
+      <c r="AN32" s="9">
+        <f t="shared" si="96"/>
+        <v>0.58158565895828851</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/V.xlsx
+++ b/Financial Analysis/V.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A69309-21A2-47D3-87CF-11AB30DFA74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A180AD14-D0C6-4A29-A367-09EEF801A243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0E0749A9-7B4C-463E-A44A-39D457257264}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{0E0749A9-7B4C-463E-A44A-39D457257264}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
   <si>
     <t>Price</t>
   </si>
@@ -215,6 +215,18 @@
   </si>
   <si>
     <t>Slightly overvalued</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -315,14 +327,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -339,7 +351,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13685520" y="0"/>
+          <a:off x="14417040" y="0"/>
           <a:ext cx="0" cy="6309360"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -365,14 +377,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -389,7 +401,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18653760" y="0"/>
+          <a:off x="22250400" y="0"/>
           <a:ext cx="0" cy="6309360"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -736,17 +748,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="11">
-        <v>345.94</v>
+        <v>329.6</v>
       </c>
       <c r="E3" s="2">
-        <v>45959</v>
+        <v>46057</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45959</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="2">
-        <v>46044</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.3">
@@ -754,11 +766,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="3">
-        <f>1696+5+120+9</f>
-        <v>1830</v>
+        <f>1681.1+4.8+120.3+8.9</f>
+        <v>1815.1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="3:7" x14ac:dyDescent="0.3">
@@ -767,7 +779,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>633070.19999999995</v>
+        <v>598256.96</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -775,11 +787,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="3">
-        <f>17092+2088+1203</f>
-        <v>20383</v>
+        <f>14756+1641+484</f>
+        <v>16881</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="3:7" x14ac:dyDescent="0.3">
@@ -787,11 +799,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="3">
-        <f>5548+19590</f>
-        <v>25138</v>
+        <f>1589+19588</f>
+        <v>21177</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="3:7" x14ac:dyDescent="0.3">
@@ -800,7 +812,7 @@
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>-4755</v>
+        <v>-4296</v>
       </c>
     </row>
     <row r="9" spans="3:7" x14ac:dyDescent="0.3">
@@ -809,7 +821,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>637825.19999999995</v>
+        <v>602552.96</v>
       </c>
     </row>
   </sheetData>
@@ -880,10 +892,18 @@
       <c r="R1" s="8">
         <v>45930</v>
       </c>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
+      <c r="S1" s="8">
+        <v>46022</v>
+      </c>
+      <c r="T1" s="8">
+        <v>46112</v>
+      </c>
+      <c r="U1" s="8">
+        <v>46203</v>
+      </c>
+      <c r="V1" s="8">
+        <v>46295</v>
+      </c>
       <c r="X1" s="8">
         <v>43738</v>
       </c>
@@ -985,10 +1005,18 @@
       <c r="R2" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
+      <c r="S2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="X2">
         <v>2019</v>
       </c>
@@ -1094,7 +1122,9 @@
       <c r="R3" s="7">
         <v>10724</v>
       </c>
-      <c r="S3" s="7"/>
+      <c r="S3" s="7">
+        <v>10901</v>
+      </c>
       <c r="T3" s="7"/>
       <c r="U3" s="7"/>
       <c r="V3" s="7"/>
@@ -1124,44 +1154,44 @@
         <v>40000</v>
       </c>
       <c r="AE3" s="7">
-        <f>AD3*1.09</f>
-        <v>43600</v>
+        <f>AD3*1.13</f>
+        <v>45199.999999999993</v>
       </c>
       <c r="AF3" s="7">
         <f>AE3*1.07</f>
-        <v>46652</v>
+        <v>48363.999999999993</v>
       </c>
       <c r="AG3" s="7">
         <f>AF3*1.05</f>
-        <v>48984.6</v>
+        <v>50782.2</v>
       </c>
       <c r="AH3" s="7">
         <f>AG3*1.04</f>
-        <v>50943.983999999997</v>
+        <v>52813.487999999998</v>
       </c>
       <c r="AI3" s="7">
         <f>AH3*1.03</f>
-        <v>52472.303520000001</v>
+        <v>54397.892639999998</v>
       </c>
       <c r="AJ3" s="7">
         <f t="shared" ref="AJ3:AN3" si="0">AI3*1.02</f>
-        <v>53521.749590400002</v>
+        <v>55485.850492799997</v>
       </c>
       <c r="AK3" s="7">
         <f t="shared" si="0"/>
-        <v>54592.184582208007</v>
+        <v>56595.567502655998</v>
       </c>
       <c r="AL3" s="7">
         <f t="shared" si="0"/>
-        <v>55684.028273852171</v>
+        <v>57727.478852709122</v>
       </c>
       <c r="AM3" s="7">
         <f t="shared" si="0"/>
-        <v>56797.708839329214</v>
+        <v>58882.028429763304</v>
       </c>
       <c r="AN3" s="7">
         <f t="shared" si="0"/>
-        <v>57933.663016115803</v>
+        <v>60059.668998358575</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.3">
@@ -1216,7 +1246,9 @@
       <c r="R4" s="3">
         <v>1742</v>
       </c>
-      <c r="S4" s="3"/>
+      <c r="S4" s="3">
+        <v>1764</v>
+      </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
@@ -1247,43 +1279,43 @@
       </c>
       <c r="AE4" s="3">
         <f t="shared" ref="AE4:AN4" si="1">AE3-AE5</f>
-        <v>6976</v>
+        <v>7232</v>
       </c>
       <c r="AF4" s="3">
         <f t="shared" si="1"/>
-        <v>7464.32</v>
+        <v>7738.239999999998</v>
       </c>
       <c r="AG4" s="3">
         <f t="shared" si="1"/>
-        <v>7837.5360000000001</v>
+        <v>8125.1520000000019</v>
       </c>
       <c r="AH4" s="3">
         <f t="shared" si="1"/>
-        <v>8151.0374400000001</v>
+        <v>8450.1580800000011</v>
       </c>
       <c r="AI4" s="3">
         <f t="shared" si="1"/>
-        <v>8395.5685632000022</v>
+        <v>8703.6628224000015</v>
       </c>
       <c r="AJ4" s="3">
         <f t="shared" si="1"/>
-        <v>8563.4799344640051</v>
+        <v>8877.736078848</v>
       </c>
       <c r="AK4" s="3">
         <f t="shared" si="1"/>
-        <v>8734.7495331532846</v>
+        <v>9055.2908004249621</v>
       </c>
       <c r="AL4" s="3">
         <f t="shared" si="1"/>
-        <v>8909.4445238163462</v>
+        <v>9236.3966164334634</v>
       </c>
       <c r="AM4" s="3">
         <f t="shared" si="1"/>
-        <v>9087.6334142926789</v>
+        <v>9421.1245487621272</v>
       </c>
       <c r="AN4" s="3">
         <f t="shared" si="1"/>
-        <v>9269.3860825785305</v>
+        <v>9609.547039737372</v>
       </c>
     </row>
     <row r="5" spans="1:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1355,77 +1387,80 @@
         <f t="shared" si="3"/>
         <v>8982</v>
       </c>
-      <c r="S5" s="7"/>
+      <c r="S5" s="7">
+        <f t="shared" ref="S5" si="4">S3-S4</f>
+        <v>9137</v>
+      </c>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
       <c r="X5" s="7">
-        <f t="shared" ref="X5:AD5" si="4">X3-X4</f>
+        <f t="shared" ref="X5:AD5" si="5">X3-X4</f>
         <v>19533</v>
       </c>
       <c r="Y5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>18061</v>
       </c>
       <c r="Z5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19865</v>
       </c>
       <c r="AA5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>24320</v>
       </c>
       <c r="AB5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>26822</v>
       </c>
       <c r="AC5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>29662</v>
       </c>
       <c r="AD5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>33039</v>
       </c>
       <c r="AE5" s="7">
         <f>AE3*0.84</f>
-        <v>36624</v>
+        <v>37967.999999999993</v>
       </c>
       <c r="AF5" s="7">
-        <f t="shared" ref="AF5:AN5" si="5">AF3*0.84</f>
-        <v>39187.68</v>
+        <f t="shared" ref="AF5:AN5" si="6">AF3*0.84</f>
+        <v>40625.759999999995</v>
       </c>
       <c r="AG5" s="7">
-        <f t="shared" si="5"/>
-        <v>41147.063999999998</v>
+        <f t="shared" si="6"/>
+        <v>42657.047999999995</v>
       </c>
       <c r="AH5" s="7">
-        <f t="shared" si="5"/>
-        <v>42792.946559999997</v>
+        <f t="shared" si="6"/>
+        <v>44363.329919999996</v>
       </c>
       <c r="AI5" s="7">
-        <f t="shared" si="5"/>
-        <v>44076.734956799999</v>
+        <f t="shared" si="6"/>
+        <v>45694.229817599997</v>
       </c>
       <c r="AJ5" s="7">
-        <f t="shared" si="5"/>
-        <v>44958.269655935997</v>
+        <f t="shared" si="6"/>
+        <v>46608.114413951997</v>
       </c>
       <c r="AK5" s="7">
-        <f t="shared" si="5"/>
-        <v>45857.435049054722</v>
+        <f t="shared" si="6"/>
+        <v>47540.276702231036</v>
       </c>
       <c r="AL5" s="7">
-        <f t="shared" si="5"/>
-        <v>46774.583750035825</v>
+        <f t="shared" si="6"/>
+        <v>48491.082236275659</v>
       </c>
       <c r="AM5" s="7">
-        <f t="shared" si="5"/>
-        <v>47710.075425036535</v>
+        <f t="shared" si="6"/>
+        <v>49460.903881001177</v>
       </c>
       <c r="AN5" s="7">
-        <f t="shared" si="5"/>
-        <v>48664.276933537272</v>
+        <f t="shared" si="6"/>
+        <v>50450.121958621203</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.3">
@@ -1480,7 +1515,9 @@
       <c r="R6" s="3">
         <v>576</v>
       </c>
-      <c r="S6" s="3"/>
+      <c r="S6" s="3">
+        <v>410</v>
+      </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
@@ -1494,60 +1531,60 @@
         <v>1136</v>
       </c>
       <c r="AA6" s="3">
-        <f t="shared" ref="AA6:AA11" si="6">SUM(C6:F6)</f>
+        <f t="shared" ref="AA6:AA11" si="7">SUM(C6:F6)</f>
         <v>1336</v>
       </c>
       <c r="AB6" s="3">
-        <f t="shared" ref="AB6:AB11" si="7">SUM(G6:J6)</f>
+        <f t="shared" ref="AB6:AB11" si="8">SUM(G6:J6)</f>
         <v>1341</v>
       </c>
       <c r="AC6" s="3">
-        <f t="shared" ref="AC6:AC11" si="8">SUM(K6:N6)</f>
+        <f t="shared" ref="AC6:AC11" si="9">SUM(K6:N6)</f>
         <v>1560</v>
       </c>
       <c r="AD6" s="3">
-        <f t="shared" ref="AD6:AD11" si="9">SUM(O6:R6)</f>
+        <f t="shared" ref="AD6:AD11" si="10">SUM(O6:R6)</f>
         <v>1684</v>
       </c>
       <c r="AE6" s="3">
-        <f t="shared" ref="AE6:AN6" si="10">AE3*0.04</f>
-        <v>1744</v>
+        <f t="shared" ref="AE6:AN6" si="11">AE3*0.04</f>
+        <v>1807.9999999999998</v>
       </c>
       <c r="AF6" s="3">
-        <f t="shared" si="10"/>
-        <v>1866.08</v>
+        <f t="shared" si="11"/>
+        <v>1934.5599999999997</v>
       </c>
       <c r="AG6" s="3">
-        <f t="shared" si="10"/>
-        <v>1959.384</v>
+        <f t="shared" si="11"/>
+        <v>2031.288</v>
       </c>
       <c r="AH6" s="3">
-        <f t="shared" si="10"/>
-        <v>2037.75936</v>
+        <f t="shared" si="11"/>
+        <v>2112.5395199999998</v>
       </c>
       <c r="AI6" s="3">
-        <f t="shared" si="10"/>
-        <v>2098.8921408000001</v>
+        <f t="shared" si="11"/>
+        <v>2175.9157055999999</v>
       </c>
       <c r="AJ6" s="3">
-        <f t="shared" si="10"/>
-        <v>2140.8699836160004</v>
+        <f t="shared" si="11"/>
+        <v>2219.434019712</v>
       </c>
       <c r="AK6" s="3">
-        <f t="shared" si="10"/>
-        <v>2183.6873832883202</v>
+        <f t="shared" si="11"/>
+        <v>2263.8227001062401</v>
       </c>
       <c r="AL6" s="3">
-        <f t="shared" si="10"/>
-        <v>2227.361130954087</v>
+        <f t="shared" si="11"/>
+        <v>2309.0991541083649</v>
       </c>
       <c r="AM6" s="3">
-        <f t="shared" si="10"/>
-        <v>2271.9083535731688</v>
+        <f t="shared" si="11"/>
+        <v>2355.2811371905323</v>
       </c>
       <c r="AN6" s="3">
-        <f t="shared" si="10"/>
-        <v>2317.3465206446322</v>
+        <f t="shared" si="11"/>
+        <v>2402.386759934343</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.3">
@@ -1602,7 +1639,9 @@
       <c r="R7" s="3">
         <v>239</v>
       </c>
-      <c r="S7" s="3"/>
+      <c r="S7" s="3">
+        <v>233</v>
+      </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
@@ -1616,19 +1655,19 @@
         <v>730</v>
       </c>
       <c r="AA7" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>743</v>
       </c>
       <c r="AB7" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>736</v>
       </c>
       <c r="AC7" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>778</v>
       </c>
       <c r="AD7" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>894</v>
       </c>
       <c r="AE7" s="3">
@@ -1648,27 +1687,27 @@
         <v>1074.9560598</v>
       </c>
       <c r="AI7" s="3">
-        <f t="shared" ref="AI7:AN7" si="11">AH7*1.01</f>
+        <f t="shared" ref="AI7:AN7" si="12">AH7*1.01</f>
         <v>1085.7056203980001</v>
       </c>
       <c r="AJ7" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1096.56267660198</v>
       </c>
       <c r="AK7" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1107.5283033679998</v>
       </c>
       <c r="AL7" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1118.6035864016799</v>
       </c>
       <c r="AM7" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1129.7896222656966</v>
       </c>
       <c r="AN7" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1141.0875184883537</v>
       </c>
     </row>
@@ -1724,7 +1763,9 @@
       <c r="R8" s="3">
         <v>256</v>
       </c>
-      <c r="S8" s="3"/>
+      <c r="S8" s="3">
+        <v>208</v>
+      </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
@@ -1738,60 +1779,60 @@
         <v>403</v>
       </c>
       <c r="AA8" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>505</v>
       </c>
       <c r="AB8" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>545</v>
       </c>
       <c r="AC8" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>635</v>
       </c>
       <c r="AD8" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>759</v>
       </c>
       <c r="AE8" s="3">
-        <f t="shared" ref="AE8:AN8" si="12">AE3*0.02</f>
-        <v>872</v>
+        <f t="shared" ref="AE8:AN8" si="13">AE3*0.02</f>
+        <v>903.99999999999989</v>
       </c>
       <c r="AF8" s="3">
-        <f t="shared" si="12"/>
-        <v>933.04</v>
+        <f t="shared" si="13"/>
+        <v>967.27999999999986</v>
       </c>
       <c r="AG8" s="3">
-        <f t="shared" si="12"/>
-        <v>979.69200000000001</v>
+        <f t="shared" si="13"/>
+        <v>1015.644</v>
       </c>
       <c r="AH8" s="3">
-        <f t="shared" si="12"/>
-        <v>1018.87968</v>
+        <f t="shared" si="13"/>
+        <v>1056.2697599999999</v>
       </c>
       <c r="AI8" s="3">
-        <f t="shared" si="12"/>
-        <v>1049.4460704000001</v>
+        <f t="shared" si="13"/>
+        <v>1087.9578528</v>
       </c>
       <c r="AJ8" s="3">
-        <f t="shared" si="12"/>
-        <v>1070.4349918080002</v>
+        <f t="shared" si="13"/>
+        <v>1109.717009856</v>
       </c>
       <c r="AK8" s="3">
-        <f t="shared" si="12"/>
-        <v>1091.8436916441601</v>
+        <f t="shared" si="13"/>
+        <v>1131.91135005312</v>
       </c>
       <c r="AL8" s="3">
-        <f t="shared" si="12"/>
-        <v>1113.6805654770435</v>
+        <f t="shared" si="13"/>
+        <v>1154.5495770541825</v>
       </c>
       <c r="AM8" s="3">
-        <f t="shared" si="12"/>
-        <v>1135.9541767865844</v>
+        <f t="shared" si="13"/>
+        <v>1177.6405685952661</v>
       </c>
       <c r="AN8" s="3">
-        <f t="shared" si="12"/>
-        <v>1158.6732603223161</v>
+        <f t="shared" si="13"/>
+        <v>1201.1933799671715</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.3">
@@ -1846,7 +1887,9 @@
       <c r="R9" s="3">
         <v>316</v>
       </c>
-      <c r="S9" s="3"/>
+      <c r="S9" s="3">
+        <v>326</v>
+      </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
@@ -1860,22 +1903,25 @@
         <v>804</v>
       </c>
       <c r="AA9" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>861</v>
       </c>
       <c r="AB9" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>943</v>
       </c>
       <c r="AC9" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1034</v>
       </c>
       <c r="AD9" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1220</v>
       </c>
-      <c r="AE9" s="3"/>
+      <c r="AE9" s="3">
+        <f>SUM(S9:V9)</f>
+        <v>326</v>
+      </c>
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
@@ -1938,7 +1984,9 @@
       <c r="R10" s="3">
         <v>544</v>
       </c>
-      <c r="S10" s="3"/>
+      <c r="S10" s="3">
+        <v>515</v>
+      </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
@@ -1952,19 +2000,19 @@
         <v>985</v>
       </c>
       <c r="AA10" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1194</v>
       </c>
       <c r="AB10" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1330</v>
       </c>
       <c r="AC10" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1598</v>
       </c>
       <c r="AD10" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1926</v>
       </c>
       <c r="AE10" s="3">
@@ -1980,7 +2028,7 @@
         <v>2270.4362100000003</v>
       </c>
       <c r="AH10" s="3">
-        <f t="shared" ref="AH10" si="13">AG10*1.02</f>
+        <f t="shared" ref="AH10" si="14">AG10*1.02</f>
         <v>2315.8449342000004</v>
       </c>
       <c r="AI10" s="3">
@@ -1988,23 +2036,23 @@
         <v>2339.0033835420004</v>
       </c>
       <c r="AJ10" s="3">
-        <f t="shared" ref="AJ10:AN10" si="14">AI10*1.01</f>
+        <f t="shared" ref="AJ10:AN10" si="15">AI10*1.01</f>
         <v>2362.3934173774205</v>
       </c>
       <c r="AK10" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2386.0173515511947</v>
       </c>
       <c r="AL10" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2409.8775250667068</v>
       </c>
       <c r="AM10" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2433.9763003173739</v>
       </c>
       <c r="AN10" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2458.3160633205475</v>
       </c>
     </row>
@@ -2060,7 +2108,9 @@
       <c r="R11" s="3">
         <v>903</v>
       </c>
-      <c r="S11" s="3"/>
+      <c r="S11" s="3">
+        <v>708</v>
+      </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
@@ -2074,60 +2124,60 @@
         <v>3</v>
       </c>
       <c r="AA11" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>868</v>
       </c>
       <c r="AB11" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>927</v>
       </c>
       <c r="AC11" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>462</v>
       </c>
       <c r="AD11" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2562</v>
       </c>
       <c r="AE11" s="3">
         <f>AE3*0.02</f>
-        <v>872</v>
+        <v>903.99999999999989</v>
       </c>
       <c r="AF11" s="3">
-        <f t="shared" ref="AF11:AN11" si="15">AF3*0.01</f>
-        <v>466.52</v>
+        <f t="shared" ref="AF11:AN11" si="16">AF3*0.01</f>
+        <v>483.63999999999993</v>
       </c>
       <c r="AG11" s="3">
-        <f t="shared" si="15"/>
-        <v>489.846</v>
+        <f t="shared" si="16"/>
+        <v>507.822</v>
       </c>
       <c r="AH11" s="3">
-        <f t="shared" si="15"/>
-        <v>509.43984</v>
+        <f t="shared" si="16"/>
+        <v>528.13487999999995</v>
       </c>
       <c r="AI11" s="3">
-        <f t="shared" si="15"/>
-        <v>524.72303520000003</v>
+        <f t="shared" si="16"/>
+        <v>543.97892639999998</v>
       </c>
       <c r="AJ11" s="3">
-        <f t="shared" si="15"/>
-        <v>535.21749590400009</v>
+        <f t="shared" si="16"/>
+        <v>554.858504928</v>
       </c>
       <c r="AK11" s="3">
-        <f t="shared" si="15"/>
-        <v>545.92184582208006</v>
+        <f t="shared" si="16"/>
+        <v>565.95567502656002</v>
       </c>
       <c r="AL11" s="3">
-        <f t="shared" si="15"/>
-        <v>556.84028273852175</v>
+        <f t="shared" si="16"/>
+        <v>577.27478852709123</v>
       </c>
       <c r="AM11" s="3">
-        <f t="shared" si="15"/>
-        <v>567.97708839329221</v>
+        <f t="shared" si="16"/>
+        <v>588.82028429763307</v>
       </c>
       <c r="AN11" s="3">
-        <f t="shared" si="15"/>
-        <v>579.33663016115804</v>
+        <f t="shared" si="16"/>
+        <v>600.59668998358575</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.3">
@@ -2135,140 +2185,143 @@
         <v>18</v>
       </c>
       <c r="C12" s="3">
-        <f t="shared" ref="C12:L12" si="16">SUM(C6:C11)</f>
+        <f t="shared" ref="C12:L12" si="17">SUM(C6:C11)</f>
         <v>1158</v>
       </c>
       <c r="D12" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1161</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1844</v>
       </c>
       <c r="F12" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1344</v>
       </c>
       <c r="G12" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1509</v>
       </c>
       <c r="H12" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1134</v>
       </c>
       <c r="I12" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1618</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1561</v>
       </c>
       <c r="K12" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1201</v>
       </c>
       <c r="L12" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1818</v>
       </c>
       <c r="M12" s="3">
-        <f t="shared" ref="M12:N12" si="17">SUM(M6:M11)</f>
+        <f t="shared" ref="M12:N12" si="18">SUM(M6:M11)</f>
         <v>1389</v>
       </c>
       <c r="N12" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1659</v>
       </c>
       <c r="O12" s="3">
-        <f t="shared" ref="O12:R12" si="18">SUM(O6:O11)</f>
+        <f t="shared" ref="O12:R12" si="19">SUM(O6:O11)</f>
         <v>1463</v>
       </c>
       <c r="P12" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2502</v>
       </c>
       <c r="Q12" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2246</v>
       </c>
       <c r="R12" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2834</v>
       </c>
-      <c r="S12" s="3"/>
+      <c r="S12" s="3">
+        <f t="shared" ref="S12" si="20">SUM(S6:S11)</f>
+        <v>2400</v>
+      </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="X12" s="3">
-        <f t="shared" ref="X12:AC12" si="19">SUM(X6:X11)</f>
+        <f t="shared" ref="X12:AC12" si="21">SUM(X6:X11)</f>
         <v>4532</v>
       </c>
       <c r="Y12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>3980</v>
       </c>
       <c r="Z12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>4061</v>
       </c>
       <c r="AA12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>5507</v>
       </c>
       <c r="AB12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>5822</v>
       </c>
       <c r="AC12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>6067</v>
       </c>
       <c r="AD12" s="3">
-        <f t="shared" ref="AD12:AN12" si="20">SUM(AD6:AD11)</f>
+        <f t="shared" ref="AD12:AN12" si="22">SUM(AD6:AD11)</f>
         <v>9045</v>
       </c>
       <c r="AE12" s="3">
-        <f t="shared" si="20"/>
-        <v>6561.8</v>
+        <f t="shared" si="22"/>
+        <v>7015.8</v>
       </c>
       <c r="AF12" s="3">
-        <f t="shared" si="20"/>
-        <v>6493.130000000001</v>
+        <f t="shared" si="22"/>
+        <v>6612.97</v>
       </c>
       <c r="AG12" s="3">
-        <f t="shared" si="20"/>
-        <v>6753.2366999999995</v>
+        <f t="shared" si="22"/>
+        <v>6879.0686999999998</v>
       </c>
       <c r="AH12" s="3">
-        <f t="shared" si="20"/>
-        <v>6956.8798740000002</v>
+        <f t="shared" si="22"/>
+        <v>7087.7451540000002</v>
       </c>
       <c r="AI12" s="3">
-        <f t="shared" si="20"/>
-        <v>7097.7702503400005</v>
+        <f t="shared" si="22"/>
+        <v>7232.5614887399997</v>
       </c>
       <c r="AJ12" s="3">
-        <f t="shared" si="20"/>
-        <v>7205.4785653074014</v>
+        <f t="shared" si="22"/>
+        <v>7342.9656284754001</v>
       </c>
       <c r="AK12" s="3">
-        <f t="shared" si="20"/>
-        <v>7314.9985756737551</v>
+        <f t="shared" si="22"/>
+        <v>7455.235380105114</v>
       </c>
       <c r="AL12" s="3">
-        <f t="shared" si="20"/>
-        <v>7426.3630906380386</v>
+        <f t="shared" si="22"/>
+        <v>7569.404631158025</v>
       </c>
       <c r="AM12" s="3">
-        <f t="shared" si="20"/>
-        <v>7539.6055413361155</v>
+        <f t="shared" si="22"/>
+        <v>7685.5079126665023</v>
       </c>
       <c r="AN12" s="3">
-        <f t="shared" si="20"/>
-        <v>7654.7599929370072</v>
+        <f t="shared" si="22"/>
+        <v>7803.5804116940017</v>
       </c>
     </row>
     <row r="13" spans="1:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2277,140 +2330,143 @@
         <v>19</v>
       </c>
       <c r="C13" s="7">
-        <f t="shared" ref="C13:L13" si="21">C5-C12</f>
+        <f t="shared" ref="C13:L13" si="23">C5-C12</f>
         <v>4776</v>
       </c>
       <c r="D13" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>4802</v>
       </c>
       <c r="E13" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>4148</v>
       </c>
       <c r="F13" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>5087</v>
       </c>
       <c r="G13" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>5090</v>
       </c>
       <c r="H13" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>5336</v>
       </c>
       <c r="I13" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>5024</v>
       </c>
       <c r="J13" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>5550</v>
       </c>
       <c r="K13" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>5954</v>
       </c>
       <c r="L13" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>5354</v>
       </c>
       <c r="M13" s="7">
-        <f t="shared" ref="M13:N13" si="22">M5-M12</f>
+        <f t="shared" ref="M13:N13" si="24">M5-M12</f>
         <v>5938</v>
       </c>
       <c r="N13" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>6349</v>
       </c>
       <c r="O13" s="7">
-        <f t="shared" ref="O13:R13" si="23">O5-O12</f>
+        <f t="shared" ref="O13:R13" si="25">O5-O12</f>
         <v>6234</v>
       </c>
       <c r="P13" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>5435</v>
       </c>
       <c r="Q13" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>6177</v>
       </c>
       <c r="R13" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>6148</v>
       </c>
-      <c r="S13" s="7"/>
+      <c r="S13" s="7">
+        <f t="shared" ref="S13" si="26">S5-S12</f>
+        <v>6737</v>
+      </c>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
       <c r="X13" s="7">
-        <f t="shared" ref="X13:AC13" si="24">X5-X12</f>
+        <f t="shared" ref="X13:AC13" si="27">X5-X12</f>
         <v>15001</v>
       </c>
       <c r="Y13" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>14081</v>
       </c>
       <c r="Z13" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>15804</v>
       </c>
       <c r="AA13" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>18813</v>
       </c>
       <c r="AB13" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>21000</v>
       </c>
       <c r="AC13" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>23595</v>
       </c>
       <c r="AD13" s="7">
-        <f t="shared" ref="AD13:AN13" si="25">AD5-AD12</f>
+        <f t="shared" ref="AD13:AN13" si="28">AD5-AD12</f>
         <v>23994</v>
       </c>
       <c r="AE13" s="7">
-        <f t="shared" si="25"/>
-        <v>30062.2</v>
+        <f t="shared" si="28"/>
+        <v>30952.199999999993</v>
       </c>
       <c r="AF13" s="7">
-        <f t="shared" si="25"/>
-        <v>32694.55</v>
+        <f t="shared" si="28"/>
+        <v>34012.789999999994</v>
       </c>
       <c r="AG13" s="7">
-        <f t="shared" si="25"/>
-        <v>34393.827299999997</v>
+        <f t="shared" si="28"/>
+        <v>35777.979299999992</v>
       </c>
       <c r="AH13" s="7">
-        <f t="shared" si="25"/>
-        <v>35836.066685999998</v>
+        <f t="shared" si="28"/>
+        <v>37275.584766</v>
       </c>
       <c r="AI13" s="7">
-        <f t="shared" si="25"/>
-        <v>36978.964706459999</v>
+        <f t="shared" si="28"/>
+        <v>38461.668328859996</v>
       </c>
       <c r="AJ13" s="7">
-        <f t="shared" si="25"/>
-        <v>37752.791090628598</v>
+        <f t="shared" si="28"/>
+        <v>39265.148785476595</v>
       </c>
       <c r="AK13" s="7">
-        <f t="shared" si="25"/>
-        <v>38542.436473380963</v>
+        <f t="shared" si="28"/>
+        <v>40085.041322125922</v>
       </c>
       <c r="AL13" s="7">
-        <f t="shared" si="25"/>
-        <v>39348.22065939779</v>
+        <f t="shared" si="28"/>
+        <v>40921.677605117635</v>
       </c>
       <c r="AM13" s="7">
-        <f t="shared" si="25"/>
-        <v>40170.469883700418</v>
+        <f t="shared" si="28"/>
+        <v>41775.395968334677</v>
       </c>
       <c r="AN13" s="7">
-        <f t="shared" si="25"/>
-        <v>41009.516940600268</v>
+        <f t="shared" si="28"/>
+        <v>42646.541546927197</v>
       </c>
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.3">
@@ -2465,7 +2521,9 @@
       <c r="R14" s="3">
         <v>210</v>
       </c>
-      <c r="S14" s="3"/>
+      <c r="S14" s="3">
+        <v>194</v>
+      </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
@@ -2495,43 +2553,43 @@
         <v>589</v>
       </c>
       <c r="AE14" s="3">
-        <f t="shared" ref="AE14:AN14" si="26">AD14*1.03</f>
+        <f t="shared" ref="AE14:AN14" si="29">AD14*1.03</f>
         <v>606.66999999999996</v>
       </c>
       <c r="AF14" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>624.87009999999998</v>
       </c>
       <c r="AG14" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>643.61620300000004</v>
       </c>
       <c r="AH14" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>662.92468909000002</v>
       </c>
       <c r="AI14" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>682.81242976270005</v>
       </c>
       <c r="AJ14" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>703.29680265558102</v>
       </c>
       <c r="AK14" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>724.3957067352485</v>
       </c>
       <c r="AL14" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>746.127577937306</v>
       </c>
       <c r="AM14" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>768.5114052754252</v>
       </c>
       <c r="AN14" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>791.56674743368796</v>
       </c>
     </row>
@@ -2587,7 +2645,9 @@
       <c r="R15" s="3">
         <v>-285</v>
       </c>
-      <c r="S15" s="3"/>
+      <c r="S15" s="3">
+        <v>-183</v>
+      </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
@@ -2617,43 +2677,43 @@
         <v>-789</v>
       </c>
       <c r="AE15" s="3">
-        <f t="shared" ref="AE15:AN15" si="27">AD15*1.01</f>
+        <f t="shared" ref="AE15:AN15" si="30">AD15*1.01</f>
         <v>-796.89</v>
       </c>
       <c r="AF15" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-804.85889999999995</v>
       </c>
       <c r="AG15" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-812.90748899999994</v>
       </c>
       <c r="AH15" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-821.03656388999991</v>
       </c>
       <c r="AI15" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-829.24692952889995</v>
       </c>
       <c r="AJ15" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-837.53939882418899</v>
       </c>
       <c r="AK15" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-845.91479281243085</v>
       </c>
       <c r="AL15" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-854.37394074055521</v>
       </c>
       <c r="AM15" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-862.91768014796082</v>
       </c>
       <c r="AN15" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-871.54685694944044</v>
       </c>
     </row>
@@ -2663,140 +2723,143 @@
         <v>22</v>
       </c>
       <c r="C16" s="7">
-        <f t="shared" ref="C16:L16" si="28">C13-C14-C15</f>
+        <f t="shared" ref="C16:L16" si="31">C13-C14-C15</f>
         <v>4897</v>
       </c>
       <c r="D16" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4542</v>
       </c>
       <c r="E16" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>3829</v>
       </c>
       <c r="F16" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4868</v>
       </c>
       <c r="G16" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4977</v>
       </c>
       <c r="H16" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>5278</v>
       </c>
       <c r="I16" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>5146</v>
       </c>
       <c r="J16" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>5636</v>
       </c>
       <c r="K16" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>6042</v>
       </c>
       <c r="L16" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>5513</v>
       </c>
       <c r="M16" s="7">
-        <f t="shared" ref="M16:N16" si="29">M13-M14-M15</f>
+        <f t="shared" ref="M16:N16" si="32">M13-M14-M15</f>
         <v>5989</v>
       </c>
       <c r="N16" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>6372</v>
       </c>
       <c r="O16" s="7">
-        <f t="shared" ref="O16:R16" si="30">O13-O14-O15</f>
+        <f t="shared" ref="O16:R16" si="33">O13-O14-O15</f>
         <v>6200</v>
       </c>
       <c r="P16" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>5438</v>
       </c>
       <c r="Q16" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>6333</v>
       </c>
       <c r="R16" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>6223</v>
       </c>
-      <c r="S16" s="7"/>
+      <c r="S16" s="7">
+        <f t="shared" ref="S16" si="34">S13-S14-S15</f>
+        <v>6726</v>
+      </c>
       <c r="T16" s="7"/>
       <c r="U16" s="7"/>
       <c r="V16" s="7"/>
       <c r="X16" s="7">
-        <f t="shared" ref="X16:AD16" si="31">X13-X14-X15</f>
+        <f t="shared" ref="X16:AD16" si="35">X13-X14-X15</f>
         <v>14884</v>
       </c>
       <c r="Y16" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>13790</v>
       </c>
       <c r="Z16" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>16063</v>
       </c>
       <c r="AA16" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>18136</v>
       </c>
       <c r="AB16" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>21037</v>
       </c>
       <c r="AC16" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>23916</v>
       </c>
       <c r="AD16" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>24194</v>
       </c>
       <c r="AE16" s="7">
-        <f t="shared" ref="AE16:AN16" si="32">AE13-AE14-AE15</f>
-        <v>30252.420000000002</v>
+        <f t="shared" ref="AE16:AN16" si="36">AE13-AE14-AE15</f>
+        <v>31142.419999999995</v>
       </c>
       <c r="AF16" s="7">
-        <f t="shared" si="32"/>
-        <v>32874.538800000002</v>
+        <f t="shared" si="36"/>
+        <v>34192.778799999993</v>
       </c>
       <c r="AG16" s="7">
-        <f t="shared" si="32"/>
-        <v>34563.118585999997</v>
+        <f t="shared" si="36"/>
+        <v>35947.270585999991</v>
       </c>
       <c r="AH16" s="7">
-        <f t="shared" si="32"/>
-        <v>35994.178560799992</v>
+        <f t="shared" si="36"/>
+        <v>37433.696640799993</v>
       </c>
       <c r="AI16" s="7">
-        <f t="shared" si="32"/>
-        <v>37125.399206226197</v>
+        <f t="shared" si="36"/>
+        <v>38608.102828626194</v>
       </c>
       <c r="AJ16" s="7">
-        <f t="shared" si="32"/>
-        <v>37887.033686797207</v>
+        <f t="shared" si="36"/>
+        <v>39399.391381645204</v>
       </c>
       <c r="AK16" s="7">
-        <f t="shared" si="32"/>
-        <v>38663.955559458147</v>
+        <f t="shared" si="36"/>
+        <v>40206.560408203106</v>
       </c>
       <c r="AL16" s="7">
-        <f t="shared" si="32"/>
-        <v>39456.467022201039</v>
+        <f t="shared" si="36"/>
+        <v>41029.923967920884</v>
       </c>
       <c r="AM16" s="7">
-        <f t="shared" si="32"/>
-        <v>40264.876158572952</v>
+        <f t="shared" si="36"/>
+        <v>41869.802243207218</v>
       </c>
       <c r="AN16" s="7">
-        <f t="shared" si="32"/>
-        <v>41089.497050116021</v>
+        <f t="shared" si="36"/>
+        <v>42726.52165644295</v>
       </c>
     </row>
     <row r="17" spans="1:151" x14ac:dyDescent="0.3">
@@ -2851,7 +2914,9 @@
       <c r="R17" s="3">
         <v>1133</v>
       </c>
-      <c r="S17" s="3"/>
+      <c r="S17" s="3">
+        <v>873</v>
+      </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
@@ -2881,44 +2946,44 @@
         <v>4136</v>
       </c>
       <c r="AE17" s="3">
-        <f t="shared" ref="AE17:AN17" si="33">AE16*0.18</f>
-        <v>5445.4355999999998</v>
+        <f t="shared" ref="AE17:AN17" si="37">AE16*0.18</f>
+        <v>5605.6355999999987</v>
       </c>
       <c r="AF17" s="3">
-        <f t="shared" si="33"/>
-        <v>5917.4169840000004</v>
+        <f t="shared" si="37"/>
+        <v>6154.7001839999984</v>
       </c>
       <c r="AG17" s="3">
-        <f t="shared" si="33"/>
-        <v>6221.3613454799988</v>
+        <f t="shared" si="37"/>
+        <v>6470.5087054799978</v>
       </c>
       <c r="AH17" s="3">
-        <f t="shared" si="33"/>
-        <v>6478.9521409439985</v>
+        <f t="shared" si="37"/>
+        <v>6738.0653953439987</v>
       </c>
       <c r="AI17" s="3">
-        <f t="shared" si="33"/>
-        <v>6682.5718571207153</v>
+        <f t="shared" si="37"/>
+        <v>6949.4585091527142</v>
       </c>
       <c r="AJ17" s="3">
-        <f t="shared" si="33"/>
-        <v>6819.6660636234974</v>
+        <f t="shared" si="37"/>
+        <v>7091.8904486961364</v>
       </c>
       <c r="AK17" s="3">
-        <f t="shared" si="33"/>
-        <v>6959.5120007024661</v>
+        <f t="shared" si="37"/>
+        <v>7237.1808734765591</v>
       </c>
       <c r="AL17" s="3">
-        <f t="shared" si="33"/>
-        <v>7102.164063996187</v>
+        <f t="shared" si="37"/>
+        <v>7385.3863142257587</v>
       </c>
       <c r="AM17" s="3">
-        <f t="shared" si="33"/>
-        <v>7247.6777085431313</v>
+        <f t="shared" si="37"/>
+        <v>7536.564403777299</v>
       </c>
       <c r="AN17" s="3">
-        <f t="shared" si="33"/>
-        <v>7396.1094690208838</v>
+        <f t="shared" si="37"/>
+        <v>7690.7738981597304</v>
       </c>
     </row>
     <row r="18" spans="1:151" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2927,584 +2992,587 @@
         <v>24</v>
       </c>
       <c r="C18" s="7">
-        <f t="shared" ref="C18:L18" si="34">C16-C17</f>
+        <f t="shared" ref="C18:L18" si="38">C16-C17</f>
         <v>4059</v>
       </c>
       <c r="D18" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>3647</v>
       </c>
       <c r="E18" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>3411</v>
       </c>
       <c r="F18" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>3940</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>4179</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>4257</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>4156</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>4681</v>
       </c>
       <c r="K18" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>4890</v>
       </c>
       <c r="L18" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>4663</v>
       </c>
       <c r="M18" s="7">
-        <f t="shared" ref="M18:O18" si="35">M16-M17</f>
+        <f t="shared" ref="M18:O18" si="39">M16-M17</f>
         <v>4872</v>
       </c>
       <c r="N18" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>5318</v>
       </c>
       <c r="O18" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>5119</v>
       </c>
       <c r="P18" s="7">
-        <f t="shared" ref="P18:R18" si="36">P16-P17</f>
+        <f t="shared" ref="P18:R18" si="40">P16-P17</f>
         <v>4577</v>
       </c>
       <c r="Q18" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>5272</v>
       </c>
       <c r="R18" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>5090</v>
       </c>
-      <c r="S18" s="7"/>
+      <c r="S18" s="7">
+        <f t="shared" ref="S18" si="41">S16-S17</f>
+        <v>5853</v>
+      </c>
       <c r="T18" s="7"/>
       <c r="U18" s="7"/>
       <c r="V18" s="7"/>
       <c r="X18" s="7">
-        <f t="shared" ref="X18:AD18" si="37">X16-X17</f>
+        <f t="shared" ref="X18:AD18" si="42">X16-X17</f>
         <v>12080</v>
       </c>
       <c r="Y18" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>10866</v>
       </c>
       <c r="Z18" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>12311</v>
       </c>
       <c r="AA18" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>15057</v>
       </c>
       <c r="AB18" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>17273</v>
       </c>
       <c r="AC18" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>19743</v>
       </c>
       <c r="AD18" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>20058</v>
       </c>
       <c r="AE18" s="7">
-        <f t="shared" ref="AE18:AN18" si="38">AE16-AE17</f>
-        <v>24806.984400000001</v>
+        <f t="shared" ref="AE18:AN18" si="43">AE16-AE17</f>
+        <v>25536.784399999997</v>
       </c>
       <c r="AF18" s="7">
-        <f t="shared" si="38"/>
-        <v>26957.121816000003</v>
+        <f t="shared" si="43"/>
+        <v>28038.078615999995</v>
       </c>
       <c r="AG18" s="7">
-        <f t="shared" si="38"/>
-        <v>28341.757240519997</v>
+        <f t="shared" si="43"/>
+        <v>29476.761880519993</v>
       </c>
       <c r="AH18" s="7">
-        <f t="shared" si="38"/>
-        <v>29515.226419855993</v>
+        <f t="shared" si="43"/>
+        <v>30695.631245455996</v>
       </c>
       <c r="AI18" s="7">
-        <f t="shared" si="38"/>
-        <v>30442.827349105482</v>
+        <f t="shared" si="43"/>
+        <v>31658.644319473478</v>
       </c>
       <c r="AJ18" s="7">
-        <f t="shared" si="38"/>
-        <v>31067.367623173712</v>
+        <f t="shared" si="43"/>
+        <v>32307.500932949068</v>
       </c>
       <c r="AK18" s="7">
-        <f t="shared" si="38"/>
-        <v>31704.44355875568</v>
+        <f t="shared" si="43"/>
+        <v>32969.379534726548</v>
       </c>
       <c r="AL18" s="7">
-        <f t="shared" si="38"/>
-        <v>32354.302958204851</v>
+        <f t="shared" si="43"/>
+        <v>33644.537653695123</v>
       </c>
       <c r="AM18" s="7">
-        <f t="shared" si="38"/>
-        <v>33017.19845002982</v>
+        <f t="shared" si="43"/>
+        <v>34333.237839429916</v>
       </c>
       <c r="AN18" s="7">
-        <f t="shared" si="38"/>
-        <v>33693.387581095136</v>
+        <f t="shared" si="43"/>
+        <v>35035.747758283222</v>
       </c>
       <c r="AO18" s="6">
         <f>AN18+($AR$23*AN18)</f>
-        <v>33356.453705284184</v>
+        <v>34685.390280700391</v>
       </c>
       <c r="AP18" s="6">
-        <f t="shared" ref="AP18:DA18" si="39">AO18+($AR$23*AO18)</f>
-        <v>33022.889168231341</v>
+        <f t="shared" ref="AP18:DA18" si="44">AO18+($AR$23*AO18)</f>
+        <v>34338.53637789339</v>
       </c>
       <c r="AQ18" s="6">
-        <f t="shared" si="39"/>
-        <v>32692.660276549028</v>
+        <f t="shared" si="44"/>
+        <v>33995.151014114454</v>
       </c>
       <c r="AR18" s="6">
-        <f t="shared" si="39"/>
-        <v>32365.733673783539</v>
+        <f t="shared" si="44"/>
+        <v>33655.199503973308</v>
       </c>
       <c r="AS18" s="6">
-        <f t="shared" si="39"/>
-        <v>32042.076337045703</v>
+        <f t="shared" si="44"/>
+        <v>33318.647508933573</v>
       </c>
       <c r="AT18" s="6">
-        <f t="shared" si="39"/>
-        <v>31721.655573675245</v>
+        <f t="shared" si="44"/>
+        <v>32985.461033844236</v>
       </c>
       <c r="AU18" s="6">
-        <f t="shared" si="39"/>
-        <v>31404.439017938494</v>
+        <f t="shared" si="44"/>
+        <v>32655.606423505793</v>
       </c>
       <c r="AV18" s="6">
-        <f t="shared" si="39"/>
-        <v>31090.394627759109</v>
+        <f t="shared" si="44"/>
+        <v>32329.050359270735</v>
       </c>
       <c r="AW18" s="6">
-        <f t="shared" si="39"/>
-        <v>30779.490681481519</v>
+        <f t="shared" si="44"/>
+        <v>32005.759855678029</v>
       </c>
       <c r="AX18" s="6">
-        <f t="shared" si="39"/>
-        <v>30471.695774666703</v>
+        <f t="shared" si="44"/>
+        <v>31685.702257121247</v>
       </c>
       <c r="AY18" s="6">
-        <f t="shared" si="39"/>
-        <v>30166.978816920036</v>
+        <f t="shared" si="44"/>
+        <v>31368.845234550034</v>
       </c>
       <c r="AZ18" s="6">
-        <f t="shared" si="39"/>
-        <v>29865.309028750835</v>
+        <f t="shared" si="44"/>
+        <v>31055.156782204533</v>
       </c>
       <c r="BA18" s="6">
-        <f t="shared" si="39"/>
-        <v>29566.655938463326</v>
+        <f t="shared" si="44"/>
+        <v>30744.605214382489</v>
       </c>
       <c r="BB18" s="6">
-        <f t="shared" si="39"/>
-        <v>29270.989379078692</v>
+        <f t="shared" si="44"/>
+        <v>30437.159162238666</v>
       </c>
       <c r="BC18" s="6">
-        <f t="shared" si="39"/>
-        <v>28978.279485287905</v>
+        <f t="shared" si="44"/>
+        <v>30132.787570616278</v>
       </c>
       <c r="BD18" s="6">
-        <f t="shared" si="39"/>
-        <v>28688.496690435026</v>
+        <f t="shared" si="44"/>
+        <v>29831.459694910114</v>
       </c>
       <c r="BE18" s="6">
-        <f t="shared" si="39"/>
-        <v>28401.611723530674</v>
+        <f t="shared" si="44"/>
+        <v>29533.145097961013</v>
       </c>
       <c r="BF18" s="6">
-        <f t="shared" si="39"/>
-        <v>28117.595606295366</v>
+        <f t="shared" si="44"/>
+        <v>29237.813646981402</v>
       </c>
       <c r="BG18" s="6">
-        <f t="shared" si="39"/>
-        <v>27836.419650232412</v>
+        <f t="shared" si="44"/>
+        <v>28945.435510511586</v>
       </c>
       <c r="BH18" s="6">
-        <f t="shared" si="39"/>
-        <v>27558.055453730089</v>
+        <f t="shared" si="44"/>
+        <v>28655.981155406469</v>
       </c>
       <c r="BI18" s="6">
-        <f t="shared" si="39"/>
-        <v>27282.474899192788</v>
+        <f t="shared" si="44"/>
+        <v>28369.421343852406</v>
       </c>
       <c r="BJ18" s="6">
-        <f t="shared" si="39"/>
-        <v>27009.650150200861</v>
+        <f t="shared" si="44"/>
+        <v>28085.727130413881</v>
       </c>
       <c r="BK18" s="6">
-        <f t="shared" si="39"/>
-        <v>26739.553648698853</v>
+        <f t="shared" si="44"/>
+        <v>27804.869859109742</v>
       </c>
       <c r="BL18" s="6">
-        <f t="shared" si="39"/>
-        <v>26472.158112211866</v>
+        <f t="shared" si="44"/>
+        <v>27526.821160518644</v>
       </c>
       <c r="BM18" s="6">
-        <f t="shared" si="39"/>
-        <v>26207.436531089748</v>
+        <f t="shared" si="44"/>
+        <v>27251.552948913457</v>
       </c>
       <c r="BN18" s="6">
-        <f t="shared" si="39"/>
-        <v>25945.36216577885</v>
+        <f t="shared" si="44"/>
+        <v>26979.037419424323</v>
       </c>
       <c r="BO18" s="6">
-        <f t="shared" si="39"/>
-        <v>25685.908544121063</v>
+        <f t="shared" si="44"/>
+        <v>26709.24704523008</v>
       </c>
       <c r="BP18" s="6">
-        <f t="shared" si="39"/>
-        <v>25429.049458679852</v>
+        <f t="shared" si="44"/>
+        <v>26442.154574777778</v>
       </c>
       <c r="BQ18" s="6">
-        <f t="shared" si="39"/>
-        <v>25174.758964093053</v>
+        <f t="shared" si="44"/>
+        <v>26177.733029030001</v>
       </c>
       <c r="BR18" s="6">
-        <f t="shared" si="39"/>
-        <v>24923.011374452122</v>
+        <f t="shared" si="44"/>
+        <v>25915.955698739701</v>
       </c>
       <c r="BS18" s="6">
-        <f t="shared" si="39"/>
-        <v>24673.781260707601</v>
+        <f t="shared" si="44"/>
+        <v>25656.796141752304</v>
       </c>
       <c r="BT18" s="6">
-        <f t="shared" si="39"/>
-        <v>24427.043448100525</v>
+        <f t="shared" si="44"/>
+        <v>25400.22818033478</v>
       </c>
       <c r="BU18" s="6">
-        <f t="shared" si="39"/>
-        <v>24182.77301361952</v>
+        <f t="shared" si="44"/>
+        <v>25146.225898531433</v>
       </c>
       <c r="BV18" s="6">
-        <f t="shared" si="39"/>
-        <v>23940.945283483325</v>
+        <f t="shared" si="44"/>
+        <v>24894.76363954612</v>
       </c>
       <c r="BW18" s="6">
-        <f t="shared" si="39"/>
-        <v>23701.535830648492</v>
+        <f t="shared" si="44"/>
+        <v>24645.81600315066</v>
       </c>
       <c r="BX18" s="6">
-        <f t="shared" si="39"/>
-        <v>23464.520472342007</v>
+        <f t="shared" si="44"/>
+        <v>24399.357843119153</v>
       </c>
       <c r="BY18" s="6">
-        <f t="shared" si="39"/>
-        <v>23229.875267618587</v>
+        <f t="shared" si="44"/>
+        <v>24155.36426468796</v>
       </c>
       <c r="BZ18" s="6">
-        <f t="shared" si="39"/>
-        <v>22997.576514942401</v>
+        <f t="shared" si="44"/>
+        <v>23913.810622041081</v>
       </c>
       <c r="CA18" s="6">
-        <f t="shared" si="39"/>
-        <v>22767.600749792975</v>
+        <f t="shared" si="44"/>
+        <v>23674.672515820672</v>
       </c>
       <c r="CB18" s="6">
-        <f t="shared" si="39"/>
-        <v>22539.924742295047</v>
+        <f t="shared" si="44"/>
+        <v>23437.925790662466</v>
       </c>
       <c r="CC18" s="6">
-        <f t="shared" si="39"/>
-        <v>22314.525494872098</v>
+        <f t="shared" si="44"/>
+        <v>23203.546532755841</v>
       </c>
       <c r="CD18" s="6">
-        <f t="shared" si="39"/>
-        <v>22091.380239923375</v>
+        <f t="shared" si="44"/>
+        <v>22971.511067428284</v>
       </c>
       <c r="CE18" s="6">
-        <f t="shared" si="39"/>
-        <v>21870.466437524141</v>
+        <f t="shared" si="44"/>
+        <v>22741.795956754002</v>
       </c>
       <c r="CF18" s="6">
-        <f t="shared" si="39"/>
-        <v>21651.761773148901</v>
+        <f t="shared" si="44"/>
+        <v>22514.377997186461</v>
       </c>
       <c r="CG18" s="6">
-        <f t="shared" si="39"/>
-        <v>21435.244155417411</v>
+        <f t="shared" si="44"/>
+        <v>22289.234217214595</v>
       </c>
       <c r="CH18" s="6">
-        <f t="shared" si="39"/>
-        <v>21220.891713863239</v>
+        <f t="shared" si="44"/>
+        <v>22066.34187504245</v>
       </c>
       <c r="CI18" s="6">
-        <f t="shared" si="39"/>
-        <v>21008.682796724606</v>
+        <f t="shared" si="44"/>
+        <v>21845.678456292026</v>
       </c>
       <c r="CJ18" s="6">
-        <f t="shared" si="39"/>
-        <v>20798.59596875736</v>
+        <f t="shared" si="44"/>
+        <v>21627.221671729105</v>
       </c>
       <c r="CK18" s="6">
-        <f t="shared" si="39"/>
-        <v>20590.610009069787</v>
+        <f t="shared" si="44"/>
+        <v>21410.949455011814</v>
       </c>
       <c r="CL18" s="6">
-        <f t="shared" si="39"/>
-        <v>20384.703908979089</v>
+        <f t="shared" si="44"/>
+        <v>21196.839960461697</v>
       </c>
       <c r="CM18" s="6">
-        <f t="shared" si="39"/>
-        <v>20180.8568698893</v>
+        <f t="shared" si="44"/>
+        <v>20984.871560857078</v>
       </c>
       <c r="CN18" s="6">
-        <f t="shared" si="39"/>
-        <v>19979.048301190407</v>
+        <f t="shared" si="44"/>
+        <v>20775.022845248506</v>
       </c>
       <c r="CO18" s="6">
-        <f t="shared" si="39"/>
-        <v>19779.257818178503</v>
+        <f t="shared" si="44"/>
+        <v>20567.272616796021</v>
       </c>
       <c r="CP18" s="6">
-        <f t="shared" si="39"/>
-        <v>19581.465239996716</v>
+        <f t="shared" si="44"/>
+        <v>20361.599890628062</v>
       </c>
       <c r="CQ18" s="6">
-        <f t="shared" si="39"/>
-        <v>19385.650587596749</v>
+        <f t="shared" si="44"/>
+        <v>20157.983891721782</v>
       </c>
       <c r="CR18" s="6">
-        <f t="shared" si="39"/>
-        <v>19191.794081720782</v>
+        <f t="shared" si="44"/>
+        <v>19956.404052804563</v>
       </c>
       <c r="CS18" s="6">
-        <f t="shared" si="39"/>
-        <v>18999.876140903572</v>
+        <f t="shared" si="44"/>
+        <v>19756.840012276516</v>
       </c>
       <c r="CT18" s="6">
-        <f t="shared" si="39"/>
-        <v>18809.877379494537</v>
+        <f t="shared" si="44"/>
+        <v>19559.271612153752</v>
       </c>
       <c r="CU18" s="6">
-        <f t="shared" si="39"/>
-        <v>18621.77860569959</v>
+        <f t="shared" si="44"/>
+        <v>19363.678896032216</v>
       </c>
       <c r="CV18" s="6">
-        <f t="shared" si="39"/>
-        <v>18435.560819642593</v>
+        <f t="shared" si="44"/>
+        <v>19170.042107071895</v>
       </c>
       <c r="CW18" s="6">
-        <f t="shared" si="39"/>
-        <v>18251.205211446166</v>
+        <f t="shared" si="44"/>
+        <v>18978.341686001175</v>
       </c>
       <c r="CX18" s="6">
-        <f t="shared" si="39"/>
-        <v>18068.693159331706</v>
+        <f t="shared" si="44"/>
+        <v>18788.558269141162</v>
       </c>
       <c r="CY18" s="6">
-        <f t="shared" si="39"/>
-        <v>17888.006227738388</v>
+        <f t="shared" si="44"/>
+        <v>18600.67268644975</v>
       </c>
       <c r="CZ18" s="6">
-        <f t="shared" si="39"/>
-        <v>17709.126165461003</v>
+        <f t="shared" si="44"/>
+        <v>18414.665959585254</v>
       </c>
       <c r="DA18" s="6">
-        <f t="shared" si="39"/>
-        <v>17532.034903806394</v>
+        <f t="shared" si="44"/>
+        <v>18230.519299989402</v>
       </c>
       <c r="DB18" s="6">
-        <f t="shared" ref="DB18:EU18" si="40">DA18+($AR$23*DA18)</f>
-        <v>17356.714554768329</v>
+        <f t="shared" ref="DB18:EU18" si="45">DA18+($AR$23*DA18)</f>
+        <v>18048.214106989508</v>
       </c>
       <c r="DC18" s="6">
-        <f t="shared" si="40"/>
-        <v>17183.147409220644</v>
+        <f t="shared" si="45"/>
+        <v>17867.731965919615</v>
       </c>
       <c r="DD18" s="6">
-        <f t="shared" si="40"/>
-        <v>17011.315935128438</v>
+        <f t="shared" si="45"/>
+        <v>17689.054646260418</v>
       </c>
       <c r="DE18" s="6">
-        <f t="shared" si="40"/>
-        <v>16841.202775777154</v>
+        <f t="shared" si="45"/>
+        <v>17512.164099797814</v>
       </c>
       <c r="DF18" s="6">
-        <f t="shared" si="40"/>
-        <v>16672.790748019383</v>
+        <f t="shared" si="45"/>
+        <v>17337.042458799835</v>
       </c>
       <c r="DG18" s="6">
-        <f t="shared" si="40"/>
-        <v>16506.062840539187</v>
+        <f t="shared" si="45"/>
+        <v>17163.672034211835</v>
       </c>
       <c r="DH18" s="6">
-        <f t="shared" si="40"/>
-        <v>16341.002212133795</v>
+        <f t="shared" si="45"/>
+        <v>16992.035313869717</v>
       </c>
       <c r="DI18" s="6">
-        <f t="shared" si="40"/>
-        <v>16177.592190012458</v>
+        <f t="shared" si="45"/>
+        <v>16822.114960731022</v>
       </c>
       <c r="DJ18" s="6">
-        <f t="shared" si="40"/>
-        <v>16015.816268112332</v>
+        <f t="shared" si="45"/>
+        <v>16653.893811123711</v>
       </c>
       <c r="DK18" s="6">
-        <f t="shared" si="40"/>
-        <v>15855.658105431208</v>
+        <f t="shared" si="45"/>
+        <v>16487.354873012475</v>
       </c>
       <c r="DL18" s="6">
-        <f t="shared" si="40"/>
-        <v>15697.101524376896</v>
+        <f t="shared" si="45"/>
+        <v>16322.481324282349</v>
       </c>
       <c r="DM18" s="6">
-        <f t="shared" si="40"/>
-        <v>15540.130509133127</v>
+        <f t="shared" si="45"/>
+        <v>16159.256511039526</v>
       </c>
       <c r="DN18" s="6">
-        <f t="shared" si="40"/>
-        <v>15384.729204041796</v>
+        <f t="shared" si="45"/>
+        <v>15997.663945929131</v>
       </c>
       <c r="DO18" s="6">
-        <f t="shared" si="40"/>
-        <v>15230.881912001378</v>
+        <f t="shared" si="45"/>
+        <v>15837.687306469839</v>
       </c>
       <c r="DP18" s="6">
-        <f t="shared" si="40"/>
-        <v>15078.573092881365</v>
+        <f t="shared" si="45"/>
+        <v>15679.31043340514</v>
       </c>
       <c r="DQ18" s="6">
-        <f t="shared" si="40"/>
-        <v>14927.787361952551</v>
+        <f t="shared" si="45"/>
+        <v>15522.517329071088</v>
       </c>
       <c r="DR18" s="6">
-        <f t="shared" si="40"/>
-        <v>14778.509488333026</v>
+        <f t="shared" si="45"/>
+        <v>15367.292155780377</v>
       </c>
       <c r="DS18" s="6">
-        <f t="shared" si="40"/>
-        <v>14630.724393449695</v>
+        <f t="shared" si="45"/>
+        <v>15213.619234222573</v>
       </c>
       <c r="DT18" s="6">
-        <f t="shared" si="40"/>
-        <v>14484.417149515197</v>
+        <f t="shared" si="45"/>
+        <v>15061.483041880347</v>
       </c>
       <c r="DU18" s="6">
-        <f t="shared" si="40"/>
-        <v>14339.572978020045</v>
+        <f t="shared" si="45"/>
+        <v>14910.868211461544</v>
       </c>
       <c r="DV18" s="6">
-        <f t="shared" si="40"/>
-        <v>14196.177248239845</v>
+        <f t="shared" si="45"/>
+        <v>14761.759529346929</v>
       </c>
       <c r="DW18" s="6">
-        <f t="shared" si="40"/>
-        <v>14054.215475757446</v>
+        <f t="shared" si="45"/>
+        <v>14614.141934053459</v>
       </c>
       <c r="DX18" s="6">
-        <f t="shared" si="40"/>
-        <v>13913.673320999871</v>
+        <f t="shared" si="45"/>
+        <v>14468.000514712925</v>
       </c>
       <c r="DY18" s="6">
-        <f t="shared" si="40"/>
-        <v>13774.536587789873</v>
+        <f t="shared" si="45"/>
+        <v>14323.320509565796</v>
       </c>
       <c r="DZ18" s="6">
-        <f t="shared" si="40"/>
-        <v>13636.791221911973</v>
+        <f t="shared" si="45"/>
+        <v>14180.087304470138</v>
       </c>
       <c r="EA18" s="6">
-        <f t="shared" si="40"/>
-        <v>13500.423309692853</v>
+        <f t="shared" si="45"/>
+        <v>14038.286431425437</v>
       </c>
       <c r="EB18" s="6">
-        <f t="shared" si="40"/>
-        <v>13365.419076595925</v>
+        <f t="shared" si="45"/>
+        <v>13897.903567111181</v>
       </c>
       <c r="EC18" s="6">
-        <f t="shared" si="40"/>
-        <v>13231.764885829965</v>
+        <f t="shared" si="45"/>
+        <v>13758.92453144007</v>
       </c>
       <c r="ED18" s="6">
-        <f t="shared" si="40"/>
-        <v>13099.447236971666</v>
+        <f t="shared" si="45"/>
+        <v>13621.33528612567</v>
       </c>
       <c r="EE18" s="6">
-        <f t="shared" si="40"/>
-        <v>12968.452764601949</v>
+        <f t="shared" si="45"/>
+        <v>13485.121933264412</v>
       </c>
       <c r="EF18" s="6">
-        <f t="shared" si="40"/>
-        <v>12838.76823695593</v>
+        <f t="shared" si="45"/>
+        <v>13350.270713931768</v>
       </c>
       <c r="EG18" s="6">
-        <f t="shared" si="40"/>
-        <v>12710.380554586371</v>
+        <f t="shared" si="45"/>
+        <v>13216.76800679245</v>
       </c>
       <c r="EH18" s="6">
-        <f t="shared" si="40"/>
-        <v>12583.276749040508</v>
+        <f t="shared" si="45"/>
+        <v>13084.600326724525</v>
       </c>
       <c r="EI18" s="6">
-        <f t="shared" si="40"/>
-        <v>12457.443981550103</v>
+        <f t="shared" si="45"/>
+        <v>12953.75432345728</v>
       </c>
       <c r="EJ18" s="6">
-        <f t="shared" si="40"/>
-        <v>12332.869541734603</v>
+        <f t="shared" si="45"/>
+        <v>12824.216780222707</v>
       </c>
       <c r="EK18" s="6">
-        <f t="shared" si="40"/>
-        <v>12209.540846317257</v>
+        <f t="shared" si="45"/>
+        <v>12695.974612420479</v>
       </c>
       <c r="EL18" s="6">
-        <f t="shared" si="40"/>
-        <v>12087.445437854085</v>
+        <f t="shared" si="45"/>
+        <v>12569.014866296275</v>
       </c>
       <c r="EM18" s="6">
-        <f t="shared" si="40"/>
-        <v>11966.570983475543</v>
+        <f t="shared" si="45"/>
+        <v>12443.324717633312</v>
       </c>
       <c r="EN18" s="6">
-        <f t="shared" si="40"/>
-        <v>11846.905273640788</v>
+        <f t="shared" si="45"/>
+        <v>12318.891470456978</v>
       </c>
       <c r="EO18" s="6">
-        <f t="shared" si="40"/>
-        <v>11728.436220904381</v>
+        <f t="shared" si="45"/>
+        <v>12195.702555752408</v>
       </c>
       <c r="EP18" s="6">
-        <f t="shared" si="40"/>
-        <v>11611.151858695337</v>
+        <f t="shared" si="45"/>
+        <v>12073.745530194885</v>
       </c>
       <c r="EQ18" s="6">
-        <f t="shared" si="40"/>
-        <v>11495.040340108384</v>
+        <f t="shared" si="45"/>
+        <v>11953.008074892936</v>
       </c>
       <c r="ER18" s="6">
-        <f t="shared" si="40"/>
-        <v>11380.0899367073</v>
+        <f t="shared" si="45"/>
+        <v>11833.477994144007</v>
       </c>
       <c r="ES18" s="6">
-        <f t="shared" si="40"/>
-        <v>11266.289037340226</v>
+        <f t="shared" si="45"/>
+        <v>11715.143214202566</v>
       </c>
       <c r="ET18" s="6">
-        <f t="shared" si="40"/>
-        <v>11153.626146966824</v>
+        <f t="shared" si="45"/>
+        <v>11597.991782060541</v>
       </c>
       <c r="EU18" s="6">
-        <f t="shared" si="40"/>
-        <v>11042.089885497157</v>
+        <f t="shared" si="45"/>
+        <v>11482.011864239936</v>
       </c>
     </row>
     <row r="19" spans="1:151" x14ac:dyDescent="0.3">
@@ -3512,43 +3580,43 @@
         <v>1</v>
       </c>
       <c r="C19" s="3">
-        <f t="shared" ref="C19:L19" si="41">1574.2+245.5+9.3</f>
+        <f t="shared" ref="C19:L19" si="46">1574.2+245.5+9.3</f>
         <v>1829</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="G19" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="I19" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="K19" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="L19" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>1829</v>
       </c>
       <c r="M19" s="3">
@@ -3574,77 +3642,89 @@
         <f>1696+5+120+9</f>
         <v>1830</v>
       </c>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
+      <c r="S19" s="3">
+        <f>1681.1+4.8+120.3+8.9</f>
+        <v>1815.1</v>
+      </c>
+      <c r="T19" s="3">
+        <f>1681.1+4.8+120.3+8.9</f>
+        <v>1815.1</v>
+      </c>
+      <c r="U19" s="3">
+        <f>1681.1+4.8+120.3+8.9</f>
+        <v>1815.1</v>
+      </c>
+      <c r="V19" s="3">
+        <f>1681.1+4.8+120.3+8.9</f>
+        <v>1815.1</v>
+      </c>
       <c r="X19" s="3">
-        <f t="shared" ref="X19:AB19" si="42">1574.2+245.5+9.3</f>
+        <f t="shared" ref="X19:AB19" si="47">1574.2+245.5+9.3</f>
         <v>1829</v>
       </c>
       <c r="Y19" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>1829</v>
       </c>
       <c r="Z19" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>1829</v>
       </c>
       <c r="AA19" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>1829</v>
       </c>
       <c r="AB19" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>1829</v>
       </c>
       <c r="AC19" s="3">
-        <f t="shared" ref="AC19" si="43">1728.1+4.8+120.3+9.6</f>
+        <f t="shared" ref="AC19" si="48">1728.1+4.8+120.3+9.6</f>
         <v>1862.7999999999997</v>
       </c>
       <c r="AD19" s="3">
-        <f t="shared" ref="AD19:AN19" si="44">1696+5+120+9</f>
+        <f t="shared" ref="AD19" si="49">1696+5+120+9</f>
         <v>1830</v>
       </c>
       <c r="AE19" s="3">
-        <f t="shared" si="44"/>
-        <v>1830</v>
+        <f t="shared" ref="AE19:AN19" si="50">1681.1+4.8+120.3+8.9</f>
+        <v>1815.1</v>
       </c>
       <c r="AF19" s="3">
-        <f t="shared" si="44"/>
-        <v>1830</v>
+        <f t="shared" si="50"/>
+        <v>1815.1</v>
       </c>
       <c r="AG19" s="3">
-        <f t="shared" si="44"/>
-        <v>1830</v>
+        <f t="shared" si="50"/>
+        <v>1815.1</v>
       </c>
       <c r="AH19" s="3">
-        <f t="shared" si="44"/>
-        <v>1830</v>
+        <f t="shared" si="50"/>
+        <v>1815.1</v>
       </c>
       <c r="AI19" s="3">
-        <f t="shared" si="44"/>
-        <v>1830</v>
+        <f t="shared" si="50"/>
+        <v>1815.1</v>
       </c>
       <c r="AJ19" s="3">
-        <f t="shared" si="44"/>
-        <v>1830</v>
+        <f t="shared" si="50"/>
+        <v>1815.1</v>
       </c>
       <c r="AK19" s="3">
-        <f t="shared" si="44"/>
-        <v>1830</v>
+        <f t="shared" si="50"/>
+        <v>1815.1</v>
       </c>
       <c r="AL19" s="3">
-        <f t="shared" si="44"/>
-        <v>1830</v>
+        <f t="shared" si="50"/>
+        <v>1815.1</v>
       </c>
       <c r="AM19" s="3">
-        <f t="shared" si="44"/>
-        <v>1830</v>
+        <f t="shared" si="50"/>
+        <v>1815.1</v>
       </c>
       <c r="AN19" s="3">
-        <f t="shared" si="44"/>
-        <v>1830</v>
+        <f t="shared" si="50"/>
+        <v>1815.1</v>
       </c>
     </row>
     <row r="20" spans="1:151" x14ac:dyDescent="0.3">
@@ -3652,140 +3732,143 @@
         <v>25</v>
       </c>
       <c r="C20" s="5">
-        <f t="shared" ref="C20:L20" si="45">C18/C19</f>
+        <f t="shared" ref="C20:L20" si="51">C18/C19</f>
         <v>2.2192454893384364</v>
       </c>
       <c r="D20" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>1.9939857845817386</v>
       </c>
       <c r="E20" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>1.8649535265172226</v>
       </c>
       <c r="F20" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2.1541826134499726</v>
       </c>
       <c r="G20" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2.2848551120831053</v>
       </c>
       <c r="H20" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2.3275013668671405</v>
       </c>
       <c r="I20" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2.2722799343903772</v>
       </c>
       <c r="J20" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2.5593220338983049</v>
       </c>
       <c r="K20" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2.6735921268452705</v>
       </c>
       <c r="L20" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2.5494805904866049</v>
       </c>
       <c r="M20" s="5">
-        <f t="shared" ref="M20:O20" si="46">M18/M19</f>
+        <f t="shared" ref="M20:O20" si="52">M18/M19</f>
         <v>2.6739846322722283</v>
       </c>
       <c r="N20" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>2.854842173072794</v>
       </c>
       <c r="O20" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>2.7555579480002153</v>
       </c>
       <c r="P20" s="5">
-        <f t="shared" ref="P20:R20" si="47">P18/P19</f>
+        <f t="shared" ref="P20:S20" si="53">P18/P19</f>
         <v>2.4806243564034469</v>
       </c>
       <c r="Q20" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>2.8605534454693435</v>
       </c>
       <c r="R20" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>2.7814207650273226</v>
       </c>
-      <c r="S20" s="5"/>
+      <c r="S20" s="5">
+        <f t="shared" si="53"/>
+        <v>3.2246157236515898</v>
+      </c>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
       <c r="V20" s="5"/>
       <c r="X20" s="5">
-        <f t="shared" ref="X20:AD20" si="48">X18/X19</f>
+        <f t="shared" ref="X20:AD20" si="54">X18/X19</f>
         <v>6.6047020229633677</v>
       </c>
       <c r="Y20" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>5.9409513395297981</v>
       </c>
       <c r="Z20" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>6.7310005467468565</v>
       </c>
       <c r="AA20" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>8.2323674138873706</v>
       </c>
       <c r="AB20" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>9.4439584472389289</v>
       </c>
       <c r="AC20" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>10.598561305561521</v>
       </c>
       <c r="AD20" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>10.960655737704919</v>
       </c>
       <c r="AE20" s="5">
-        <f t="shared" ref="AE20:AN20" si="49">AE18/AE19</f>
-        <v>13.555729180327869</v>
+        <f t="shared" ref="AE20:AN20" si="55">AE18/AE19</f>
+        <v>14.069078508071179</v>
       </c>
       <c r="AF20" s="5">
-        <f t="shared" si="49"/>
-        <v>14.730667659016396</v>
+        <f t="shared" si="55"/>
+        <v>15.447126117569278</v>
       </c>
       <c r="AG20" s="5">
-        <f t="shared" si="49"/>
-        <v>15.487299038535518</v>
+        <f t="shared" si="55"/>
+        <v>16.239745402743647</v>
       </c>
       <c r="AH20" s="5">
-        <f t="shared" si="49"/>
-        <v>16.128539027243711</v>
+        <f t="shared" si="55"/>
+        <v>16.911261773707231</v>
       </c>
       <c r="AI20" s="5">
-        <f t="shared" si="49"/>
-        <v>16.635424780931956</v>
+        <f t="shared" si="55"/>
+        <v>17.441818257657143</v>
       </c>
       <c r="AJ20" s="5">
-        <f t="shared" si="49"/>
-        <v>16.976703619220608</v>
+        <f t="shared" si="55"/>
+        <v>17.799295318687165</v>
       </c>
       <c r="AK20" s="5">
-        <f t="shared" si="49"/>
-        <v>17.324832545768132</v>
+        <f t="shared" si="55"/>
+        <v>18.163946633643629</v>
       </c>
       <c r="AL20" s="5">
-        <f t="shared" si="49"/>
-        <v>17.679946971696641</v>
+        <f t="shared" si="55"/>
+        <v>18.535914083904537</v>
       </c>
       <c r="AM20" s="5">
-        <f t="shared" si="49"/>
-        <v>18.042184945371485</v>
+        <f t="shared" si="55"/>
+        <v>18.915342316913623</v>
       </c>
       <c r="AN20" s="5">
-        <f t="shared" si="49"/>
-        <v>18.411687202784226</v>
+        <f t="shared" si="55"/>
+        <v>19.30237879912028</v>
       </c>
     </row>
     <row r="22" spans="1:151" x14ac:dyDescent="0.3">
@@ -3797,50 +3880,53 @@
         <v>0.12423856070264905</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22:N22" si="50">H3/D3-1</f>
+        <f t="shared" ref="H22:N22" si="56">H3/D3-1</f>
         <v>0.11072471831965514</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>0.11656357388316141</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>0.1055605496340053</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>8.7953629032258007E-2</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>9.8935504070131408E-2</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>9.5654314908285132E-2</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>0.11708676965965847</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" ref="O22" si="51">O3/K3-1</f>
+        <f t="shared" ref="O22" si="57">O3/K3-1</f>
         <v>0.10145934676858936</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" ref="P22" si="52">P3/L3-1</f>
+        <f t="shared" ref="P22" si="58">P3/L3-1</f>
         <v>9.3333333333333268E-2</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22" si="53">Q3/M3-1</f>
+        <f t="shared" ref="Q22" si="59">Q3/M3-1</f>
         <v>0.14292134831460679</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" ref="R22" si="54">R3/N3-1</f>
+        <f t="shared" ref="R22:S22" si="60">R3/N3-1</f>
         <v>0.11510866174482692</v>
       </c>
-      <c r="S22" s="9"/>
+      <c r="S22" s="9">
+        <f t="shared" si="60"/>
+        <v>0.14626708727655102</v>
+      </c>
       <c r="T22" s="9"/>
       <c r="U22" s="9"/>
       <c r="V22" s="9"/>
@@ -3850,63 +3936,63 @@
         <v>-4.92231361796579E-2</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22:AN22" si="55">Z3/Y3-1</f>
+        <f t="shared" ref="Z22:AN22" si="61">Z3/Y3-1</f>
         <v>0.10340565778632249</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>0.21593030491599263</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>0.11405663596042315</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>0.10023581294214923</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>0.11339976618604908</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="55"/>
-        <v>9.000000000000008E-2</v>
+        <f t="shared" si="61"/>
+        <v>0.12999999999999989</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -3915,19 +4001,19 @@
         <v>40</v>
       </c>
       <c r="C23" s="9">
-        <f t="shared" ref="C23:F23" si="56">C5/C3</f>
+        <f t="shared" ref="C23:F23" si="62">C5/C3</f>
         <v>0.84062898427539312</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>0.82946167756294342</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>0.82364261168384878</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>0.82586361885193271</v>
       </c>
       <c r="G23" s="9">
@@ -3935,119 +4021,122 @@
         <v>0.8315272177419355</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" ref="H23:N23" si="57">H5/H3</f>
+        <f t="shared" ref="H23:N23" si="63">H5/H3</f>
         <v>0.81026925485284906</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>0.81767819771020556</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>0.82599605064467418</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>0.82870048644892291</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>0.81732193732193736</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>0.82325842696629215</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>0.83269210772590208</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" ref="O23:R23" si="58">O5/O3</f>
+        <f t="shared" ref="O23:R23" si="64">O5/O3</f>
         <v>0.80935856992639332</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="64"/>
         <v>0.82728788826349797</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="64"/>
         <v>0.82805741250491549</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="64"/>
         <v>0.83756061171204776</v>
       </c>
-      <c r="S23" s="9"/>
+      <c r="S23" s="9">
+        <f t="shared" ref="S23" si="65">S5/S3</f>
+        <v>0.83817998348775347</v>
+      </c>
       <c r="T23" s="9"/>
       <c r="U23" s="9"/>
       <c r="V23" s="9"/>
       <c r="X23" s="9">
-        <f t="shared" ref="X23:AN23" si="59">X5/X3</f>
+        <f t="shared" ref="X23:AN23" si="66">X5/X3</f>
         <v>0.85011098054576317</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0.82674173761787051</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0.82410288321924907</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0.82975093824633228</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0.82142529017241905</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0.82564159661526471</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0.82597500000000001</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0.84</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0.84</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0.84</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0.84</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0.84</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="59"/>
-        <v>0.83999999999999986</v>
+        <f t="shared" si="66"/>
+        <v>0.84</v>
       </c>
       <c r="AK23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0.84</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0.84</v>
       </c>
       <c r="AM23" s="9">
-        <f t="shared" si="59"/>
-        <v>0.84</v>
+        <f t="shared" si="66"/>
+        <v>0.84000000000000008</v>
       </c>
       <c r="AN23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0.84</v>
       </c>
       <c r="AQ23" t="s">
@@ -4062,19 +4151,19 @@
         <v>41</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:F24" si="60">C6/C3</f>
+        <f t="shared" ref="C24:F24" si="67">C6/C3</f>
         <v>3.9665675024791049E-2</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>4.3677841146195578E-2</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>4.3024054982817868E-2</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>5.5091819699499167E-2</v>
       </c>
       <c r="G24" s="9">
@@ -4082,119 +4171,122 @@
         <v>4.1834677419354836E-2</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24:N24" si="61">H6/H3</f>
+        <f t="shared" ref="H24:N24" si="68">H6/H3</f>
         <v>3.8697557921102063E-2</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="68"/>
         <v>3.6562846239074236E-2</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="68"/>
         <v>4.6811476361946797E-2</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="68"/>
         <v>3.3935603428306697E-2</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="68"/>
         <v>3.8518518518518521E-2</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="68"/>
         <v>4.2471910112359554E-2</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="68"/>
         <v>5.7294374545076431E-2</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" ref="O24:R24" si="62">O6/O3</f>
+        <f t="shared" ref="O24:R24" si="69">O6/O3</f>
         <v>3.2176656151419555E-2</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="69"/>
         <v>3.9712320200125079E-2</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="69"/>
         <v>4.1388124262681875E-2</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="69"/>
         <v>5.3711301753077208E-2</v>
       </c>
-      <c r="S24" s="9"/>
+      <c r="S24" s="9">
+        <f t="shared" ref="S24" si="70">S6/S3</f>
+        <v>3.7611228327676362E-2</v>
+      </c>
       <c r="T24" s="9"/>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="X24" s="9">
-        <f t="shared" ref="X24:AN24" si="63">X6/X3</f>
+        <f t="shared" ref="X24:AN24" si="71">X6/X3</f>
         <v>4.8091569830700266E-2</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>4.4447496109127529E-2</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>4.7127152043144577E-2</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>4.5581712726032071E-2</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>4.1068202002878758E-2</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>4.3422590881255912E-2</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>4.2099999999999999E-2</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>0.04</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>0.04</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>0.04</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>0.04</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>0.04</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="63"/>
-        <v>4.0000000000000008E-2</v>
+        <f t="shared" si="71"/>
+        <v>0.04</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>0.04</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>0.04</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" si="63"/>
-        <v>4.0000000000000008E-2</v>
+        <f t="shared" si="71"/>
+        <v>0.04</v>
       </c>
       <c r="AN24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>0.04</v>
       </c>
       <c r="AQ24" t="s">
@@ -4217,50 +4309,53 @@
         <v>-6.315789473684208E-2</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" ref="H25:N25" si="64">H7/D7-1</f>
+        <f t="shared" ref="H25:N25" si="72">H7/D7-1</f>
         <v>-5.7894736842105221E-2</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="72"/>
         <v>2.2471910112359605E-2</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="72"/>
         <v>6.4864864864864868E-2</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="72"/>
         <v>1.6853932584269593E-2</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="72"/>
         <v>5.5865921787709549E-2</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="72"/>
         <v>9.8901098901098994E-2</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="72"/>
         <v>5.5837563451776706E-2</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" ref="O25" si="65">O7/K7-1</f>
+        <f t="shared" ref="O25" si="73">O7/K7-1</f>
         <v>0.14364640883977908</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" ref="P25" si="66">P7/L7-1</f>
+        <f t="shared" ref="P25" si="74">P7/L7-1</f>
         <v>0.18518518518518512</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" ref="Q25" si="67">Q7/M7-1</f>
+        <f t="shared" ref="Q25" si="75">Q7/M7-1</f>
         <v>0.12000000000000011</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" ref="R25" si="68">R7/N7-1</f>
+        <f t="shared" ref="R25:S25" si="76">R7/N7-1</f>
         <v>0.14903846153846145</v>
       </c>
-      <c r="S25" s="9"/>
+      <c r="S25" s="9">
+        <f t="shared" si="76"/>
+        <v>0.12560386473429941</v>
+      </c>
       <c r="T25" s="9"/>
       <c r="U25" s="9"/>
       <c r="V25" s="9"/>
@@ -4271,71 +4366,71 @@
         <v>8.3217753120665705E-3</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" ref="Z25:AN25" si="69">Z7/Y7-1</f>
+        <f t="shared" ref="Z25:AN25" si="77">Z7/Y7-1</f>
         <v>4.126547455295837E-3</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>1.7808219178082174E-2</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>-9.421265141319024E-3</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>5.7065217391304435E-2</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>0.14910025706940866</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ25" t="s">
         <v>50</v>
       </c>
       <c r="AR25" s="3">
-        <f>NPV(AR24,AD18:EU18)</f>
-        <v>476387.45635461435</v>
+        <f>NPV(AR24,AE18:EU18)</f>
+        <v>504008.89551760507</v>
       </c>
     </row>
     <row r="26" spans="1:151" x14ac:dyDescent="0.3">
@@ -4343,19 +4438,19 @@
         <v>42</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:F26" si="70">C8/C3</f>
+        <f t="shared" ref="C26:F26" si="78">C8/C3</f>
         <v>1.4166312508853945E-2</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>1.7387675615523717E-2</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>1.6082474226804123E-2</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>2.0932323102606908E-2</v>
       </c>
       <c r="G26" s="9">
@@ -4363,119 +4458,122 @@
         <v>1.3734879032258064E-2</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" ref="H26:N26" si="71">H8/H3</f>
+        <f t="shared" ref="H26:N26" si="79">H8/H3</f>
         <v>1.6280525986224169E-2</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="79"/>
         <v>1.6373261110427181E-2</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="79"/>
         <v>2.0095249157858056E-2</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="79"/>
         <v>1.5172573546444291E-2</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="79"/>
         <v>1.8233618233618232E-2</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="79"/>
         <v>1.707865168539326E-2</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="79"/>
         <v>1.9964645939482165E-2</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" ref="O26:R26" si="72">O8/O3</f>
+        <f t="shared" ref="O26:R26" si="80">O8/O3</f>
         <v>1.5036803364879074E-2</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>1.8032103397957057E-2</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>1.838379866299646E-2</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>2.3871689668034317E-2</v>
       </c>
-      <c r="S26" s="9"/>
+      <c r="S26" s="9">
+        <f t="shared" ref="S26" si="81">S8/S3</f>
+        <v>1.9080818273552885E-2</v>
+      </c>
       <c r="T26" s="9"/>
       <c r="U26" s="9"/>
       <c r="V26" s="9"/>
       <c r="X26" s="9">
-        <f t="shared" ref="X26:AN26" si="73">X8/X3</f>
+        <f t="shared" ref="X26:AN26" si="82">X8/X3</f>
         <v>1.9758889324106715E-2</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="82"/>
         <v>1.8676187860477891E-2</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="82"/>
         <v>1.6718523127981746E-2</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="82"/>
         <v>1.7229614466052541E-2</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="82"/>
         <v>1.6690656294980552E-2</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="82"/>
         <v>1.7675221288203528E-2</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="82"/>
         <v>1.8974999999999999E-2</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="82"/>
         <v>0.02</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="82"/>
         <v>0.02</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="82"/>
         <v>0.02</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="82"/>
         <v>0.02</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="82"/>
         <v>0.02</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="73"/>
-        <v>2.0000000000000004E-2</v>
+        <f t="shared" si="82"/>
+        <v>0.02</v>
       </c>
       <c r="AK26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="82"/>
         <v>0.02</v>
       </c>
       <c r="AL26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="82"/>
         <v>0.02</v>
       </c>
       <c r="AM26" s="9">
-        <f t="shared" si="73"/>
-        <v>2.0000000000000004E-2</v>
+        <f t="shared" si="82"/>
+        <v>0.02</v>
       </c>
       <c r="AN26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="82"/>
         <v>0.02</v>
       </c>
       <c r="AQ26" t="s">
@@ -4483,7 +4581,7 @@
       </c>
       <c r="AR26" s="3">
         <f>Main!D8</f>
-        <v>-4755</v>
+        <v>-4296</v>
       </c>
     </row>
     <row r="27" spans="1:151" x14ac:dyDescent="0.3">
@@ -4499,50 +4597,53 @@
         <v>0.14646464646464641</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:N27" si="74">H9/D9-1</f>
+        <f t="shared" ref="H27:N27" si="83">H9/D9-1</f>
         <v>0.13043478260869557</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="83"/>
         <v>2.1739130434782705E-2</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="83"/>
         <v>9.2920353982300918E-2</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="83"/>
         <v>8.8105726872246715E-2</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="83"/>
         <v>6.4102564102564097E-2</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="83"/>
         <v>0.123404255319149</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="83"/>
         <v>0.10931174089068829</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" ref="O27:O28" si="75">O9/K9-1</f>
+        <f t="shared" ref="O27:O28" si="84">O9/K9-1</f>
         <v>0.14170040485829949</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" ref="P27:P28" si="76">P9/L9-1</f>
+        <f t="shared" ref="P27:P28" si="85">P9/L9-1</f>
         <v>0.22489959839357421</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" ref="Q27:Q28" si="77">Q9/M9-1</f>
+        <f t="shared" ref="Q27:Q28" si="86">Q9/M9-1</f>
         <v>0.20075757575757569</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" ref="R27:R28" si="78">R9/N9-1</f>
+        <f t="shared" ref="R27:S28" si="87">R9/N9-1</f>
         <v>0.15328467153284664</v>
       </c>
-      <c r="S27" s="9"/>
+      <c r="S27" s="9">
+        <f t="shared" si="87"/>
+        <v>0.15602836879432624</v>
+      </c>
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
       <c r="V27" s="9"/>
@@ -4552,23 +4653,23 @@
         <v>0.16920731707317072</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" ref="Z27:AD27" si="79">Z9/Y9-1</f>
+        <f t="shared" ref="Z27:AD27" si="88">Z9/Y9-1</f>
         <v>4.8239895697522739E-2</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="88"/>
         <v>7.0895522388059629E-2</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="88"/>
         <v>9.5238095238095344E-2</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="88"/>
         <v>9.6500530222693559E-2</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="88"/>
         <v>0.17988394584139256</v>
       </c>
       <c r="AE27" s="9"/>
@@ -4586,7 +4687,7 @@
       </c>
       <c r="AR27" s="3">
         <f>AR25+AR26</f>
-        <v>471632.45635461435</v>
+        <v>499712.89551760507</v>
       </c>
     </row>
     <row r="28" spans="1:151" x14ac:dyDescent="0.3">
@@ -4602,50 +4703,53 @@
         <v>0.33057851239669422</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" ref="H28:N28" si="80">H10/D10-1</f>
+        <f t="shared" ref="H28:N28" si="89">H10/D10-1</f>
         <v>-0.13230769230769235</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="89"/>
         <v>8.6505190311418678E-2</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="89"/>
         <v>0.21893491124260356</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="89"/>
         <v>5.5900621118012417E-2</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="89"/>
         <v>0.60283687943262421</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="89"/>
         <v>0.21656050955414008</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="89"/>
         <v>2.9126213592232997E-2</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="84"/>
         <v>0.41470588235294126</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="85"/>
         <v>-7.3008849557522071E-2</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="86"/>
         <v>0.26178010471204183</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="87"/>
         <v>0.28301886792452824</v>
       </c>
-      <c r="S28" s="9"/>
+      <c r="S28" s="9">
+        <f t="shared" si="87"/>
+        <v>7.0686070686070579E-2</v>
+      </c>
       <c r="T28" s="9"/>
       <c r="U28" s="9"/>
       <c r="V28" s="9"/>
@@ -4655,63 +4759,63 @@
         <v>-8.361204013377932E-2</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" ref="Z28:AN28" si="81">Z10/Y10-1</f>
+        <f t="shared" ref="Z28:AN28" si="90">Z10/Y10-1</f>
         <v>-0.10127737226277367</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="90"/>
         <v>0.21218274111675117</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="90"/>
         <v>0.11390284757118918</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="90"/>
         <v>0.2015037593984963</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="90"/>
         <v>0.20525657071339176</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="90"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="90"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="90"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="90"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="90"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="90"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK28" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="90"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL28" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="90"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM28" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="90"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN28" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="90"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ28" t="s">
@@ -4719,7 +4823,7 @@
       </c>
       <c r="AR28" s="11">
         <f>AR27/AN19</f>
-        <v>257.72265374569088</v>
+        <v>275.30874085042427</v>
       </c>
     </row>
     <row r="29" spans="1:151" x14ac:dyDescent="0.3">
@@ -4727,19 +4831,19 @@
         <v>45</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:F29" si="82">C11/C3</f>
+        <f t="shared" ref="C29:F29" si="91">C11/C3</f>
         <v>2.0966142513103841E-2</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="91"/>
         <v>9.855670103092784E-2</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="91"/>
         <v>3.8525748041607808E-4</v>
       </c>
       <c r="G29" s="9">
@@ -4747,119 +4851,122 @@
         <v>4.296875E-2</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" ref="H29:N29" si="83">H11/H3</f>
+        <f t="shared" ref="H29:N29" si="92">H11/H3</f>
         <v>0</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="92"/>
         <v>5.6260002462144527E-2</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="92"/>
         <v>1.4984318736206296E-2</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="92"/>
         <v>1.0423905489923557E-3</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="92"/>
         <v>4.9002849002849E-2</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="92"/>
         <v>1.4606741573033708E-3</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="92"/>
         <v>1.0398253093480295E-3</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" ref="O29:R29" si="84">O11/O3</f>
+        <f t="shared" ref="O29:R29" si="93">O11/O3</f>
         <v>4.6267087276550996E-3</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="93"/>
         <v>0.10423181154888472</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="93"/>
         <v>6.0460086511993708E-2</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="93"/>
         <v>8.4203655352480422E-2</v>
       </c>
-      <c r="S29" s="9"/>
+      <c r="S29" s="9">
+        <f t="shared" ref="S29" si="94">S11/S3</f>
+        <v>6.4948169892670396E-2</v>
+      </c>
       <c r="T29" s="9"/>
       <c r="U29" s="9"/>
       <c r="V29" s="9"/>
       <c r="X29" s="9">
-        <f t="shared" ref="X29:AN29" si="85">X11/X3</f>
+        <f t="shared" ref="X29:AN29" si="95">X11/X3</f>
         <v>1.7408713060886975E-2</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="95"/>
         <v>5.0352467270896274E-4</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="95"/>
         <v>1.2445550715619165E-4</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="95"/>
         <v>2.9614466052541796E-2</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="95"/>
         <v>2.838942823017793E-2</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="95"/>
         <v>1.2859767299448868E-2</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="95"/>
         <v>6.4049999999999996E-2</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="95"/>
         <v>0.02</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="95"/>
         <v>0.01</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="95"/>
         <v>0.01</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="95"/>
         <v>0.01</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="95"/>
         <v>0.01</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="85"/>
-        <v>1.0000000000000002E-2</v>
+        <f t="shared" si="95"/>
+        <v>0.01</v>
       </c>
       <c r="AK29" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="95"/>
         <v>0.01</v>
       </c>
       <c r="AL29" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="95"/>
         <v>0.01</v>
       </c>
       <c r="AM29" s="9">
-        <f t="shared" si="85"/>
-        <v>1.0000000000000002E-2</v>
+        <f t="shared" si="95"/>
+        <v>0.01</v>
       </c>
       <c r="AN29" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="95"/>
         <v>0.01</v>
       </c>
       <c r="AQ29" t="s">
@@ -4867,7 +4974,7 @@
       </c>
       <c r="AR29" s="11">
         <f>Main!D3</f>
-        <v>345.94</v>
+        <v>329.6</v>
       </c>
     </row>
     <row r="30" spans="1:151" x14ac:dyDescent="0.3">
@@ -4875,19 +4982,19 @@
         <v>46</v>
       </c>
       <c r="C30" s="9">
-        <f t="shared" ref="C30:F30" si="86">C13/C3</f>
+        <f t="shared" ref="C30:F30" si="96">C13/C3</f>
         <v>0.67658308542286438</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="96"/>
         <v>0.66796494644595905</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="96"/>
         <v>0.57017182130584187</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="96"/>
         <v>0.6532682676255297</v>
       </c>
       <c r="G30" s="9">
@@ -4895,127 +5002,130 @@
         <v>0.64138104838709675</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" ref="H30:N30" si="87">H13/H3</f>
+        <f t="shared" ref="H30:N30" si="97">H13/H3</f>
         <v>0.66825297432686281</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="97"/>
         <v>0.6184907054044072</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="97"/>
         <v>0.64467417818561967</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="97"/>
         <v>0.68959925874449846</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="97"/>
         <v>0.61014245014245017</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="97"/>
         <v>0.66719101123595503</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="97"/>
         <v>0.660185088905064</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" ref="O30:R30" si="88">O13/O3</f>
+        <f t="shared" ref="O30:R30" si="98">O13/O3</f>
         <v>0.65552050473186119</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="98"/>
         <v>0.56649989576818849</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="98"/>
         <v>0.60725521038143926</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="98"/>
         <v>0.57329354718388659</v>
       </c>
-      <c r="S30" s="9"/>
+      <c r="S30" s="9">
+        <f t="shared" ref="S30" si="99">S13/S3</f>
+        <v>0.61801669571598938</v>
+      </c>
       <c r="T30" s="9"/>
       <c r="U30" s="9"/>
       <c r="V30" s="9"/>
       <c r="X30" s="9">
-        <f t="shared" ref="X30:AN30" si="89">X13/X3</f>
+        <f t="shared" ref="X30:AN30" si="100">X13/X3</f>
         <v>0.65287026156591377</v>
       </c>
       <c r="Y30" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="100"/>
         <v>0.64455735603771858</v>
       </c>
       <c r="Z30" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="100"/>
         <v>0.65563161169881767</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="100"/>
         <v>0.64186284544524053</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="100"/>
         <v>0.64312620586163594</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="100"/>
         <v>0.65676668707899566</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="100"/>
         <v>0.59984999999999999</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="89"/>
-        <v>0.6895</v>
+        <f t="shared" si="100"/>
+        <v>0.68478318584070796</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="89"/>
-        <v>0.70081775700934579</v>
+        <f t="shared" si="100"/>
+        <v>0.70326668596476716</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="89"/>
-        <v>0.70213551401869156</v>
+        <f t="shared" si="100"/>
+        <v>0.70453779670829531</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="89"/>
-        <v>0.70344060028756294</v>
+        <f t="shared" si="100"/>
+        <v>0.70579668523313588</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="89"/>
-        <v>0.70473301581595971</v>
+        <f t="shared" si="100"/>
+        <v>0.70704335153928854</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="89"/>
-        <v>0.70537288820992083</v>
+        <f t="shared" si="100"/>
+        <v>0.70766057358302104</v>
       </c>
       <c r="AK30" s="9">
-        <f t="shared" si="89"/>
-        <v>0.70600648734511762</v>
+        <f t="shared" si="100"/>
+        <v>0.70827174443024632</v>
       </c>
       <c r="AL30" s="9">
-        <f t="shared" si="89"/>
-        <v>0.70663387472408734</v>
+        <f t="shared" si="100"/>
+        <v>0.70887692340642039</v>
       </c>
       <c r="AM30" s="9">
-        <f t="shared" si="89"/>
-        <v>0.70725511124639995</v>
+        <f t="shared" si="100"/>
+        <v>0.70947616925537715</v>
       </c>
       <c r="AN30" s="9">
-        <f t="shared" si="89"/>
-        <v>0.70787025721457264</v>
+        <f t="shared" si="100"/>
+        <v>0.71006954014503021</v>
       </c>
       <c r="AQ30" s="6" t="s">
         <v>55</v>
       </c>
       <c r="AR30" s="10">
         <f>AR28/AR29-1</f>
-        <v>-0.25500764946033738</v>
+        <v>-0.16471862606060605</v>
       </c>
     </row>
     <row r="31" spans="1:151" x14ac:dyDescent="0.3">
@@ -5023,19 +5133,19 @@
         <v>23</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:F31" si="90">C17/C16</f>
+        <f t="shared" ref="C31:F31" si="101">C17/C16</f>
         <v>0.171125178680825</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0.19704975781594011</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0.10916688430399582</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0.19063270336894</v>
       </c>
       <c r="G31" s="9">
@@ -5043,119 +5153,122 @@
         <v>0.16033755274261605</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" ref="H31:N31" si="91">H17/H16</f>
+        <f t="shared" ref="H31:N31" si="102">H17/H16</f>
         <v>0.19344448654793484</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="102"/>
         <v>0.19238243295763699</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="102"/>
         <v>0.16944641589779985</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="102"/>
         <v>0.1906653426017875</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="102"/>
         <v>0.15418102666424813</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="102"/>
         <v>0.18650859909834697</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="102"/>
         <v>0.16541117388575016</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" ref="O31:R31" si="92">O17/O16</f>
+        <f t="shared" ref="O31:R31" si="103">O17/O16</f>
         <v>0.17435483870967741</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="103"/>
         <v>0.15833026848105922</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="103"/>
         <v>0.16753513342807516</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="103"/>
         <v>0.18206652739836091</v>
       </c>
-      <c r="S31" s="9"/>
+      <c r="S31" s="9">
+        <f t="shared" ref="S31" si="104">S17/S16</f>
+        <v>0.12979482604817127</v>
+      </c>
       <c r="T31" s="9"/>
       <c r="U31" s="9"/>
       <c r="V31" s="9"/>
       <c r="X31" s="9">
-        <f t="shared" ref="X31:AN31" si="93">X17/X16</f>
+        <f t="shared" ref="X31:AN31" si="105">X17/X16</f>
         <v>0.18839021768341843</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.212037708484409</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.23358027765672665</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.16977282752536391</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.17892285021628559</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.17448569994982438</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.17095147557245599</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.18</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.18</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.18</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.18</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.18</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.18</v>
       </c>
       <c r="AK31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.18</v>
       </c>
       <c r="AL31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.18</v>
       </c>
       <c r="AM31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.18</v>
       </c>
       <c r="AN31" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>0.18</v>
       </c>
       <c r="AQ31" t="s">
@@ -5174,136 +5287,139 @@
         <v>0.57501062473438169</v>
       </c>
       <c r="D32" s="9">
-        <f t="shared" ref="D32:N32" si="94">D18/D3</f>
+        <f t="shared" ref="D32:N32" si="106">D18/D3</f>
         <v>0.50730282375851998</v>
       </c>
       <c r="E32" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="106"/>
         <v>0.46886597938144331</v>
       </c>
       <c r="F32" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="106"/>
         <v>0.50597149094644922</v>
       </c>
       <c r="G32" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="106"/>
         <v>0.52658770161290325</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="106"/>
         <v>0.53312460864120226</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="106"/>
         <v>0.5116336328942509</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="106"/>
         <v>0.54373330235799744</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="106"/>
         <v>0.56636553161918002</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="106"/>
         <v>0.53139601139601145</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="106"/>
         <v>0.54741573033707869</v>
       </c>
       <c r="N32" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="106"/>
         <v>0.5529790995112821</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" ref="O32:R32" si="95">O18/O3</f>
+        <f t="shared" ref="O32:R32" si="107">O18/O3</f>
         <v>0.5382754994742377</v>
       </c>
       <c r="P32" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="107"/>
         <v>0.47706900145924536</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="107"/>
         <v>0.51828548957923715</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="107"/>
         <v>0.47463632972771352</v>
       </c>
-      <c r="S32" s="9"/>
+      <c r="S32" s="9">
+        <f t="shared" ref="S32" si="108">S18/S3</f>
+        <v>0.53692321805338961</v>
+      </c>
       <c r="T32" s="9"/>
       <c r="U32" s="9"/>
       <c r="V32" s="9"/>
       <c r="X32" s="9">
-        <f t="shared" ref="X32:AN32" si="96">X18/X3</f>
+        <f t="shared" ref="X32:AN32" si="109">X18/X3</f>
         <v>0.52574313443878662</v>
       </c>
       <c r="Y32" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="109"/>
         <v>0.49739082669596263</v>
       </c>
       <c r="Z32" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="109"/>
         <v>0.51072391619995849</v>
       </c>
       <c r="AA32" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="109"/>
         <v>0.51371545547594677</v>
       </c>
       <c r="AB32" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="109"/>
         <v>0.52898661684990655</v>
       </c>
       <c r="AC32" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="109"/>
         <v>0.54954628959527918</v>
       </c>
       <c r="AD32" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="109"/>
         <v>0.50144999999999995</v>
       </c>
       <c r="AE32" s="9">
-        <f t="shared" si="96"/>
-        <v>0.56896753211009177</v>
+        <f t="shared" si="109"/>
+        <v>0.56497310619469032</v>
       </c>
       <c r="AF32" s="9">
-        <f t="shared" si="96"/>
-        <v>0.57783421538197721</v>
+        <f t="shared" si="109"/>
+        <v>0.57973034935075674</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="96"/>
-        <v>0.5785850500059202</v>
+        <f t="shared" si="109"/>
+        <v>0.58045460575792296</v>
       </c>
       <c r="AH32" s="9">
-        <f t="shared" si="96"/>
-        <v>0.57936627845705968</v>
+        <f t="shared" si="109"/>
+        <v>0.58120818010459752</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="96"/>
-        <v>0.58016944763063605</v>
+        <f t="shared" si="109"/>
+        <v>0.58198291851096751</v>
       </c>
       <c r="AJ32" s="9">
-        <f t="shared" si="96"/>
-        <v>0.58046248227928166</v>
+        <f t="shared" si="109"/>
+        <v>0.5822655802516965</v>
       </c>
       <c r="AK32" s="9">
-        <f t="shared" si="96"/>
-        <v>0.58075059280716879</v>
+        <f t="shared" si="109"/>
+        <v>0.58254349217682666</v>
       </c>
       <c r="AL32" s="9">
-        <f t="shared" si="96"/>
-        <v>0.58103380737987353</v>
+        <f t="shared" si="109"/>
+        <v>0.58281668145492205</v>
       </c>
       <c r="AM32" s="9">
-        <f t="shared" si="96"/>
-        <v>0.5813121536896797</v>
+        <f t="shared" si="109"/>
+        <v>0.5830851747980097</v>
       </c>
       <c r="AN32" s="9">
-        <f t="shared" si="96"/>
-        <v>0.58158565895828851</v>
+        <f t="shared" si="109"/>
+        <v>0.58334899846418975</v>
       </c>
     </row>
   </sheetData>
